--- a/inventario_expandido.xlsx
+++ b/inventario_expandido.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>€/m (4.7€/kg)</t>
+          <t>€/m (6.5€/kg)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>7.95</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>6.08</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="4">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1.46</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="5">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.27</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="6">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>2.85</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="7">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>5.09</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="8">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>7.93</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="9">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>11.42</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="10">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>20.38</v>
+        <v>28.18</v>
       </c>
     </row>
     <row r="11">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="12">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>31.84</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="13">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>25.69</v>
+        <v>35.52</v>
       </c>
     </row>
     <row r="14">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>15.55</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="15">
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="16">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1.43</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="17">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>1.68</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="18">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="19">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>2.55</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="20">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>3.99</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="21">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>6.23</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>8.970000000000001</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="23">
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>12.21</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="24">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>15.95</v>
+        <v>22.05</v>
       </c>
     </row>
     <row r="25">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>24.92</v>
+        <v>34.47</v>
       </c>
     </row>
     <row r="26">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>35.88</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="27">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="O27" s="2" t="n">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="28">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>4.82</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="29">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>2.24</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="30">
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="O30" s="2" t="n">
-        <v>0.76</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="31">
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="O31" s="2" t="n">
-        <v>2.53</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="32">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="33">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="O33" s="2" t="n">
-        <v>1.14</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="34">
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="O34" s="2" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="35">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="O35" s="2" t="n">
-        <v>2.28</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="36">
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="O36" s="2" t="n">
-        <v>3.05</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="37">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="O37" s="2" t="n">
-        <v>3.82</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="38">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="O38" s="2" t="n">
-        <v>7.61</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="39">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="O39" s="2" t="n">
-        <v>3.05</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="40">
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="O40" s="2" t="n">
-        <v>4.07</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="41">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="O41" s="2" t="n">
-        <v>5.09</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="42">
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="O42" s="2" t="n">
-        <v>7.61</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="43">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="O43" s="2" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="44">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="O44" s="2" t="n">
-        <v>3.17</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="45">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="O45" s="2" t="n">
-        <v>3.17</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="46">
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="O46" s="2" t="n">
-        <v>3.17</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="47">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="O47" s="2" t="n">
-        <v>5.08</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="48">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="O48" s="2" t="n">
-        <v>6.37</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="49">
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="O49" s="2" t="n">
-        <v>9.52</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="50">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>12.69</v>
+        <v>17.56</v>
       </c>
     </row>
     <row r="51">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="O51" s="2" t="n">
-        <v>7.61</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="52">
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>9.140000000000001</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="53">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>11.42</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="54">
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="O54" s="2" t="n">
-        <v>15.22</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="55">
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="56">
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="O56" s="2" t="n">
-        <v>8.15</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="57">
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="O57" s="2" t="n">
-        <v>8.15</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="58">
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="O58" s="2" t="n">
-        <v>10.18</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="59">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="O59" s="2" t="n">
-        <v>15.28</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="60">
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="O60" s="2" t="n">
-        <v>20.3</v>
+        <v>28.08</v>
       </c>
     </row>
     <row r="61">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="O61" s="2" t="n">
-        <v>10.15</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="62">
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="O62" s="2" t="n">
-        <v>12.73</v>
+        <v>17.61</v>
       </c>
     </row>
     <row r="63">
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="O63" s="2" t="n">
-        <v>14.94</v>
+        <v>20.66</v>
       </c>
     </row>
     <row r="64">
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="O64" s="2" t="n">
-        <v>15.2</v>
+        <v>21.02</v>
       </c>
     </row>
     <row r="65">
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="O65" s="2" t="n">
-        <v>18.27</v>
+        <v>25.27</v>
       </c>
     </row>
     <row r="66">
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="O66" s="2" t="n">
-        <v>24.75</v>
+        <v>34.22</v>
       </c>
     </row>
     <row r="67">
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="O67" s="2" t="n">
-        <v>19.03</v>
+        <v>26.31</v>
       </c>
     </row>
     <row r="68">
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="O68" s="2" t="n">
-        <v>6.35</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="O69" s="2" t="n">
-        <v>14.27</v>
+        <v>19.74</v>
       </c>
     </row>
     <row r="70">
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="O70" s="2" t="n">
-        <v>25.38</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="71">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="O71" s="2" t="n">
-        <v>10.15</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="72">
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="O72" s="2" t="n">
-        <v>2.03</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="73">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="O73" s="2" t="n">
-        <v>3.81</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="74">
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="O74" s="2" t="n">
-        <v>5.71</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="75">
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="O75" s="2" t="n">
-        <v>0.57</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="76">
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="O76" s="2" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="77">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="O77" s="2" t="n">
-        <v>2.22</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="78">
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="O78" s="2" t="n">
-        <v>0.95</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="79">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="O79" s="2" t="n">
-        <v>2.28</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="80">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="O80" s="2" t="n">
-        <v>0.76</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="81">
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="O81" s="2" t="n">
-        <v>2.54</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="82">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="O82" s="2" t="n">
-        <v>25.38</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="83">
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="O83" s="2" t="n">
-        <v>22.84</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="84">
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="O84" s="2" t="n">
-        <v>30.46</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="85">
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="O85" s="2" t="n">
-        <v>38.07</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="86">
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="O86" s="2" t="n">
-        <v>18.68</v>
+        <v>25.83</v>
       </c>
     </row>
     <row r="87">
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="O87" s="2" t="n">
-        <v>6.09</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="88">
@@ -5336,7 +5336,7 @@
         </is>
       </c>
       <c r="O88" s="2" t="n">
-        <v>28.55</v>
+        <v>39.49</v>
       </c>
     </row>
     <row r="89">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="O89" s="2" t="n">
-        <v>17.77</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="90">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="O90" s="2" t="n">
-        <v>5.08</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="91">
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="O91" s="2" t="n">
-        <v>2.22</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="92">
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="O92" s="2" t="n">
-        <v>3.81</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="93">
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="O93" s="2" t="n">
-        <v>3.81</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="94">
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="O94" s="2" t="n">
-        <v>15.12</v>
+        <v>20.92</v>
       </c>
     </row>
     <row r="95">
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="O95" s="2" t="n">
-        <v>15.12</v>
+        <v>20.92</v>
       </c>
     </row>
     <row r="96">
@@ -5776,7 +5776,7 @@
         </is>
       </c>
       <c r="O96" s="2" t="n">
-        <v>3.81</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="97">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="O97" s="2" t="n">
-        <v>5.71</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="98">
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="O98" s="2" t="n">
-        <v>4.44</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="99">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="O99" s="2" t="n">
-        <v>3.43</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="100">
@@ -5996,7 +5996,7 @@
         </is>
       </c>
       <c r="O100" s="2" t="n">
-        <v>3.43</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="101">
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="O101" s="2" t="n">
-        <v>3.43</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="102">
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="O102" s="2" t="n">
-        <v>5.71</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="103">
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="O103" s="2" t="n">
-        <v>11.42</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="104">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="O104" s="2" t="n">
-        <v>12.18</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="105">
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="O105" s="2" t="n">
-        <v>3.05</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="106">
@@ -6326,7 +6326,7 @@
         </is>
       </c>
       <c r="O106" s="2" t="n">
-        <v>9.140000000000001</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="107">
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="O107" s="2" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="108">
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="O108" s="2" t="n">
-        <v>3.17</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="109">
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="O109" s="2" t="n">
-        <v>0.95</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="110">
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="O110" s="2" t="n">
-        <v>20.3</v>
+        <v>28.08</v>
       </c>
     </row>
     <row r="111">
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="O111" s="2" t="n">
-        <v>1.52</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="112">
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="O112" s="2" t="n">
-        <v>9.52</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="113">
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="O113" s="2" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="114">
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="O114" s="2" t="n">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="115">
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="O115" s="2" t="n">
-        <v>7.8</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="116">
@@ -6884,7 +6884,7 @@
         </is>
       </c>
       <c r="O116" s="2" t="n">
-        <v>6.98</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="117">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="O117" s="2" t="n">
-        <v>11.39</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="118">
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="O118" s="2" t="n">
-        <v>18.2</v>
+        <v>25.17</v>
       </c>
     </row>
     <row r="119">
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="O119" s="2" t="n">
-        <v>42.18</v>
+        <v>58.34</v>
       </c>
     </row>
     <row r="120">
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="O120" s="2" t="n">
-        <v>3.59</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="121">
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="O121" s="2" t="n">
-        <v>5.12</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="122">
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="O122" s="2" t="n">
-        <v>2.19</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="123">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="O123" s="2" t="n">
-        <v>16.29</v>
+        <v>22.53</v>
       </c>
     </row>
     <row r="124">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="O124" s="2" t="n">
-        <v>5.77</v>
+        <v>7.98</v>
       </c>
     </row>
     <row r="125">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="O125" s="2" t="n">
-        <v>5.88</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="O126" s="2" t="n">
-        <v>5.88</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="O127" s="2" t="n">
-        <v>5.69</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="128">
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="O128" s="2" t="n">
-        <v>4.32</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="129">
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="O129" s="2" t="n">
-        <v>11.27</v>
+        <v>15.58</v>
       </c>
     </row>
     <row r="130">
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="O130" s="2" t="n">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="131">
@@ -7739,7 +7739,7 @@
         </is>
       </c>
       <c r="O131" s="2" t="n">
-        <v>5.73</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="132">
@@ -7796,7 +7796,7 @@
         </is>
       </c>
       <c r="O132" s="2" t="n">
-        <v>7.21</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="133">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="O133" s="2" t="n">
-        <v>1.85</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="134">
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="O134" s="2" t="n">
-        <v>1.81</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="135">
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="O135" s="2" t="n">
-        <v>2.17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="O136" s="2" t="n">
-        <v>1.98</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="137">
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="O137" s="2" t="n">
-        <v>1.98</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="138">
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="O138" s="2" t="n">
-        <v>3.87</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="139">
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="O139" s="2" t="n">
-        <v>6.03</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="140">
@@ -8252,7 +8252,7 @@
         </is>
       </c>
       <c r="O140" s="2" t="n">
-        <v>6.03</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="141">
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="O141" s="2" t="n">
-        <v>8.68</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="142">
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="O142" s="2" t="n">
-        <v>10.2</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="143">
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="O143" s="2" t="n">
-        <v>15.43</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="144">
@@ -8480,7 +8480,7 @@
         </is>
       </c>
       <c r="O144" s="2" t="n">
-        <v>24.11</v>
+        <v>33.34</v>
       </c>
     </row>
     <row r="145">
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="O145" s="2" t="n">
-        <v>0.96</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="146">
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c r="O146" s="2" t="n">
-        <v>0.96</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="147">
@@ -8651,7 +8651,7 @@
         </is>
       </c>
       <c r="O147" s="2" t="n">
-        <v>3.31</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="148">
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="O148" s="2" t="n">
-        <v>3.69</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="149">
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="O149" s="2" t="n">
-        <v>5.89</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="150">
@@ -8822,7 +8822,7 @@
         </is>
       </c>
       <c r="O150" s="2" t="n">
-        <v>4.12</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="151">
@@ -8879,7 +8879,7 @@
         </is>
       </c>
       <c r="O151" s="2" t="n">
-        <v>29.28</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="152">
@@ -8936,7 +8936,7 @@
         </is>
       </c>
       <c r="O152" s="2" t="n">
-        <v>29.28</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="153">
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="O153" s="2" t="n">
-        <v>7.92</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="154">
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="O154" s="2" t="n">
-        <v>14.77</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="155">
@@ -9107,7 +9107,7 @@
         </is>
       </c>
       <c r="O155" s="2" t="n">
-        <v>7.5</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="156">
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="O156" s="2" t="n">
-        <v>4.76</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="157">
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="O157" s="2" t="n">
-        <v>2.99</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="158">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="O158" s="2" t="n">
-        <v>7.41</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="159">
@@ -9335,7 +9335,7 @@
         </is>
       </c>
       <c r="O159" s="2" t="n">
-        <v>1.85</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="160">
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="O160" s="2" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="161">
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="O161" s="2" t="n">
-        <v>7.59</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="162">
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="O162" s="2" t="n">
-        <v>3.26</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="163">
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="O163" s="2" t="n">
-        <v>27.79</v>
+        <v>38.43</v>
       </c>
     </row>
     <row r="164">
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="O164" s="2" t="n">
-        <v>30.56</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="165">
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="O165" s="2" t="n">
-        <v>1.47</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="166">
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="O166" s="2" t="n">
-        <v>4.89</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="167">
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="O167" s="2" t="n">
-        <v>5.88</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="168">
@@ -9848,7 +9848,7 @@
         </is>
       </c>
       <c r="O168" s="2" t="n">
-        <v>2.99</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="169">
@@ -9905,7 +9905,7 @@
         </is>
       </c>
       <c r="O169" s="2" t="n">
-        <v>1.47</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="170">
@@ -9962,7 +9962,7 @@
         </is>
       </c>
       <c r="O170" s="2" t="n">
-        <v>2.93</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="171">
@@ -10019,7 +10019,7 @@
         </is>
       </c>
       <c r="O171" s="2" t="n">
-        <v>10.97</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="172">
@@ -10076,7 +10076,7 @@
         </is>
       </c>
       <c r="O172" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="173">
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="O173" s="2" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="174">
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="O174" s="2" t="n">
-        <v>1.79</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="175">
@@ -10247,7 +10247,7 @@
         </is>
       </c>
       <c r="O175" s="2" t="n">
-        <v>3.5</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="176">
@@ -10304,7 +10304,7 @@
         </is>
       </c>
       <c r="O176" s="2" t="n">
-        <v>6.36</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="177">
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="O177" s="2" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="178">
@@ -10418,7 +10418,7 @@
         </is>
       </c>
       <c r="O178" s="2" t="n">
-        <v>2.84</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="179">
@@ -10475,7 +10475,7 @@
         </is>
       </c>
       <c r="O179" s="2" t="n">
-        <v>4.43</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="180">
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="O180" s="2" t="n">
-        <v>2.95</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="181">
@@ -10589,7 +10589,7 @@
         </is>
       </c>
       <c r="O181" s="2" t="n">
-        <v>2.95</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="182">
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="O182" s="2" t="n">
-        <v>2.24</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="183">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="O183" s="2" t="n">
-        <v>2.24</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="184">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="O184" s="2" t="n">
-        <v>3.92</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="185">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="O185" s="2" t="n">
-        <v>1.72</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="186">
@@ -10874,7 +10874,7 @@
         </is>
       </c>
       <c r="O186" s="2" t="n">
-        <v>2.74</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="187">
@@ -10931,7 +10931,7 @@
         </is>
       </c>
       <c r="O187" s="2" t="n">
-        <v>2.99</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="188">
@@ -10988,7 +10988,7 @@
         </is>
       </c>
       <c r="O188" s="2" t="n">
-        <v>7.12</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="189">
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="O189" s="2" t="n">
-        <v>2.74</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="190">
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="O190" s="2" t="n">
-        <v>4.39</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="191">
@@ -11159,7 +11159,7 @@
         </is>
       </c>
       <c r="O191" s="2" t="n">
-        <v>3.87</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="192">
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="O192" s="2" t="n">
-        <v>1.98</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="193">
@@ -11273,7 +11273,7 @@
         </is>
       </c>
       <c r="O193" s="2" t="n">
-        <v>2.17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194">
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="O194" s="2" t="n">
-        <v>2.17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195">
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="O195" s="2" t="n">
-        <v>6.03</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="196">
@@ -11444,7 +11444,7 @@
         </is>
       </c>
       <c r="O196" s="2" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="197">
@@ -11501,7 +11501,7 @@
         </is>
       </c>
       <c r="O197" s="2" t="n">
-        <v>2.49</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="198">
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="O198" s="2" t="n">
-        <v>5.8</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="199">
@@ -11615,7 +11615,7 @@
         </is>
       </c>
       <c r="O199" s="2" t="n">
-        <v>1.43</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="200">
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="O200" s="2" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="201">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="O201" s="2" t="n">
-        <v>2.64</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="202">
@@ -11786,7 +11786,7 @@
         </is>
       </c>
       <c r="O202" s="2" t="n">
-        <v>3.82</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="203">
@@ -11843,7 +11843,7 @@
         </is>
       </c>
       <c r="O203" s="2" t="n">
-        <v>2.74</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="204">
@@ -11900,7 +11900,7 @@
         </is>
       </c>
       <c r="O204" s="2" t="n">
-        <v>4.98</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="205">
@@ -11957,7 +11957,7 @@
         </is>
       </c>
       <c r="O205" s="2" t="n">
-        <v>3.23</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="206">
@@ -12014,7 +12014,7 @@
         </is>
       </c>
       <c r="O206" s="2" t="n">
-        <v>3.75</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="207">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="O207" s="2" t="n">
-        <v>6.97</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="208">
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="O208" s="2" t="n">
-        <v>6.97</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="209">
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="O209" s="2" t="n">
-        <v>5.62</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="210">
@@ -12242,7 +12242,7 @@
         </is>
       </c>
       <c r="O210" s="2" t="n">
-        <v>8.970000000000001</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="211">
@@ -12299,7 +12299,7 @@
         </is>
       </c>
       <c r="O211" s="2" t="n">
-        <v>8.970000000000001</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="212">
@@ -12356,7 +12356,7 @@
         </is>
       </c>
       <c r="O212" s="2" t="n">
-        <v>8.960000000000001</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="213">
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="O213" s="2" t="n">
-        <v>10.96</v>
+        <v>15.16</v>
       </c>
     </row>
     <row r="214">
@@ -12470,7 +12470,7 @@
         </is>
       </c>
       <c r="O214" s="2" t="n">
-        <v>15.01</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="215">
@@ -12527,7 +12527,7 @@
         </is>
       </c>
       <c r="O215" s="2" t="n">
-        <v>35.88</v>
+        <v>49.62</v>
       </c>
     </row>
     <row r="216">
@@ -12584,7 +12584,7 @@
         </is>
       </c>
       <c r="O216" s="2" t="n">
-        <v>35.88</v>
+        <v>49.62</v>
       </c>
     </row>
     <row r="217">
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="O217" s="2" t="n">
-        <v>18.19</v>
+        <v>25.16</v>
       </c>
     </row>
     <row r="218">
@@ -12698,7 +12698,7 @@
         </is>
       </c>
       <c r="O218" s="2" t="n">
-        <v>12.79</v>
+        <v>17.69</v>
       </c>
     </row>
     <row r="219">
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="O219" s="2" t="n">
-        <v>18.93</v>
+        <v>26.18</v>
       </c>
     </row>
     <row r="220">
@@ -12812,7 +12812,7 @@
         </is>
       </c>
       <c r="O220" s="2" t="n">
-        <v>18.93</v>
+        <v>26.18</v>
       </c>
     </row>
     <row r="221">
@@ -12869,7 +12869,7 @@
         </is>
       </c>
       <c r="O221" s="2" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="222">
@@ -12926,7 +12926,7 @@
         </is>
       </c>
       <c r="O222" s="2" t="n">
-        <v>3.03</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="223">
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="O223" s="2" t="n">
-        <v>4.24</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="224">
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="O224" s="2" t="n">
-        <v>9.24</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="225">
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="O225" s="2" t="n">
-        <v>16.94</v>
+        <v>23.43</v>
       </c>
     </row>
     <row r="226">
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="O226" s="2" t="n">
-        <v>46.41</v>
+        <v>64.18000000000001</v>
       </c>
     </row>
     <row r="227">
@@ -13211,7 +13211,7 @@
         </is>
       </c>
       <c r="O227" s="2" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="228">
@@ -13268,7 +13268,7 @@
         </is>
       </c>
       <c r="O228" s="2" t="n">
-        <v>4.62</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="229">
@@ -13325,7 +13325,7 @@
         </is>
       </c>
       <c r="O229" s="2" t="n">
-        <v>16.5</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="230">
@@ -13382,7 +13382,7 @@
         </is>
       </c>
       <c r="O230" s="2" t="n">
-        <v>7.84</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="231">
@@ -13439,7 +13439,7 @@
         </is>
       </c>
       <c r="O231" s="2" t="n">
-        <v>5.76</v>
+        <v>7.97</v>
       </c>
     </row>
     <row r="232">
@@ -13496,7 +13496,7 @@
         </is>
       </c>
       <c r="O232" s="2" t="n">
-        <v>3.82</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="233">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="O233" s="2" t="n">
-        <v>7.72</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="234">
@@ -13610,7 +13610,7 @@
         </is>
       </c>
       <c r="O234" s="2" t="n">
-        <v>5.73</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="235">
@@ -13667,7 +13667,7 @@
         </is>
       </c>
       <c r="O235" s="2" t="n">
-        <v>0.87</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="236">
@@ -13724,7 +13724,7 @@
         </is>
       </c>
       <c r="O236" s="2" t="n">
-        <v>3.2</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="237">
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="O237" s="2" t="n">
-        <v>14</v>
+        <v>19.36</v>
       </c>
     </row>
     <row r="238">
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="O238" s="2" t="n">
-        <v>1.41</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="239">
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="O239" s="2" t="n">
-        <v>6.06</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="240">
@@ -13952,7 +13952,7 @@
         </is>
       </c>
       <c r="O240" s="2" t="n">
-        <v>3.48</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="241">
@@ -14009,7 +14009,7 @@
         </is>
       </c>
       <c r="O241" s="2" t="n">
-        <v>3.84</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="242">
@@ -14066,7 +14066,7 @@
         </is>
       </c>
       <c r="O242" s="2" t="n">
-        <v>1.6</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="243">
@@ -14123,7 +14123,7 @@
         </is>
       </c>
       <c r="O243" s="2" t="n">
-        <v>49.14</v>
+        <v>67.95999999999999</v>
       </c>
     </row>
     <row r="244">
@@ -14180,7 +14180,7 @@
         </is>
       </c>
       <c r="O244" s="2" t="n">
-        <v>10.52</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="245">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="O245" s="2" t="n">
-        <v>29.52</v>
+        <v>40.82</v>
       </c>
     </row>
     <row r="246">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="O246" s="2" t="n">
-        <v>2.03</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="247">
@@ -14351,7 +14351,7 @@
         </is>
       </c>
       <c r="O247" s="2" t="n">
-        <v>5.4</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="248">
@@ -14408,7 +14408,7 @@
         </is>
       </c>
       <c r="O248" s="2" t="n">
-        <v>4.23</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="249">
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="O249" s="2" t="n">
-        <v>2.89</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="250">
@@ -14522,7 +14522,7 @@
         </is>
       </c>
       <c r="O250" s="2" t="n">
-        <v>15.36</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="251">
@@ -14579,7 +14579,7 @@
         </is>
       </c>
       <c r="O251" s="2" t="n">
-        <v>2.24</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="252">
@@ -14636,7 +14636,7 @@
         </is>
       </c>
       <c r="O252" s="2" t="n">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="253">
@@ -14693,7 +14693,7 @@
         </is>
       </c>
       <c r="O253" s="2" t="n">
-        <v>2.29</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="254">
@@ -14750,7 +14750,7 @@
         </is>
       </c>
       <c r="O254" s="2" t="n">
-        <v>2.29</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="255">
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="O255" s="2" t="n">
-        <v>4.11</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="256">
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="O256" s="2" t="n">
-        <v>3.35</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="257">
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="O257" s="2" t="n">
-        <v>3.87</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="258">
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="O258" s="2" t="n">
-        <v>4.78</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="259">
@@ -15035,7 +15035,7 @@
         </is>
       </c>
       <c r="O259" s="2" t="n">
-        <v>7.31</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="260">
@@ -15092,7 +15092,7 @@
         </is>
       </c>
       <c r="O260" s="2" t="n">
-        <v>4.89</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="261">
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="O261" s="2" t="n">
-        <v>9.34</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="262">
@@ -15206,7 +15206,7 @@
         </is>
       </c>
       <c r="O262" s="2" t="n">
-        <v>8.720000000000001</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="263">
@@ -15263,7 +15263,7 @@
         </is>
       </c>
       <c r="O263" s="2" t="n">
-        <v>11.37</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="264">
@@ -15320,7 +15320,7 @@
         </is>
       </c>
       <c r="O264" s="2" t="n">
-        <v>13.4</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="265">
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="O265" s="2" t="n">
-        <v>15.43</v>
+        <v>21.33</v>
       </c>
     </row>
     <row r="266">
@@ -15434,7 +15434,7 @@
         </is>
       </c>
       <c r="O266" s="2" t="n">
-        <v>29.24</v>
+        <v>40.44</v>
       </c>
     </row>
     <row r="267">
@@ -15491,7 +15491,7 @@
         </is>
       </c>
       <c r="O267" s="2" t="n">
-        <v>19.42</v>
+        <v>26.86</v>
       </c>
     </row>
     <row r="268">
@@ -15548,7 +15548,7 @@
         </is>
       </c>
       <c r="O268" s="2" t="n">
-        <v>11.77</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="269">
@@ -15605,7 +15605,7 @@
         </is>
       </c>
       <c r="O269" s="2" t="n">
-        <v>2.85</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="270">
@@ -15662,7 +15662,7 @@
         </is>
       </c>
       <c r="O270" s="2" t="n">
-        <v>4.37</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="271">
@@ -15719,7 +15719,7 @@
         </is>
       </c>
       <c r="O271" s="2" t="n">
-        <v>6.93</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="272">
@@ -15776,7 +15776,7 @@
         </is>
       </c>
       <c r="O272" s="2" t="n">
-        <v>6.93</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="273">
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="O273" s="2" t="n">
-        <v>18.77</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="274">
@@ -15890,7 +15890,7 @@
         </is>
       </c>
       <c r="O274" s="2" t="n">
-        <v>18.77</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="275">
@@ -15947,7 +15947,7 @@
         </is>
       </c>
       <c r="O275" s="2" t="n">
-        <v>29.19</v>
+        <v>40.36</v>
       </c>
     </row>
     <row r="276">
@@ -16004,7 +16004,7 @@
         </is>
       </c>
       <c r="O276" s="2" t="n">
-        <v>3.52</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="277">
@@ -16061,7 +16061,7 @@
         </is>
       </c>
       <c r="O277" s="2" t="n">
-        <v>5.89</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="278">
@@ -16118,7 +16118,7 @@
         </is>
       </c>
       <c r="O278" s="2" t="n">
-        <v>5.89</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="279">
@@ -16175,7 +16175,7 @@
         </is>
       </c>
       <c r="O279" s="2" t="n">
-        <v>5.64</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="280">
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="O280" s="2" t="n">
-        <v>2.59</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="281">
@@ -16289,7 +16289,7 @@
         </is>
       </c>
       <c r="O281" s="2" t="n">
-        <v>7.13</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="282">
@@ -16346,7 +16346,7 @@
         </is>
       </c>
       <c r="O282" s="2" t="n">
-        <v>4.01</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="283">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="O283" s="2" t="n">
-        <v>8.67</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="284">
@@ -16460,7 +16460,7 @@
         </is>
       </c>
       <c r="O284" s="2" t="n">
-        <v>9.24</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="285">
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="O285" s="2" t="n">
-        <v>28.37</v>
+        <v>39.23</v>
       </c>
     </row>
     <row r="286">
@@ -16574,7 +16574,7 @@
         </is>
       </c>
       <c r="O286" s="2" t="n">
-        <v>7.16</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="287">
@@ -16631,7 +16631,7 @@
         </is>
       </c>
       <c r="O287" s="2" t="n">
-        <v>19.44</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="288">
@@ -16688,7 +16688,7 @@
         </is>
       </c>
       <c r="O288" s="2" t="n">
-        <v>19.44</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="289">
@@ -16745,7 +16745,7 @@
         </is>
       </c>
       <c r="O289" s="2" t="n">
-        <v>1.79</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="290">
@@ -16802,7 +16802,7 @@
         </is>
       </c>
       <c r="O290" s="2" t="n">
-        <v>1.79</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="291">
@@ -16859,7 +16859,7 @@
         </is>
       </c>
       <c r="O291" s="2" t="n">
-        <v>15.08</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="292">
@@ -16916,7 +16916,7 @@
         </is>
       </c>
       <c r="O292" s="2" t="n">
-        <v>49.17</v>
+        <v>68</v>
       </c>
     </row>
     <row r="293">
@@ -16973,7 +16973,7 @@
         </is>
       </c>
       <c r="O293" s="2" t="n">
-        <v>49.17</v>
+        <v>68</v>
       </c>
     </row>
     <row r="294">
@@ -17030,7 +17030,7 @@
         </is>
       </c>
       <c r="O294" s="2" t="n">
-        <v>49.17</v>
+        <v>68</v>
       </c>
     </row>
     <row r="295">
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="O295" s="2" t="n">
-        <v>7.3</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="296">
@@ -17144,7 +17144,7 @@
         </is>
       </c>
       <c r="O296" s="2" t="n">
-        <v>2.84</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="297">
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="O297" s="2" t="n">
-        <v>2.84</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="298">
@@ -17258,7 +17258,7 @@
         </is>
       </c>
       <c r="O298" s="2" t="n">
-        <v>3.35</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="299">
@@ -17315,7 +17315,7 @@
         </is>
       </c>
       <c r="O299" s="2" t="n">
-        <v>5.64</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="300">
@@ -17372,7 +17372,7 @@
         </is>
       </c>
       <c r="O300" s="2" t="n">
-        <v>5.64</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="301">
@@ -17429,7 +17429,7 @@
         </is>
       </c>
       <c r="O301" s="2" t="n">
-        <v>3.86</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="302">
@@ -17486,7 +17486,7 @@
         </is>
       </c>
       <c r="O302" s="2" t="n">
-        <v>7.16</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="303">
@@ -17543,7 +17543,7 @@
         </is>
       </c>
       <c r="O303" s="2" t="n">
-        <v>7.16</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="304">
@@ -17600,7 +17600,7 @@
         </is>
       </c>
       <c r="O304" s="2" t="n">
-        <v>7.18</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="305">
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="O305" s="2" t="n">
-        <v>11.37</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="306">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="O306" s="2" t="n">
-        <v>13.4</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="307">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="O307" s="2" t="n">
-        <v>14.41</v>
+        <v>19.94</v>
       </c>
     </row>
     <row r="308">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="O308" s="2" t="n">
-        <v>2.33</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="309">
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="O309" s="2" t="n">
-        <v>2.33</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="310">
@@ -17942,7 +17942,7 @@
         </is>
       </c>
       <c r="O310" s="2" t="n">
-        <v>28.8</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="311">
@@ -17999,7 +17999,7 @@
         </is>
       </c>
       <c r="O311" s="2" t="n">
-        <v>16.14</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="312">
@@ -18056,7 +18056,7 @@
         </is>
       </c>
       <c r="O312" s="2" t="n">
-        <v>17.06</v>
+        <v>23.59</v>
       </c>
     </row>
     <row r="313">
@@ -18113,7 +18113,7 @@
         </is>
       </c>
       <c r="O313" s="2" t="n">
-        <v>6.39</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="314">
@@ -18170,7 +18170,7 @@
         </is>
       </c>
       <c r="O314" s="2" t="n">
-        <v>12.49</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="315">
@@ -18227,7 +18227,7 @@
         </is>
       </c>
       <c r="O315" s="2" t="n">
-        <v>6.9</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="316">
@@ -18284,7 +18284,7 @@
         </is>
       </c>
       <c r="O316" s="2" t="n">
-        <v>13.4</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="317">
@@ -18341,7 +18341,7 @@
         </is>
       </c>
       <c r="O317" s="2" t="n">
-        <v>21.57</v>
+        <v>29.84</v>
       </c>
     </row>
     <row r="318">
@@ -18398,7 +18398,7 @@
         </is>
       </c>
       <c r="O318" s="2" t="n">
-        <v>5.89</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="319">
@@ -18455,7 +18455,7 @@
         </is>
       </c>
       <c r="O319" s="2" t="n">
-        <v>5.89</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="320">
@@ -18512,7 +18512,7 @@
         </is>
       </c>
       <c r="O320" s="2" t="n">
-        <v>5.89</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="321">
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="O321" s="2" t="n">
-        <v>5.89</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="322">
@@ -18626,7 +18626,7 @@
         </is>
       </c>
       <c r="O322" s="2" t="n">
-        <v>7.41</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="323">
@@ -18683,7 +18683,7 @@
         </is>
       </c>
       <c r="O323" s="2" t="n">
-        <v>7.41</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="324">
@@ -18740,7 +18740,7 @@
         </is>
       </c>
       <c r="O324" s="2" t="n">
-        <v>14.76</v>
+        <v>20.41</v>
       </c>
     </row>
     <row r="325">
@@ -18797,7 +18797,7 @@
         </is>
       </c>
       <c r="O325" s="2" t="n">
-        <v>11.17</v>
+        <v>15.45</v>
       </c>
     </row>
     <row r="326">
@@ -18854,7 +18854,7 @@
         </is>
       </c>
       <c r="O326" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="327">
@@ -18911,7 +18911,7 @@
         </is>
       </c>
       <c r="O327" s="2" t="n">
-        <v>8.93</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="328">
@@ -18968,7 +18968,7 @@
         </is>
       </c>
       <c r="O328" s="2" t="n">
-        <v>8.93</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="329">
@@ -19025,7 +19025,7 @@
         </is>
       </c>
       <c r="O329" s="2" t="n">
-        <v>17.46</v>
+        <v>24.15</v>
       </c>
     </row>
     <row r="330">
@@ -19082,7 +19082,7 @@
         </is>
       </c>
       <c r="O330" s="2" t="n">
-        <v>5.25</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="331">
@@ -19139,7 +19139,7 @@
         </is>
       </c>
       <c r="O331" s="2" t="n">
-        <v>14.73</v>
+        <v>20.38</v>
       </c>
     </row>
     <row r="332">
@@ -19196,7 +19196,7 @@
         </is>
       </c>
       <c r="O332" s="2" t="n">
-        <v>4.11</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="333">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="O333" s="2" t="n">
-        <v>11.73</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="334">
@@ -19310,7 +19310,7 @@
         </is>
       </c>
       <c r="O334" s="2" t="n">
-        <v>17.82</v>
+        <v>24.64</v>
       </c>
     </row>
     <row r="335">
@@ -19367,7 +19367,7 @@
         </is>
       </c>
       <c r="O335" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>12.04</v>
       </c>
     </row>
     <row r="336">
@@ -19424,7 +19424,7 @@
         </is>
       </c>
       <c r="O336" s="2" t="n">
-        <v>4.9</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="337">
@@ -19481,7 +19481,7 @@
         </is>
       </c>
       <c r="O337" s="2" t="n">
-        <v>4.9</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="338">
@@ -19538,7 +19538,7 @@
         </is>
       </c>
       <c r="O338" s="2" t="n">
-        <v>5.26</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="339">
@@ -19595,7 +19595,7 @@
         </is>
       </c>
       <c r="O339" s="2" t="n">
-        <v>5.4</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="340">
@@ -19652,7 +19652,7 @@
         </is>
       </c>
       <c r="O340" s="2" t="n">
-        <v>5.4</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="341">
@@ -19709,7 +19709,7 @@
         </is>
       </c>
       <c r="O341" s="2" t="n">
-        <v>4.89</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="342">
@@ -19766,7 +19766,7 @@
         </is>
       </c>
       <c r="O342" s="2" t="n">
-        <v>4.89</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="343">
@@ -19823,7 +19823,7 @@
         </is>
       </c>
       <c r="O343" s="2" t="n">
-        <v>3.35</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="344">
@@ -19880,7 +19880,7 @@
         </is>
       </c>
       <c r="O344" s="2" t="n">
-        <v>3.6</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="345">
@@ -19937,7 +19937,7 @@
         </is>
       </c>
       <c r="O345" s="2" t="n">
-        <v>33.76</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="346">
@@ -19994,7 +19994,7 @@
         </is>
       </c>
       <c r="O346" s="2" t="n">
-        <v>2.34</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="347">
@@ -20051,7 +20051,7 @@
         </is>
       </c>
       <c r="O347" s="2" t="n">
-        <v>4.87</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="348">
@@ -20108,7 +20108,7 @@
         </is>
       </c>
       <c r="O348" s="2" t="n">
-        <v>8.68</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="349">
@@ -20165,7 +20165,7 @@
         </is>
       </c>
       <c r="O349" s="2" t="n">
-        <v>3.86</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="350">
@@ -20222,7 +20222,7 @@
         </is>
       </c>
       <c r="O350" s="2" t="n">
-        <v>2.17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="351">
@@ -20279,7 +20279,7 @@
         </is>
       </c>
       <c r="O351" s="2" t="n">
-        <v>8.68</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="352">
@@ -20336,7 +20336,7 @@
         </is>
       </c>
       <c r="O352" s="2" t="n">
-        <v>8.68</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="353">
@@ -20393,7 +20393,7 @@
         </is>
       </c>
       <c r="O353" s="2" t="n">
-        <v>14.18</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="354">
@@ -20450,7 +20450,7 @@
         </is>
       </c>
       <c r="O354" s="2" t="n">
-        <v>14.47</v>
+        <v>20.01</v>
       </c>
     </row>
     <row r="355">
@@ -20507,7 +20507,7 @@
         </is>
       </c>
       <c r="O355" s="2" t="n">
-        <v>28.63</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="356">
@@ -20564,7 +20564,7 @@
         </is>
       </c>
       <c r="O356" s="2" t="n">
-        <v>6.4</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="357">
@@ -20621,7 +20621,7 @@
         </is>
       </c>
       <c r="O357" s="2" t="n">
-        <v>9.210000000000001</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="358">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="O358" s="2" t="n">
-        <v>9.210000000000001</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="359">
@@ -20735,7 +20735,7 @@
         </is>
       </c>
       <c r="O359" s="2" t="n">
-        <v>24.13</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="360">
@@ -20792,7 +20792,7 @@
         </is>
       </c>
       <c r="O360" s="2" t="n">
-        <v>24.13</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="361">
@@ -20849,7 +20849,7 @@
         </is>
       </c>
       <c r="O361" s="2" t="n">
-        <v>24.13</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="362">
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="O362" s="2" t="n">
-        <v>24.13</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="363">
@@ -20963,7 +20963,7 @@
         </is>
       </c>
       <c r="O363" s="2" t="n">
-        <v>24.13</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="364">
@@ -21020,7 +21020,7 @@
         </is>
       </c>
       <c r="O364" s="2" t="n">
-        <v>12.38</v>
+        <v>17.13</v>
       </c>
     </row>
     <row r="365">
@@ -21077,7 +21077,7 @@
         </is>
       </c>
       <c r="O365" s="2" t="n">
-        <v>23.92</v>
+        <v>33.08</v>
       </c>
     </row>
     <row r="366">
@@ -21134,7 +21134,7 @@
         </is>
       </c>
       <c r="O366" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="367">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="O367" s="2" t="n">
-        <v>6.9</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="368">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="O368" s="2" t="n">
-        <v>3.19</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="369">
@@ -21305,7 +21305,7 @@
         </is>
       </c>
       <c r="O369" s="2" t="n">
-        <v>9.34</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="370">
@@ -21362,7 +21362,7 @@
         </is>
       </c>
       <c r="O370" s="2" t="n">
-        <v>3.88</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="371">
@@ -21419,7 +21419,7 @@
         </is>
       </c>
       <c r="O371" s="2" t="n">
-        <v>19.51</v>
+        <v>26.98</v>
       </c>
     </row>
     <row r="372">
@@ -21476,7 +21476,7 @@
         </is>
       </c>
       <c r="O372" s="2" t="n">
-        <v>12.38</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="373">
@@ -21533,7 +21533,7 @@
         </is>
       </c>
       <c r="O373" s="2" t="n">
-        <v>12.38</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="374">
@@ -21590,7 +21590,7 @@
         </is>
       </c>
       <c r="O374" s="2" t="n">
-        <v>16.45</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="375">
@@ -21647,7 +21647,7 @@
         </is>
       </c>
       <c r="O375" s="2" t="n">
-        <v>9.449999999999999</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="376">
@@ -21704,7 +21704,7 @@
         </is>
       </c>
       <c r="O376" s="2" t="n">
-        <v>8.93</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="377">
@@ -21761,7 +21761,7 @@
         </is>
       </c>
       <c r="O377" s="2" t="n">
-        <v>3.31</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="378">
@@ -21818,7 +21818,7 @@
         </is>
       </c>
       <c r="O378" s="2" t="n">
-        <v>4.37</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="379">
@@ -21875,7 +21875,7 @@
         </is>
       </c>
       <c r="O379" s="2" t="n">
-        <v>5.38</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="380">
@@ -21932,7 +21932,7 @@
         </is>
       </c>
       <c r="O380" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="381">
@@ -21989,7 +21989,7 @@
         </is>
       </c>
       <c r="O381" s="2" t="n">
-        <v>10.35</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="382">
@@ -22046,7 +22046,7 @@
         </is>
       </c>
       <c r="O382" s="2" t="n">
-        <v>4.91</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="383">
@@ -22103,7 +22103,7 @@
         </is>
       </c>
       <c r="O383" s="2" t="n">
-        <v>6.4</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="384">
@@ -22160,7 +22160,7 @@
         </is>
       </c>
       <c r="O384" s="2" t="n">
-        <v>11.74</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="385">
@@ -22217,7 +22217,7 @@
         </is>
       </c>
       <c r="O385" s="2" t="n">
-        <v>9.449999999999999</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="386">
@@ -22274,7 +22274,7 @@
         </is>
       </c>
       <c r="O386" s="2" t="n">
-        <v>3.35</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="387">
@@ -22331,7 +22331,7 @@
         </is>
       </c>
       <c r="O387" s="2" t="n">
-        <v>23.69</v>
+        <v>32.77</v>
       </c>
     </row>
     <row r="388">
@@ -22388,7 +22388,7 @@
         </is>
       </c>
       <c r="O388" s="2" t="n">
-        <v>3.1</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="389">
@@ -22445,7 +22445,7 @@
         </is>
       </c>
       <c r="O389" s="2" t="n">
-        <v>10.97</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="390">
@@ -22502,7 +22502,7 @@
         </is>
       </c>
       <c r="O390" s="2" t="n">
-        <v>13</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="391">
@@ -22559,7 +22559,7 @@
         </is>
       </c>
       <c r="O391" s="2" t="n">
-        <v>19.49</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="392">
@@ -22616,7 +22616,7 @@
         </is>
       </c>
       <c r="O392" s="2" t="n">
-        <v>5.9</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="393">
@@ -22673,7 +22673,7 @@
         </is>
       </c>
       <c r="O393" s="2" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="394">
@@ -22730,7 +22730,7 @@
         </is>
       </c>
       <c r="O394" s="2" t="n">
-        <v>2.23</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="395">
@@ -22787,7 +22787,7 @@
         </is>
       </c>
       <c r="O395" s="2" t="n">
-        <v>4.28</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="396">
@@ -22842,7 +22842,7 @@
         </is>
       </c>
       <c r="O396" s="2" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="397">
@@ -22897,7 +22897,7 @@
         </is>
       </c>
       <c r="O397" s="2" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="398">
@@ -22952,7 +22952,7 @@
         </is>
       </c>
       <c r="O398" s="2" t="n">
-        <v>2.03</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="399">
@@ -23007,7 +23007,7 @@
         </is>
       </c>
       <c r="O399" s="2" t="n">
-        <v>2.03</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="400">
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="O400" s="2" t="n">
-        <v>0.63</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="401">
@@ -23121,7 +23121,7 @@
         </is>
       </c>
       <c r="O401" s="2" t="n">
-        <v>0.63</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="402">
@@ -23178,7 +23178,7 @@
         </is>
       </c>
       <c r="O402" s="2" t="n">
-        <v>0.93</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="403">
@@ -23235,7 +23235,7 @@
         </is>
       </c>
       <c r="O403" s="2" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="404">
@@ -23292,7 +23292,7 @@
         </is>
       </c>
       <c r="O404" s="2" t="n">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="405">
@@ -23349,7 +23349,7 @@
         </is>
       </c>
       <c r="O405" s="2" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="406">
@@ -23406,7 +23406,7 @@
         </is>
       </c>
       <c r="O406" s="2" t="n">
-        <v>0.48</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="407">
@@ -23463,7 +23463,7 @@
         </is>
       </c>
       <c r="O407" s="2" t="n">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="408">
@@ -23520,7 +23520,7 @@
         </is>
       </c>
       <c r="O408" s="2" t="n">
-        <v>1.8</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="409">
@@ -23577,7 +23577,7 @@
         </is>
       </c>
       <c r="O409" s="2" t="n">
-        <v>1.8</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="410">
@@ -23634,7 +23634,7 @@
         </is>
       </c>
       <c r="O410" s="2" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="411">
@@ -23691,7 +23691,7 @@
         </is>
       </c>
       <c r="O411" s="2" t="n">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="412">
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="O412" s="2" t="n">
-        <v>0.8</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="413">
@@ -23805,7 +23805,7 @@
         </is>
       </c>
       <c r="O413" s="2" t="n">
-        <v>0.9</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="414">
@@ -23862,7 +23862,7 @@
         </is>
       </c>
       <c r="O414" s="2" t="n">
-        <v>0.9</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="415">
@@ -23919,7 +23919,7 @@
         </is>
       </c>
       <c r="O415" s="2" t="n">
-        <v>0.9</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="416">
@@ -23976,7 +23976,7 @@
         </is>
       </c>
       <c r="O416" s="2" t="n">
-        <v>0.9</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="417">
@@ -24033,7 +24033,7 @@
         </is>
       </c>
       <c r="O417" s="2" t="n">
-        <v>1.29</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="418">
@@ -24090,7 +24090,7 @@
         </is>
       </c>
       <c r="O418" s="2" t="n">
-        <v>1.29</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="419">
@@ -24147,7 +24147,7 @@
         </is>
       </c>
       <c r="O419" s="2" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="420">
@@ -24204,7 +24204,7 @@
         </is>
       </c>
       <c r="O420" s="2" t="n">
-        <v>2.11</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="421">
@@ -24261,7 +24261,7 @@
         </is>
       </c>
       <c r="O421" s="2" t="n">
-        <v>0.97</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="422">
@@ -24318,7 +24318,7 @@
         </is>
       </c>
       <c r="O422" s="2" t="n">
-        <v>0.97</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="423">
@@ -24375,7 +24375,7 @@
         </is>
       </c>
       <c r="O423" s="2" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="424">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="O424" s="2" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="425">
@@ -24489,7 +24489,7 @@
         </is>
       </c>
       <c r="O425" s="2" t="n">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="426">
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="O426" s="2" t="n">
-        <v>3.16</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="427">
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="O427" s="2" t="n">
-        <v>0.93</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="428">
@@ -24660,7 +24660,7 @@
         </is>
       </c>
       <c r="O428" s="2" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="429">
@@ -24717,7 +24717,7 @@
         </is>
       </c>
       <c r="O429" s="2" t="n">
-        <v>1.5</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="430">
@@ -24774,7 +24774,7 @@
         </is>
       </c>
       <c r="O430" s="2" t="n">
-        <v>0.97</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="431">
@@ -24831,7 +24831,7 @@
         </is>
       </c>
       <c r="O431" s="2" t="n">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="432">
@@ -24888,7 +24888,7 @@
         </is>
       </c>
       <c r="O432" s="2" t="n">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="433">
@@ -24945,7 +24945,7 @@
         </is>
       </c>
       <c r="O433" s="2" t="n">
-        <v>1.56</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="434">
@@ -25002,7 +25002,7 @@
         </is>
       </c>
       <c r="O434" s="2" t="n">
-        <v>1.56</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="435">
@@ -25059,7 +25059,7 @@
         </is>
       </c>
       <c r="O435" s="2" t="n">
-        <v>1.89</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="436">
@@ -25116,7 +25116,7 @@
         </is>
       </c>
       <c r="O436" s="2" t="n">
-        <v>2.55</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="437">
@@ -25173,7 +25173,7 @@
         </is>
       </c>
       <c r="O437" s="2" t="n">
-        <v>3.31</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="438">
@@ -25230,7 +25230,7 @@
         </is>
       </c>
       <c r="O438" s="2" t="n">
-        <v>3.31</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="439">
@@ -25287,7 +25287,7 @@
         </is>
       </c>
       <c r="O439" s="2" t="n">
-        <v>3.21</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="440">
@@ -25344,7 +25344,7 @@
         </is>
       </c>
       <c r="O440" s="2" t="n">
-        <v>3.21</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="441">
@@ -25401,7 +25401,7 @@
         </is>
       </c>
       <c r="O441" s="2" t="n">
-        <v>3.87</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="442">
@@ -25458,7 +25458,7 @@
         </is>
       </c>
       <c r="O442" s="2" t="n">
-        <v>4.53</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="443">
@@ -25515,7 +25515,7 @@
         </is>
       </c>
       <c r="O443" s="2" t="n">
-        <v>5.98</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="444">
@@ -25572,7 +25572,7 @@
         </is>
       </c>
       <c r="O444" s="2" t="n">
-        <v>9.470000000000001</v>
+        <v>13.09</v>
       </c>
     </row>
     <row r="445">
@@ -25629,7 +25629,7 @@
         </is>
       </c>
       <c r="O445" s="2" t="n">
-        <v>9.470000000000001</v>
+        <v>13.09</v>
       </c>
     </row>
     <row r="446">
@@ -25686,7 +25686,7 @@
         </is>
       </c>
       <c r="O446" s="2" t="n">
-        <v>2.23</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="447">
@@ -25743,7 +25743,7 @@
         </is>
       </c>
       <c r="O447" s="2" t="n">
-        <v>11.98</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="448">
@@ -25800,7 +25800,7 @@
         </is>
       </c>
       <c r="O448" s="2" t="n">
-        <v>2.93</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="449">
@@ -25857,7 +25857,7 @@
         </is>
       </c>
       <c r="O449" s="2" t="n">
-        <v>0.78</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="450">
@@ -25914,7 +25914,7 @@
         </is>
       </c>
       <c r="O450" s="2" t="n">
-        <v>1.4</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="451">
@@ -25971,7 +25971,7 @@
         </is>
       </c>
       <c r="O451" s="2" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -26028,7 +26028,7 @@
         </is>
       </c>
       <c r="O452" s="2" t="n">
-        <v>1.89</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="453">
@@ -26085,7 +26085,7 @@
         </is>
       </c>
       <c r="O453" s="2" t="n">
-        <v>2.23</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="454">
@@ -26142,7 +26142,7 @@
         </is>
       </c>
       <c r="O454" s="2" t="n">
-        <v>2.55</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="455">
@@ -26199,7 +26199,7 @@
         </is>
       </c>
       <c r="O455" s="2" t="n">
-        <v>2.88</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="456">
@@ -26256,7 +26256,7 @@
         </is>
       </c>
       <c r="O456" s="2" t="n">
-        <v>3.21</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="457">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="O457" s="2" t="n">
-        <v>5.22</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="458">
@@ -26370,7 +26370,7 @@
         </is>
       </c>
       <c r="O458" s="2" t="n">
-        <v>5.22</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="459">
@@ -26427,7 +26427,7 @@
         </is>
       </c>
       <c r="O459" s="2" t="n">
-        <v>7.18</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="460">
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="O460" s="2" t="n">
-        <v>7.54</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="461">
@@ -26541,7 +26541,7 @@
         </is>
       </c>
       <c r="O461" s="2" t="n">
-        <v>3.21</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="462">
@@ -26598,7 +26598,7 @@
         </is>
       </c>
       <c r="O462" s="2" t="n">
-        <v>4.46</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="463">
@@ -26655,7 +26655,7 @@
         </is>
       </c>
       <c r="O463" s="2" t="n">
-        <v>2.74</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="464">
@@ -26712,7 +26712,7 @@
         </is>
       </c>
       <c r="O464" s="2" t="n">
-        <v>2.74</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="465">
@@ -26769,7 +26769,7 @@
         </is>
       </c>
       <c r="O465" s="2" t="n">
-        <v>2.22</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="466">
@@ -26826,7 +26826,7 @@
         </is>
       </c>
       <c r="O466" s="2" t="n">
-        <v>4.47</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="467">
@@ -26883,7 +26883,7 @@
         </is>
       </c>
       <c r="O467" s="2" t="n">
-        <v>5.24</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="468">
@@ -26940,7 +26940,7 @@
         </is>
       </c>
       <c r="O468" s="2" t="n">
-        <v>1.91</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="469">
@@ -26997,7 +26997,7 @@
         </is>
       </c>
       <c r="O469" s="2" t="n">
-        <v>5.98</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="470">
@@ -27054,7 +27054,7 @@
         </is>
       </c>
       <c r="O470" s="2" t="n">
-        <v>5.98</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="471">
@@ -27111,7 +27111,7 @@
         </is>
       </c>
       <c r="O471" s="2" t="n">
-        <v>6.36</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="472">
@@ -27168,7 +27168,7 @@
         </is>
       </c>
       <c r="O472" s="2" t="n">
-        <v>5.62</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="473">
@@ -27225,7 +27225,7 @@
         </is>
       </c>
       <c r="O473" s="2" t="n">
-        <v>5.62</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="474">
@@ -27282,7 +27282,7 @@
         </is>
       </c>
       <c r="O474" s="2" t="n">
-        <v>7.17</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="475">
@@ -27339,7 +27339,7 @@
         </is>
       </c>
       <c r="O475" s="2" t="n">
-        <v>0.76</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="476">
@@ -27396,7 +27396,7 @@
         </is>
       </c>
       <c r="O476" s="2" t="n">
-        <v>0.9</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="477">
@@ -27453,7 +27453,7 @@
         </is>
       </c>
       <c r="O477" s="2" t="n">
-        <v>0.9</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="478">
@@ -27510,7 +27510,7 @@
         </is>
       </c>
       <c r="O478" s="2" t="n">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="479">
@@ -27567,7 +27567,7 @@
         </is>
       </c>
       <c r="O479" s="2" t="n">
-        <v>2.01</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="480">
@@ -27624,7 +27624,7 @@
         </is>
       </c>
       <c r="O480" s="2" t="n">
-        <v>2.91</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="481">
@@ -27681,7 +27681,7 @@
         </is>
       </c>
       <c r="O481" s="2" t="n">
-        <v>3.27</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="482">
@@ -27738,7 +27738,7 @@
         </is>
       </c>
       <c r="O482" s="2" t="n">
-        <v>3.27</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="483">
@@ -27795,7 +27795,7 @@
         </is>
       </c>
       <c r="O483" s="2" t="n">
-        <v>5.01</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="484">
@@ -27852,7 +27852,7 @@
         </is>
       </c>
       <c r="O484" s="2" t="n">
-        <v>5.01</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="485">
@@ -27909,7 +27909,7 @@
         </is>
       </c>
       <c r="O485" s="2" t="n">
-        <v>4.1</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="486">
@@ -27966,7 +27966,7 @@
         </is>
       </c>
       <c r="O486" s="2" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>

--- a/inventario_expandido.xlsx
+++ b/inventario_expandido.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inventario'!$A$1:$O$486</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inventario'!$A$1:$O$485</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O486"/>
+  <dimension ref="A1:O485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>€/m (6.5€/kg)</t>
+          <t>€/m (6.8€/kg)</t>
         </is>
       </c>
     </row>
@@ -618,13 +618,13 @@
         <v>45</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>25</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>10.99</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>8.41</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="5">
@@ -787,13 +787,13 @@
         <v>300</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>567</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="6">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>3.95</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="7">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>7.05</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="8">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>10.97</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="9">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>15.79</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="10">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>28.18</v>
+        <v>29.48</v>
       </c>
     </row>
     <row r="11">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="12">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>44.04</v>
+        <v>46.07</v>
       </c>
     </row>
     <row r="13">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>35.52</v>
+        <v>37.16</v>
       </c>
     </row>
     <row r="14">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>21.5</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="15">
@@ -1332,16 +1332,16 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>90</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="16">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="17">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="18">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="19">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>3.53</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="20">
@@ -1603,10 +1603,10 @@
         <v>7</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>5.51</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="21">
@@ -1653,13 +1653,13 @@
         <v>30</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>8.609999999999999</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="22">
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>12.41</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="23">
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>16.89</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="24">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>22.05</v>
+        <v>23.07</v>
       </c>
     </row>
     <row r="25">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>34.47</v>
+        <v>36.06</v>
       </c>
     </row>
     <row r="26">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>49.63</v>
+        <v>51.92</v>
       </c>
     </row>
     <row r="27">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="O27" s="2" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>6.67</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="29">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="30">
@@ -2132,13 +2132,13 @@
         <v>616</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1174</v>
+        <v>1155</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="31">
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="O31" s="2" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="32">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="33">
@@ -2300,10 +2300,10 @@
         <v>254</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="O33" s="2" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="34">
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="O34" s="2" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="35">
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>79</v>
@@ -2413,7 +2413,7 @@
         <v>1</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="O35" s="2" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="36">
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="O36" s="2" t="n">
-        <v>4.21</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="37">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="O37" s="2" t="n">
-        <v>5.28</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="38">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="O38" s="2" t="n">
-        <v>10.53</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="39">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="O39" s="2" t="n">
-        <v>4.21</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="40">
@@ -2682,13 +2682,13 @@
         <v>19</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>187</v>
+        <v>342</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>17</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>223</v>
+        <v>378</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="O40" s="2" t="n">
-        <v>5.63</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="41">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="O41" s="2" t="n">
-        <v>7.05</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="42">
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="O42" s="2" t="n">
-        <v>10.53</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="43">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="O43" s="2" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="44">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="O44" s="2" t="n">
-        <v>4.39</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="45">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="O45" s="2" t="n">
-        <v>4.39</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="46">
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="O46" s="2" t="n">
-        <v>4.39</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="47">
@@ -3067,13 +3067,13 @@
         <v>66</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>119</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="O47" s="2" t="n">
-        <v>7.02</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="48">
@@ -3125,10 +3125,10 @@
         <v>151</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="O48" s="2" t="n">
-        <v>8.81</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="O49" s="2" t="n">
-        <v>13.16</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="50">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>17.56</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="51">
@@ -3290,10 +3290,10 @@
         <v>328</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N51" s="6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="O51" s="2" t="n">
-        <v>10.53</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="52">
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>12.64</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="53">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>15.79</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="54">
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="O54" s="2" t="n">
-        <v>21.05</v>
+        <v>22.03</v>
       </c>
     </row>
     <row r="55">
@@ -3510,10 +3510,10 @@
         <v>79</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>12.28</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="56">
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="O56" s="2" t="n">
-        <v>11.26</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="57">
@@ -3617,13 +3617,13 @@
         <v>0</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="O57" s="2" t="n">
-        <v>11.26</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="58">
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>24</v>
@@ -3678,7 +3678,7 @@
         <v>29</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="O58" s="2" t="n">
-        <v>14.09</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="59">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="O59" s="2" t="n">
-        <v>21.14</v>
+        <v>22.11</v>
       </c>
     </row>
     <row r="60">
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="O60" s="2" t="n">
-        <v>28.08</v>
+        <v>29.38</v>
       </c>
     </row>
     <row r="61">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="O61" s="2" t="n">
-        <v>14.04</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="62">
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="O62" s="2" t="n">
-        <v>17.61</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="63">
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="O63" s="2" t="n">
-        <v>20.66</v>
+        <v>21.61</v>
       </c>
     </row>
     <row r="64">
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="O64" s="2" t="n">
-        <v>21.02</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="65">
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="O65" s="2" t="n">
-        <v>25.27</v>
+        <v>26.44</v>
       </c>
     </row>
     <row r="66">
@@ -4112,13 +4112,13 @@
         <v>5</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N66" s="6" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="O66" s="2" t="n">
-        <v>34.22</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="67">
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="O67" s="2" t="n">
-        <v>26.31</v>
+        <v>27.53</v>
       </c>
     </row>
     <row r="68">
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="O68" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="69">
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="O69" s="2" t="n">
-        <v>19.74</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="70">
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="O70" s="2" t="n">
-        <v>35.1</v>
+        <v>36.72</v>
       </c>
     </row>
     <row r="71">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="O71" s="2" t="n">
-        <v>14.04</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="72">
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="O72" s="2" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="73">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="O73" s="2" t="n">
-        <v>5.26</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="74">
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="O74" s="2" t="n">
-        <v>7.9</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="75">
@@ -4607,13 +4607,13 @@
         <v>206</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>267</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="O75" s="2" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="76">
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="O76" s="2" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="77">
@@ -4717,13 +4717,13 @@
         <v>117</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>7</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="O77" s="2" t="n">
-        <v>3.07</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="78">
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="O78" s="2" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="79">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="O79" s="2" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="80">
@@ -4885,10 +4885,10 @@
         <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="N80" s="6" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="O80" s="2" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="81">
@@ -4937,13 +4937,13 @@
         <v>3</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>4</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="N81" s="6" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="O81" s="2" t="n">
-        <v>3.51</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="82">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="O82" s="2" t="n">
-        <v>35.1</v>
+        <v>36.72</v>
       </c>
     </row>
     <row r="83">
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="O83" s="2" t="n">
-        <v>31.59</v>
+        <v>33.05</v>
       </c>
     </row>
     <row r="84">
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="O84" s="2" t="n">
-        <v>42.12</v>
+        <v>44.06</v>
       </c>
     </row>
     <row r="85">
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="O85" s="2" t="n">
-        <v>52.65</v>
+        <v>55.08</v>
       </c>
     </row>
     <row r="86">
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="O86" s="2" t="n">
-        <v>25.83</v>
+        <v>27.02</v>
       </c>
     </row>
     <row r="87">
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="O87" s="2" t="n">
-        <v>8.42</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="88">
@@ -5336,7 +5336,7 @@
         </is>
       </c>
       <c r="O88" s="2" t="n">
-        <v>39.49</v>
+        <v>41.31</v>
       </c>
     </row>
     <row r="89">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="O89" s="2" t="n">
-        <v>24.57</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="90">
@@ -5432,13 +5432,13 @@
         <v>66</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>97</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="O90" s="2" t="n">
-        <v>7.02</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="91">
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="O91" s="2" t="n">
-        <v>3.07</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="92">
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="O92" s="2" t="n">
-        <v>5.26</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="93">
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="O93" s="2" t="n">
-        <v>5.26</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="94">
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="O94" s="2" t="n">
-        <v>20.92</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="95">
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="O95" s="2" t="n">
-        <v>20.92</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="96">
@@ -5776,7 +5776,7 @@
         </is>
       </c>
       <c r="O96" s="2" t="n">
-        <v>5.26</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="97">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="O97" s="2" t="n">
-        <v>7.9</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="98">
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="O98" s="2" t="n">
-        <v>6.14</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="99">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="O99" s="2" t="n">
-        <v>4.74</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="100">
@@ -5996,7 +5996,7 @@
         </is>
       </c>
       <c r="O100" s="2" t="n">
-        <v>4.74</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="101">
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="O101" s="2" t="n">
-        <v>4.74</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="102">
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="O102" s="2" t="n">
-        <v>7.9</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="103">
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="O103" s="2" t="n">
-        <v>15.8</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="104">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="O104" s="2" t="n">
-        <v>16.85</v>
+        <v>17.63</v>
       </c>
     </row>
     <row r="105">
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="O105" s="2" t="n">
-        <v>4.21</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="106">
@@ -6326,7 +6326,7 @@
         </is>
       </c>
       <c r="O106" s="2" t="n">
-        <v>12.64</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="107">
@@ -6364,16 +6364,16 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>80</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="N107" s="4" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="O107" s="2" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="108">
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="O108" s="2" t="n">
-        <v>4.39</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="109">
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="O109" s="2" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="110">
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="O110" s="2" t="n">
-        <v>28.08</v>
+        <v>29.38</v>
       </c>
     </row>
     <row r="111">
@@ -6587,13 +6587,13 @@
         <v>0</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M111" s="2" t="n">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="N111" s="6" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="O111" s="2" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="112">
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="O112" s="2" t="n">
-        <v>13.16</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="113">
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="O113" s="2" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="114">
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="O114" s="2" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="115">
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="O115" s="2" t="n">
-        <v>10.78</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="116">
@@ -6884,7 +6884,7 @@
         </is>
       </c>
       <c r="O116" s="2" t="n">
-        <v>9.65</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="117">
@@ -6930,10 +6930,10 @@
         <v>42</v>
       </c>
       <c r="L117" s="2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M117" s="2" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N117" s="4" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="O117" s="2" t="n">
-        <v>15.76</v>
+        <v>16.48</v>
       </c>
     </row>
     <row r="118">
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="O118" s="2" t="n">
-        <v>25.17</v>
+        <v>26.34</v>
       </c>
     </row>
     <row r="119">
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="O119" s="2" t="n">
-        <v>58.34</v>
+        <v>61.03</v>
       </c>
     </row>
     <row r="120">
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="O120" s="2" t="n">
-        <v>4.97</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="121">
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="O121" s="2" t="n">
-        <v>7.08</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="122">
@@ -7212,10 +7212,10 @@
         <v>9</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M122" s="2" t="n">
         <v>34</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="O122" s="2" t="n">
-        <v>3.03</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="123">
@@ -7269,13 +7269,13 @@
         <v>0</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M123" s="2" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="N123" s="6" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="O123" s="2" t="n">
-        <v>22.53</v>
+        <v>23.57</v>
       </c>
     </row>
     <row r="124">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="O124" s="2" t="n">
-        <v>7.98</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="125">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="O125" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="126">
@@ -7440,13 +7440,13 @@
         <v>0</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L126" s="2" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="M126" s="2" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="N126" s="6" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="O126" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="127">
@@ -7500,10 +7500,10 @@
         <v>121</v>
       </c>
       <c r="L127" s="2" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M127" s="2" t="n">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N127" s="4" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="O127" s="2" t="n">
-        <v>7.86</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="128">
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="O128" s="2" t="n">
-        <v>5.98</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="129">
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="O129" s="2" t="n">
-        <v>15.58</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="130">
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="O130" s="2" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="131">
@@ -7739,7 +7739,7 @@
         </is>
       </c>
       <c r="O131" s="2" t="n">
-        <v>7.93</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="132">
@@ -7796,7 +7796,7 @@
         </is>
       </c>
       <c r="O132" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="133">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="O133" s="2" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="134">
@@ -7896,13 +7896,13 @@
         <v>106</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L134" s="2" t="n">
         <v>124</v>
       </c>
       <c r="M134" s="2" t="n">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="N134" s="4" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="O134" s="2" t="n">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="135">
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="O135" s="2" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="136">
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>395</v>
@@ -8016,7 +8016,7 @@
         <v>2</v>
       </c>
       <c r="M136" s="2" t="n">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="N136" s="4" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="O136" s="2" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="137">
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="O137" s="2" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="138">
@@ -8124,13 +8124,13 @@
         <v>55</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="L138" s="2" t="n">
         <v>37</v>
       </c>
       <c r="M138" s="2" t="n">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="N138" s="4" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="O138" s="2" t="n">
-        <v>5.36</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="139">
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="O139" s="2" t="n">
-        <v>8.33</v>
+        <v>8.720000000000001</v>
       </c>
     </row>
     <row r="140">
@@ -8252,7 +8252,7 @@
         </is>
       </c>
       <c r="O140" s="2" t="n">
-        <v>8.33</v>
+        <v>8.720000000000001</v>
       </c>
     </row>
     <row r="141">
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="O141" s="2" t="n">
-        <v>12.01</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="142">
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="O142" s="2" t="n">
-        <v>14.1</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="143">
@@ -8409,13 +8409,13 @@
         <v>52</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L143" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M143" s="2" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="N143" s="4" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="O143" s="2" t="n">
-        <v>21.34</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="144">
@@ -8480,7 +8480,7 @@
         </is>
       </c>
       <c r="O144" s="2" t="n">
-        <v>33.34</v>
+        <v>34.88</v>
       </c>
     </row>
     <row r="145">
@@ -8523,13 +8523,13 @@
         <v>343</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="L145" s="2" t="n">
         <v>248</v>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1111</v>
+        <v>1085</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="O145" s="2" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="146">
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c r="O146" s="2" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="147">
@@ -8637,13 +8637,13 @@
         <v>62</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>225</v>
+        <v>367</v>
       </c>
       <c r="L147" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M147" s="2" t="n">
-        <v>287</v>
+        <v>429</v>
       </c>
       <c r="N147" s="4" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         </is>
       </c>
       <c r="O147" s="2" t="n">
-        <v>4.58</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="148">
@@ -8694,13 +8694,13 @@
         <v>0</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="L148" s="2" t="n">
         <v>22</v>
       </c>
       <c r="M148" s="2" t="n">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="N148" s="6" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="O148" s="2" t="n">
-        <v>5.11</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="149">
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="O149" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="150">
@@ -8822,7 +8822,7 @@
         </is>
       </c>
       <c r="O150" s="2" t="n">
-        <v>5.7</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="151">
@@ -8879,7 +8879,7 @@
         </is>
       </c>
       <c r="O151" s="2" t="n">
-        <v>40.5</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="152">
@@ -8936,7 +8936,7 @@
         </is>
       </c>
       <c r="O152" s="2" t="n">
-        <v>40.5</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="153">
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="O153" s="2" t="n">
-        <v>10.95</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="154">
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="O154" s="2" t="n">
-        <v>20.43</v>
+        <v>21.37</v>
       </c>
     </row>
     <row r="155">
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K155" s="2" t="n">
         <v>0</v>
@@ -9099,7 +9099,7 @@
         <v>82</v>
       </c>
       <c r="M155" s="2" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="N155" s="4" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         </is>
       </c>
       <c r="O155" s="2" t="n">
-        <v>10.37</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="156">
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="O156" s="2" t="n">
-        <v>6.58</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="157">
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="O157" s="2" t="n">
-        <v>4.14</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="158">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="O158" s="2" t="n">
-        <v>10.25</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="159">
@@ -9321,13 +9321,13 @@
         <v>162</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="L159" s="2" t="n">
         <v>166</v>
       </c>
       <c r="M159" s="2" t="n">
-        <v>604</v>
+        <v>570</v>
       </c>
       <c r="N159" s="4" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         </is>
       </c>
       <c r="O159" s="2" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="160">
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="O160" s="2" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="161">
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="O161" s="2" t="n">
-        <v>10.49</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="162">
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="O162" s="2" t="n">
-        <v>4.51</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="163">
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="O163" s="2" t="n">
-        <v>38.43</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="164">
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="O164" s="2" t="n">
-        <v>42.26</v>
+        <v>44.21</v>
       </c>
     </row>
     <row r="165">
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="O165" s="2" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="166">
@@ -9720,13 +9720,13 @@
         <v>192</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L166" s="2" t="n">
         <v>4</v>
       </c>
       <c r="M166" s="2" t="n">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="N166" s="4" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="O166" s="2" t="n">
-        <v>6.76</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="167">
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="O167" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="168">
@@ -9848,7 +9848,7 @@
         </is>
       </c>
       <c r="O168" s="2" t="n">
-        <v>4.14</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="169">
@@ -9894,10 +9894,10 @@
         <v>184</v>
       </c>
       <c r="L169" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M169" s="2" t="n">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="N169" s="4" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         </is>
       </c>
       <c r="O169" s="2" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="170">
@@ -9948,10 +9948,10 @@
         <v>116</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="L170" s="2" t="n">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="M170" s="2" t="n">
         <v>291</v>
@@ -9962,7 +9962,7 @@
         </is>
       </c>
       <c r="O170" s="2" t="n">
-        <v>4.05</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="171">
@@ -10019,7 +10019,7 @@
         </is>
       </c>
       <c r="O171" s="2" t="n">
-        <v>15.16</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="172">
@@ -10076,7 +10076,7 @@
         </is>
       </c>
       <c r="O172" s="2" t="n">
-        <v>12.73</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="173">
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="O173" s="2" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="174">
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="O174" s="2" t="n">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="175">
@@ -10230,24 +10230,24 @@
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="L175" s="2" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="M175" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="N175" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>54</v>
+      </c>
+      <c r="N175" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O175" s="2" t="n">
-        <v>4.84</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="176">
@@ -10304,7 +10304,7 @@
         </is>
       </c>
       <c r="O176" s="2" t="n">
-        <v>8.789999999999999</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="177">
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="O177" s="2" t="n">
-        <v>3.45</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="178">
@@ -10418,7 +10418,7 @@
         </is>
       </c>
       <c r="O178" s="2" t="n">
-        <v>3.93</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="179">
@@ -10475,7 +10475,7 @@
         </is>
       </c>
       <c r="O179" s="2" t="n">
-        <v>6.12</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="180">
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="O180" s="2" t="n">
-        <v>4.08</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="181">
@@ -10575,13 +10575,13 @@
         <v>1</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="L181" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M181" s="2" t="n">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="N181" s="6" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         </is>
       </c>
       <c r="O181" s="2" t="n">
-        <v>4.08</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="182">
@@ -10632,13 +10632,13 @@
         <v>0</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="L182" s="2" t="n">
         <v>100</v>
       </c>
       <c r="M182" s="2" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="N182" s="6" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="O182" s="2" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="183">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="O183" s="2" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="184">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="O184" s="2" t="n">
-        <v>5.43</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="185">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="O185" s="2" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="186">
@@ -10874,7 +10874,7 @@
         </is>
       </c>
       <c r="O186" s="2" t="n">
-        <v>3.79</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="187">
@@ -10931,7 +10931,7 @@
         </is>
       </c>
       <c r="O187" s="2" t="n">
-        <v>4.14</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="188">
@@ -10988,7 +10988,7 @@
         </is>
       </c>
       <c r="O188" s="2" t="n">
-        <v>9.85</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="189">
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="O189" s="2" t="n">
-        <v>3.79</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="190">
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="O190" s="2" t="n">
-        <v>6.07</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="191">
@@ -11159,7 +11159,7 @@
         </is>
       </c>
       <c r="O191" s="2" t="n">
-        <v>5.36</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="192">
@@ -11199,16 +11199,16 @@
         </is>
       </c>
       <c r="J192" s="2" t="n">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="K192" s="2" t="n">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="L192" s="2" t="n">
-        <v>160</v>
+        <v>286</v>
       </c>
       <c r="M192" s="2" t="n">
-        <v>386</v>
+        <v>652</v>
       </c>
       <c r="N192" s="4" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="O192" s="2" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="193">
@@ -11273,7 +11273,7 @@
         </is>
       </c>
       <c r="O193" s="2" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="194">
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="O194" s="2" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="195">
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="O195" s="2" t="n">
-        <v>8.33</v>
+        <v>8.720000000000001</v>
       </c>
     </row>
     <row r="196">
@@ -11444,7 +11444,7 @@
         </is>
       </c>
       <c r="O196" s="2" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="197">
@@ -11484,7 +11484,7 @@
         </is>
       </c>
       <c r="J197" s="2" t="n">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="K197" s="2" t="n">
         <v>60</v>
@@ -11493,7 +11493,7 @@
         <v>180</v>
       </c>
       <c r="M197" s="2" t="n">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="N197" s="4" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         </is>
       </c>
       <c r="O197" s="2" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="198">
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="O198" s="2" t="n">
-        <v>8.029999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="199">
@@ -11598,16 +11598,16 @@
         </is>
       </c>
       <c r="J199" s="2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K199" s="2" t="n">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="L199" s="2" t="n">
         <v>300</v>
       </c>
       <c r="M199" s="2" t="n">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="N199" s="4" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         </is>
       </c>
       <c r="O199" s="2" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="200">
@@ -11655,7 +11655,7 @@
         </is>
       </c>
       <c r="J200" s="2" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K200" s="2" t="n">
         <v>84</v>
@@ -11664,7 +11664,7 @@
         <v>45</v>
       </c>
       <c r="M200" s="2" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N200" s="4" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="O200" s="2" t="n">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="201">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="O201" s="2" t="n">
-        <v>3.65</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="202">
@@ -11772,13 +11772,13 @@
         <v>9</v>
       </c>
       <c r="K202" s="2" t="n">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="L202" s="2" t="n">
         <v>26</v>
       </c>
       <c r="M202" s="2" t="n">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="N202" s="6" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         </is>
       </c>
       <c r="O202" s="2" t="n">
-        <v>5.28</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="203">
@@ -11843,7 +11843,7 @@
         </is>
       </c>
       <c r="O203" s="2" t="n">
-        <v>3.79</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="204">
@@ -11886,13 +11886,13 @@
         <v>81</v>
       </c>
       <c r="K204" s="2" t="n">
-        <v>224</v>
+        <v>302</v>
       </c>
       <c r="L204" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M204" s="2" t="n">
-        <v>305</v>
+        <v>383</v>
       </c>
       <c r="N204" s="4" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         </is>
       </c>
       <c r="O204" s="2" t="n">
-        <v>6.89</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="205">
@@ -11943,13 +11943,13 @@
         <v>151</v>
       </c>
       <c r="K205" s="2" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L205" s="2" t="n">
         <v>96</v>
       </c>
       <c r="M205" s="2" t="n">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="N205" s="4" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         </is>
       </c>
       <c r="O205" s="2" t="n">
-        <v>4.47</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="206">
@@ -12014,7 +12014,7 @@
         </is>
       </c>
       <c r="O206" s="2" t="n">
-        <v>5.19</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="207">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="O207" s="2" t="n">
-        <v>9.65</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="208">
@@ -12111,24 +12111,24 @@
         </is>
       </c>
       <c r="J208" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K208" s="2" t="n">
         <v>70</v>
       </c>
       <c r="L208" s="2" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="M208" s="2" t="n">
-        <v>175</v>
-      </c>
-      <c r="N208" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>168</v>
+      </c>
+      <c r="N208" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O208" s="2" t="n">
-        <v>9.65</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="209">
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="O209" s="2" t="n">
-        <v>7.77</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="210">
@@ -12242,7 +12242,7 @@
         </is>
       </c>
       <c r="O210" s="2" t="n">
-        <v>12.41</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="211">
@@ -12282,7 +12282,7 @@
         </is>
       </c>
       <c r="J211" s="2" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K211" s="2" t="n">
         <v>61</v>
@@ -12291,7 +12291,7 @@
         <v>41</v>
       </c>
       <c r="M211" s="2" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N211" s="4" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         </is>
       </c>
       <c r="O211" s="2" t="n">
-        <v>12.41</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="212">
@@ -12356,7 +12356,7 @@
         </is>
       </c>
       <c r="O212" s="2" t="n">
-        <v>12.4</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="213">
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="O213" s="2" t="n">
-        <v>15.16</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="214">
@@ -12470,7 +12470,7 @@
         </is>
       </c>
       <c r="O214" s="2" t="n">
-        <v>20.75</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="215">
@@ -12527,7 +12527,7 @@
         </is>
       </c>
       <c r="O215" s="2" t="n">
-        <v>49.62</v>
+        <v>51.91</v>
       </c>
     </row>
     <row r="216">
@@ -12584,7 +12584,7 @@
         </is>
       </c>
       <c r="O216" s="2" t="n">
-        <v>49.62</v>
+        <v>51.91</v>
       </c>
     </row>
     <row r="217">
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="O217" s="2" t="n">
-        <v>25.16</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="218">
@@ -12698,7 +12698,7 @@
         </is>
       </c>
       <c r="O218" s="2" t="n">
-        <v>17.69</v>
+        <v>18.51</v>
       </c>
     </row>
     <row r="219">
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="O219" s="2" t="n">
-        <v>26.18</v>
+        <v>27.39</v>
       </c>
     </row>
     <row r="220">
@@ -12812,7 +12812,7 @@
         </is>
       </c>
       <c r="O220" s="2" t="n">
-        <v>26.18</v>
+        <v>27.39</v>
       </c>
     </row>
     <row r="221">
@@ -12869,7 +12869,7 @@
         </is>
       </c>
       <c r="O221" s="2" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="222">
@@ -12912,13 +12912,13 @@
         <v>0</v>
       </c>
       <c r="K222" s="2" t="n">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="L222" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M222" s="2" t="n">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="N222" s="6" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         </is>
       </c>
       <c r="O222" s="2" t="n">
-        <v>4.19</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="223">
@@ -12969,13 +12969,13 @@
         <v>74</v>
       </c>
       <c r="K223" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L223" s="2" t="n">
         <v>130</v>
       </c>
       <c r="M223" s="2" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N223" s="4" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="O223" s="2" t="n">
-        <v>5.86</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="224">
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="O224" s="2" t="n">
-        <v>12.78</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="225">
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="O225" s="2" t="n">
-        <v>23.43</v>
+        <v>24.51</v>
       </c>
     </row>
     <row r="226">
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="O226" s="2" t="n">
-        <v>64.18000000000001</v>
+        <v>67.14</v>
       </c>
     </row>
     <row r="227">
@@ -13197,13 +13197,13 @@
         <v>396</v>
       </c>
       <c r="K227" s="2" t="n">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="L227" s="2" t="n">
         <v>108</v>
       </c>
       <c r="M227" s="2" t="n">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="N227" s="4" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         </is>
       </c>
       <c r="O227" s="2" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="228">
@@ -13254,13 +13254,13 @@
         <v>16</v>
       </c>
       <c r="K228" s="2" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L228" s="2" t="n">
         <v>30</v>
       </c>
       <c r="M228" s="2" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N228" s="4" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         </is>
       </c>
       <c r="O228" s="2" t="n">
-        <v>6.4</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="229">
@@ -13325,7 +13325,7 @@
         </is>
       </c>
       <c r="O229" s="2" t="n">
-        <v>22.82</v>
+        <v>23.87</v>
       </c>
     </row>
     <row r="230">
@@ -13382,7 +13382,7 @@
         </is>
       </c>
       <c r="O230" s="2" t="n">
-        <v>10.85</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="231">
@@ -13439,7 +13439,7 @@
         </is>
       </c>
       <c r="O231" s="2" t="n">
-        <v>7.97</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="232">
@@ -13496,7 +13496,7 @@
         </is>
       </c>
       <c r="O232" s="2" t="n">
-        <v>5.28</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="233">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="O233" s="2" t="n">
-        <v>10.67</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="234">
@@ -13610,7 +13610,7 @@
         </is>
       </c>
       <c r="O234" s="2" t="n">
-        <v>7.92</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="235">
@@ -13650,16 +13650,16 @@
         </is>
       </c>
       <c r="J235" s="2" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K235" s="2" t="n">
         <v>174</v>
       </c>
       <c r="L235" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M235" s="2" t="n">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="N235" s="4" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         </is>
       </c>
       <c r="O235" s="2" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="236">
@@ -13724,7 +13724,7 @@
         </is>
       </c>
       <c r="O236" s="2" t="n">
-        <v>4.42</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="237">
@@ -13767,13 +13767,13 @@
         <v>0</v>
       </c>
       <c r="K237" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L237" s="2" t="n">
         <v>13</v>
       </c>
       <c r="M237" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N237" s="6" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="O237" s="2" t="n">
-        <v>19.36</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="238">
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="O238" s="2" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="239">
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="O239" s="2" t="n">
-        <v>8.380000000000001</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="240">
@@ -13952,7 +13952,7 @@
         </is>
       </c>
       <c r="O240" s="2" t="n">
-        <v>4.81</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="241">
@@ -14009,7 +14009,7 @@
         </is>
       </c>
       <c r="O241" s="2" t="n">
-        <v>5.3</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="242">
@@ -14066,7 +14066,7 @@
         </is>
       </c>
       <c r="O242" s="2" t="n">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="243">
@@ -14123,7 +14123,7 @@
         </is>
       </c>
       <c r="O243" s="2" t="n">
-        <v>67.95999999999999</v>
+        <v>71.09</v>
       </c>
     </row>
     <row r="244">
@@ -14180,7 +14180,7 @@
         </is>
       </c>
       <c r="O244" s="2" t="n">
-        <v>14.55</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="245">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="O245" s="2" t="n">
-        <v>40.82</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="246">
@@ -14277,7 +14277,7 @@
         </is>
       </c>
       <c r="J246" s="2" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K246" s="2" t="n">
         <v>192</v>
@@ -14286,7 +14286,7 @@
         <v>182</v>
       </c>
       <c r="M246" s="2" t="n">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="N246" s="4" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="O246" s="2" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="247">
@@ -14351,7 +14351,7 @@
         </is>
       </c>
       <c r="O247" s="2" t="n">
-        <v>7.46</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="248">
@@ -14394,13 +14394,13 @@
         <v>18</v>
       </c>
       <c r="K248" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L248" s="2" t="n">
         <v>26</v>
       </c>
       <c r="M248" s="2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N248" s="4" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         </is>
       </c>
       <c r="O248" s="2" t="n">
-        <v>5.84</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="249">
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="O249" s="2" t="n">
-        <v>3.99</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="250">
@@ -14522,7 +14522,7 @@
         </is>
       </c>
       <c r="O250" s="2" t="n">
-        <v>21.24</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="251">
@@ -14562,7 +14562,7 @@
         </is>
       </c>
       <c r="J251" s="2" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K251" s="2" t="n">
         <v>0</v>
@@ -14571,7 +14571,7 @@
         <v>222</v>
       </c>
       <c r="M251" s="2" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="N251" s="4" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         </is>
       </c>
       <c r="O251" s="2" t="n">
-        <v>3.09</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="252">
@@ -14636,7 +14636,7 @@
         </is>
       </c>
       <c r="O252" s="2" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="253">
@@ -14693,7 +14693,7 @@
         </is>
       </c>
       <c r="O253" s="2" t="n">
-        <v>3.17</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="254">
@@ -14750,7 +14750,7 @@
         </is>
       </c>
       <c r="O254" s="2" t="n">
-        <v>3.17</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="255">
@@ -14790,16 +14790,16 @@
         </is>
       </c>
       <c r="J255" s="2" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K255" s="2" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="L255" s="2" t="n">
         <v>295</v>
       </c>
       <c r="M255" s="2" t="n">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="N255" s="4" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="O255" s="2" t="n">
-        <v>5.69</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="256">
@@ -14850,13 +14850,13 @@
         <v>139</v>
       </c>
       <c r="K256" s="2" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L256" s="2" t="n">
         <v>36</v>
       </c>
       <c r="M256" s="2" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="N256" s="4" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="O256" s="2" t="n">
-        <v>4.63</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="257">
@@ -14904,16 +14904,16 @@
         </is>
       </c>
       <c r="J257" s="2" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K257" s="2" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L257" s="2" t="n">
         <v>79</v>
       </c>
       <c r="M257" s="2" t="n">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="N257" s="4" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="O257" s="2" t="n">
-        <v>5.36</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="258">
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="O258" s="2" t="n">
-        <v>6.61</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="259">
@@ -15021,13 +15021,13 @@
         <v>71</v>
       </c>
       <c r="K259" s="2" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="L259" s="2" t="n">
         <v>44</v>
       </c>
       <c r="M259" s="2" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N259" s="4" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         </is>
       </c>
       <c r="O259" s="2" t="n">
-        <v>10.11</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="260">
@@ -15078,13 +15078,13 @@
         <v>95</v>
       </c>
       <c r="K260" s="2" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L260" s="2" t="n">
         <v>116</v>
       </c>
       <c r="M260" s="2" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N260" s="4" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         </is>
       </c>
       <c r="O260" s="2" t="n">
-        <v>6.77</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="261">
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="O261" s="2" t="n">
-        <v>12.92</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="262">
@@ -15192,13 +15192,13 @@
         <v>57</v>
       </c>
       <c r="K262" s="2" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="L262" s="2" t="n">
         <v>142</v>
       </c>
       <c r="M262" s="2" t="n">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="N262" s="4" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         </is>
       </c>
       <c r="O262" s="2" t="n">
-        <v>12.06</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="263">
@@ -15252,10 +15252,10 @@
         <v>49</v>
       </c>
       <c r="L263" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M263" s="2" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N263" s="4" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         </is>
       </c>
       <c r="O263" s="2" t="n">
-        <v>15.72</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="264">
@@ -15320,7 +15320,7 @@
         </is>
       </c>
       <c r="O264" s="2" t="n">
-        <v>18.53</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="265">
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="O265" s="2" t="n">
-        <v>21.33</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="266">
@@ -15417,16 +15417,16 @@
         </is>
       </c>
       <c r="J266" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K266" s="2" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="L266" s="2" t="n">
         <v>12</v>
       </c>
       <c r="M266" s="2" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="N266" s="6" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         </is>
       </c>
       <c r="O266" s="2" t="n">
-        <v>40.44</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="267">
@@ -15474,16 +15474,16 @@
         </is>
       </c>
       <c r="J267" s="2" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="K267" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L267" s="2" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="M267" s="2" t="n">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="N267" s="4" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         </is>
       </c>
       <c r="O267" s="2" t="n">
-        <v>26.86</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="268">
@@ -15548,7 +15548,7 @@
         </is>
       </c>
       <c r="O268" s="2" t="n">
-        <v>16.28</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="269">
@@ -15591,13 +15591,13 @@
         <v>53</v>
       </c>
       <c r="K269" s="2" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="L269" s="2" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="M269" s="2" t="n">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="N269" s="4" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         </is>
       </c>
       <c r="O269" s="2" t="n">
-        <v>3.95</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="270">
@@ -15662,7 +15662,7 @@
         </is>
       </c>
       <c r="O270" s="2" t="n">
-        <v>6.04</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="271">
@@ -15719,7 +15719,7 @@
         </is>
       </c>
       <c r="O271" s="2" t="n">
-        <v>9.58</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="272">
@@ -15776,7 +15776,7 @@
         </is>
       </c>
       <c r="O272" s="2" t="n">
-        <v>9.58</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="273">
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="O273" s="2" t="n">
-        <v>25.96</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="274">
@@ -15890,7 +15890,7 @@
         </is>
       </c>
       <c r="O274" s="2" t="n">
-        <v>25.96</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="275">
@@ -15947,7 +15947,7 @@
         </is>
       </c>
       <c r="O275" s="2" t="n">
-        <v>40.36</v>
+        <v>42.23</v>
       </c>
     </row>
     <row r="276">
@@ -15987,16 +15987,16 @@
         </is>
       </c>
       <c r="J276" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K276" s="2" t="n">
         <v>3</v>
       </c>
       <c r="L276" s="2" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="M276" s="2" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N276" s="6" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         </is>
       </c>
       <c r="O276" s="2" t="n">
-        <v>4.86</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="277">
@@ -16061,7 +16061,7 @@
         </is>
       </c>
       <c r="O277" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="278">
@@ -16118,7 +16118,7 @@
         </is>
       </c>
       <c r="O278" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="279">
@@ -16158,16 +16158,16 @@
         </is>
       </c>
       <c r="J279" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K279" s="2" t="n">
-        <v>424</v>
+        <v>513</v>
       </c>
       <c r="L279" s="2" t="n">
         <v>76</v>
       </c>
       <c r="M279" s="2" t="n">
-        <v>534</v>
+        <v>621</v>
       </c>
       <c r="N279" s="4" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         </is>
       </c>
       <c r="O279" s="2" t="n">
-        <v>7.79</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="280">
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="O280" s="2" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="281">
@@ -16289,7 +16289,7 @@
         </is>
       </c>
       <c r="O281" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="282">
@@ -16346,7 +16346,7 @@
         </is>
       </c>
       <c r="O282" s="2" t="n">
-        <v>5.55</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="283">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="O283" s="2" t="n">
-        <v>11.99</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="284">
@@ -16460,7 +16460,7 @@
         </is>
       </c>
       <c r="O284" s="2" t="n">
-        <v>12.78</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="285">
@@ -16500,10 +16500,10 @@
         </is>
       </c>
       <c r="J285" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="K285" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="K285" s="2" t="n">
-        <v>17</v>
       </c>
       <c r="L285" s="2" t="n">
         <v>0</v>
@@ -16511,13 +16511,13 @@
       <c r="M285" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="N285" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+      <c r="N285" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O285" s="2" t="n">
-        <v>39.23</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="286">
@@ -16574,7 +16574,7 @@
         </is>
       </c>
       <c r="O286" s="2" t="n">
-        <v>9.9</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="287">
@@ -16631,7 +16631,7 @@
         </is>
       </c>
       <c r="O287" s="2" t="n">
-        <v>26.88</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="288">
@@ -16671,16 +16671,16 @@
         </is>
       </c>
       <c r="J288" s="2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K288" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L288" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M288" s="2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N288" s="4" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         </is>
       </c>
       <c r="O288" s="2" t="n">
-        <v>26.88</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="289">
@@ -16745,7 +16745,7 @@
         </is>
       </c>
       <c r="O289" s="2" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="290">
@@ -16802,7 +16802,7 @@
         </is>
       </c>
       <c r="O290" s="2" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="291">
@@ -16859,7 +16859,7 @@
         </is>
       </c>
       <c r="O291" s="2" t="n">
-        <v>20.86</v>
+        <v>21.82</v>
       </c>
     </row>
     <row r="292">
@@ -16916,7 +16916,7 @@
         </is>
       </c>
       <c r="O292" s="2" t="n">
-        <v>68</v>
+        <v>71.13</v>
       </c>
     </row>
     <row r="293">
@@ -16973,7 +16973,7 @@
         </is>
       </c>
       <c r="O293" s="2" t="n">
-        <v>68</v>
+        <v>71.13</v>
       </c>
     </row>
     <row r="294">
@@ -17030,7 +17030,7 @@
         </is>
       </c>
       <c r="O294" s="2" t="n">
-        <v>68</v>
+        <v>71.13</v>
       </c>
     </row>
     <row r="295">
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="O295" s="2" t="n">
-        <v>10.09</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="296">
@@ -17130,13 +17130,13 @@
         <v>81</v>
       </c>
       <c r="K296" s="2" t="n">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="L296" s="2" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="M296" s="2" t="n">
-        <v>489</v>
+        <v>451</v>
       </c>
       <c r="N296" s="4" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         </is>
       </c>
       <c r="O296" s="2" t="n">
-        <v>3.93</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="297">
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="O297" s="2" t="n">
-        <v>3.93</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="298">
@@ -17258,7 +17258,7 @@
         </is>
       </c>
       <c r="O298" s="2" t="n">
-        <v>4.63</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="299">
@@ -17315,7 +17315,7 @@
         </is>
       </c>
       <c r="O299" s="2" t="n">
-        <v>7.79</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="300">
@@ -17358,13 +17358,13 @@
         <v>132</v>
       </c>
       <c r="K300" s="2" t="n">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="L300" s="2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M300" s="2" t="n">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="N300" s="4" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         </is>
       </c>
       <c r="O300" s="2" t="n">
-        <v>7.79</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="301">
@@ -17429,7 +17429,7 @@
         </is>
       </c>
       <c r="O301" s="2" t="n">
-        <v>5.34</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="302">
@@ -17469,16 +17469,16 @@
         </is>
       </c>
       <c r="J302" s="2" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="K302" s="2" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="L302" s="2" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="M302" s="2" t="n">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="N302" s="4" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         </is>
       </c>
       <c r="O302" s="2" t="n">
-        <v>9.9</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="303">
@@ -17543,7 +17543,7 @@
         </is>
       </c>
       <c r="O303" s="2" t="n">
-        <v>9.9</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="304">
@@ -17600,7 +17600,7 @@
         </is>
       </c>
       <c r="O304" s="2" t="n">
-        <v>9.93</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="305">
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="O305" s="2" t="n">
-        <v>15.72</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="306">
@@ -17700,13 +17700,13 @@
         <v>46</v>
       </c>
       <c r="K306" s="2" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="L306" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M306" s="2" t="n">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="N306" s="4" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="O306" s="2" t="n">
-        <v>18.53</v>
+        <v>19.39</v>
       </c>
     </row>
     <row r="307">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="O307" s="2" t="n">
-        <v>19.94</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="308">
@@ -17814,13 +17814,13 @@
         <v>179</v>
       </c>
       <c r="K308" s="2" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="L308" s="2" t="n">
         <v>127</v>
       </c>
       <c r="M308" s="2" t="n">
-        <v>347</v>
+        <v>307</v>
       </c>
       <c r="N308" s="4" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="O308" s="2" t="n">
-        <v>3.23</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="309">
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="O309" s="2" t="n">
-        <v>3.23</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="310">
@@ -17942,7 +17942,7 @@
         </is>
       </c>
       <c r="O310" s="2" t="n">
-        <v>39.83</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="311">
@@ -17999,7 +17999,7 @@
         </is>
       </c>
       <c r="O311" s="2" t="n">
-        <v>22.32</v>
+        <v>23.35</v>
       </c>
     </row>
     <row r="312">
@@ -18039,10 +18039,10 @@
         </is>
       </c>
       <c r="J312" s="2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K312" s="2" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="L312" s="2" t="n">
         <v>41</v>
@@ -18050,13 +18050,13 @@
       <c r="M312" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="N312" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+      <c r="N312" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O312" s="2" t="n">
-        <v>23.59</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="313">
@@ -18113,7 +18113,7 @@
         </is>
       </c>
       <c r="O313" s="2" t="n">
-        <v>8.84</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="314">
@@ -18170,7 +18170,7 @@
         </is>
       </c>
       <c r="O314" s="2" t="n">
-        <v>17.27</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="315">
@@ -18210,7 +18210,7 @@
         </is>
       </c>
       <c r="J315" s="2" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K315" s="2" t="n">
         <v>11</v>
@@ -18219,7 +18219,7 @@
         <v>74</v>
       </c>
       <c r="M315" s="2" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N315" s="4" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         </is>
       </c>
       <c r="O315" s="2" t="n">
-        <v>9.550000000000001</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="316">
@@ -18284,7 +18284,7 @@
         </is>
       </c>
       <c r="O316" s="2" t="n">
-        <v>18.53</v>
+        <v>19.39</v>
       </c>
     </row>
     <row r="317">
@@ -18327,13 +18327,13 @@
         <v>12</v>
       </c>
       <c r="K317" s="2" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="L317" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M317" s="2" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="N317" s="4" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         </is>
       </c>
       <c r="O317" s="2" t="n">
-        <v>29.84</v>
+        <v>31.21</v>
       </c>
     </row>
     <row r="318">
@@ -18398,7 +18398,7 @@
         </is>
       </c>
       <c r="O318" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="319">
@@ -18455,7 +18455,7 @@
         </is>
       </c>
       <c r="O319" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="320">
@@ -18512,7 +18512,7 @@
         </is>
       </c>
       <c r="O320" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="321">
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="O321" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="322">
@@ -18612,13 +18612,13 @@
         <v>14</v>
       </c>
       <c r="K322" s="2" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="L322" s="2" t="n">
         <v>17</v>
       </c>
       <c r="M322" s="2" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="N322" s="4" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         </is>
       </c>
       <c r="O322" s="2" t="n">
-        <v>10.25</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="323">
@@ -18683,7 +18683,7 @@
         </is>
       </c>
       <c r="O323" s="2" t="n">
-        <v>10.25</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="324">
@@ -18740,7 +18740,7 @@
         </is>
       </c>
       <c r="O324" s="2" t="n">
-        <v>20.41</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="325">
@@ -18797,7 +18797,7 @@
         </is>
       </c>
       <c r="O325" s="2" t="n">
-        <v>15.45</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="326">
@@ -18854,7 +18854,7 @@
         </is>
       </c>
       <c r="O326" s="2" t="n">
-        <v>13.79</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="327">
@@ -18911,7 +18911,7 @@
         </is>
       </c>
       <c r="O327" s="2" t="n">
-        <v>12.36</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="328">
@@ -18968,7 +18968,7 @@
         </is>
       </c>
       <c r="O328" s="2" t="n">
-        <v>12.36</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="329">
@@ -19025,7 +19025,7 @@
         </is>
       </c>
       <c r="O329" s="2" t="n">
-        <v>24.15</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="330">
@@ -19082,7 +19082,7 @@
         </is>
       </c>
       <c r="O330" s="2" t="n">
-        <v>7.27</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="331">
@@ -19122,7 +19122,7 @@
         </is>
       </c>
       <c r="J331" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K331" s="2" t="n">
         <v>24</v>
@@ -19131,7 +19131,7 @@
         <v>0</v>
       </c>
       <c r="M331" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N331" s="6" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         </is>
       </c>
       <c r="O331" s="2" t="n">
-        <v>20.38</v>
+        <v>21.32</v>
       </c>
     </row>
     <row r="332">
@@ -19179,7 +19179,7 @@
         </is>
       </c>
       <c r="J332" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K332" s="2" t="n">
         <v>85</v>
@@ -19188,7 +19188,7 @@
         <v>155</v>
       </c>
       <c r="M332" s="2" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N332" s="4" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         </is>
       </c>
       <c r="O332" s="2" t="n">
-        <v>5.69</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="333">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="O333" s="2" t="n">
-        <v>16.22</v>
+        <v>16.96</v>
       </c>
     </row>
     <row r="334">
@@ -19310,7 +19310,7 @@
         </is>
       </c>
       <c r="O334" s="2" t="n">
-        <v>24.64</v>
+        <v>25.78</v>
       </c>
     </row>
     <row r="335">
@@ -19356,10 +19356,10 @@
         <v>3</v>
       </c>
       <c r="L335" s="2" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M335" s="2" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="N335" s="4" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         </is>
       </c>
       <c r="O335" s="2" t="n">
-        <v>12.04</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="336">
@@ -19407,16 +19407,16 @@
         </is>
       </c>
       <c r="J336" s="2" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K336" s="2" t="n">
         <v>9</v>
       </c>
       <c r="L336" s="2" t="n">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="M336" s="2" t="n">
-        <v>103</v>
+        <v>187</v>
       </c>
       <c r="N336" s="4" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         </is>
       </c>
       <c r="O336" s="2" t="n">
-        <v>6.77</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="337">
@@ -19481,7 +19481,7 @@
         </is>
       </c>
       <c r="O337" s="2" t="n">
-        <v>6.77</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="338">
@@ -19538,7 +19538,7 @@
         </is>
       </c>
       <c r="O338" s="2" t="n">
-        <v>7.28</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="339">
@@ -19595,7 +19595,7 @@
         </is>
       </c>
       <c r="O339" s="2" t="n">
-        <v>7.47</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="340">
@@ -19652,7 +19652,7 @@
         </is>
       </c>
       <c r="O340" s="2" t="n">
-        <v>7.47</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="341">
@@ -19709,7 +19709,7 @@
         </is>
       </c>
       <c r="O341" s="2" t="n">
-        <v>6.77</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="342">
@@ -19766,7 +19766,7 @@
         </is>
       </c>
       <c r="O342" s="2" t="n">
-        <v>6.77</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="343">
@@ -19806,16 +19806,16 @@
         </is>
       </c>
       <c r="J343" s="2" t="n">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="K343" s="2" t="n">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="L343" s="2" t="n">
         <v>4</v>
       </c>
       <c r="M343" s="2" t="n">
-        <v>242</v>
+        <v>158</v>
       </c>
       <c r="N343" s="4" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         </is>
       </c>
       <c r="O343" s="2" t="n">
-        <v>4.63</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="344">
@@ -19880,7 +19880,7 @@
         </is>
       </c>
       <c r="O344" s="2" t="n">
-        <v>4.99</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="345">
@@ -19937,7 +19937,7 @@
         </is>
       </c>
       <c r="O345" s="2" t="n">
-        <v>46.68</v>
+        <v>48.84</v>
       </c>
     </row>
     <row r="346">
@@ -19994,7 +19994,7 @@
         </is>
       </c>
       <c r="O346" s="2" t="n">
-        <v>3.23</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="347">
@@ -20051,7 +20051,7 @@
         </is>
       </c>
       <c r="O347" s="2" t="n">
-        <v>6.74</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="348">
@@ -20108,7 +20108,7 @@
         </is>
       </c>
       <c r="O348" s="2" t="n">
-        <v>12.01</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="349">
@@ -20165,7 +20165,7 @@
         </is>
       </c>
       <c r="O349" s="2" t="n">
-        <v>5.34</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="350">
@@ -20222,7 +20222,7 @@
         </is>
       </c>
       <c r="O350" s="2" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="351">
@@ -20279,7 +20279,7 @@
         </is>
       </c>
       <c r="O351" s="2" t="n">
-        <v>12.01</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="352">
@@ -20336,7 +20336,7 @@
         </is>
       </c>
       <c r="O352" s="2" t="n">
-        <v>12.01</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="353">
@@ -20393,7 +20393,7 @@
         </is>
       </c>
       <c r="O353" s="2" t="n">
-        <v>19.62</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="354">
@@ -20450,7 +20450,7 @@
         </is>
       </c>
       <c r="O354" s="2" t="n">
-        <v>20.01</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="355">
@@ -20507,7 +20507,7 @@
         </is>
       </c>
       <c r="O355" s="2" t="n">
-        <v>39.6</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="356">
@@ -20564,7 +20564,7 @@
         </is>
       </c>
       <c r="O356" s="2" t="n">
-        <v>8.85</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="357">
@@ -20621,7 +20621,7 @@
         </is>
       </c>
       <c r="O357" s="2" t="n">
-        <v>12.74</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="358">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="O358" s="2" t="n">
-        <v>12.74</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="359">
@@ -20735,7 +20735,7 @@
         </is>
       </c>
       <c r="O359" s="2" t="n">
-        <v>33.38</v>
+        <v>34.92</v>
       </c>
     </row>
     <row r="360">
@@ -20792,7 +20792,7 @@
         </is>
       </c>
       <c r="O360" s="2" t="n">
-        <v>33.38</v>
+        <v>34.92</v>
       </c>
     </row>
     <row r="361">
@@ -20849,7 +20849,7 @@
         </is>
       </c>
       <c r="O361" s="2" t="n">
-        <v>33.38</v>
+        <v>34.92</v>
       </c>
     </row>
     <row r="362">
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="O362" s="2" t="n">
-        <v>33.38</v>
+        <v>34.92</v>
       </c>
     </row>
     <row r="363">
@@ -20963,7 +20963,7 @@
         </is>
       </c>
       <c r="O363" s="2" t="n">
-        <v>33.38</v>
+        <v>34.92</v>
       </c>
     </row>
     <row r="364">
@@ -21020,7 +21020,7 @@
         </is>
       </c>
       <c r="O364" s="2" t="n">
-        <v>17.13</v>
+        <v>17.92</v>
       </c>
     </row>
     <row r="365">
@@ -21077,7 +21077,7 @@
         </is>
       </c>
       <c r="O365" s="2" t="n">
-        <v>33.08</v>
+        <v>34.61</v>
       </c>
     </row>
     <row r="366">
@@ -21120,13 +21120,13 @@
         <v>3</v>
       </c>
       <c r="K366" s="2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L366" s="2" t="n">
         <v>7</v>
       </c>
       <c r="M366" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N366" s="6" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         </is>
       </c>
       <c r="O366" s="2" t="n">
-        <v>13.76</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="367">
@@ -21177,13 +21177,13 @@
         <v>100</v>
       </c>
       <c r="K367" s="2" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L367" s="2" t="n">
         <v>76</v>
       </c>
       <c r="M367" s="2" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="N367" s="4" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="O367" s="2" t="n">
-        <v>9.550000000000001</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="368">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="O368" s="2" t="n">
-        <v>4.41</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="369">
@@ -21291,13 +21291,13 @@
         <v>38</v>
       </c>
       <c r="K369" s="2" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L369" s="2" t="n">
         <v>47</v>
       </c>
       <c r="M369" s="2" t="n">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="N369" s="4" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         </is>
       </c>
       <c r="O369" s="2" t="n">
-        <v>12.92</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="370">
@@ -21362,7 +21362,7 @@
         </is>
       </c>
       <c r="O370" s="2" t="n">
-        <v>5.36</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="371">
@@ -21419,7 +21419,7 @@
         </is>
       </c>
       <c r="O371" s="2" t="n">
-        <v>26.98</v>
+        <v>28.22</v>
       </c>
     </row>
     <row r="372">
@@ -21476,7 +21476,7 @@
         </is>
       </c>
       <c r="O372" s="2" t="n">
-        <v>17.12</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="373">
@@ -21533,7 +21533,7 @@
         </is>
       </c>
       <c r="O373" s="2" t="n">
-        <v>17.12</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="374">
@@ -21590,7 +21590,7 @@
         </is>
       </c>
       <c r="O374" s="2" t="n">
-        <v>22.76</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="375">
@@ -21647,7 +21647,7 @@
         </is>
       </c>
       <c r="O375" s="2" t="n">
-        <v>13.06</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="376">
@@ -21704,7 +21704,7 @@
         </is>
       </c>
       <c r="O376" s="2" t="n">
-        <v>12.36</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="377">
@@ -21761,7 +21761,7 @@
         </is>
       </c>
       <c r="O377" s="2" t="n">
-        <v>4.58</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="378">
@@ -21818,7 +21818,7 @@
         </is>
       </c>
       <c r="O378" s="2" t="n">
-        <v>6.04</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="379">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="J379" s="2" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K379" s="2" t="n">
         <v>139</v>
@@ -21867,7 +21867,7 @@
         <v>25</v>
       </c>
       <c r="M379" s="2" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N379" s="4" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         </is>
       </c>
       <c r="O379" s="2" t="n">
-        <v>7.44</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="380">
@@ -21918,13 +21918,13 @@
         <v>58</v>
       </c>
       <c r="K380" s="2" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="L380" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M380" s="2" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="N380" s="4" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         </is>
       </c>
       <c r="O380" s="2" t="n">
-        <v>13.76</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="381">
@@ -21972,10 +21972,10 @@
         </is>
       </c>
       <c r="J381" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K381" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L381" s="2" t="n">
         <v>0</v>
@@ -21989,7 +21989,7 @@
         </is>
       </c>
       <c r="O381" s="2" t="n">
-        <v>14.32</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="382">
@@ -22035,10 +22035,10 @@
         <v>57</v>
       </c>
       <c r="L382" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M382" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N382" s="6" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         </is>
       </c>
       <c r="O382" s="2" t="n">
-        <v>6.79</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="383">
@@ -22103,7 +22103,7 @@
         </is>
       </c>
       <c r="O383" s="2" t="n">
-        <v>8.85</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="384">
@@ -22160,7 +22160,7 @@
         </is>
       </c>
       <c r="O384" s="2" t="n">
-        <v>16.24</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="385">
@@ -22217,7 +22217,7 @@
         </is>
       </c>
       <c r="O385" s="2" t="n">
-        <v>13.06</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="386">
@@ -22274,7 +22274,7 @@
         </is>
       </c>
       <c r="O386" s="2" t="n">
-        <v>4.63</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="387">
@@ -22331,7 +22331,7 @@
         </is>
       </c>
       <c r="O387" s="2" t="n">
-        <v>32.77</v>
+        <v>34.28</v>
       </c>
     </row>
     <row r="388">
@@ -22388,7 +22388,7 @@
         </is>
       </c>
       <c r="O388" s="2" t="n">
-        <v>4.28</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="389">
@@ -22445,7 +22445,7 @@
         </is>
       </c>
       <c r="O389" s="2" t="n">
-        <v>15.17</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="390">
@@ -22502,7 +22502,7 @@
         </is>
       </c>
       <c r="O390" s="2" t="n">
-        <v>17.99</v>
+        <v>18.82</v>
       </c>
     </row>
     <row r="391">
@@ -22559,7 +22559,7 @@
         </is>
       </c>
       <c r="O391" s="2" t="n">
-        <v>26.96</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="392">
@@ -22616,7 +22616,7 @@
         </is>
       </c>
       <c r="O392" s="2" t="n">
-        <v>8.16</v>
+        <v>8.539999999999999</v>
       </c>
     </row>
     <row r="393">
@@ -22659,13 +22659,13 @@
         <v>118</v>
       </c>
       <c r="K393" s="2" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="L393" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M393" s="2" t="n">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="N393" s="4" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         </is>
       </c>
       <c r="O393" s="2" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="394">
@@ -22730,7 +22730,7 @@
         </is>
       </c>
       <c r="O394" s="2" t="n">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="395">
@@ -22787,7 +22787,7 @@
         </is>
       </c>
       <c r="O395" s="2" t="n">
-        <v>5.92</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="396">
@@ -22842,7 +22842,7 @@
         </is>
       </c>
       <c r="O396" s="2" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="397">
@@ -22897,7 +22897,7 @@
         </is>
       </c>
       <c r="O397" s="2" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="398">
@@ -22952,7 +22952,7 @@
         </is>
       </c>
       <c r="O398" s="2" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="399">
@@ -23007,7 +23007,7 @@
         </is>
       </c>
       <c r="O399" s="2" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="400">
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="O400" s="2" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="401">
@@ -23121,7 +23121,7 @@
         </is>
       </c>
       <c r="O401" s="2" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="402">
@@ -23178,7 +23178,7 @@
         </is>
       </c>
       <c r="O402" s="2" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="403">
@@ -23235,7 +23235,7 @@
         </is>
       </c>
       <c r="O403" s="2" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="404">
@@ -23292,7 +23292,7 @@
         </is>
       </c>
       <c r="O404" s="2" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="405">
@@ -23335,13 +23335,13 @@
         <v>139</v>
       </c>
       <c r="K405" s="2" t="n">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="L405" s="2" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M405" s="2" t="n">
-        <v>208</v>
+        <v>901</v>
       </c>
       <c r="N405" s="4" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         </is>
       </c>
       <c r="O405" s="2" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="406">
@@ -23406,7 +23406,7 @@
         </is>
       </c>
       <c r="O406" s="2" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="407">
@@ -23452,10 +23452,10 @@
         <v>94</v>
       </c>
       <c r="L407" s="2" t="n">
-        <v>1274</v>
+        <v>1260</v>
       </c>
       <c r="M407" s="2" t="n">
-        <v>1441</v>
+        <v>1427</v>
       </c>
       <c r="N407" s="4" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         </is>
       </c>
       <c r="O407" s="2" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="408">
@@ -23520,7 +23520,7 @@
         </is>
       </c>
       <c r="O408" s="2" t="n">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="409">
@@ -23577,7 +23577,7 @@
         </is>
       </c>
       <c r="O409" s="2" t="n">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="410">
@@ -23634,7 +23634,7 @@
         </is>
       </c>
       <c r="O410" s="2" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="411">
@@ -23691,7 +23691,7 @@
         </is>
       </c>
       <c r="O411" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="412">
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="O412" s="2" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="413">
@@ -23805,7 +23805,7 @@
         </is>
       </c>
       <c r="O413" s="2" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="414">
@@ -23851,10 +23851,10 @@
         <v>0</v>
       </c>
       <c r="L414" s="2" t="n">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="M414" s="2" t="n">
-        <v>428</v>
+        <v>396</v>
       </c>
       <c r="N414" s="4" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         </is>
       </c>
       <c r="O414" s="2" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="415">
@@ -23919,7 +23919,7 @@
         </is>
       </c>
       <c r="O415" s="2" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="416">
@@ -23976,7 +23976,7 @@
         </is>
       </c>
       <c r="O416" s="2" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="417">
@@ -24033,7 +24033,7 @@
         </is>
       </c>
       <c r="O417" s="2" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="418">
@@ -24090,7 +24090,7 @@
         </is>
       </c>
       <c r="O418" s="2" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="419">
@@ -24130,7 +24130,7 @@
         </is>
       </c>
       <c r="J419" s="2" t="n">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="K419" s="2" t="n">
         <v>0</v>
@@ -24139,7 +24139,7 @@
         <v>83</v>
       </c>
       <c r="M419" s="2" t="n">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="N419" s="4" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         </is>
       </c>
       <c r="O419" s="2" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="420">
@@ -24204,7 +24204,7 @@
         </is>
       </c>
       <c r="O420" s="2" t="n">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="421">
@@ -24247,13 +24247,13 @@
         <v>85</v>
       </c>
       <c r="K421" s="2" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="L421" s="2" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M421" s="2" t="n">
-        <v>175</v>
+        <v>359</v>
       </c>
       <c r="N421" s="4" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         </is>
       </c>
       <c r="O421" s="2" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="422">
@@ -24318,7 +24318,7 @@
         </is>
       </c>
       <c r="O422" s="2" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="423">
@@ -24375,7 +24375,7 @@
         </is>
       </c>
       <c r="O423" s="2" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="424">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="O424" s="2" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="425">
@@ -24489,7 +24489,7 @@
         </is>
       </c>
       <c r="O425" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="426">
@@ -24532,10 +24532,10 @@
         <v>144</v>
       </c>
       <c r="K426" s="2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L426" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M426" s="2" t="n">
         <v>186</v>
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="O426" s="2" t="n">
-        <v>4.37</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="427">
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="O427" s="2" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="428">
@@ -24660,7 +24660,7 @@
         </is>
       </c>
       <c r="O428" s="2" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="429">
@@ -24717,7 +24717,7 @@
         </is>
       </c>
       <c r="O429" s="2" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="430">
@@ -24760,13 +24760,13 @@
         <v>137</v>
       </c>
       <c r="K430" s="2" t="n">
-        <v>535</v>
+        <v>510</v>
       </c>
       <c r="L430" s="2" t="n">
         <v>82</v>
       </c>
       <c r="M430" s="2" t="n">
-        <v>754</v>
+        <v>729</v>
       </c>
       <c r="N430" s="4" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         </is>
       </c>
       <c r="O430" s="2" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="431">
@@ -24831,18 +24831,18 @@
         </is>
       </c>
       <c r="O431" s="2" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>NOR0032201</t>
+          <t>NOR0032202</t>
         </is>
       </c>
       <c r="B432" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 20 X 1,3</t>
+          <t>TUBO CUADRADO 25 X 1.3</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
@@ -24851,19 +24851,19 @@
         </is>
       </c>
       <c r="D432" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E432" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F432" s="2" t="n">
         <v>1.3</v>
       </c>
       <c r="G432" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H432" s="2" t="n">
-        <v>0.2624</v>
+        <v>0.332</v>
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
@@ -24874,13 +24874,13 @@
         <v>0</v>
       </c>
       <c r="K432" s="2" t="n">
-        <v>350</v>
+        <v>55</v>
       </c>
       <c r="L432" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M432" s="2" t="n">
-        <v>350</v>
+        <v>101</v>
       </c>
       <c r="N432" s="6" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         </is>
       </c>
       <c r="O432" s="2" t="n">
-        <v>1.71</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="433">
@@ -24917,7 +24917,7 @@
         <v>1.3</v>
       </c>
       <c r="G433" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H433" s="2" t="n">
         <v>0.332</v>
@@ -24931,13 +24931,13 @@
         <v>0</v>
       </c>
       <c r="K433" s="2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L433" s="2" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="M433" s="2" t="n">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="N433" s="6" t="inlineStr">
         <is>
@@ -24945,18 +24945,18 @@
         </is>
       </c>
       <c r="O433" s="2" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>NOR0032202</t>
+          <t>NOR0032203</t>
         </is>
       </c>
       <c r="B434" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 25 X 1.3</t>
+          <t>TUBO CUADRADO 30 X 1.3</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
@@ -24965,10 +24965,10 @@
         </is>
       </c>
       <c r="D434" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E434" s="2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F434" s="2" t="n">
         <v>1.3</v>
@@ -24977,7 +24977,7 @@
         <v>6.4</v>
       </c>
       <c r="H434" s="2" t="n">
-        <v>0.332</v>
+        <v>0.402</v>
       </c>
       <c r="I434" s="2" t="inlineStr">
         <is>
@@ -24985,16 +24985,16 @@
         </is>
       </c>
       <c r="J434" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K434" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L434" s="2" t="n">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="M434" s="2" t="n">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="N434" s="6" t="inlineStr">
         <is>
@@ -25002,18 +25002,18 @@
         </is>
       </c>
       <c r="O434" s="2" t="n">
-        <v>2.16</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>NOR0032203</t>
+          <t>NOR0032204</t>
         </is>
       </c>
       <c r="B435" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 30 X 1.3</t>
+          <t>TUBO CUADRADO 40 X 1.3</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
@@ -25022,10 +25022,10 @@
         </is>
       </c>
       <c r="D435" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E435" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F435" s="2" t="n">
         <v>1.3</v>
@@ -25034,7 +25034,7 @@
         <v>6.4</v>
       </c>
       <c r="H435" s="2" t="n">
-        <v>0.402</v>
+        <v>0.543</v>
       </c>
       <c r="I435" s="2" t="inlineStr">
         <is>
@@ -25042,16 +25042,16 @@
         </is>
       </c>
       <c r="J435" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K435" s="2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="L435" s="2" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="M435" s="2" t="n">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="N435" s="6" t="inlineStr">
         <is>
@@ -25059,18 +25059,18 @@
         </is>
       </c>
       <c r="O435" s="2" t="n">
-        <v>2.61</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>NOR0032204</t>
+          <t>NOR0032205</t>
         </is>
       </c>
       <c r="B436" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 40 X 1.3</t>
+          <t>TUBO CUADRADO 45 X 1.5</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
@@ -25079,19 +25079,19 @@
         </is>
       </c>
       <c r="D436" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E436" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F436" s="2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G436" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H436" s="2" t="n">
-        <v>0.543</v>
+        <v>0.705</v>
       </c>
       <c r="I436" s="2" t="inlineStr">
         <is>
@@ -25102,21 +25102,21 @@
         <v>0</v>
       </c>
       <c r="K436" s="2" t="n">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="L436" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M436" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="N436" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>5</v>
+      </c>
+      <c r="N436" s="5" t="inlineStr">
+        <is>
+          <t>Sin stock</t>
         </is>
       </c>
       <c r="O436" s="2" t="n">
-        <v>3.53</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="437">
@@ -25145,7 +25145,7 @@
         <v>1.5</v>
       </c>
       <c r="G437" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H437" s="2" t="n">
         <v>0.705</v>
@@ -25159,32 +25159,32 @@
         <v>0</v>
       </c>
       <c r="K437" s="2" t="n">
-        <v>2</v>
+        <v>139</v>
       </c>
       <c r="L437" s="2" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="M437" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N437" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>198</v>
+      </c>
+      <c r="N437" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O437" s="2" t="n">
-        <v>4.58</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>NOR0032205</t>
+          <t>NOR0032206</t>
         </is>
       </c>
       <c r="B438" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 45 X 1.5</t>
+          <t>TUBO CUADRADO 50 X 1,3</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
@@ -25193,19 +25193,19 @@
         </is>
       </c>
       <c r="D438" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E438" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F438" s="2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G438" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H438" s="2" t="n">
-        <v>0.705</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
@@ -25216,13 +25216,13 @@
         <v>0</v>
       </c>
       <c r="K438" s="2" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="L438" s="2" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="M438" s="2" t="n">
-        <v>219</v>
+        <v>36</v>
       </c>
       <c r="N438" s="6" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         </is>
       </c>
       <c r="O438" s="2" t="n">
-        <v>4.58</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="439">
@@ -25259,7 +25259,7 @@
         <v>1.3</v>
       </c>
       <c r="G439" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H439" s="2" t="n">
         <v>0.6830000000000001</v>
@@ -25270,35 +25270,35 @@
         </is>
       </c>
       <c r="J439" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K439" s="2" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L439" s="2" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="M439" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="N439" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>147</v>
+      </c>
+      <c r="N439" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O439" s="2" t="n">
-        <v>4.44</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>NOR0032206</t>
+          <t>NOR0032207</t>
         </is>
       </c>
       <c r="B440" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 50 X 1,3</t>
+          <t>TUBO CUADRADO 60 X 1,3</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
@@ -25307,10 +25307,10 @@
         </is>
       </c>
       <c r="D440" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E440" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F440" s="2" t="n">
         <v>1.3</v>
@@ -25319,7 +25319,7 @@
         <v>6.4</v>
       </c>
       <c r="H440" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.8235</v>
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
@@ -25327,35 +25327,35 @@
         </is>
       </c>
       <c r="J440" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K440" s="2" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="L440" s="2" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="M440" s="2" t="n">
-        <v>147</v>
-      </c>
-      <c r="N440" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>181</v>
+      </c>
+      <c r="N440" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O440" s="2" t="n">
-        <v>4.44</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>NOR0032207</t>
+          <t>NOR0032208</t>
         </is>
       </c>
       <c r="B441" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 60 X 1,3</t>
+          <t>TUBO CUADRADO 70 X 1,3</t>
         </is>
       </c>
       <c r="C441" s="2" t="inlineStr">
@@ -25364,10 +25364,10 @@
         </is>
       </c>
       <c r="D441" s="2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E441" s="2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F441" s="2" t="n">
         <v>1.3</v>
@@ -25376,7 +25376,7 @@
         <v>6.4</v>
       </c>
       <c r="H441" s="2" t="n">
-        <v>0.8235</v>
+        <v>0.96454</v>
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
@@ -25384,16 +25384,16 @@
         </is>
       </c>
       <c r="J441" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K441" s="2" t="n">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="L441" s="2" t="n">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="M441" s="2" t="n">
-        <v>181</v>
+        <v>72</v>
       </c>
       <c r="N441" s="6" t="inlineStr">
         <is>
@@ -25401,18 +25401,18 @@
         </is>
       </c>
       <c r="O441" s="2" t="n">
-        <v>5.35</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>NOR0032208</t>
+          <t>NOR0032209</t>
         </is>
       </c>
       <c r="B442" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 70 X 1,3</t>
+          <t>TUBO CUADRADO 80 X 1,5</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
@@ -25421,19 +25421,19 @@
         </is>
       </c>
       <c r="D442" s="2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E442" s="2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F442" s="2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G442" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H442" s="2" t="n">
-        <v>0.96454</v>
+        <v>1.2717</v>
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
@@ -25441,35 +25441,35 @@
         </is>
       </c>
       <c r="J442" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K442" s="2" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="L442" s="2" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="M442" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="N442" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>75</v>
+      </c>
+      <c r="N442" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O442" s="2" t="n">
-        <v>6.27</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>NOR0032209</t>
+          <t>NOR0032210</t>
         </is>
       </c>
       <c r="B443" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 80 X 1,5</t>
+          <t>TUBO CUADRADO 100 X 1,9</t>
         </is>
       </c>
       <c r="C443" s="2" t="inlineStr">
@@ -25478,19 +25478,19 @@
         </is>
       </c>
       <c r="D443" s="2" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E443" s="2" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F443" s="2" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="G443" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H443" s="2" t="n">
-        <v>1.2717</v>
+        <v>2.0142</v>
       </c>
       <c r="I443" s="2" t="inlineStr">
         <is>
@@ -25498,16 +25498,16 @@
         </is>
       </c>
       <c r="J443" s="2" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="K443" s="2" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="L443" s="2" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="M443" s="2" t="n">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="N443" s="4" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         </is>
       </c>
       <c r="O443" s="2" t="n">
-        <v>8.27</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="444">
@@ -25544,7 +25544,7 @@
         <v>1.9</v>
       </c>
       <c r="G444" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H444" s="2" t="n">
         <v>2.0142</v>
@@ -25555,35 +25555,35 @@
         </is>
       </c>
       <c r="J444" s="2" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K444" s="2" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="L444" s="2" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="M444" s="2" t="n">
-        <v>117</v>
-      </c>
-      <c r="N444" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>42</v>
+      </c>
+      <c r="N444" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O444" s="2" t="n">
-        <v>13.09</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>NOR0032210</t>
+          <t>NOR0032211</t>
         </is>
       </c>
       <c r="B445" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 100 X 1,9</t>
+          <t>TUBO CUADRADO 35 X 1.3</t>
         </is>
       </c>
       <c r="C445" s="2" t="inlineStr">
@@ -25592,19 +25592,19 @@
         </is>
       </c>
       <c r="D445" s="2" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E445" s="2" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="F445" s="2" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="G445" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H445" s="2" t="n">
-        <v>2.0142</v>
+        <v>0.475</v>
       </c>
       <c r="I445" s="2" t="inlineStr">
         <is>
@@ -25612,16 +25612,16 @@
         </is>
       </c>
       <c r="J445" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K445" s="2" t="n">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="L445" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M445" s="2" t="n">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="N445" s="6" t="inlineStr">
         <is>
@@ -25629,18 +25629,18 @@
         </is>
       </c>
       <c r="O445" s="2" t="n">
-        <v>13.09</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>NOR0032211</t>
+          <t>NOR0032212</t>
         </is>
       </c>
       <c r="B446" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 35 X 1.3</t>
+          <t>TUBO CUADRADO 120 X 2</t>
         </is>
       </c>
       <c r="C446" s="2" t="inlineStr">
@@ -25649,19 +25649,19 @@
         </is>
       </c>
       <c r="D446" s="2" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="E446" s="2" t="n">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="F446" s="2" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="G446" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H446" s="2" t="n">
-        <v>0.475</v>
+        <v>2.549</v>
       </c>
       <c r="I446" s="2" t="inlineStr">
         <is>
@@ -25669,35 +25669,35 @@
         </is>
       </c>
       <c r="J446" s="2" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="K446" s="2" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="L446" s="2" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M446" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="N446" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>130</v>
+      </c>
+      <c r="N446" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O446" s="2" t="n">
-        <v>3.09</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>NOR0032212</t>
+          <t>NOR0032213</t>
         </is>
       </c>
       <c r="B447" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 120 X 2</t>
+          <t>TUBO CUADRADO 40 X 1.5</t>
         </is>
       </c>
       <c r="C447" s="2" t="inlineStr">
@@ -25706,19 +25706,19 @@
         </is>
       </c>
       <c r="D447" s="2" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="E447" s="2" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="F447" s="2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G447" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H447" s="2" t="n">
-        <v>2.549</v>
+        <v>0.624</v>
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
@@ -25726,56 +25726,56 @@
         </is>
       </c>
       <c r="J447" s="2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K447" s="2" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="L447" s="2" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="M447" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="N447" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>42</v>
+      </c>
+      <c r="N447" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O447" s="2" t="n">
-        <v>16.57</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>NOR0032213</t>
+          <t>NOR0032300</t>
         </is>
       </c>
       <c r="B448" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 40 X 1.5</t>
+          <t>RECTANGULAR 20 X 10 X 1.3</t>
         </is>
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO</t>
+          <t>TUBO RECTANGULAR</t>
         </is>
       </c>
       <c r="D448" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E448" s="2" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F448" s="2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G448" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H448" s="2" t="n">
-        <v>0.624</v>
+        <v>0.16594</v>
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
@@ -25783,35 +25783,35 @@
         </is>
       </c>
       <c r="J448" s="2" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="K448" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L448" s="2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M448" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="N448" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>81</v>
+      </c>
+      <c r="N448" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O448" s="2" t="n">
-        <v>4.06</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>NOR0032300</t>
+          <t>NOR0032301</t>
         </is>
       </c>
       <c r="B449" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 20 X 10 X 1.3</t>
+          <t>RECTANGULAR 30 X 15 X 1.3</t>
         </is>
       </c>
       <c r="C449" s="2" t="inlineStr">
@@ -25820,10 +25820,10 @@
         </is>
       </c>
       <c r="D449" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E449" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F449" s="2" t="n">
         <v>1.3</v>
@@ -25832,7 +25832,7 @@
         <v>6.4</v>
       </c>
       <c r="H449" s="2" t="n">
-        <v>0.16594</v>
+        <v>0.298</v>
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         </is>
       </c>
       <c r="J449" s="2" t="n">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="K449" s="2" t="n">
         <v>0</v>
@@ -25849,26 +25849,26 @@
         <v>0</v>
       </c>
       <c r="M449" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="N449" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>7</v>
+      </c>
+      <c r="N449" s="5" t="inlineStr">
+        <is>
+          <t>Sin stock</t>
         </is>
       </c>
       <c r="O449" s="2" t="n">
-        <v>1.08</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>NOR0032301</t>
+          <t>NOR0032302</t>
         </is>
       </c>
       <c r="B450" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 30 X 15 X 1.3</t>
+          <t>RECTANGULAR 30 x 20 X 1,2</t>
         </is>
       </c>
       <c r="C450" s="2" t="inlineStr">
@@ -25880,16 +25880,16 @@
         <v>30</v>
       </c>
       <c r="E450" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F450" s="2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G450" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H450" s="2" t="n">
-        <v>0.298</v>
+        <v>0.3078</v>
       </c>
       <c r="I450" s="2" t="inlineStr">
         <is>
@@ -25897,35 +25897,35 @@
         </is>
       </c>
       <c r="J450" s="2" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="K450" s="2" t="n">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="L450" s="2" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="M450" s="2" t="n">
-        <v>340</v>
-      </c>
-      <c r="N450" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>161</v>
+      </c>
+      <c r="N450" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O450" s="2" t="n">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>NOR0032302</t>
+          <t>NOR0032303</t>
         </is>
       </c>
       <c r="B451" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 30 x 20 X 1,2</t>
+          <t>RECTANGULAR 40 X 20 X 1,3</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -25934,19 +25934,19 @@
         </is>
       </c>
       <c r="D451" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E451" s="2" t="n">
         <v>20</v>
       </c>
       <c r="F451" s="2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G451" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H451" s="2" t="n">
-        <v>0.3078</v>
+        <v>0.402</v>
       </c>
       <c r="I451" s="2" t="inlineStr">
         <is>
@@ -25954,35 +25954,35 @@
         </is>
       </c>
       <c r="J451" s="2" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="K451" s="2" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L451" s="2" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="M451" s="2" t="n">
-        <v>161</v>
-      </c>
-      <c r="N451" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>302</v>
+      </c>
+      <c r="N451" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O451" s="2" t="n">
-        <v>2</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>NOR0032303</t>
+          <t>NOR0032304</t>
         </is>
       </c>
       <c r="B452" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 40 X 20 X 1,3</t>
+          <t>RECTANGULAR 50 X 20 X 1.3</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -25991,7 +25991,7 @@
         </is>
       </c>
       <c r="D452" s="2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E452" s="2" t="n">
         <v>20</v>
@@ -26003,7 +26003,7 @@
         <v>6.4</v>
       </c>
       <c r="H452" s="2" t="n">
-        <v>0.402</v>
+        <v>0.474</v>
       </c>
       <c r="I452" s="2" t="inlineStr">
         <is>
@@ -26011,35 +26011,35 @@
         </is>
       </c>
       <c r="J452" s="2" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="K452" s="2" t="n">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="L452" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M452" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="N452" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>131</v>
+      </c>
+      <c r="N452" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O452" s="2" t="n">
-        <v>2.61</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>NOR0032304</t>
+          <t>NOR0032305</t>
         </is>
       </c>
       <c r="B453" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 50 X 20 X 1.3</t>
+          <t>RECTANGULAR 60 X 20 X 1,3</t>
         </is>
       </c>
       <c r="C453" s="2" t="inlineStr">
@@ -26048,7 +26048,7 @@
         </is>
       </c>
       <c r="D453" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E453" s="2" t="n">
         <v>20</v>
@@ -26060,7 +26060,7 @@
         <v>6.4</v>
       </c>
       <c r="H453" s="2" t="n">
-        <v>0.474</v>
+        <v>0.5427</v>
       </c>
       <c r="I453" s="2" t="inlineStr">
         <is>
@@ -26068,16 +26068,16 @@
         </is>
       </c>
       <c r="J453" s="2" t="n">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="K453" s="2" t="n">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="L453" s="2" t="n">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="M453" s="2" t="n">
-        <v>131</v>
+        <v>301</v>
       </c>
       <c r="N453" s="4" t="inlineStr">
         <is>
@@ -26085,18 +26085,18 @@
         </is>
       </c>
       <c r="O453" s="2" t="n">
-        <v>3.08</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>NOR0032305</t>
+          <t>NOR0032306</t>
         </is>
       </c>
       <c r="B454" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 60 X 20 X 1,3</t>
+          <t>RECTANGULAR 70 X 20 X 1.3</t>
         </is>
       </c>
       <c r="C454" s="2" t="inlineStr">
@@ -26105,7 +26105,7 @@
         </is>
       </c>
       <c r="D454" s="2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E454" s="2" t="n">
         <v>20</v>
@@ -26117,7 +26117,7 @@
         <v>6.4</v>
       </c>
       <c r="H454" s="2" t="n">
-        <v>0.5427</v>
+        <v>0.6129</v>
       </c>
       <c r="I454" s="2" t="inlineStr">
         <is>
@@ -26125,16 +26125,16 @@
         </is>
       </c>
       <c r="J454" s="2" t="n">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="K454" s="2" t="n">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="L454" s="2" t="n">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="M454" s="2" t="n">
-        <v>303</v>
+        <v>144</v>
       </c>
       <c r="N454" s="4" t="inlineStr">
         <is>
@@ -26142,18 +26142,18 @@
         </is>
       </c>
       <c r="O454" s="2" t="n">
-        <v>3.53</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>NOR0032306</t>
+          <t>NOR0032307</t>
         </is>
       </c>
       <c r="B455" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 70 X 20 X 1.3</t>
+          <t>RECTANGULAR 80 X 20 X 1.3</t>
         </is>
       </c>
       <c r="C455" s="2" t="inlineStr">
@@ -26162,7 +26162,7 @@
         </is>
       </c>
       <c r="D455" s="2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E455" s="2" t="n">
         <v>20</v>
@@ -26174,7 +26174,7 @@
         <v>6.4</v>
       </c>
       <c r="H455" s="2" t="n">
-        <v>0.6129</v>
+        <v>0.6831</v>
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
@@ -26182,35 +26182,35 @@
         </is>
       </c>
       <c r="J455" s="2" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="K455" s="2" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="L455" s="2" t="n">
-        <v>9</v>
+        <v>124</v>
       </c>
       <c r="M455" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="N455" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>186</v>
+      </c>
+      <c r="N455" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O455" s="2" t="n">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>NOR0032307</t>
+          <t>NOR0032308</t>
         </is>
       </c>
       <c r="B456" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 80 X 20 X 1.3</t>
+          <t>RECTANGULAR 100 X 40 X 1.5</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
@@ -26219,19 +26219,19 @@
         </is>
       </c>
       <c r="D456" s="2" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E456" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F456" s="2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G456" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H456" s="2" t="n">
-        <v>0.6831</v>
+        <v>1.1097</v>
       </c>
       <c r="I456" s="2" t="inlineStr">
         <is>
@@ -26239,16 +26239,16 @@
         </is>
       </c>
       <c r="J456" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K456" s="2" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="L456" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M456" s="2" t="n">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="N456" s="6" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         </is>
       </c>
       <c r="O456" s="2" t="n">
-        <v>4.44</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="457">
@@ -26285,7 +26285,7 @@
         <v>1.5</v>
       </c>
       <c r="G457" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H457" s="2" t="n">
         <v>1.1097</v>
@@ -26296,16 +26296,16 @@
         </is>
       </c>
       <c r="J457" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K457" s="2" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="L457" s="2" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="M457" s="2" t="n">
-        <v>13</v>
+        <v>167</v>
       </c>
       <c r="N457" s="6" t="inlineStr">
         <is>
@@ -26313,18 +26313,18 @@
         </is>
       </c>
       <c r="O457" s="2" t="n">
-        <v>7.21</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>NOR0032308</t>
+          <t>NOR0032309</t>
         </is>
       </c>
       <c r="B458" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 100 X 40 X 1.5</t>
+          <t>RECTANGULAR 100 X 45 X 1.7</t>
         </is>
       </c>
       <c r="C458" s="2" t="inlineStr">
@@ -26336,16 +26336,16 @@
         <v>100</v>
       </c>
       <c r="E458" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F458" s="2" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="G458" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H458" s="2" t="n">
-        <v>1.1097</v>
+        <v>1.528</v>
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
@@ -26353,35 +26353,35 @@
         </is>
       </c>
       <c r="J458" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K458" s="2" t="n">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="L458" s="2" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M458" s="2" t="n">
-        <v>170</v>
-      </c>
-      <c r="N458" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>1</v>
+      </c>
+      <c r="N458" s="5" t="inlineStr">
+        <is>
+          <t>Sin stock</t>
         </is>
       </c>
       <c r="O458" s="2" t="n">
-        <v>7.21</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>NOR0032309</t>
+          <t>NOR0032310</t>
         </is>
       </c>
       <c r="B459" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 100 X 45 X 1.7</t>
+          <t>RECTANGULAR 120 X 40 X 1.9</t>
         </is>
       </c>
       <c r="C459" s="2" t="inlineStr">
@@ -26390,19 +26390,19 @@
         </is>
       </c>
       <c r="D459" s="2" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E459" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F459" s="2" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="G459" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H459" s="2" t="n">
-        <v>1.528</v>
+        <v>1.604</v>
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
@@ -26413,32 +26413,32 @@
         <v>0</v>
       </c>
       <c r="K459" s="2" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="L459" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M459" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N459" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>65</v>
+      </c>
+      <c r="N459" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O459" s="2" t="n">
-        <v>9.93</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>NOR0032310</t>
+          <t>NOR0032311</t>
         </is>
       </c>
       <c r="B460" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 120 X 40 X 1.9</t>
+          <t>RECTANGULAR 60 X 40 X 1.3</t>
         </is>
       </c>
       <c r="C460" s="2" t="inlineStr">
@@ -26447,19 +26447,19 @@
         </is>
       </c>
       <c r="D460" s="2" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E460" s="2" t="n">
         <v>40</v>
       </c>
       <c r="F460" s="2" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="G460" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H460" s="2" t="n">
-        <v>1.604</v>
+        <v>0.6831</v>
       </c>
       <c r="I460" s="2" t="inlineStr">
         <is>
@@ -26467,35 +26467,35 @@
         </is>
       </c>
       <c r="J460" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K460" s="2" t="n">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="L460" s="2" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="M460" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="N460" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>251</v>
+      </c>
+      <c r="N460" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O460" s="2" t="n">
-        <v>10.43</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>NOR0032311</t>
+          <t>NOR0032312</t>
         </is>
       </c>
       <c r="B461" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 60 X 40 X 1.3</t>
+          <t>RECTANGULAR 80 X 40 X 1.5</t>
         </is>
       </c>
       <c r="C461" s="2" t="inlineStr">
@@ -26504,19 +26504,19 @@
         </is>
       </c>
       <c r="D461" s="2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E461" s="2" t="n">
         <v>40</v>
       </c>
       <c r="F461" s="2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G461" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H461" s="2" t="n">
-        <v>0.6831</v>
+        <v>0.948</v>
       </c>
       <c r="I461" s="2" t="inlineStr">
         <is>
@@ -26524,35 +26524,35 @@
         </is>
       </c>
       <c r="J461" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K461" s="2" t="n">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="L461" s="2" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M461" s="2" t="n">
-        <v>251</v>
-      </c>
-      <c r="N461" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>124</v>
+      </c>
+      <c r="N461" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O461" s="2" t="n">
-        <v>4.44</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>NOR0032312</t>
+          <t>NOR0032313</t>
         </is>
       </c>
       <c r="B462" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 80 X 40 X 1.5</t>
+          <t>RECTANGULAR 50 X 25 X 1.5</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -26561,19 +26561,19 @@
         </is>
       </c>
       <c r="D462" s="2" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E462" s="2" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F462" s="2" t="n">
         <v>1.5</v>
       </c>
       <c r="G462" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H462" s="2" t="n">
-        <v>0.948</v>
+        <v>0.583</v>
       </c>
       <c r="I462" s="2" t="inlineStr">
         <is>
@@ -26584,13 +26584,13 @@
         <v>0</v>
       </c>
       <c r="K462" s="2" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="L462" s="2" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M462" s="2" t="n">
-        <v>129</v>
+        <v>39</v>
       </c>
       <c r="N462" s="6" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         </is>
       </c>
       <c r="O462" s="2" t="n">
-        <v>6.16</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="463">
@@ -26627,7 +26627,7 @@
         <v>1.5</v>
       </c>
       <c r="G463" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H463" s="2" t="n">
         <v>0.583</v>
@@ -26638,35 +26638,35 @@
         </is>
       </c>
       <c r="J463" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K463" s="2" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="L463" s="2" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="M463" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="N463" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>224</v>
+      </c>
+      <c r="N463" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O463" s="2" t="n">
-        <v>3.79</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>NOR0032313</t>
+          <t>NOR0032314</t>
         </is>
       </c>
       <c r="B464" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 50 X 25 X 1.5</t>
+          <t>RECTANGULAR 60 X 10 X 1.3</t>
         </is>
       </c>
       <c r="C464" s="2" t="inlineStr">
@@ -26675,19 +26675,19 @@
         </is>
       </c>
       <c r="D464" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E464" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F464" s="2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G464" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H464" s="2" t="n">
-        <v>0.583</v>
+        <v>0.473</v>
       </c>
       <c r="I464" s="2" t="inlineStr">
         <is>
@@ -26695,16 +26695,16 @@
         </is>
       </c>
       <c r="J464" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K464" s="2" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="L464" s="2" t="n">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="M464" s="2" t="n">
-        <v>224</v>
+        <v>165</v>
       </c>
       <c r="N464" s="4" t="inlineStr">
         <is>
@@ -26712,18 +26712,18 @@
         </is>
       </c>
       <c r="O464" s="2" t="n">
-        <v>3.79</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>NOR0032314</t>
+          <t>NOR0032315</t>
         </is>
       </c>
       <c r="B465" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 60 X 10 X 1.3</t>
+          <t>RECTANGULAR 100 X 20 X 1.5</t>
         </is>
       </c>
       <c r="C465" s="2" t="inlineStr">
@@ -26732,19 +26732,19 @@
         </is>
       </c>
       <c r="D465" s="2" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E465" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F465" s="2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G465" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H465" s="2" t="n">
-        <v>0.473</v>
+        <v>0.95118</v>
       </c>
       <c r="I465" s="2" t="inlineStr">
         <is>
@@ -26752,16 +26752,16 @@
         </is>
       </c>
       <c r="J465" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K465" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L465" s="2" t="n">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="M465" s="2" t="n">
-        <v>166</v>
+        <v>56</v>
       </c>
       <c r="N465" s="4" t="inlineStr">
         <is>
@@ -26769,18 +26769,18 @@
         </is>
       </c>
       <c r="O465" s="2" t="n">
-        <v>3.07</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>NOR0032315</t>
+          <t>NOR0032316</t>
         </is>
       </c>
       <c r="B466" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 100 X 20 X 1.5</t>
+          <t>RECTANGULAR 120 X 20 X 1.5</t>
         </is>
       </c>
       <c r="C466" s="2" t="inlineStr">
@@ -26789,7 +26789,7 @@
         </is>
       </c>
       <c r="D466" s="2" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E466" s="2" t="n">
         <v>20</v>
@@ -26801,7 +26801,7 @@
         <v>6.4</v>
       </c>
       <c r="H466" s="2" t="n">
-        <v>0.95118</v>
+        <v>1.114</v>
       </c>
       <c r="I466" s="2" t="inlineStr">
         <is>
@@ -26809,16 +26809,16 @@
         </is>
       </c>
       <c r="J466" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K466" s="2" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="L466" s="2" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="M466" s="2" t="n">
-        <v>56</v>
+        <v>186</v>
       </c>
       <c r="N466" s="4" t="inlineStr">
         <is>
@@ -26826,18 +26826,18 @@
         </is>
       </c>
       <c r="O466" s="2" t="n">
-        <v>6.18</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>NOR0032316</t>
+          <t>NOR0032319</t>
         </is>
       </c>
       <c r="B467" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 120 X 20 X 1.5</t>
+          <t>RECTANGULAR 50 X 15 X 1.2</t>
         </is>
       </c>
       <c r="C467" s="2" t="inlineStr">
@@ -26846,19 +26846,19 @@
         </is>
       </c>
       <c r="D467" s="2" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E467" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F467" s="2" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G467" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H467" s="2" t="n">
-        <v>1.114</v>
+        <v>0.406</v>
       </c>
       <c r="I467" s="2" t="inlineStr">
         <is>
@@ -26866,35 +26866,35 @@
         </is>
       </c>
       <c r="J467" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K467" s="2" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="L467" s="2" t="n">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="M467" s="2" t="n">
-        <v>186</v>
-      </c>
-      <c r="N467" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>61</v>
+      </c>
+      <c r="N467" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O467" s="2" t="n">
-        <v>7.24</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>NOR0032319</t>
+          <t>NOR0032320</t>
         </is>
       </c>
       <c r="B468" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 50 X 15 X 1.2</t>
+          <t>RECTANGULAR 120 X 40 X 1.5</t>
         </is>
       </c>
       <c r="C468" s="2" t="inlineStr">
@@ -26903,19 +26903,19 @@
         </is>
       </c>
       <c r="D468" s="2" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="E468" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F468" s="2" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G468" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H468" s="2" t="n">
-        <v>0.406</v>
+        <v>1.272</v>
       </c>
       <c r="I468" s="2" t="inlineStr">
         <is>
@@ -26929,10 +26929,10 @@
         <v>0</v>
       </c>
       <c r="L468" s="2" t="n">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="M468" s="2" t="n">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="N468" s="6" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         </is>
       </c>
       <c r="O468" s="2" t="n">
-        <v>2.64</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="469">
@@ -26969,7 +26969,7 @@
         <v>1.5</v>
       </c>
       <c r="G469" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H469" s="2" t="n">
         <v>1.272</v>
@@ -26980,35 +26980,35 @@
         </is>
       </c>
       <c r="J469" s="2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K469" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L469" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M469" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N469" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>28</v>
+      </c>
+      <c r="N469" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O469" s="2" t="n">
-        <v>8.27</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>NOR0032320</t>
+          <t>NOR0032321</t>
         </is>
       </c>
       <c r="B470" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 120 X 40 X 1.5</t>
+          <t>RECTANGULAR 150 X 20 X 1.5</t>
         </is>
       </c>
       <c r="C470" s="2" t="inlineStr">
@@ -27017,10 +27017,10 @@
         </is>
       </c>
       <c r="D470" s="2" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E470" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F470" s="2" t="n">
         <v>1.5</v>
@@ -27029,7 +27029,7 @@
         <v>6.4</v>
       </c>
       <c r="H470" s="2" t="n">
-        <v>1.272</v>
+        <v>1.353</v>
       </c>
       <c r="I470" s="2" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         </is>
       </c>
       <c r="J470" s="2" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="K470" s="2" t="n">
         <v>0</v>
@@ -27046,26 +27046,26 @@
         <v>0</v>
       </c>
       <c r="M470" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="N470" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>1</v>
+      </c>
+      <c r="N470" s="5" t="inlineStr">
+        <is>
+          <t>Sin stock</t>
         </is>
       </c>
       <c r="O470" s="2" t="n">
-        <v>8.27</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>NOR0032321</t>
+          <t>NOR0032323</t>
         </is>
       </c>
       <c r="B471" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 150 X 20 X 1.5</t>
+          <t>RECTANGULAR 100 X 50 X 1.5</t>
         </is>
       </c>
       <c r="C471" s="2" t="inlineStr">
@@ -27074,10 +27074,10 @@
         </is>
       </c>
       <c r="D471" s="2" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E471" s="2" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F471" s="2" t="n">
         <v>1.5</v>
@@ -27086,7 +27086,7 @@
         <v>6.4</v>
       </c>
       <c r="H471" s="2" t="n">
-        <v>1.353</v>
+        <v>1.195</v>
       </c>
       <c r="I471" s="2" t="inlineStr">
         <is>
@@ -27094,24 +27094,24 @@
         </is>
       </c>
       <c r="J471" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K471" s="2" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="L471" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M471" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N471" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>43</v>
+      </c>
+      <c r="N471" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O471" s="2" t="n">
-        <v>8.789999999999999</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="472">
@@ -27140,7 +27140,7 @@
         <v>1.5</v>
       </c>
       <c r="G472" s="2" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="H472" s="2" t="n">
         <v>1.195</v>
@@ -27154,32 +27154,32 @@
         <v>0</v>
       </c>
       <c r="K472" s="2" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L472" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M472" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="N472" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>4</v>
+      </c>
+      <c r="N472" s="5" t="inlineStr">
+        <is>
+          <t>Sin stock</t>
         </is>
       </c>
       <c r="O472" s="2" t="n">
-        <v>7.77</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>NOR0032323</t>
+          <t>NOR0032324</t>
         </is>
       </c>
       <c r="B473" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 100 X 50 X 1.5</t>
+          <t>RECTANGULAR 100 X 60 X 1.8</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
@@ -27191,16 +27191,16 @@
         <v>100</v>
       </c>
       <c r="E473" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F473" s="2" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="G473" s="2" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="H473" s="2" t="n">
-        <v>1.195</v>
+        <v>1.526</v>
       </c>
       <c r="I473" s="2" t="inlineStr">
         <is>
@@ -27211,53 +27211,53 @@
         <v>0</v>
       </c>
       <c r="K473" s="2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L473" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M473" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N473" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>39</v>
+      </c>
+      <c r="N473" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O473" s="2" t="n">
-        <v>7.77</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>NOR0032324</t>
+          <t>NOR0032401</t>
         </is>
       </c>
       <c r="B474" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 100 X 60 X 1.8</t>
+          <t>TUBO REDONDO 16 X 1,2</t>
         </is>
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>TUBO RECTANGULAR</t>
+          <t>TUBO REDONDO</t>
         </is>
       </c>
       <c r="D474" s="2" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="E474" s="2" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="F474" s="2" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="G474" s="2" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H474" s="2" t="n">
-        <v>1.526</v>
+        <v>0.162</v>
       </c>
       <c r="I474" s="2" t="inlineStr">
         <is>
@@ -27265,35 +27265,35 @@
         </is>
       </c>
       <c r="J474" s="2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K474" s="2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L474" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M474" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="N474" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>29</v>
+      </c>
+      <c r="N474" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O474" s="2" t="n">
-        <v>9.92</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>NOR0032401</t>
+          <t>NOR0032403</t>
         </is>
       </c>
       <c r="B475" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 16 X 1,2</t>
+          <t>TUBO REDONDO 20 X 1.2</t>
         </is>
       </c>
       <c r="C475" s="2" t="inlineStr">
@@ -27302,19 +27302,19 @@
         </is>
       </c>
       <c r="D475" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E475" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F475" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="G475" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H475" s="2" t="n">
-        <v>0.162</v>
+        <v>0.1915</v>
       </c>
       <c r="I475" s="2" t="inlineStr">
         <is>
@@ -27322,24 +27322,24 @@
         </is>
       </c>
       <c r="J475" s="2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K475" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L475" s="2" t="n">
-        <v>1</v>
+        <v>238</v>
       </c>
       <c r="M475" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="N475" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>238</v>
+      </c>
+      <c r="N475" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O475" s="2" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="476">
@@ -27368,7 +27368,7 @@
         <v>1.2</v>
       </c>
       <c r="G476" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H476" s="2" t="n">
         <v>0.1915</v>
@@ -27379,35 +27379,35 @@
         </is>
       </c>
       <c r="J476" s="2" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="K476" s="2" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L476" s="2" t="n">
-        <v>238</v>
+        <v>330</v>
       </c>
       <c r="M476" s="2" t="n">
-        <v>238</v>
-      </c>
-      <c r="N476" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>484</v>
+      </c>
+      <c r="N476" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O476" s="2" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>NOR0032403</t>
+          <t>NOR0032405</t>
         </is>
       </c>
       <c r="B477" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 20 X 1.2</t>
+          <t>TUBO REDONDO 30 X 1,2</t>
         </is>
       </c>
       <c r="C477" s="2" t="inlineStr">
@@ -27416,10 +27416,10 @@
         </is>
       </c>
       <c r="D477" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E477" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F477" s="2" t="n">
         <v>1.2</v>
@@ -27428,7 +27428,7 @@
         <v>6.4</v>
       </c>
       <c r="H477" s="2" t="n">
-        <v>0.1915</v>
+        <v>0.2945</v>
       </c>
       <c r="I477" s="2" t="inlineStr">
         <is>
@@ -27436,35 +27436,35 @@
         </is>
       </c>
       <c r="J477" s="2" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="K477" s="2" t="n">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="L477" s="2" t="n">
-        <v>330</v>
+        <v>23</v>
       </c>
       <c r="M477" s="2" t="n">
-        <v>484</v>
-      </c>
-      <c r="N477" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>143</v>
+      </c>
+      <c r="N477" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O477" s="2" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>NOR0032405</t>
+          <t>NOR0032406</t>
         </is>
       </c>
       <c r="B478" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 30 X 1,2</t>
+          <t>TUBO REDONDO 40 X 1,3</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr">
@@ -27473,19 +27473,19 @@
         </is>
       </c>
       <c r="D478" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E478" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F478" s="2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G478" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H478" s="2" t="n">
-        <v>0.2945</v>
+        <v>0.427</v>
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
@@ -27493,16 +27493,16 @@
         </is>
       </c>
       <c r="J478" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K478" s="2" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="L478" s="2" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="M478" s="2" t="n">
-        <v>143</v>
+        <v>53</v>
       </c>
       <c r="N478" s="6" t="inlineStr">
         <is>
@@ -27510,18 +27510,18 @@
         </is>
       </c>
       <c r="O478" s="2" t="n">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>NOR0032406</t>
+          <t>NOR0032407</t>
         </is>
       </c>
       <c r="B479" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 40 X 1,3</t>
+          <t>TUBO REDONDO 50 X 1,5</t>
         </is>
       </c>
       <c r="C479" s="2" t="inlineStr">
@@ -27530,19 +27530,19 @@
         </is>
       </c>
       <c r="D479" s="2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E479" s="2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F479" s="2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G479" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H479" s="2" t="n">
-        <v>0.427</v>
+        <v>0.6185</v>
       </c>
       <c r="I479" s="2" t="inlineStr">
         <is>
@@ -27550,16 +27550,16 @@
         </is>
       </c>
       <c r="J479" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K479" s="2" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L479" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M479" s="2" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N479" s="6" t="inlineStr">
         <is>
@@ -27567,18 +27567,18 @@
         </is>
       </c>
       <c r="O479" s="2" t="n">
-        <v>2.78</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>NOR0032407</t>
+          <t>NOR0032408</t>
         </is>
       </c>
       <c r="B480" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 50 X 1,5</t>
+          <t>TUBO REDONDO 60 X 1,4</t>
         </is>
       </c>
       <c r="C480" s="2" t="inlineStr">
@@ -27587,19 +27587,19 @@
         </is>
       </c>
       <c r="D480" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E480" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F480" s="2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G480" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H480" s="2" t="n">
-        <v>0.6185</v>
+        <v>0.6966</v>
       </c>
       <c r="I480" s="2" t="inlineStr">
         <is>
@@ -27607,24 +27607,24 @@
         </is>
       </c>
       <c r="J480" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K480" s="2" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="L480" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M480" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="N480" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>1</v>
+      </c>
+      <c r="N480" s="5" t="inlineStr">
+        <is>
+          <t>Sin stock</t>
         </is>
       </c>
       <c r="O480" s="2" t="n">
-        <v>4.02</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="481">
@@ -27653,7 +27653,7 @@
         <v>1.4</v>
       </c>
       <c r="G481" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H481" s="2" t="n">
         <v>0.6966</v>
@@ -27664,35 +27664,35 @@
         </is>
       </c>
       <c r="J481" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K481" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="L481" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M481" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N481" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>66</v>
+      </c>
+      <c r="N481" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O481" s="2" t="n">
-        <v>4.53</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>NOR0032408</t>
+          <t>NOR0032409</t>
         </is>
       </c>
       <c r="B482" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 60 X 1,4</t>
+          <t>TUBO REDONDO 80 X 1.6</t>
         </is>
       </c>
       <c r="C482" s="2" t="inlineStr">
@@ -27701,19 +27701,19 @@
         </is>
       </c>
       <c r="D482" s="2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E482" s="2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F482" s="2" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G482" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H482" s="2" t="n">
-        <v>0.6966</v>
+        <v>1.065</v>
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
@@ -27721,24 +27721,24 @@
         </is>
       </c>
       <c r="J482" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K482" s="2" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L482" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M482" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="N482" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>3</v>
+      </c>
+      <c r="N482" s="5" t="inlineStr">
+        <is>
+          <t>Sin stock</t>
         </is>
       </c>
       <c r="O482" s="2" t="n">
-        <v>4.53</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="483">
@@ -27767,7 +27767,7 @@
         <v>1.6</v>
       </c>
       <c r="G483" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H483" s="2" t="n">
         <v>1.065</v>
@@ -27781,32 +27781,32 @@
         <v>0</v>
       </c>
       <c r="K483" s="2" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="L483" s="2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M483" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N483" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>136</v>
+      </c>
+      <c r="N483" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O483" s="2" t="n">
-        <v>6.92</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>NOR0032409</t>
+          <t>NOR0032410</t>
         </is>
       </c>
       <c r="B484" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 80 X 1.6</t>
+          <t>TUBO REDONDO 70 X 1,5</t>
         </is>
       </c>
       <c r="C484" s="2" t="inlineStr">
@@ -27815,19 +27815,19 @@
         </is>
       </c>
       <c r="D484" s="2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E484" s="2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F484" s="2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G484" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H484" s="2" t="n">
-        <v>1.065</v>
+        <v>0.8721</v>
       </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
@@ -27835,16 +27835,16 @@
         </is>
       </c>
       <c r="J484" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K484" s="2" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="L484" s="2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M484" s="2" t="n">
-        <v>136</v>
+        <v>67</v>
       </c>
       <c r="N484" s="6" t="inlineStr">
         <is>
@@ -27852,39 +27852,39 @@
         </is>
       </c>
       <c r="O484" s="2" t="n">
-        <v>6.92</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>NOR0032410</t>
+          <t>NOR0032414</t>
         </is>
       </c>
       <c r="B485" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 70 X 1,5</t>
+          <t>T - 30 X 30 X 1.5</t>
         </is>
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>TUBO REDONDO</t>
+          <t>PERFIL T</t>
         </is>
       </c>
       <c r="D485" s="2" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="E485" s="2" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="F485" s="2" t="n">
         <v>1.5</v>
       </c>
       <c r="G485" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H485" s="2" t="n">
-        <v>0.8721</v>
+        <v>0.237</v>
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
@@ -27892,16 +27892,16 @@
         </is>
       </c>
       <c r="J485" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K485" s="2" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="L485" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M485" s="2" t="n">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="N485" s="6" t="inlineStr">
         <is>
@@ -27909,68 +27909,11 @@
         </is>
       </c>
       <c r="O485" s="2" t="n">
-        <v>5.67</v>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" s="2" t="inlineStr">
-        <is>
-          <t>NOR0032414</t>
-        </is>
-      </c>
-      <c r="B486" s="3" t="inlineStr">
-        <is>
-          <t>T - 30 X 30 X 1.5</t>
-        </is>
-      </c>
-      <c r="C486" s="2" t="inlineStr">
-        <is>
-          <t>PERFIL T</t>
-        </is>
-      </c>
-      <c r="D486" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="E486" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="F486" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G486" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H486" s="2" t="n">
-        <v>0.237</v>
-      </c>
-      <c r="I486" s="2" t="inlineStr">
-        <is>
-          <t>BRUTO</t>
-        </is>
-      </c>
-      <c r="J486" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K486" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="L486" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M486" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="N486" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
-        </is>
-      </c>
-      <c r="O486" s="2" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O486"/>
+  <autoFilter ref="A1:O485"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/inventario_expandido.xlsx
+++ b/inventario_expandido.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inventario'!$A$1:$O$487</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inventario'!$A$1:$O$490</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O487"/>
+  <dimension ref="A1:O490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14736,13 +14736,13 @@
         <v>0</v>
       </c>
       <c r="K254" s="2" t="n">
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="L254" s="2" t="n">
         <v>45</v>
       </c>
       <c r="M254" s="2" t="n">
-        <v>45</v>
+        <v>460</v>
       </c>
       <c r="N254" s="6" t="inlineStr">
         <is>
@@ -22773,13 +22773,13 @@
         <v>0</v>
       </c>
       <c r="K395" s="2" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="L395" s="2" t="n">
         <v>53</v>
       </c>
       <c r="M395" s="2" t="n">
-        <v>53</v>
+        <v>276</v>
       </c>
       <c r="N395" s="6" t="inlineStr">
         <is>
@@ -22940,13 +22940,13 @@
         <v>0</v>
       </c>
       <c r="K398" s="2" t="n">
-        <v>0</v>
+        <v>851</v>
       </c>
       <c r="L398" s="2" t="n">
         <v>405</v>
       </c>
       <c r="M398" s="2" t="n">
-        <v>405</v>
+        <v>1256</v>
       </c>
       <c r="N398" s="6" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         </is>
       </c>
       <c r="J400" s="2" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="K400" s="2" t="n">
         <v>305</v>
@@ -23056,11 +23056,11 @@
         <v>93</v>
       </c>
       <c r="M400" s="2" t="n">
-        <v>398</v>
-      </c>
-      <c r="N400" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>576</v>
+      </c>
+      <c r="N400" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O400" s="2" t="n">
@@ -23338,10 +23338,10 @@
         <v>595</v>
       </c>
       <c r="L405" s="2" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="M405" s="2" t="n">
-        <v>675</v>
+        <v>843</v>
       </c>
       <c r="N405" s="4" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         </is>
       </c>
       <c r="J411" s="2" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="K411" s="2" t="n">
         <v>1290</v>
@@ -23683,11 +23683,11 @@
         <v>3</v>
       </c>
       <c r="M411" s="2" t="n">
-        <v>1293</v>
-      </c>
-      <c r="N411" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>1494</v>
+      </c>
+      <c r="N411" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O411" s="2" t="n">
@@ -23731,20 +23731,20 @@
         </is>
       </c>
       <c r="J412" s="2" t="n">
-        <v>0</v>
+        <v>399</v>
       </c>
       <c r="K412" s="2" t="n">
-        <v>0</v>
+        <v>1957</v>
       </c>
       <c r="L412" s="2" t="n">
         <v>715</v>
       </c>
       <c r="M412" s="2" t="n">
-        <v>715</v>
-      </c>
-      <c r="N412" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>3071</v>
+      </c>
+      <c r="N412" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O412" s="2" t="n">
@@ -23788,20 +23788,20 @@
         </is>
       </c>
       <c r="J413" s="2" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="K413" s="2" t="n">
-        <v>0</v>
+        <v>766</v>
       </c>
       <c r="L413" s="2" t="n">
         <v>131</v>
       </c>
       <c r="M413" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="N413" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>1086</v>
+      </c>
+      <c r="N413" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O413" s="2" t="n">
@@ -23905,13 +23905,13 @@
         <v>300</v>
       </c>
       <c r="K415" s="2" t="n">
-        <v>0</v>
+        <v>783</v>
       </c>
       <c r="L415" s="2" t="n">
         <v>96</v>
       </c>
       <c r="M415" s="2" t="n">
-        <v>396</v>
+        <v>1179</v>
       </c>
       <c r="N415" s="4" t="inlineStr">
         <is>
@@ -24079,10 +24079,10 @@
         <v>530</v>
       </c>
       <c r="L418" s="2" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="M418" s="2" t="n">
-        <v>621</v>
+        <v>903</v>
       </c>
       <c r="N418" s="4" t="inlineStr">
         <is>
@@ -24190,13 +24190,13 @@
         <v>128</v>
       </c>
       <c r="K420" s="2" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="L420" s="2" t="n">
         <v>83</v>
       </c>
       <c r="M420" s="2" t="n">
-        <v>211</v>
+        <v>493</v>
       </c>
       <c r="N420" s="4" t="inlineStr">
         <is>
@@ -24247,13 +24247,13 @@
         <v>0</v>
       </c>
       <c r="K421" s="2" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="L421" s="2" t="n">
         <v>109</v>
       </c>
       <c r="M421" s="2" t="n">
-        <v>109</v>
+        <v>302</v>
       </c>
       <c r="N421" s="6" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         </is>
       </c>
       <c r="J423" s="2" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="K423" s="2" t="n">
         <v>92</v>
@@ -24367,11 +24367,11 @@
         <v>0</v>
       </c>
       <c r="M423" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="N423" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>249</v>
+      </c>
+      <c r="N423" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O423" s="2" t="n">
@@ -24438,12 +24438,12 @@
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>NOR0032111</t>
+          <t>NOR0032110</t>
         </is>
       </c>
       <c r="B425" s="3" t="inlineStr">
         <is>
-          <t>ANGULO 80 X 40 X 1.25</t>
+          <t>ANGULO 60 X 40 X 1.5</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
@@ -24452,19 +24452,19 @@
         </is>
       </c>
       <c r="D425" s="2" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E425" s="2" t="n">
         <v>40</v>
       </c>
       <c r="F425" s="2" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="G425" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H425" s="2" t="n">
-        <v>0.4005</v>
+        <v>0.3996</v>
       </c>
       <c r="I425" s="2" t="inlineStr">
         <is>
@@ -24472,16 +24472,16 @@
         </is>
       </c>
       <c r="J425" s="2" t="n">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="K425" s="2" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="L425" s="2" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="M425" s="2" t="n">
-        <v>77</v>
+        <v>641</v>
       </c>
       <c r="N425" s="4" t="inlineStr">
         <is>
@@ -24495,12 +24495,12 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>NOR0032112</t>
+          <t>NOR0032111</t>
         </is>
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
-          <t>ANGULO 30 X 15 X 1,2</t>
+          <t>ANGULO 80 X 40 X 1.25</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
@@ -24509,19 +24509,19 @@
         </is>
       </c>
       <c r="D426" s="2" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="E426" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F426" s="2" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="G426" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H426" s="2" t="n">
-        <v>0.142</v>
+        <v>0.4005</v>
       </c>
       <c r="I426" s="2" t="inlineStr">
         <is>
@@ -24529,35 +24529,35 @@
         </is>
       </c>
       <c r="J426" s="2" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="K426" s="2" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="L426" s="2" t="n">
-        <v>60</v>
+        <v>252</v>
       </c>
       <c r="M426" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="N426" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>566</v>
+      </c>
+      <c r="N426" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O426" s="2" t="n">
-        <v>0.97</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>NOR0032115</t>
+          <t>NOR0032112</t>
         </is>
       </c>
       <c r="B427" s="3" t="inlineStr">
         <is>
-          <t>ANGULO 100 X 40 X 1,8</t>
+          <t>ANGULO 30 X 15 X 1,2</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
@@ -24566,19 +24566,19 @@
         </is>
       </c>
       <c r="D427" s="2" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E427" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F427" s="2" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="G427" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H427" s="2" t="n">
-        <v>0.672</v>
+        <v>0.142</v>
       </c>
       <c r="I427" s="2" t="inlineStr">
         <is>
@@ -24586,16 +24586,16 @@
         </is>
       </c>
       <c r="J427" s="2" t="n">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="K427" s="2" t="n">
-        <v>40</v>
+        <v>212</v>
       </c>
       <c r="L427" s="2" t="n">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="M427" s="2" t="n">
-        <v>322</v>
+        <v>463</v>
       </c>
       <c r="N427" s="4" t="inlineStr">
         <is>
@@ -24603,18 +24603,18 @@
         </is>
       </c>
       <c r="O427" s="2" t="n">
-        <v>4.57</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>NOR0032116</t>
+          <t>NOR0032115</t>
         </is>
       </c>
       <c r="B428" s="3" t="inlineStr">
         <is>
-          <t>ANGULO 25 X 1.5</t>
+          <t>ANGULO 100 X 40 X 1,8</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
@@ -24623,19 +24623,19 @@
         </is>
       </c>
       <c r="D428" s="2" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="E428" s="2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F428" s="2" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="G428" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H428" s="2" t="n">
-        <v>0.1982</v>
+        <v>0.672</v>
       </c>
       <c r="I428" s="2" t="inlineStr">
         <is>
@@ -24643,35 +24643,35 @@
         </is>
       </c>
       <c r="J428" s="2" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="K428" s="2" t="n">
-        <v>282</v>
+        <v>40</v>
       </c>
       <c r="L428" s="2" t="n">
-        <v>282</v>
+        <v>138</v>
       </c>
       <c r="M428" s="2" t="n">
-        <v>564</v>
-      </c>
-      <c r="N428" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>322</v>
+      </c>
+      <c r="N428" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O428" s="2" t="n">
-        <v>1.35</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>NOR0032117</t>
+          <t>NOR0032116</t>
         </is>
       </c>
       <c r="B429" s="3" t="inlineStr">
         <is>
-          <t>ANGULO 50 X 25 X 1,7</t>
+          <t>ANGULO 25 X 1.5</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
@@ -24680,19 +24680,19 @@
         </is>
       </c>
       <c r="D429" s="2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E429" s="2" t="n">
         <v>25</v>
       </c>
       <c r="F429" s="2" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="G429" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H429" s="2" t="n">
-        <v>0.338</v>
+        <v>0.1982</v>
       </c>
       <c r="I429" s="2" t="inlineStr">
         <is>
@@ -24700,35 +24700,35 @@
         </is>
       </c>
       <c r="J429" s="2" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="K429" s="2" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="L429" s="2" t="n">
-        <v>31</v>
+        <v>282</v>
       </c>
       <c r="M429" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="N429" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>564</v>
+      </c>
+      <c r="N429" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O429" s="2" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>NOR0032120</t>
+          <t>NOR0032117</t>
         </is>
       </c>
       <c r="B430" s="3" t="inlineStr">
         <is>
-          <t>ANGULO 53 X 28 X 1.5 CH.</t>
+          <t>ANGULO 50 X 25 X 1,7</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
@@ -24737,19 +24737,19 @@
         </is>
       </c>
       <c r="D430" s="2" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E430" s="2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F430" s="2" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="G430" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H430" s="2" t="n">
-        <v>0.32</v>
+        <v>0.338</v>
       </c>
       <c r="I430" s="2" t="inlineStr">
         <is>
@@ -24757,56 +24757,56 @@
         </is>
       </c>
       <c r="J430" s="2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K430" s="2" t="n">
-        <v>50</v>
+        <v>283</v>
       </c>
       <c r="L430" s="2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M430" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="N430" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>394</v>
+      </c>
+      <c r="N430" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O430" s="2" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>NOR0032200</t>
+          <t>NOR0032120</t>
         </is>
       </c>
       <c r="B431" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 16 X 1.3</t>
+          <t>ANGULO 53 X 28 X 1.5 CH.</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="D431" s="2" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="E431" s="2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F431" s="2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G431" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H431" s="2" t="n">
-        <v>0.206</v>
+        <v>0.32</v>
       </c>
       <c r="I431" s="2" t="inlineStr">
         <is>
@@ -24814,35 +24814,35 @@
         </is>
       </c>
       <c r="J431" s="2" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="K431" s="2" t="n">
-        <v>510</v>
+        <v>50</v>
       </c>
       <c r="L431" s="2" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M431" s="2" t="n">
-        <v>729</v>
-      </c>
-      <c r="N431" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>50</v>
+      </c>
+      <c r="N431" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O431" s="2" t="n">
-        <v>1.4</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>NOR0032201</t>
+          <t>NOR0032200</t>
         </is>
       </c>
       <c r="B432" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 20 X 1,3</t>
+          <t>TUBO CUADRADO 16 X 1.3</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
@@ -24851,19 +24851,19 @@
         </is>
       </c>
       <c r="D432" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E432" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F432" s="2" t="n">
         <v>1.3</v>
       </c>
       <c r="G432" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H432" s="2" t="n">
-        <v>0.2624</v>
+        <v>0.206</v>
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
@@ -24871,35 +24871,35 @@
         </is>
       </c>
       <c r="J432" s="2" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="K432" s="2" t="n">
-        <v>2</v>
+        <v>510</v>
       </c>
       <c r="L432" s="2" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M432" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N432" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>729</v>
+      </c>
+      <c r="N432" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O432" s="2" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>NOR0032202</t>
+          <t>NOR0032201</t>
         </is>
       </c>
       <c r="B433" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 25 X 1.3</t>
+          <t>TUBO CUADRADO 20 X 1,3</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
@@ -24908,10 +24908,10 @@
         </is>
       </c>
       <c r="D433" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E433" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F433" s="2" t="n">
         <v>1.3</v>
@@ -24920,7 +24920,7 @@
         <v>6</v>
       </c>
       <c r="H433" s="2" t="n">
-        <v>0.332</v>
+        <v>0.2624</v>
       </c>
       <c r="I433" s="2" t="inlineStr">
         <is>
@@ -24931,32 +24931,32 @@
         <v>0</v>
       </c>
       <c r="K433" s="2" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="L433" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M433" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="N433" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>2</v>
+      </c>
+      <c r="N433" s="5" t="inlineStr">
+        <is>
+          <t>Sin stock</t>
         </is>
       </c>
       <c r="O433" s="2" t="n">
-        <v>2.26</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>NOR0032202</t>
+          <t>NOR0032201</t>
         </is>
       </c>
       <c r="B434" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 25 X 1.3</t>
+          <t>TUBO CUADRADO 20 X 1,3</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
@@ -24965,10 +24965,10 @@
         </is>
       </c>
       <c r="D434" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E434" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F434" s="2" t="n">
         <v>1.3</v>
@@ -24977,7 +24977,7 @@
         <v>6.4</v>
       </c>
       <c r="H434" s="2" t="n">
-        <v>0.332</v>
+        <v>0.2624</v>
       </c>
       <c r="I434" s="2" t="inlineStr">
         <is>
@@ -24988,13 +24988,13 @@
         <v>0</v>
       </c>
       <c r="K434" s="2" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="L434" s="2" t="n">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="M434" s="2" t="n">
-        <v>24</v>
+        <v>504</v>
       </c>
       <c r="N434" s="6" t="inlineStr">
         <is>
@@ -25002,18 +25002,18 @@
         </is>
       </c>
       <c r="O434" s="2" t="n">
-        <v>2.26</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>NOR0032203</t>
+          <t>NOR0032202</t>
         </is>
       </c>
       <c r="B435" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 30 X 1.3</t>
+          <t>TUBO CUADRADO 25 X 1.3</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
@@ -25022,19 +25022,19 @@
         </is>
       </c>
       <c r="D435" s="2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E435" s="2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F435" s="2" t="n">
         <v>1.3</v>
       </c>
       <c r="G435" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H435" s="2" t="n">
-        <v>0.402</v>
+        <v>0.332</v>
       </c>
       <c r="I435" s="2" t="inlineStr">
         <is>
@@ -25042,16 +25042,16 @@
         </is>
       </c>
       <c r="J435" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K435" s="2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L435" s="2" t="n">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="M435" s="2" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="N435" s="6" t="inlineStr">
         <is>
@@ -25059,18 +25059,18 @@
         </is>
       </c>
       <c r="O435" s="2" t="n">
-        <v>2.73</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>NOR0032204</t>
+          <t>NOR0032202</t>
         </is>
       </c>
       <c r="B436" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 40 X 1.3</t>
+          <t>TUBO CUADRADO 25 X 1.3</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
@@ -25079,10 +25079,10 @@
         </is>
       </c>
       <c r="D436" s="2" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E436" s="2" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F436" s="2" t="n">
         <v>1.3</v>
@@ -25091,7 +25091,7 @@
         <v>6.4</v>
       </c>
       <c r="H436" s="2" t="n">
-        <v>0.543</v>
+        <v>0.332</v>
       </c>
       <c r="I436" s="2" t="inlineStr">
         <is>
@@ -25099,35 +25099,35 @@
         </is>
       </c>
       <c r="J436" s="2" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="K436" s="2" t="n">
-        <v>66</v>
+        <v>239</v>
       </c>
       <c r="L436" s="2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M436" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="N436" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>481</v>
+      </c>
+      <c r="N436" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O436" s="2" t="n">
-        <v>3.69</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>NOR0032205</t>
+          <t>NOR0032203</t>
         </is>
       </c>
       <c r="B437" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 45 X 1.5</t>
+          <t>TUBO CUADRADO 30 X 1.3</t>
         </is>
       </c>
       <c r="C437" s="2" t="inlineStr">
@@ -25136,19 +25136,19 @@
         </is>
       </c>
       <c r="D437" s="2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E437" s="2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F437" s="2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G437" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H437" s="2" t="n">
-        <v>0.705</v>
+        <v>0.402</v>
       </c>
       <c r="I437" s="2" t="inlineStr">
         <is>
@@ -25156,35 +25156,35 @@
         </is>
       </c>
       <c r="J437" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K437" s="2" t="n">
-        <v>2</v>
+        <v>263</v>
       </c>
       <c r="L437" s="2" t="n">
-        <v>3</v>
+        <v>119</v>
       </c>
       <c r="M437" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N437" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>384</v>
+      </c>
+      <c r="N437" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O437" s="2" t="n">
-        <v>4.79</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>NOR0032205</t>
+          <t>NOR0032204</t>
         </is>
       </c>
       <c r="B438" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 45 X 1.5</t>
+          <t>TUBO CUADRADO 40 X 1.3</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
@@ -25193,19 +25193,19 @@
         </is>
       </c>
       <c r="D438" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E438" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F438" s="2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G438" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H438" s="2" t="n">
-        <v>0.705</v>
+        <v>0.543</v>
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
@@ -25213,35 +25213,35 @@
         </is>
       </c>
       <c r="J438" s="2" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="K438" s="2" t="n">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="L438" s="2" t="n">
-        <v>59</v>
+        <v>191</v>
       </c>
       <c r="M438" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="N438" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>426</v>
+      </c>
+      <c r="N438" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O438" s="2" t="n">
-        <v>4.79</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>NOR0032206</t>
+          <t>NOR0032205</t>
         </is>
       </c>
       <c r="B439" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 50 X 1,3</t>
+          <t>TUBO CUADRADO 45 X 1.5</t>
         </is>
       </c>
       <c r="C439" s="2" t="inlineStr">
@@ -25250,19 +25250,19 @@
         </is>
       </c>
       <c r="D439" s="2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E439" s="2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F439" s="2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G439" s="2" t="n">
         <v>6</v>
       </c>
       <c r="H439" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.705</v>
       </c>
       <c r="I439" s="2" t="inlineStr">
         <is>
@@ -25273,32 +25273,32 @@
         <v>0</v>
       </c>
       <c r="K439" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L439" s="2" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="M439" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="N439" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>5</v>
+      </c>
+      <c r="N439" s="5" t="inlineStr">
+        <is>
+          <t>Sin stock</t>
         </is>
       </c>
       <c r="O439" s="2" t="n">
-        <v>4.64</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>NOR0032206</t>
+          <t>NOR0032205</t>
         </is>
       </c>
       <c r="B440" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 50 X 1,3</t>
+          <t>TUBO CUADRADO 45 X 1.5</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
@@ -25307,19 +25307,19 @@
         </is>
       </c>
       <c r="D440" s="2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E440" s="2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F440" s="2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G440" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H440" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.705</v>
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
@@ -25327,35 +25327,35 @@
         </is>
       </c>
       <c r="J440" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K440" s="2" t="n">
-        <v>67</v>
+        <v>139</v>
       </c>
       <c r="L440" s="2" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M440" s="2" t="n">
-        <v>147</v>
-      </c>
-      <c r="N440" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>198</v>
+      </c>
+      <c r="N440" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O440" s="2" t="n">
-        <v>4.64</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>NOR0032207</t>
+          <t>NOR0032206</t>
         </is>
       </c>
       <c r="B441" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 60 X 1,3</t>
+          <t>TUBO CUADRADO 50 X 1,3</t>
         </is>
       </c>
       <c r="C441" s="2" t="inlineStr">
@@ -25364,19 +25364,19 @@
         </is>
       </c>
       <c r="D441" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E441" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F441" s="2" t="n">
         <v>1.3</v>
       </c>
       <c r="G441" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H441" s="2" t="n">
-        <v>0.8235</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
@@ -25384,16 +25384,16 @@
         </is>
       </c>
       <c r="J441" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K441" s="2" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="L441" s="2" t="n">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="M441" s="2" t="n">
-        <v>181</v>
+        <v>36</v>
       </c>
       <c r="N441" s="6" t="inlineStr">
         <is>
@@ -25401,18 +25401,18 @@
         </is>
       </c>
       <c r="O441" s="2" t="n">
-        <v>5.6</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>NOR0032208</t>
+          <t>NOR0032206</t>
         </is>
       </c>
       <c r="B442" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 70 X 1,3</t>
+          <t>TUBO CUADRADO 50 X 1,3</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
@@ -25421,10 +25421,10 @@
         </is>
       </c>
       <c r="D442" s="2" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E442" s="2" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F442" s="2" t="n">
         <v>1.3</v>
@@ -25433,7 +25433,7 @@
         <v>6.4</v>
       </c>
       <c r="H442" s="2" t="n">
-        <v>0.96454</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
@@ -25441,35 +25441,35 @@
         </is>
       </c>
       <c r="J442" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K442" s="2" t="n">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="L442" s="2" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="M442" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="N442" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>147</v>
+      </c>
+      <c r="N442" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O442" s="2" t="n">
-        <v>6.56</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>NOR0032209</t>
+          <t>NOR0032207</t>
         </is>
       </c>
       <c r="B443" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 80 X 1,5</t>
+          <t>TUBO CUADRADO 60 X 1,3</t>
         </is>
       </c>
       <c r="C443" s="2" t="inlineStr">
@@ -25478,19 +25478,19 @@
         </is>
       </c>
       <c r="D443" s="2" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E443" s="2" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F443" s="2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G443" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H443" s="2" t="n">
-        <v>1.2717</v>
+        <v>0.8235</v>
       </c>
       <c r="I443" s="2" t="inlineStr">
         <is>
@@ -25498,35 +25498,35 @@
         </is>
       </c>
       <c r="J443" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K443" s="2" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="L443" s="2" t="n">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="M443" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="N443" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>181</v>
+      </c>
+      <c r="N443" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O443" s="2" t="n">
-        <v>8.65</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>NOR0032210</t>
+          <t>NOR0032208</t>
         </is>
       </c>
       <c r="B444" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 100 X 1,9</t>
+          <t>TUBO CUADRADO 70 X 1,3</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
@@ -25535,19 +25535,19 @@
         </is>
       </c>
       <c r="D444" s="2" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E444" s="2" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F444" s="2" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="G444" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H444" s="2" t="n">
-        <v>2.0142</v>
+        <v>0.96454</v>
       </c>
       <c r="I444" s="2" t="inlineStr">
         <is>
@@ -25555,35 +25555,35 @@
         </is>
       </c>
       <c r="J444" s="2" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K444" s="2" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="L444" s="2" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="M444" s="2" t="n">
-        <v>117</v>
-      </c>
-      <c r="N444" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>64</v>
+      </c>
+      <c r="N444" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O444" s="2" t="n">
-        <v>13.7</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>NOR0032210</t>
+          <t>NOR0032209</t>
         </is>
       </c>
       <c r="B445" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 100 X 1,9</t>
+          <t>TUBO CUADRADO 80 X 1,5</t>
         </is>
       </c>
       <c r="C445" s="2" t="inlineStr">
@@ -25592,19 +25592,19 @@
         </is>
       </c>
       <c r="D445" s="2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E445" s="2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F445" s="2" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="G445" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H445" s="2" t="n">
-        <v>2.0142</v>
+        <v>1.2717</v>
       </c>
       <c r="I445" s="2" t="inlineStr">
         <is>
@@ -25612,35 +25612,35 @@
         </is>
       </c>
       <c r="J445" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K445" s="2" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="L445" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M445" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="N445" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>75</v>
+      </c>
+      <c r="N445" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O445" s="2" t="n">
-        <v>13.7</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>NOR0032211</t>
+          <t>NOR0032210</t>
         </is>
       </c>
       <c r="B446" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 35 X 1.3</t>
+          <t>TUBO CUADRADO 100 X 1,9</t>
         </is>
       </c>
       <c r="C446" s="2" t="inlineStr">
@@ -25649,19 +25649,19 @@
         </is>
       </c>
       <c r="D446" s="2" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="E446" s="2" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="F446" s="2" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="G446" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H446" s="2" t="n">
-        <v>0.475</v>
+        <v>2.0142</v>
       </c>
       <c r="I446" s="2" t="inlineStr">
         <is>
@@ -25669,35 +25669,35 @@
         </is>
       </c>
       <c r="J446" s="2" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="K446" s="2" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="L446" s="2" t="n">
-        <v>260</v>
+        <v>72</v>
       </c>
       <c r="M446" s="2" t="n">
-        <v>345</v>
-      </c>
-      <c r="N446" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>117</v>
+      </c>
+      <c r="N446" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O446" s="2" t="n">
-        <v>3.23</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>NOR0032212</t>
+          <t>NOR0032210</t>
         </is>
       </c>
       <c r="B447" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 120 X 2</t>
+          <t>TUBO CUADRADO 100 X 1,9</t>
         </is>
       </c>
       <c r="C447" s="2" t="inlineStr">
@@ -25706,19 +25706,19 @@
         </is>
       </c>
       <c r="D447" s="2" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E447" s="2" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F447" s="2" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="G447" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H447" s="2" t="n">
-        <v>2.549</v>
+        <v>2.0142</v>
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
@@ -25726,35 +25726,35 @@
         </is>
       </c>
       <c r="J447" s="2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K447" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L447" s="2" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="M447" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="N447" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>42</v>
+      </c>
+      <c r="N447" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O447" s="2" t="n">
-        <v>17.33</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>NOR0032213</t>
+          <t>NOR0032211</t>
         </is>
       </c>
       <c r="B448" s="3" t="inlineStr">
         <is>
-          <t>TUBO CUADRADO 40 X 1.5</t>
+          <t>TUBO CUADRADO 35 X 1.3</t>
         </is>
       </c>
       <c r="C448" s="2" t="inlineStr">
@@ -25763,19 +25763,19 @@
         </is>
       </c>
       <c r="D448" s="2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E448" s="2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F448" s="2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G448" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H448" s="2" t="n">
-        <v>0.624</v>
+        <v>0.475</v>
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
@@ -25783,16 +25783,16 @@
         </is>
       </c>
       <c r="J448" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K448" s="2" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="L448" s="2" t="n">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="M448" s="2" t="n">
-        <v>37</v>
+        <v>345</v>
       </c>
       <c r="N448" s="6" t="inlineStr">
         <is>
@@ -25800,39 +25800,39 @@
         </is>
       </c>
       <c r="O448" s="2" t="n">
-        <v>4.24</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>NOR0032300</t>
+          <t>NOR0032212</t>
         </is>
       </c>
       <c r="B449" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 20 X 10 X 1.3</t>
+          <t>TUBO CUADRADO 120 X 2</t>
         </is>
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>TUBO RECTANGULAR</t>
+          <t>TUBO CUADRADO</t>
         </is>
       </c>
       <c r="D449" s="2" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="E449" s="2" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="F449" s="2" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="G449" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H449" s="2" t="n">
-        <v>0.16594</v>
+        <v>2.549</v>
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
@@ -25840,16 +25840,16 @@
         </is>
       </c>
       <c r="J449" s="2" t="n">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="K449" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L449" s="2" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M449" s="2" t="n">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="N449" s="4" t="inlineStr">
         <is>
@@ -25857,39 +25857,39 @@
         </is>
       </c>
       <c r="O449" s="2" t="n">
-        <v>1.13</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>NOR0032301</t>
+          <t>NOR0032213</t>
         </is>
       </c>
       <c r="B450" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 30 X 15 X 1.3</t>
+          <t>TUBO CUADRADO 40 X 1.5</t>
         </is>
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>TUBO RECTANGULAR</t>
+          <t>TUBO CUADRADO</t>
         </is>
       </c>
       <c r="D450" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E450" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F450" s="2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G450" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H450" s="2" t="n">
-        <v>0.298</v>
+        <v>0.624</v>
       </c>
       <c r="I450" s="2" t="inlineStr">
         <is>
@@ -25897,35 +25897,35 @@
         </is>
       </c>
       <c r="J450" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K450" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L450" s="2" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M450" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="N450" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>37</v>
+      </c>
+      <c r="N450" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O450" s="2" t="n">
-        <v>2.03</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>NOR0032302</t>
+          <t>NOR0032300</t>
         </is>
       </c>
       <c r="B451" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 30 x 20 X 1,2</t>
+          <t>RECTANGULAR 20 X 10 X 1.3</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
@@ -25934,19 +25934,19 @@
         </is>
       </c>
       <c r="D451" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E451" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F451" s="2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G451" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H451" s="2" t="n">
-        <v>0.3078</v>
+        <v>0.16594</v>
       </c>
       <c r="I451" s="2" t="inlineStr">
         <is>
@@ -25954,16 +25954,16 @@
         </is>
       </c>
       <c r="J451" s="2" t="n">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="K451" s="2" t="n">
-        <v>118</v>
+        <v>343</v>
       </c>
       <c r="L451" s="2" t="n">
-        <v>0</v>
+        <v>498</v>
       </c>
       <c r="M451" s="2" t="n">
-        <v>160</v>
+        <v>920</v>
       </c>
       <c r="N451" s="4" t="inlineStr">
         <is>
@@ -25971,18 +25971,18 @@
         </is>
       </c>
       <c r="O451" s="2" t="n">
-        <v>2.09</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>NOR0032303</t>
+          <t>NOR0032301</t>
         </is>
       </c>
       <c r="B452" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 40 X 20 X 1,3</t>
+          <t>RECTANGULAR 30 X 15 X 1.3</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -25991,10 +25991,10 @@
         </is>
       </c>
       <c r="D452" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E452" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F452" s="2" t="n">
         <v>1.3</v>
@@ -26003,7 +26003,7 @@
         <v>6.4</v>
       </c>
       <c r="H452" s="2" t="n">
-        <v>0.402</v>
+        <v>0.298</v>
       </c>
       <c r="I452" s="2" t="inlineStr">
         <is>
@@ -26011,16 +26011,16 @@
         </is>
       </c>
       <c r="J452" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K452" s="2" t="n">
-        <v>111</v>
+        <v>309</v>
       </c>
       <c r="L452" s="2" t="n">
-        <v>180</v>
+        <v>233</v>
       </c>
       <c r="M452" s="2" t="n">
-        <v>292</v>
+        <v>549</v>
       </c>
       <c r="N452" s="6" t="inlineStr">
         <is>
@@ -26028,18 +26028,18 @@
         </is>
       </c>
       <c r="O452" s="2" t="n">
-        <v>2.73</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>NOR0032304</t>
+          <t>NOR0032302</t>
         </is>
       </c>
       <c r="B453" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 50 X 20 X 1.3</t>
+          <t>RECTANGULAR 30 x 20 X 1,2</t>
         </is>
       </c>
       <c r="C453" s="2" t="inlineStr">
@@ -26048,19 +26048,19 @@
         </is>
       </c>
       <c r="D453" s="2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E453" s="2" t="n">
         <v>20</v>
       </c>
       <c r="F453" s="2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G453" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H453" s="2" t="n">
-        <v>0.474</v>
+        <v>0.3078</v>
       </c>
       <c r="I453" s="2" t="inlineStr">
         <is>
@@ -26068,16 +26068,16 @@
         </is>
       </c>
       <c r="J453" s="2" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="K453" s="2" t="n">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="L453" s="2" t="n">
-        <v>29</v>
+        <v>267</v>
       </c>
       <c r="M453" s="2" t="n">
-        <v>114</v>
+        <v>427</v>
       </c>
       <c r="N453" s="4" t="inlineStr">
         <is>
@@ -26085,18 +26085,18 @@
         </is>
       </c>
       <c r="O453" s="2" t="n">
-        <v>3.22</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>NOR0032305</t>
+          <t>NOR0032303</t>
         </is>
       </c>
       <c r="B454" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 60 X 20 X 1,3</t>
+          <t>RECTANGULAR 40 X 20 X 1,3</t>
         </is>
       </c>
       <c r="C454" s="2" t="inlineStr">
@@ -26105,7 +26105,7 @@
         </is>
       </c>
       <c r="D454" s="2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E454" s="2" t="n">
         <v>20</v>
@@ -26117,7 +26117,7 @@
         <v>6.4</v>
       </c>
       <c r="H454" s="2" t="n">
-        <v>0.5427</v>
+        <v>0.402</v>
       </c>
       <c r="I454" s="2" t="inlineStr">
         <is>
@@ -26125,35 +26125,35 @@
         </is>
       </c>
       <c r="J454" s="2" t="n">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="K454" s="2" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="L454" s="2" t="n">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="M454" s="2" t="n">
-        <v>298</v>
-      </c>
-      <c r="N454" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>292</v>
+      </c>
+      <c r="N454" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O454" s="2" t="n">
-        <v>3.69</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>NOR0032306</t>
+          <t>NOR0032304</t>
         </is>
       </c>
       <c r="B455" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 70 X 20 X 1.3</t>
+          <t>RECTANGULAR 50 X 20 X 1.3</t>
         </is>
       </c>
       <c r="C455" s="2" t="inlineStr">
@@ -26162,7 +26162,7 @@
         </is>
       </c>
       <c r="D455" s="2" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E455" s="2" t="n">
         <v>20</v>
@@ -26174,7 +26174,7 @@
         <v>6.4</v>
       </c>
       <c r="H455" s="2" t="n">
-        <v>0.6129</v>
+        <v>0.474</v>
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
@@ -26182,16 +26182,16 @@
         </is>
       </c>
       <c r="J455" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K455" s="2" t="n">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="L455" s="2" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="M455" s="2" t="n">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="N455" s="4" t="inlineStr">
         <is>
@@ -26199,18 +26199,18 @@
         </is>
       </c>
       <c r="O455" s="2" t="n">
-        <v>4.17</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>NOR0032307</t>
+          <t>NOR0032305</t>
         </is>
       </c>
       <c r="B456" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 80 X 20 X 1.3</t>
+          <t>RECTANGULAR 60 X 20 X 1,3</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
@@ -26219,7 +26219,7 @@
         </is>
       </c>
       <c r="D456" s="2" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E456" s="2" t="n">
         <v>20</v>
@@ -26231,7 +26231,7 @@
         <v>6.4</v>
       </c>
       <c r="H456" s="2" t="n">
-        <v>0.6831</v>
+        <v>0.5427</v>
       </c>
       <c r="I456" s="2" t="inlineStr">
         <is>
@@ -26239,35 +26239,35 @@
         </is>
       </c>
       <c r="J456" s="2" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="K456" s="2" t="n">
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="L456" s="2" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="M456" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="N456" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>298</v>
+      </c>
+      <c r="N456" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O456" s="2" t="n">
-        <v>4.65</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>NOR0032308</t>
+          <t>NOR0032306</t>
         </is>
       </c>
       <c r="B457" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 100 X 40 X 1.5</t>
+          <t>RECTANGULAR 70 X 20 X 1.3</t>
         </is>
       </c>
       <c r="C457" s="2" t="inlineStr">
@@ -26276,19 +26276,19 @@
         </is>
       </c>
       <c r="D457" s="2" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E457" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F457" s="2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G457" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H457" s="2" t="n">
-        <v>1.1097</v>
+        <v>0.6129</v>
       </c>
       <c r="I457" s="2" t="inlineStr">
         <is>
@@ -26296,35 +26296,35 @@
         </is>
       </c>
       <c r="J457" s="2" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="K457" s="2" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="L457" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M457" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="N457" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>144</v>
+      </c>
+      <c r="N457" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O457" s="2" t="n">
-        <v>7.55</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>NOR0032308</t>
+          <t>NOR0032307</t>
         </is>
       </c>
       <c r="B458" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 100 X 40 X 1.5</t>
+          <t>RECTANGULAR 80 X 20 X 1.3</t>
         </is>
       </c>
       <c r="C458" s="2" t="inlineStr">
@@ -26333,19 +26333,19 @@
         </is>
       </c>
       <c r="D458" s="2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E458" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F458" s="2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G458" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H458" s="2" t="n">
-        <v>1.1097</v>
+        <v>0.6831</v>
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
@@ -26353,13 +26353,13 @@
         </is>
       </c>
       <c r="J458" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K458" s="2" t="n">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="L458" s="2" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="M458" s="2" t="n">
         <v>157</v>
@@ -26370,18 +26370,18 @@
         </is>
       </c>
       <c r="O458" s="2" t="n">
-        <v>7.55</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>NOR0032309</t>
+          <t>NOR0032308</t>
         </is>
       </c>
       <c r="B459" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 100 X 45 X 1.7</t>
+          <t>RECTANGULAR 100 X 40 X 1.5</t>
         </is>
       </c>
       <c r="C459" s="2" t="inlineStr">
@@ -26393,16 +26393,16 @@
         <v>100</v>
       </c>
       <c r="E459" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F459" s="2" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="G459" s="2" t="n">
         <v>6</v>
       </c>
       <c r="H459" s="2" t="n">
-        <v>1.528</v>
+        <v>1.1097</v>
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
@@ -26413,32 +26413,32 @@
         <v>0</v>
       </c>
       <c r="K459" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L459" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M459" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N459" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>13</v>
+      </c>
+      <c r="N459" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O459" s="2" t="n">
-        <v>10.39</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>NOR0032310</t>
+          <t>NOR0032308</t>
         </is>
       </c>
       <c r="B460" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 120 X 40 X 1.9</t>
+          <t>RECTANGULAR 100 X 40 X 1.5</t>
         </is>
       </c>
       <c r="C460" s="2" t="inlineStr">
@@ -26447,19 +26447,19 @@
         </is>
       </c>
       <c r="D460" s="2" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E460" s="2" t="n">
         <v>40</v>
       </c>
       <c r="F460" s="2" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="G460" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H460" s="2" t="n">
-        <v>1.604</v>
+        <v>1.1097</v>
       </c>
       <c r="I460" s="2" t="inlineStr">
         <is>
@@ -26467,16 +26467,16 @@
         </is>
       </c>
       <c r="J460" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K460" s="2" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="L460" s="2" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="M460" s="2" t="n">
-        <v>65</v>
+        <v>157</v>
       </c>
       <c r="N460" s="6" t="inlineStr">
         <is>
@@ -26484,18 +26484,18 @@
         </is>
       </c>
       <c r="O460" s="2" t="n">
-        <v>10.91</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>NOR0032311</t>
+          <t>NOR0032309</t>
         </is>
       </c>
       <c r="B461" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 60 X 40 X 1.3</t>
+          <t>RECTANGULAR 100 X 45 X 1.7</t>
         </is>
       </c>
       <c r="C461" s="2" t="inlineStr">
@@ -26504,19 +26504,19 @@
         </is>
       </c>
       <c r="D461" s="2" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E461" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F461" s="2" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="G461" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H461" s="2" t="n">
-        <v>0.6831</v>
+        <v>1.528</v>
       </c>
       <c r="I461" s="2" t="inlineStr">
         <is>
@@ -26524,35 +26524,35 @@
         </is>
       </c>
       <c r="J461" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K461" s="2" t="n">
-        <v>149</v>
+        <v>1</v>
       </c>
       <c r="L461" s="2" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M461" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="N461" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>1</v>
+      </c>
+      <c r="N461" s="5" t="inlineStr">
+        <is>
+          <t>Sin stock</t>
         </is>
       </c>
       <c r="O461" s="2" t="n">
-        <v>4.65</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>NOR0032312</t>
+          <t>NOR0032310</t>
         </is>
       </c>
       <c r="B462" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 80 X 40 X 1.5</t>
+          <t>RECTANGULAR 120 X 40 X 1.9</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -26561,19 +26561,19 @@
         </is>
       </c>
       <c r="D462" s="2" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="E462" s="2" t="n">
         <v>40</v>
       </c>
       <c r="F462" s="2" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="G462" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H462" s="2" t="n">
-        <v>0.948</v>
+        <v>1.604</v>
       </c>
       <c r="I462" s="2" t="inlineStr">
         <is>
@@ -26584,13 +26584,13 @@
         <v>0</v>
       </c>
       <c r="K462" s="2" t="n">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="L462" s="2" t="n">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="M462" s="2" t="n">
-        <v>275</v>
+        <v>65</v>
       </c>
       <c r="N462" s="6" t="inlineStr">
         <is>
@@ -26598,18 +26598,18 @@
         </is>
       </c>
       <c r="O462" s="2" t="n">
-        <v>6.45</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>NOR0032313</t>
+          <t>NOR0032311</t>
         </is>
       </c>
       <c r="B463" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 50 X 25 X 1.5</t>
+          <t>RECTANGULAR 60 X 40 X 1.3</t>
         </is>
       </c>
       <c r="C463" s="2" t="inlineStr">
@@ -26618,19 +26618,19 @@
         </is>
       </c>
       <c r="D463" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E463" s="2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F463" s="2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G463" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H463" s="2" t="n">
-        <v>0.583</v>
+        <v>0.6831</v>
       </c>
       <c r="I463" s="2" t="inlineStr">
         <is>
@@ -26638,35 +26638,35 @@
         </is>
       </c>
       <c r="J463" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K463" s="2" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="L463" s="2" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="M463" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="N463" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>205</v>
+      </c>
+      <c r="N463" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O463" s="2" t="n">
-        <v>3.96</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>NOR0032313</t>
+          <t>NOR0032312</t>
         </is>
       </c>
       <c r="B464" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 50 X 25 X 1.5</t>
+          <t>RECTANGULAR 80 X 40 X 1.5</t>
         </is>
       </c>
       <c r="C464" s="2" t="inlineStr">
@@ -26675,10 +26675,10 @@
         </is>
       </c>
       <c r="D464" s="2" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E464" s="2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F464" s="2" t="n">
         <v>1.5</v>
@@ -26687,7 +26687,7 @@
         <v>6.4</v>
       </c>
       <c r="H464" s="2" t="n">
-        <v>0.583</v>
+        <v>0.948</v>
       </c>
       <c r="I464" s="2" t="inlineStr">
         <is>
@@ -26695,35 +26695,35 @@
         </is>
       </c>
       <c r="J464" s="2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K464" s="2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="L464" s="2" t="n">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="M464" s="2" t="n">
-        <v>224</v>
-      </c>
-      <c r="N464" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>275</v>
+      </c>
+      <c r="N464" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O464" s="2" t="n">
-        <v>3.96</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>NOR0032314</t>
+          <t>NOR0032313</t>
         </is>
       </c>
       <c r="B465" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 60 X 10 X 1.3</t>
+          <t>RECTANGULAR 50 X 25 X 1.5</t>
         </is>
       </c>
       <c r="C465" s="2" t="inlineStr">
@@ -26732,19 +26732,19 @@
         </is>
       </c>
       <c r="D465" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E465" s="2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F465" s="2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G465" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H465" s="2" t="n">
-        <v>0.473</v>
+        <v>0.583</v>
       </c>
       <c r="I465" s="2" t="inlineStr">
         <is>
@@ -26752,35 +26752,35 @@
         </is>
       </c>
       <c r="J465" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K465" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L465" s="2" t="n">
-        <v>148</v>
+        <v>39</v>
       </c>
       <c r="M465" s="2" t="n">
-        <v>164</v>
-      </c>
-      <c r="N465" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>39</v>
+      </c>
+      <c r="N465" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O465" s="2" t="n">
-        <v>3.22</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>NOR0032315</t>
+          <t>NOR0032313</t>
         </is>
       </c>
       <c r="B466" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 100 X 20 X 1.5</t>
+          <t>RECTANGULAR 50 X 25 X 1.5</t>
         </is>
       </c>
       <c r="C466" s="2" t="inlineStr">
@@ -26789,10 +26789,10 @@
         </is>
       </c>
       <c r="D466" s="2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E466" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F466" s="2" t="n">
         <v>1.5</v>
@@ -26801,7 +26801,7 @@
         <v>6.4</v>
       </c>
       <c r="H466" s="2" t="n">
-        <v>0.95118</v>
+        <v>0.583</v>
       </c>
       <c r="I466" s="2" t="inlineStr">
         <is>
@@ -26809,16 +26809,16 @@
         </is>
       </c>
       <c r="J466" s="2" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K466" s="2" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="L466" s="2" t="n">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="M466" s="2" t="n">
-        <v>55</v>
+        <v>224</v>
       </c>
       <c r="N466" s="4" t="inlineStr">
         <is>
@@ -26826,18 +26826,18 @@
         </is>
       </c>
       <c r="O466" s="2" t="n">
-        <v>6.47</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>NOR0032316</t>
+          <t>NOR0032314</t>
         </is>
       </c>
       <c r="B467" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 120 X 20 X 1.5</t>
+          <t>RECTANGULAR 60 X 10 X 1.3</t>
         </is>
       </c>
       <c r="C467" s="2" t="inlineStr">
@@ -26846,19 +26846,19 @@
         </is>
       </c>
       <c r="D467" s="2" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E467" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F467" s="2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G467" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H467" s="2" t="n">
-        <v>1.114</v>
+        <v>0.473</v>
       </c>
       <c r="I467" s="2" t="inlineStr">
         <is>
@@ -26866,16 +26866,16 @@
         </is>
       </c>
       <c r="J467" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K467" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="L467" s="2" t="n">
         <v>148</v>
       </c>
-      <c r="L467" s="2" t="n">
-        <v>15</v>
-      </c>
       <c r="M467" s="2" t="n">
-        <v>182</v>
+        <v>483</v>
       </c>
       <c r="N467" s="4" t="inlineStr">
         <is>
@@ -26883,18 +26883,18 @@
         </is>
       </c>
       <c r="O467" s="2" t="n">
-        <v>7.58</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>NOR0032319</t>
+          <t>NOR0032315</t>
         </is>
       </c>
       <c r="B468" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 50 X 15 X 1.2</t>
+          <t>RECTANGULAR 100 X 20 X 1.5</t>
         </is>
       </c>
       <c r="C468" s="2" t="inlineStr">
@@ -26903,19 +26903,19 @@
         </is>
       </c>
       <c r="D468" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E468" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F468" s="2" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G468" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H468" s="2" t="n">
-        <v>0.406</v>
+        <v>0.95118</v>
       </c>
       <c r="I468" s="2" t="inlineStr">
         <is>
@@ -26923,35 +26923,35 @@
         </is>
       </c>
       <c r="J468" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K468" s="2" t="n">
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="L468" s="2" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="M468" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="N468" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>393</v>
+      </c>
+      <c r="N468" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O468" s="2" t="n">
-        <v>2.76</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>NOR0032320</t>
+          <t>NOR0032316</t>
         </is>
       </c>
       <c r="B469" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 120 X 40 X 1.5</t>
+          <t>RECTANGULAR 120 X 20 X 1.5</t>
         </is>
       </c>
       <c r="C469" s="2" t="inlineStr">
@@ -26963,16 +26963,16 @@
         <v>120</v>
       </c>
       <c r="E469" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F469" s="2" t="n">
         <v>1.5</v>
       </c>
       <c r="G469" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H469" s="2" t="n">
-        <v>1.272</v>
+        <v>1.114</v>
       </c>
       <c r="I469" s="2" t="inlineStr">
         <is>
@@ -26980,35 +26980,35 @@
         </is>
       </c>
       <c r="J469" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K469" s="2" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="L469" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M469" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N469" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>182</v>
+      </c>
+      <c r="N469" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O469" s="2" t="n">
-        <v>8.65</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>NOR0032320</t>
+          <t>NOR0032319</t>
         </is>
       </c>
       <c r="B470" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 120 X 40 X 1.5</t>
+          <t>RECTANGULAR 50 X 15 X 1.2</t>
         </is>
       </c>
       <c r="C470" s="2" t="inlineStr">
@@ -27017,19 +27017,19 @@
         </is>
       </c>
       <c r="D470" s="2" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E470" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F470" s="2" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G470" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H470" s="2" t="n">
-        <v>1.272</v>
+        <v>0.406</v>
       </c>
       <c r="I470" s="2" t="inlineStr">
         <is>
@@ -27037,35 +27037,35 @@
         </is>
       </c>
       <c r="J470" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K470" s="2" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="L470" s="2" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M470" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="N470" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>260</v>
+      </c>
+      <c r="N470" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O470" s="2" t="n">
-        <v>8.65</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>NOR0032321</t>
+          <t>NOR0032320</t>
         </is>
       </c>
       <c r="B471" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 150 X 20 X 1.5</t>
+          <t>RECTANGULAR 120 X 40 X 1.5</t>
         </is>
       </c>
       <c r="C471" s="2" t="inlineStr">
@@ -27074,19 +27074,19 @@
         </is>
       </c>
       <c r="D471" s="2" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E471" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F471" s="2" t="n">
         <v>1.5</v>
       </c>
       <c r="G471" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H471" s="2" t="n">
-        <v>1.353</v>
+        <v>1.272</v>
       </c>
       <c r="I471" s="2" t="inlineStr">
         <is>
@@ -27094,35 +27094,35 @@
         </is>
       </c>
       <c r="J471" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K471" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L471" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M471" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N471" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>20</v>
+      </c>
+      <c r="N471" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O471" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>NOR0032323</t>
+          <t>NOR0032320</t>
         </is>
       </c>
       <c r="B472" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 100 X 50 X 1.5</t>
+          <t>RECTANGULAR 120 X 40 X 1.5</t>
         </is>
       </c>
       <c r="C472" s="2" t="inlineStr">
@@ -27131,10 +27131,10 @@
         </is>
       </c>
       <c r="D472" s="2" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E472" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F472" s="2" t="n">
         <v>1.5</v>
@@ -27143,7 +27143,7 @@
         <v>6.4</v>
       </c>
       <c r="H472" s="2" t="n">
-        <v>1.195</v>
+        <v>1.272</v>
       </c>
       <c r="I472" s="2" t="inlineStr">
         <is>
@@ -27151,35 +27151,35 @@
         </is>
       </c>
       <c r="J472" s="2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K472" s="2" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L472" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M472" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="N472" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>28</v>
+      </c>
+      <c r="N472" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O472" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>NOR0032323</t>
+          <t>NOR0032321</t>
         </is>
       </c>
       <c r="B473" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 100 X 50 X 1.5</t>
+          <t>RECTANGULAR 150 X 20 X 1.5</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
@@ -27188,19 +27188,19 @@
         </is>
       </c>
       <c r="D473" s="2" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E473" s="2" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F473" s="2" t="n">
         <v>1.5</v>
       </c>
       <c r="G473" s="2" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="H473" s="2" t="n">
-        <v>1.195</v>
+        <v>1.353</v>
       </c>
       <c r="I473" s="2" t="inlineStr">
         <is>
@@ -27208,16 +27208,16 @@
         </is>
       </c>
       <c r="J473" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K473" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L473" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M473" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N473" s="5" t="inlineStr">
         <is>
@@ -27225,18 +27225,18 @@
         </is>
       </c>
       <c r="O473" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>NOR0032324</t>
+          <t>NOR0032323</t>
         </is>
       </c>
       <c r="B474" s="3" t="inlineStr">
         <is>
-          <t>RECTANGULAR 100 X 60 X 1.8</t>
+          <t>RECTANGULAR 100 X 50 X 1.5</t>
         </is>
       </c>
       <c r="C474" s="2" t="inlineStr">
@@ -27248,16 +27248,16 @@
         <v>100</v>
       </c>
       <c r="E474" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F474" s="2" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="G474" s="2" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H474" s="2" t="n">
-        <v>1.526</v>
+        <v>1.195</v>
       </c>
       <c r="I474" s="2" t="inlineStr">
         <is>
@@ -27268,13 +27268,13 @@
         <v>0</v>
       </c>
       <c r="K474" s="2" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L474" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M474" s="2" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N474" s="6" t="inlineStr">
         <is>
@@ -27282,39 +27282,39 @@
         </is>
       </c>
       <c r="O474" s="2" t="n">
-        <v>10.38</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>NOR0032401</t>
+          <t>NOR0032323</t>
         </is>
       </c>
       <c r="B475" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 16 X 1,2</t>
+          <t>RECTANGULAR 100 X 50 X 1.5</t>
         </is>
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>TUBO REDONDO</t>
+          <t>TUBO RECTANGULAR</t>
         </is>
       </c>
       <c r="D475" s="2" t="n">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="E475" s="2" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F475" s="2" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G475" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H475" s="2" t="n">
-        <v>0.162</v>
+        <v>1.195</v>
       </c>
       <c r="I475" s="2" t="inlineStr">
         <is>
@@ -27325,53 +27325,53 @@
         <v>0</v>
       </c>
       <c r="K475" s="2" t="n">
-        <v>793</v>
+        <v>0</v>
       </c>
       <c r="L475" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M475" s="2" t="n">
-        <v>793</v>
-      </c>
-      <c r="N475" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>4</v>
+      </c>
+      <c r="N475" s="5" t="inlineStr">
+        <is>
+          <t>Sin stock</t>
         </is>
       </c>
       <c r="O475" s="2" t="n">
-        <v>1.1</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>NOR0032401</t>
+          <t>NOR0032324</t>
         </is>
       </c>
       <c r="B476" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 16 X 1,2</t>
+          <t>RECTANGULAR 100 X 60 X 1.8</t>
         </is>
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>TUBO REDONDO</t>
+          <t>TUBO RECTANGULAR</t>
         </is>
       </c>
       <c r="D476" s="2" t="n">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="E476" s="2" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="F476" s="2" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="G476" s="2" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H476" s="2" t="n">
-        <v>0.162</v>
+        <v>1.526</v>
       </c>
       <c r="I476" s="2" t="inlineStr">
         <is>
@@ -27379,35 +27379,35 @@
         </is>
       </c>
       <c r="J476" s="2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K476" s="2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L476" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M476" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="N476" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>39</v>
+      </c>
+      <c r="N476" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O476" s="2" t="n">
-        <v>1.1</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>NOR0032403</t>
+          <t>NOR0032401</t>
         </is>
       </c>
       <c r="B477" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 20 X 1.2</t>
+          <t>TUBO REDONDO 16 X 1,2</t>
         </is>
       </c>
       <c r="C477" s="2" t="inlineStr">
@@ -27416,10 +27416,10 @@
         </is>
       </c>
       <c r="D477" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E477" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F477" s="2" t="n">
         <v>1.2</v>
@@ -27428,7 +27428,7 @@
         <v>6</v>
       </c>
       <c r="H477" s="2" t="n">
-        <v>0.1915</v>
+        <v>0.162</v>
       </c>
       <c r="I477" s="2" t="inlineStr">
         <is>
@@ -27439,13 +27439,13 @@
         <v>0</v>
       </c>
       <c r="K477" s="2" t="n">
-        <v>0</v>
+        <v>793</v>
       </c>
       <c r="L477" s="2" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="M477" s="2" t="n">
-        <v>238</v>
+        <v>793</v>
       </c>
       <c r="N477" s="6" t="inlineStr">
         <is>
@@ -27453,18 +27453,18 @@
         </is>
       </c>
       <c r="O477" s="2" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>NOR0032403</t>
+          <t>NOR0032401</t>
         </is>
       </c>
       <c r="B478" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 20 X 1.2</t>
+          <t>TUBO REDONDO 16 X 1,2</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr">
@@ -27473,10 +27473,10 @@
         </is>
       </c>
       <c r="D478" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E478" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F478" s="2" t="n">
         <v>1.2</v>
@@ -27485,7 +27485,7 @@
         <v>6.4</v>
       </c>
       <c r="H478" s="2" t="n">
-        <v>0.1915</v>
+        <v>0.162</v>
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
@@ -27493,16 +27493,16 @@
         </is>
       </c>
       <c r="J478" s="2" t="n">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="K478" s="2" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L478" s="2" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="M478" s="2" t="n">
-        <v>484</v>
+        <v>29</v>
       </c>
       <c r="N478" s="4" t="inlineStr">
         <is>
@@ -27510,18 +27510,18 @@
         </is>
       </c>
       <c r="O478" s="2" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>NOR0032405</t>
+          <t>NOR0032403</t>
         </is>
       </c>
       <c r="B479" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 30 X 1,2</t>
+          <t>TUBO REDONDO 20 X 1.2</t>
         </is>
       </c>
       <c r="C479" s="2" t="inlineStr">
@@ -27530,19 +27530,19 @@
         </is>
       </c>
       <c r="D479" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E479" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F479" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="G479" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H479" s="2" t="n">
-        <v>0.2945</v>
+        <v>0.1915</v>
       </c>
       <c r="I479" s="2" t="inlineStr">
         <is>
@@ -27553,13 +27553,13 @@
         <v>0</v>
       </c>
       <c r="K479" s="2" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="L479" s="2" t="n">
-        <v>23</v>
+        <v>238</v>
       </c>
       <c r="M479" s="2" t="n">
-        <v>143</v>
+        <v>238</v>
       </c>
       <c r="N479" s="6" t="inlineStr">
         <is>
@@ -27567,18 +27567,18 @@
         </is>
       </c>
       <c r="O479" s="2" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>NOR0032406</t>
+          <t>NOR0032403</t>
         </is>
       </c>
       <c r="B480" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 40 X 1,3</t>
+          <t>TUBO REDONDO 20 X 1.2</t>
         </is>
       </c>
       <c r="C480" s="2" t="inlineStr">
@@ -27587,19 +27587,19 @@
         </is>
       </c>
       <c r="D480" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E480" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F480" s="2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G480" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H480" s="2" t="n">
-        <v>0.427</v>
+        <v>0.1915</v>
       </c>
       <c r="I480" s="2" t="inlineStr">
         <is>
@@ -27607,35 +27607,35 @@
         </is>
       </c>
       <c r="J480" s="2" t="n">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="K480" s="2" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L480" s="2" t="n">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="M480" s="2" t="n">
-        <v>53</v>
-      </c>
-      <c r="N480" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>484</v>
+      </c>
+      <c r="N480" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O480" s="2" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>NOR0032407</t>
+          <t>NOR0032405</t>
         </is>
       </c>
       <c r="B481" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 50 X 1,5</t>
+          <t>TUBO REDONDO 30 X 1,2</t>
         </is>
       </c>
       <c r="C481" s="2" t="inlineStr">
@@ -27644,19 +27644,19 @@
         </is>
       </c>
       <c r="D481" s="2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E481" s="2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F481" s="2" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G481" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H481" s="2" t="n">
-        <v>0.6185</v>
+        <v>0.2945</v>
       </c>
       <c r="I481" s="2" t="inlineStr">
         <is>
@@ -27664,16 +27664,16 @@
         </is>
       </c>
       <c r="J481" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K481" s="2" t="n">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="L481" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M481" s="2" t="n">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="N481" s="6" t="inlineStr">
         <is>
@@ -27681,18 +27681,18 @@
         </is>
       </c>
       <c r="O481" s="2" t="n">
-        <v>4.21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>NOR0032408</t>
+          <t>NOR0032406</t>
         </is>
       </c>
       <c r="B482" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 60 X 1,4</t>
+          <t>TUBO REDONDO 40 X 1,3</t>
         </is>
       </c>
       <c r="C482" s="2" t="inlineStr">
@@ -27701,19 +27701,19 @@
         </is>
       </c>
       <c r="D482" s="2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E482" s="2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F482" s="2" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G482" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H482" s="2" t="n">
-        <v>0.6966</v>
+        <v>0.427</v>
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
@@ -27721,35 +27721,35 @@
         </is>
       </c>
       <c r="J482" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K482" s="2" t="n">
-        <v>1</v>
+        <v>195</v>
       </c>
       <c r="L482" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M482" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N482" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>248</v>
+      </c>
+      <c r="N482" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O482" s="2" t="n">
-        <v>4.74</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>NOR0032408</t>
+          <t>NOR0032407</t>
         </is>
       </c>
       <c r="B483" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 60 X 1,4</t>
+          <t>TUBO REDONDO 50 X 1,5</t>
         </is>
       </c>
       <c r="C483" s="2" t="inlineStr">
@@ -27758,19 +27758,19 @@
         </is>
       </c>
       <c r="D483" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E483" s="2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F483" s="2" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G483" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H483" s="2" t="n">
-        <v>0.6966</v>
+        <v>0.6185</v>
       </c>
       <c r="I483" s="2" t="inlineStr">
         <is>
@@ -27778,16 +27778,16 @@
         </is>
       </c>
       <c r="J483" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K483" s="2" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="L483" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M483" s="2" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="N483" s="6" t="inlineStr">
         <is>
@@ -27795,18 +27795,18 @@
         </is>
       </c>
       <c r="O483" s="2" t="n">
-        <v>4.74</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>NOR0032409</t>
+          <t>NOR0032408</t>
         </is>
       </c>
       <c r="B484" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 80 X 1.6</t>
+          <t>TUBO REDONDO 60 X 1,4</t>
         </is>
       </c>
       <c r="C484" s="2" t="inlineStr">
@@ -27815,19 +27815,19 @@
         </is>
       </c>
       <c r="D484" s="2" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E484" s="2" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F484" s="2" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G484" s="2" t="n">
         <v>6</v>
       </c>
       <c r="H484" s="2" t="n">
-        <v>1.065</v>
+        <v>0.6966</v>
       </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
@@ -27838,13 +27838,13 @@
         <v>0</v>
       </c>
       <c r="K484" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L484" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M484" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N484" s="5" t="inlineStr">
         <is>
@@ -27852,18 +27852,18 @@
         </is>
       </c>
       <c r="O484" s="2" t="n">
-        <v>7.24</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>NOR0032409</t>
+          <t>NOR0032408</t>
         </is>
       </c>
       <c r="B485" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 80 X 1.6</t>
+          <t>TUBO REDONDO 60 X 1,4</t>
         </is>
       </c>
       <c r="C485" s="2" t="inlineStr">
@@ -27872,19 +27872,19 @@
         </is>
       </c>
       <c r="D485" s="2" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E485" s="2" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F485" s="2" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G485" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="H485" s="2" t="n">
-        <v>1.065</v>
+        <v>0.6966</v>
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
@@ -27892,16 +27892,16 @@
         </is>
       </c>
       <c r="J485" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K485" s="2" t="n">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="L485" s="2" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="M485" s="2" t="n">
-        <v>136</v>
+        <v>66</v>
       </c>
       <c r="N485" s="6" t="inlineStr">
         <is>
@@ -27909,18 +27909,18 @@
         </is>
       </c>
       <c r="O485" s="2" t="n">
-        <v>7.24</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>NOR0032410</t>
+          <t>NOR0032409</t>
         </is>
       </c>
       <c r="B486" s="3" t="inlineStr">
         <is>
-          <t>TUBO REDONDO 70 X 1,5</t>
+          <t>TUBO REDONDO 80 X 1.6</t>
         </is>
       </c>
       <c r="C486" s="2" t="inlineStr">
@@ -27929,19 +27929,19 @@
         </is>
       </c>
       <c r="D486" s="2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E486" s="2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F486" s="2" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G486" s="2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H486" s="2" t="n">
-        <v>0.8721</v>
+        <v>1.065</v>
       </c>
       <c r="I486" s="2" t="inlineStr">
         <is>
@@ -27949,85 +27949,256 @@
         </is>
       </c>
       <c r="J486" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K486" s="2" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="L486" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M486" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="N486" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>3</v>
+      </c>
+      <c r="N486" s="5" t="inlineStr">
+        <is>
+          <t>Sin stock</t>
         </is>
       </c>
       <c r="O486" s="2" t="n">
-        <v>5.93</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
+          <t>NOR0032409</t>
+        </is>
+      </c>
+      <c r="B487" s="3" t="inlineStr">
+        <is>
+          <t>TUBO REDONDO 80 X 1.6</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>TUBO REDONDO</t>
+        </is>
+      </c>
+      <c r="D487" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E487" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F487" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G487" s="2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H487" s="2" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="I487" s="2" t="inlineStr">
+        <is>
+          <t>BRUTO</t>
+        </is>
+      </c>
+      <c r="J487" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K487" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="L487" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="M487" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="N487" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
+        </is>
+      </c>
+      <c r="O487" s="2" t="n">
+        <v>7.24</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>NOR0032410</t>
+        </is>
+      </c>
+      <c r="B488" s="3" t="inlineStr">
+        <is>
+          <t>TUBO REDONDO 70 X 1,5</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>TUBO REDONDO</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="E488" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F488" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G488" s="2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H488" s="2" t="n">
+        <v>0.8721</v>
+      </c>
+      <c r="I488" s="2" t="inlineStr">
+        <is>
+          <t>BRUTO</t>
+        </is>
+      </c>
+      <c r="J488" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K488" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L488" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="M488" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="N488" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
+        </is>
+      </c>
+      <c r="O488" s="2" t="n">
+        <v>5.93</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
           <t>NOR0032414</t>
         </is>
       </c>
-      <c r="B487" s="3" t="inlineStr">
+      <c r="B489" s="3" t="inlineStr">
         <is>
           <t>T - 30 X 30 X 1.5</t>
         </is>
       </c>
-      <c r="C487" s="2" t="inlineStr">
+      <c r="C489" s="2" t="inlineStr">
         <is>
           <t>PERFIL T</t>
         </is>
       </c>
-      <c r="D487" s="2" t="n">
+      <c r="D489" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="E487" s="2" t="n">
+      <c r="E489" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F487" s="2" t="n">
+      <c r="F489" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="G487" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H487" s="2" t="n">
+      <c r="G489" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H489" s="2" t="n">
         <v>0.237</v>
       </c>
-      <c r="I487" s="2" t="inlineStr">
-        <is>
-          <t>BRUTO</t>
-        </is>
-      </c>
-      <c r="J487" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K487" s="2" t="n">
+      <c r="I489" s="2" t="inlineStr">
+        <is>
+          <t>BRUTO</t>
+        </is>
+      </c>
+      <c r="J489" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K489" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="L487" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M487" s="2" t="n">
+      <c r="L489" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M489" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="N487" s="6" t="inlineStr">
+      <c r="N489" s="6" t="inlineStr">
         <is>
           <t>7/10 Días</t>
         </is>
       </c>
-      <c r="O487" s="2" t="n">
+      <c r="O489" s="2" t="n">
         <v>1.61</v>
       </c>
     </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>NOR0032414</t>
+        </is>
+      </c>
+      <c r="B490" s="3" t="inlineStr">
+        <is>
+          <t>T - 30 X 30 X 1.5</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>PERFIL T</t>
+        </is>
+      </c>
+      <c r="D490" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E490" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F490" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G490" s="2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H490" s="2" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="I490" s="2" t="inlineStr">
+        <is>
+          <t>BRUTO</t>
+        </is>
+      </c>
+      <c r="J490" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K490" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="L490" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M490" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="N490" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
+        </is>
+      </c>
+      <c r="O490" s="2" t="n">
+        <v>1.61</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O487"/>
+  <autoFilter ref="A1:O490"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/inventario_expandido.xlsx
+++ b/inventario_expandido.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>€/m (6.8€/kg)</t>
+          <t>€/m (6.85€/kg)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>11.5</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="5">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="6">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>4.13</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="7">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>7.37</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="8">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>11.47</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="9">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>16.52</v>
+        <v>16.64</v>
       </c>
     </row>
     <row r="10">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>29.48</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="11">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="12">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>46.07</v>
+        <v>46.41</v>
       </c>
     </row>
     <row r="13">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>37.16</v>
+        <v>37.44</v>
       </c>
     </row>
     <row r="14">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>22.49</v>
+        <v>22.66</v>
       </c>
     </row>
     <row r="15">
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="16">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="17">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="18">
@@ -1497,10 +1497,10 @@
         <v>173</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
@@ -1550,10 +1550,10 @@
         <v>128</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="20">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>5.77</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="21">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>9.01</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="22">
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>12.98</v>
+        <v>13.08</v>
       </c>
     </row>
     <row r="23">
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>17.67</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="24">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>23.07</v>
+        <v>23.24</v>
       </c>
     </row>
     <row r="25">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>36.06</v>
+        <v>36.33</v>
       </c>
     </row>
     <row r="26">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>51.92</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="27">
@@ -1971,13 +1971,13 @@
         <v>320</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>324</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="O27" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="28">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>6.98</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="29">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="30">
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="31">
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="O31" s="2" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="32">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="33">
@@ -2294,16 +2294,16 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>183</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>794</v>
+        <v>776</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="O33" s="2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="34">
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="O34" s="2" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="35">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="O35" s="2" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="36">
@@ -2465,10 +2465,10 @@
         <v>251</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="O36" s="2" t="n">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="37">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="O37" s="2" t="n">
-        <v>5.53</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="38">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="O38" s="2" t="n">
-        <v>11.02</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="39">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="O39" s="2" t="n">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="40">
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="O40" s="2" t="n">
-        <v>5.89</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="41">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="O41" s="2" t="n">
-        <v>7.37</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="42">
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="O42" s="2" t="n">
-        <v>11.02</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="43">
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>203</v>
@@ -2853,7 +2853,7 @@
         <v>42</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="O43" s="2" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="44">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="O44" s="2" t="n">
-        <v>4.59</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="45">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="O45" s="2" t="n">
-        <v>4.59</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="46">
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="O46" s="2" t="n">
-        <v>4.59</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="47">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="O47" s="2" t="n">
-        <v>7.34</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="48">
@@ -3122,13 +3122,13 @@
         <v>21</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>70</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="O48" s="2" t="n">
-        <v>9.210000000000001</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="O49" s="2" t="n">
-        <v>13.77</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="50">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>18.37</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="51">
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="O51" s="2" t="n">
-        <v>11.02</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="52">
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>13.22</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="53">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>16.52</v>
+        <v>16.64</v>
       </c>
     </row>
     <row r="54">
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="O54" s="2" t="n">
-        <v>22.03</v>
+        <v>22.19</v>
       </c>
     </row>
     <row r="55">
@@ -3507,13 +3507,13 @@
         <v>35</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>12.85</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="56">
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="O56" s="2" t="n">
-        <v>11.78</v>
+        <v>11.87</v>
       </c>
     </row>
     <row r="57">
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="O57" s="2" t="n">
-        <v>11.78</v>
+        <v>11.87</v>
       </c>
     </row>
     <row r="58">
@@ -3675,10 +3675,10 @@
         <v>24</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="O58" s="2" t="n">
-        <v>14.74</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="59">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="O59" s="2" t="n">
-        <v>22.11</v>
+        <v>22.28</v>
       </c>
     </row>
     <row r="60">
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="O60" s="2" t="n">
-        <v>29.38</v>
+        <v>29.59</v>
       </c>
     </row>
     <row r="61">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="O61" s="2" t="n">
-        <v>14.69</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="62">
@@ -3895,10 +3895,10 @@
         <v>65</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="O62" s="2" t="n">
-        <v>18.42</v>
+        <v>18.56</v>
       </c>
     </row>
     <row r="63">
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="O63" s="2" t="n">
-        <v>21.61</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="64">
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="O64" s="2" t="n">
-        <v>21.99</v>
+        <v>22.15</v>
       </c>
     </row>
     <row r="65">
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="O65" s="2" t="n">
-        <v>26.44</v>
+        <v>26.63</v>
       </c>
     </row>
     <row r="66">
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="O66" s="2" t="n">
-        <v>35.8</v>
+        <v>36.07</v>
       </c>
     </row>
     <row r="67">
@@ -4167,13 +4167,13 @@
         <v>18</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>30</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="O67" s="2" t="n">
-        <v>27.53</v>
+        <v>27.73</v>
       </c>
     </row>
     <row r="68">
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="O68" s="2" t="n">
-        <v>9.18</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="69">
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="O69" s="2" t="n">
-        <v>20.65</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="70">
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="O70" s="2" t="n">
-        <v>36.72</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="71">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="O71" s="2" t="n">
-        <v>14.69</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="72">
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="O72" s="2" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="73">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="O73" s="2" t="n">
-        <v>5.51</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="74">
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="O74" s="2" t="n">
-        <v>8.26</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="75">
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4613,7 +4613,7 @@
         <v>267</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="O75" s="2" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="76">
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="O76" s="2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="77">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="O77" s="2" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="78">
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="O78" s="2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="79">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="O79" s="2" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="80">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="O80" s="2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="81">
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="O81" s="2" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="82">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="O82" s="2" t="n">
-        <v>36.72</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="83">
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="O83" s="2" t="n">
-        <v>33.05</v>
+        <v>33.29</v>
       </c>
     </row>
     <row r="84">
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="O84" s="2" t="n">
-        <v>44.06</v>
+        <v>44.39</v>
       </c>
     </row>
     <row r="85">
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="O85" s="2" t="n">
-        <v>55.08</v>
+        <v>55.48</v>
       </c>
     </row>
     <row r="86">
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="O86" s="2" t="n">
-        <v>27.02</v>
+        <v>27.22</v>
       </c>
     </row>
     <row r="87">
@@ -5267,13 +5267,13 @@
         <v>49</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>50</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="O87" s="2" t="n">
-        <v>8.81</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -5336,7 +5336,7 @@
         </is>
       </c>
       <c r="O88" s="2" t="n">
-        <v>41.31</v>
+        <v>41.61</v>
       </c>
     </row>
     <row r="89">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="O89" s="2" t="n">
-        <v>25.7</v>
+        <v>25.89</v>
       </c>
     </row>
     <row r="90">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="O90" s="2" t="n">
-        <v>7.34</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="91">
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="O91" s="2" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="92">
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="O92" s="2" t="n">
-        <v>5.51</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="93">
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="O93" s="2" t="n">
-        <v>5.51</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="94">
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="O94" s="2" t="n">
-        <v>21.88</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="95">
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="O95" s="2" t="n">
-        <v>21.88</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="96">
@@ -5776,7 +5776,7 @@
         </is>
       </c>
       <c r="O96" s="2" t="n">
-        <v>5.51</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="97">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="O97" s="2" t="n">
-        <v>8.26</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="98">
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="O98" s="2" t="n">
-        <v>6.43</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="99">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="O99" s="2" t="n">
-        <v>4.96</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="100">
@@ -5996,7 +5996,7 @@
         </is>
       </c>
       <c r="O100" s="2" t="n">
-        <v>4.96</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="101">
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="O101" s="2" t="n">
-        <v>4.96</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="102">
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="O102" s="2" t="n">
-        <v>8.26</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="103">
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="O103" s="2" t="n">
-        <v>16.52</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="104">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="O104" s="2" t="n">
-        <v>17.63</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="105">
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="O105" s="2" t="n">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="106">
@@ -6326,7 +6326,7 @@
         </is>
       </c>
       <c r="O106" s="2" t="n">
-        <v>13.22</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="107">
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="O107" s="2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="108">
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="O108" s="2" t="n">
-        <v>4.59</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="109">
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="O109" s="2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="110">
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="O110" s="2" t="n">
-        <v>29.38</v>
+        <v>29.59</v>
       </c>
     </row>
     <row r="111">
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="O111" s="2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="112">
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="O112" s="2" t="n">
-        <v>13.77</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="113">
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="O113" s="2" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="114">
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="O114" s="2" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="115">
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="O115" s="2" t="n">
-        <v>11.28</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="116">
@@ -6884,7 +6884,7 @@
         </is>
       </c>
       <c r="O116" s="2" t="n">
-        <v>10.09</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="117">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="O117" s="2" t="n">
-        <v>16.48</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="118">
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="O118" s="2" t="n">
-        <v>26.34</v>
+        <v>26.53</v>
       </c>
     </row>
     <row r="119">
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="O119" s="2" t="n">
-        <v>61.03</v>
+        <v>61.48</v>
       </c>
     </row>
     <row r="120">
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="O120" s="2" t="n">
-        <v>5.2</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="121">
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="O121" s="2" t="n">
-        <v>7.41</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="122">
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="O122" s="2" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="123">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="O123" s="2" t="n">
-        <v>23.57</v>
+        <v>23.74</v>
       </c>
     </row>
     <row r="124">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="O124" s="2" t="n">
-        <v>8.34</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="125">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="O125" s="2" t="n">
-        <v>8.5</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="126">
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="O126" s="2" t="n">
-        <v>8.5</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="127">
@@ -7497,13 +7497,13 @@
         <v>64</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>82</v>
       </c>
       <c r="M127" s="2" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N127" s="4" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="O127" s="2" t="n">
-        <v>8.23</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="128">
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="O128" s="2" t="n">
-        <v>6.26</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="129">
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="O129" s="2" t="n">
-        <v>16.3</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="130">
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="O130" s="2" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="131">
@@ -7739,7 +7739,7 @@
         </is>
       </c>
       <c r="O131" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="132">
@@ -7796,7 +7796,7 @@
         </is>
       </c>
       <c r="O132" s="2" t="n">
-        <v>10.42</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="133">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="O133" s="2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="134">
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="O134" s="2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="135">
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="O135" s="2" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="136">
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="O136" s="2" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="137">
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="O137" s="2" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="138">
@@ -8124,13 +8124,13 @@
         <v>55</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="L138" s="2" t="n">
         <v>37</v>
       </c>
       <c r="M138" s="2" t="n">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="N138" s="4" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="O138" s="2" t="n">
-        <v>5.6</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="139">
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="O139" s="2" t="n">
-        <v>8.720000000000001</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="140">
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K140" s="2" t="n">
         <v>131</v>
@@ -8244,15 +8244,15 @@
         <v>2</v>
       </c>
       <c r="M140" s="2" t="n">
-        <v>161</v>
-      </c>
-      <c r="N140" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>133</v>
+      </c>
+      <c r="N140" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O140" s="2" t="n">
-        <v>8.720000000000001</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="141">
@@ -8295,13 +8295,13 @@
         <v>124</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L141" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M141" s="2" t="n">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="N141" s="4" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="O141" s="2" t="n">
-        <v>12.56</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="142">
@@ -8349,7 +8349,7 @@
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K142" s="2" t="n">
         <v>34</v>
@@ -8358,7 +8358,7 @@
         <v>45</v>
       </c>
       <c r="M142" s="2" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="N142" s="4" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="O142" s="2" t="n">
-        <v>14.76</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="143">
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="O143" s="2" t="n">
-        <v>22.32</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="144">
@@ -8480,7 +8480,7 @@
         </is>
       </c>
       <c r="O144" s="2" t="n">
-        <v>34.88</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="145">
@@ -8523,13 +8523,13 @@
         <v>343</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L145" s="2" t="n">
         <v>248</v>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="O145" s="2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="146">
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c r="O146" s="2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="147">
@@ -8651,7 +8651,7 @@
         </is>
       </c>
       <c r="O147" s="2" t="n">
-        <v>4.79</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="148">
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="O148" s="2" t="n">
-        <v>5.34</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="149">
@@ -8751,13 +8751,13 @@
         <v>84</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L149" s="2" t="n">
         <v>80</v>
       </c>
       <c r="M149" s="2" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N149" s="4" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="O149" s="2" t="n">
-        <v>8.52</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="150">
@@ -8822,7 +8822,7 @@
         </is>
       </c>
       <c r="O150" s="2" t="n">
-        <v>5.96</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="151">
@@ -8879,7 +8879,7 @@
         </is>
       </c>
       <c r="O151" s="2" t="n">
-        <v>42.36</v>
+        <v>42.68</v>
       </c>
     </row>
     <row r="152">
@@ -8936,7 +8936,7 @@
         </is>
       </c>
       <c r="O152" s="2" t="n">
-        <v>42.36</v>
+        <v>42.68</v>
       </c>
     </row>
     <row r="153">
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="O153" s="2" t="n">
-        <v>11.46</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="154">
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="O154" s="2" t="n">
-        <v>21.37</v>
+        <v>21.53</v>
       </c>
     </row>
     <row r="155">
@@ -9107,7 +9107,7 @@
         </is>
       </c>
       <c r="O155" s="2" t="n">
-        <v>10.85</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="156">
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="O156" s="2" t="n">
-        <v>6.88</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="157">
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="O157" s="2" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="158">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="O158" s="2" t="n">
-        <v>10.72</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="159">
@@ -9321,13 +9321,13 @@
         <v>162</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="L159" s="2" t="n">
         <v>166</v>
       </c>
       <c r="M159" s="2" t="n">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="N159" s="4" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         </is>
       </c>
       <c r="O159" s="2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="160">
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="O160" s="2" t="n">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="161">
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="O161" s="2" t="n">
-        <v>10.98</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="162">
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="O162" s="2" t="n">
-        <v>10.98</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="163">
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="O163" s="2" t="n">
-        <v>4.72</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="164">
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="O164" s="2" t="n">
-        <v>40.2</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="165">
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="O165" s="2" t="n">
-        <v>44.21</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="166">
@@ -9720,10 +9720,10 @@
         <v>112</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="L166" s="2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="M166" s="2" t="n">
         <v>860</v>
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="O166" s="2" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="167">
@@ -9780,10 +9780,10 @@
         <v>149</v>
       </c>
       <c r="L167" s="2" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M167" s="2" t="n">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="N167" s="4" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="O167" s="2" t="n">
-        <v>7.07</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="168">
@@ -9848,7 +9848,7 @@
         </is>
       </c>
       <c r="O168" s="2" t="n">
-        <v>8.51</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="169">
@@ -9905,7 +9905,7 @@
         </is>
       </c>
       <c r="O169" s="2" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="170">
@@ -9962,7 +9962,7 @@
         </is>
       </c>
       <c r="O170" s="2" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="171">
@@ -10008,10 +10008,10 @@
         <v>78</v>
       </c>
       <c r="L171" s="2" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="M171" s="2" t="n">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="N171" s="4" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         </is>
       </c>
       <c r="O171" s="2" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="172">
@@ -10076,7 +10076,7 @@
         </is>
       </c>
       <c r="O172" s="2" t="n">
-        <v>15.86</v>
+        <v>15.98</v>
       </c>
     </row>
     <row r="173">
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="O173" s="2" t="n">
-        <v>13.31</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="174">
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="O174" s="2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="175">
@@ -10247,7 +10247,7 @@
         </is>
       </c>
       <c r="O175" s="2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="176">
@@ -10293,10 +10293,10 @@
         <v>52</v>
       </c>
       <c r="L176" s="2" t="n">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="M176" s="2" t="n">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="N176" s="6" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         </is>
       </c>
       <c r="O176" s="2" t="n">
-        <v>5.07</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="177">
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="O177" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="178">
@@ -10407,10 +10407,10 @@
         <v>0</v>
       </c>
       <c r="L178" s="2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M178" s="2" t="n">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N178" s="4" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         </is>
       </c>
       <c r="O178" s="2" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="179">
@@ -10475,7 +10475,7 @@
         </is>
       </c>
       <c r="O179" s="2" t="n">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="180">
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="O180" s="2" t="n">
-        <v>6.41</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="181">
@@ -10589,7 +10589,7 @@
         </is>
       </c>
       <c r="O181" s="2" t="n">
-        <v>4.26</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="182">
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="O182" s="2" t="n">
-        <v>4.26</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="183">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="O183" s="2" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="184">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="O184" s="2" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="185">
@@ -10803,13 +10803,13 @@
         <v>0</v>
       </c>
       <c r="K185" s="2" t="n">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="L185" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M185" s="2" t="n">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="N185" s="6" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="O185" s="2" t="n">
-        <v>5.68</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="186">
@@ -10874,7 +10874,7 @@
         </is>
       </c>
       <c r="O186" s="2" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="187">
@@ -10931,7 +10931,7 @@
         </is>
       </c>
       <c r="O187" s="2" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="188">
@@ -10988,7 +10988,7 @@
         </is>
       </c>
       <c r="O188" s="2" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="189">
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="O189" s="2" t="n">
-        <v>10.3</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="190">
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="O190" s="2" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="191">
@@ -11159,7 +11159,7 @@
         </is>
       </c>
       <c r="O191" s="2" t="n">
-        <v>6.35</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="192">
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="O192" s="2" t="n">
-        <v>5.6</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="193">
@@ -11273,7 +11273,7 @@
         </is>
       </c>
       <c r="O193" s="2" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="194">
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="O194" s="2" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="195">
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="O195" s="2" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="196">
@@ -11444,7 +11444,7 @@
         </is>
       </c>
       <c r="O196" s="2" t="n">
-        <v>8.720000000000001</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="197">
@@ -11501,7 +11501,7 @@
         </is>
       </c>
       <c r="O197" s="2" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="198">
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="O198" s="2" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="199">
@@ -11615,7 +11615,7 @@
         </is>
       </c>
       <c r="O199" s="2" t="n">
-        <v>8.4</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="200">
@@ -11655,16 +11655,16 @@
         </is>
       </c>
       <c r="J200" s="2" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K200" s="2" t="n">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="L200" s="2" t="n">
         <v>300</v>
       </c>
       <c r="M200" s="2" t="n">
-        <v>767</v>
+        <v>749</v>
       </c>
       <c r="N200" s="4" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="O200" s="2" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="201">
@@ -11718,10 +11718,10 @@
         <v>84</v>
       </c>
       <c r="L201" s="2" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="M201" s="2" t="n">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="N201" s="4" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="O201" s="2" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="202">
@@ -11786,7 +11786,7 @@
         </is>
       </c>
       <c r="O202" s="2" t="n">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="203">
@@ -11843,7 +11843,7 @@
         </is>
       </c>
       <c r="O203" s="2" t="n">
-        <v>5.52</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="204">
@@ -11900,7 +11900,7 @@
         </is>
       </c>
       <c r="O204" s="2" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="205">
@@ -11957,7 +11957,7 @@
         </is>
       </c>
       <c r="O205" s="2" t="n">
-        <v>7.21</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="206">
@@ -12014,7 +12014,7 @@
         </is>
       </c>
       <c r="O206" s="2" t="n">
-        <v>4.68</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="207">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="O207" s="2" t="n">
-        <v>5.43</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="208">
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="O208" s="2" t="n">
-        <v>10.09</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="209">
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="O209" s="2" t="n">
-        <v>10.09</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="210">
@@ -12242,7 +12242,7 @@
         </is>
       </c>
       <c r="O210" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="211">
@@ -12299,7 +12299,7 @@
         </is>
       </c>
       <c r="O211" s="2" t="n">
-        <v>12.98</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="212">
@@ -12356,7 +12356,7 @@
         </is>
       </c>
       <c r="O212" s="2" t="n">
-        <v>12.98</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="213">
@@ -12402,10 +12402,10 @@
         <v>29</v>
       </c>
       <c r="L213" s="2" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="M213" s="2" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="N213" s="6" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="O213" s="2" t="n">
-        <v>12.97</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="214">
@@ -12470,7 +12470,7 @@
         </is>
       </c>
       <c r="O214" s="2" t="n">
-        <v>15.86</v>
+        <v>15.97</v>
       </c>
     </row>
     <row r="215">
@@ -12527,7 +12527,7 @@
         </is>
       </c>
       <c r="O215" s="2" t="n">
-        <v>21.71</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="216">
@@ -12584,7 +12584,7 @@
         </is>
       </c>
       <c r="O216" s="2" t="n">
-        <v>51.91</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="217">
@@ -12627,21 +12627,21 @@
         <v>4</v>
       </c>
       <c r="K217" s="2" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="L217" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M217" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="N217" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>35</v>
+      </c>
+      <c r="N217" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O217" s="2" t="n">
-        <v>51.91</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="218">
@@ -12698,7 +12698,7 @@
         </is>
       </c>
       <c r="O218" s="2" t="n">
-        <v>26.32</v>
+        <v>26.51</v>
       </c>
     </row>
     <row r="219">
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="O219" s="2" t="n">
-        <v>18.51</v>
+        <v>18.65</v>
       </c>
     </row>
     <row r="220">
@@ -12812,7 +12812,7 @@
         </is>
       </c>
       <c r="O220" s="2" t="n">
-        <v>27.39</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="221">
@@ -12869,7 +12869,7 @@
         </is>
       </c>
       <c r="O221" s="2" t="n">
-        <v>27.39</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="222">
@@ -12926,7 +12926,7 @@
         </is>
       </c>
       <c r="O222" s="2" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="223">
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="O223" s="2" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="224">
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="O224" s="2" t="n">
-        <v>6.13</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="225">
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="O225" s="2" t="n">
-        <v>13.37</v>
+        <v>13.47</v>
       </c>
     </row>
     <row r="226">
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="O226" s="2" t="n">
-        <v>24.51</v>
+        <v>24.69</v>
       </c>
     </row>
     <row r="227">
@@ -13211,7 +13211,7 @@
         </is>
       </c>
       <c r="O227" s="2" t="n">
-        <v>67.14</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="228">
@@ -13268,7 +13268,7 @@
         </is>
       </c>
       <c r="O228" s="2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="229">
@@ -13311,13 +13311,13 @@
         <v>16</v>
       </c>
       <c r="K229" s="2" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L229" s="2" t="n">
         <v>30</v>
       </c>
       <c r="M229" s="2" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N229" s="4" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         </is>
       </c>
       <c r="O229" s="2" t="n">
-        <v>6.69</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="230">
@@ -13382,7 +13382,7 @@
         </is>
       </c>
       <c r="O230" s="2" t="n">
-        <v>23.87</v>
+        <v>24.04</v>
       </c>
     </row>
     <row r="231">
@@ -13439,7 +13439,7 @@
         </is>
       </c>
       <c r="O231" s="2" t="n">
-        <v>11.35</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="232">
@@ -13485,10 +13485,10 @@
         <v>179</v>
       </c>
       <c r="L232" s="2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M232" s="2" t="n">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="N232" s="4" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         </is>
       </c>
       <c r="O232" s="2" t="n">
-        <v>8.34</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="233">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="O233" s="2" t="n">
-        <v>5.53</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="234">
@@ -13610,7 +13610,7 @@
         </is>
       </c>
       <c r="O234" s="2" t="n">
-        <v>11.17</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="235">
@@ -13667,7 +13667,7 @@
         </is>
       </c>
       <c r="O235" s="2" t="n">
-        <v>8.289999999999999</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="236">
@@ -13724,7 +13724,7 @@
         </is>
       </c>
       <c r="O236" s="2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="237">
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="O237" s="2" t="n">
-        <v>4.62</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="238">
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="O238" s="2" t="n">
-        <v>20.25</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="239">
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="O239" s="2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="240">
@@ -13952,7 +13952,7 @@
         </is>
       </c>
       <c r="O240" s="2" t="n">
-        <v>8.77</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="241">
@@ -13998,10 +13998,10 @@
         <v>69</v>
       </c>
       <c r="L241" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M241" s="2" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="N241" s="6" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         </is>
       </c>
       <c r="O241" s="2" t="n">
-        <v>5.03</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="242">
@@ -14066,7 +14066,7 @@
         </is>
       </c>
       <c r="O242" s="2" t="n">
-        <v>5.55</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="243">
@@ -14123,7 +14123,7 @@
         </is>
       </c>
       <c r="O243" s="2" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="244">
@@ -14180,7 +14180,7 @@
         </is>
       </c>
       <c r="O244" s="2" t="n">
-        <v>71.09</v>
+        <v>71.62</v>
       </c>
     </row>
     <row r="245">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="O245" s="2" t="n">
-        <v>15.22</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="246">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="O246" s="2" t="n">
-        <v>42.7</v>
+        <v>43.02</v>
       </c>
     </row>
     <row r="247">
@@ -14351,7 +14351,7 @@
         </is>
       </c>
       <c r="O247" s="2" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="248">
@@ -14408,7 +14408,7 @@
         </is>
       </c>
       <c r="O248" s="2" t="n">
-        <v>7.81</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="249">
@@ -14451,13 +14451,13 @@
         <v>18</v>
       </c>
       <c r="K249" s="2" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L249" s="2" t="n">
         <v>26</v>
       </c>
       <c r="M249" s="2" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="N249" s="4" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="O249" s="2" t="n">
-        <v>6.11</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="250">
@@ -14522,7 +14522,7 @@
         </is>
       </c>
       <c r="O250" s="2" t="n">
-        <v>4.18</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="251">
@@ -14579,7 +14579,7 @@
         </is>
       </c>
       <c r="O251" s="2" t="n">
-        <v>22.22</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="252">
@@ -14636,7 +14636,7 @@
         </is>
       </c>
       <c r="O252" s="2" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="253">
@@ -14693,7 +14693,7 @@
         </is>
       </c>
       <c r="O253" s="2" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="254">
@@ -14736,13 +14736,13 @@
         <v>0</v>
       </c>
       <c r="K254" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="L254" s="2" t="n">
         <v>45</v>
       </c>
       <c r="M254" s="2" t="n">
-        <v>460</v>
+        <v>333</v>
       </c>
       <c r="N254" s="6" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         </is>
       </c>
       <c r="O254" s="2" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="255">
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="O255" s="2" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="256">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="J256" s="2" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K256" s="2" t="n">
         <v>228</v>
@@ -14856,7 +14856,7 @@
         <v>295</v>
       </c>
       <c r="M256" s="2" t="n">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="N256" s="4" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="O256" s="2" t="n">
-        <v>5.95</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="257">
@@ -14907,13 +14907,13 @@
         <v>139</v>
       </c>
       <c r="K257" s="2" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="L257" s="2" t="n">
         <v>36</v>
       </c>
       <c r="M257" s="2" t="n">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="N257" s="4" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="O257" s="2" t="n">
-        <v>4.85</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="258">
@@ -14964,13 +14964,13 @@
         <v>73</v>
       </c>
       <c r="K258" s="2" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L258" s="2" t="n">
         <v>79</v>
       </c>
       <c r="M258" s="2" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="N258" s="4" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="O258" s="2" t="n">
-        <v>5.6</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="259">
@@ -15035,7 +15035,7 @@
         </is>
       </c>
       <c r="O259" s="2" t="n">
-        <v>6.92</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="260">
@@ -15092,7 +15092,7 @@
         </is>
       </c>
       <c r="O260" s="2" t="n">
-        <v>10.57</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="261">
@@ -15132,7 +15132,7 @@
         </is>
       </c>
       <c r="J261" s="2" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K261" s="2" t="n">
         <v>103</v>
@@ -15141,7 +15141,7 @@
         <v>116</v>
       </c>
       <c r="M261" s="2" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N261" s="4" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="O261" s="2" t="n">
-        <v>7.08</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="262">
@@ -15206,7 +15206,7 @@
         </is>
       </c>
       <c r="O262" s="2" t="n">
-        <v>13.51</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="263">
@@ -15249,13 +15249,13 @@
         <v>57</v>
       </c>
       <c r="K263" s="2" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L263" s="2" t="n">
         <v>142</v>
       </c>
       <c r="M263" s="2" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="N263" s="4" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         </is>
       </c>
       <c r="O263" s="2" t="n">
-        <v>12.61</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="264">
@@ -15320,7 +15320,7 @@
         </is>
       </c>
       <c r="O264" s="2" t="n">
-        <v>16.45</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="265">
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="O265" s="2" t="n">
-        <v>19.38</v>
+        <v>19.52</v>
       </c>
     </row>
     <row r="266">
@@ -15434,7 +15434,7 @@
         </is>
       </c>
       <c r="O266" s="2" t="n">
-        <v>22.32</v>
+        <v>22.48</v>
       </c>
     </row>
     <row r="267">
@@ -15491,7 +15491,7 @@
         </is>
       </c>
       <c r="O267" s="2" t="n">
-        <v>42.3</v>
+        <v>42.61</v>
       </c>
     </row>
     <row r="268">
@@ -15534,13 +15534,13 @@
         <v>58</v>
       </c>
       <c r="K268" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L268" s="2" t="n">
         <v>67</v>
       </c>
       <c r="M268" s="2" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N268" s="4" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         </is>
       </c>
       <c r="O268" s="2" t="n">
-        <v>28.1</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="269">
@@ -15591,13 +15591,13 @@
         <v>39</v>
       </c>
       <c r="K269" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L269" s="2" t="n">
         <v>10</v>
       </c>
       <c r="M269" s="2" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N269" s="4" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         </is>
       </c>
       <c r="O269" s="2" t="n">
-        <v>17.03</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="270">
@@ -15645,16 +15645,16 @@
         </is>
       </c>
       <c r="J270" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K270" s="2" t="n">
-        <v>49</v>
+        <v>227</v>
       </c>
       <c r="L270" s="2" t="n">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="M270" s="2" t="n">
-        <v>316</v>
+        <v>458</v>
       </c>
       <c r="N270" s="4" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         </is>
       </c>
       <c r="O270" s="2" t="n">
-        <v>4.13</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="271">
@@ -15719,7 +15719,7 @@
         </is>
       </c>
       <c r="O271" s="2" t="n">
-        <v>6.32</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="272">
@@ -15776,7 +15776,7 @@
         </is>
       </c>
       <c r="O272" s="2" t="n">
-        <v>10.02</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="273">
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="O273" s="2" t="n">
-        <v>10.02</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="274">
@@ -15890,7 +15890,7 @@
         </is>
       </c>
       <c r="O274" s="2" t="n">
-        <v>27.16</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="275">
@@ -15947,7 +15947,7 @@
         </is>
       </c>
       <c r="O275" s="2" t="n">
-        <v>27.16</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="276">
@@ -16004,7 +16004,7 @@
         </is>
       </c>
       <c r="O276" s="2" t="n">
-        <v>42.23</v>
+        <v>42.54</v>
       </c>
     </row>
     <row r="277">
@@ -16061,7 +16061,7 @@
         </is>
       </c>
       <c r="O277" s="2" t="n">
-        <v>5.09</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="278">
@@ -16118,7 +16118,7 @@
         </is>
       </c>
       <c r="O278" s="2" t="n">
-        <v>8.52</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="279">
@@ -16158,7 +16158,7 @@
         </is>
       </c>
       <c r="J279" s="2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K279" s="2" t="n">
         <v>95</v>
@@ -16167,7 +16167,7 @@
         <v>69</v>
       </c>
       <c r="M279" s="2" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N279" s="4" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         </is>
       </c>
       <c r="O279" s="2" t="n">
-        <v>8.52</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="280">
@@ -16215,16 +16215,16 @@
         </is>
       </c>
       <c r="J280" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K280" s="2" t="n">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="L280" s="2" t="n">
         <v>56</v>
       </c>
       <c r="M280" s="2" t="n">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="N280" s="4" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="O280" s="2" t="n">
-        <v>8.15</v>
+        <v>8.210000000000001</v>
       </c>
     </row>
     <row r="281">
@@ -16289,7 +16289,7 @@
         </is>
       </c>
       <c r="O281" s="2" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="282">
@@ -16332,13 +16332,13 @@
         <v>64</v>
       </c>
       <c r="K282" s="2" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="L282" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M282" s="2" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="N282" s="4" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         </is>
       </c>
       <c r="O282" s="2" t="n">
-        <v>10.32</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="283">
@@ -16389,13 +16389,13 @@
         <v>5</v>
       </c>
       <c r="K283" s="2" t="n">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="L283" s="2" t="n">
         <v>72</v>
       </c>
       <c r="M283" s="2" t="n">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="N283" s="6" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="O283" s="2" t="n">
-        <v>5.81</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="284">
@@ -16460,7 +16460,7 @@
         </is>
       </c>
       <c r="O284" s="2" t="n">
-        <v>12.55</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="285">
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="O285" s="2" t="n">
-        <v>13.37</v>
+        <v>13.47</v>
       </c>
     </row>
     <row r="286">
@@ -16574,7 +16574,7 @@
         </is>
       </c>
       <c r="O286" s="2" t="n">
-        <v>41.04</v>
+        <v>41.35</v>
       </c>
     </row>
     <row r="287">
@@ -16614,16 +16614,16 @@
         </is>
       </c>
       <c r="J287" s="2" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K287" s="2" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L287" s="2" t="n">
         <v>54</v>
       </c>
       <c r="M287" s="2" t="n">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N287" s="4" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         </is>
       </c>
       <c r="O287" s="2" t="n">
-        <v>10.36</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="288">
@@ -16688,7 +16688,7 @@
         </is>
       </c>
       <c r="O288" s="2" t="n">
-        <v>28.12</v>
+        <v>28.33</v>
       </c>
     </row>
     <row r="289">
@@ -16745,7 +16745,7 @@
         </is>
       </c>
       <c r="O289" s="2" t="n">
-        <v>28.12</v>
+        <v>28.33</v>
       </c>
     </row>
     <row r="290">
@@ -16802,7 +16802,7 @@
         </is>
       </c>
       <c r="O290" s="2" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="291">
@@ -16859,7 +16859,7 @@
         </is>
       </c>
       <c r="O291" s="2" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="292">
@@ -16916,7 +16916,7 @@
         </is>
       </c>
       <c r="O292" s="2" t="n">
-        <v>21.82</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="293">
@@ -16973,7 +16973,7 @@
         </is>
       </c>
       <c r="O293" s="2" t="n">
-        <v>71.13</v>
+        <v>71.66</v>
       </c>
     </row>
     <row r="294">
@@ -17030,7 +17030,7 @@
         </is>
       </c>
       <c r="O294" s="2" t="n">
-        <v>71.13</v>
+        <v>71.66</v>
       </c>
     </row>
     <row r="295">
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="O295" s="2" t="n">
-        <v>71.13</v>
+        <v>71.66</v>
       </c>
     </row>
     <row r="296">
@@ -17144,7 +17144,7 @@
         </is>
       </c>
       <c r="O296" s="2" t="n">
-        <v>10.56</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="297">
@@ -17190,10 +17190,10 @@
         <v>197</v>
       </c>
       <c r="L297" s="2" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M297" s="2" t="n">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="N297" s="4" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="O297" s="2" t="n">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="298">
@@ -17258,7 +17258,7 @@
         </is>
       </c>
       <c r="O298" s="2" t="n">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="299">
@@ -17315,7 +17315,7 @@
         </is>
       </c>
       <c r="O299" s="2" t="n">
-        <v>4.85</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="300">
@@ -17372,7 +17372,7 @@
         </is>
       </c>
       <c r="O300" s="2" t="n">
-        <v>8.15</v>
+        <v>8.210000000000001</v>
       </c>
     </row>
     <row r="301">
@@ -17415,13 +17415,13 @@
         <v>132</v>
       </c>
       <c r="K301" s="2" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L301" s="2" t="n">
         <v>85</v>
       </c>
       <c r="M301" s="2" t="n">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="N301" s="4" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         </is>
       </c>
       <c r="O301" s="2" t="n">
-        <v>8.15</v>
+        <v>8.210000000000001</v>
       </c>
     </row>
     <row r="302">
@@ -17486,7 +17486,7 @@
         </is>
       </c>
       <c r="O302" s="2" t="n">
-        <v>5.58</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="303">
@@ -17529,13 +17529,13 @@
         <v>54</v>
       </c>
       <c r="K303" s="2" t="n">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="L303" s="2" t="n">
         <v>58</v>
       </c>
       <c r="M303" s="2" t="n">
-        <v>135</v>
+        <v>247</v>
       </c>
       <c r="N303" s="4" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         </is>
       </c>
       <c r="O303" s="2" t="n">
-        <v>10.36</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="304">
@@ -17600,7 +17600,7 @@
         </is>
       </c>
       <c r="O304" s="2" t="n">
-        <v>10.36</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="305">
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="O305" s="2" t="n">
-        <v>10.39</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="306">
@@ -17700,13 +17700,13 @@
         <v>43</v>
       </c>
       <c r="K306" s="2" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="L306" s="2" t="n">
         <v>92</v>
       </c>
       <c r="M306" s="2" t="n">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="N306" s="4" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="O306" s="2" t="n">
-        <v>16.45</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="307">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="O307" s="2" t="n">
-        <v>19.39</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="308">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="O308" s="2" t="n">
-        <v>20.86</v>
+        <v>21.01</v>
       </c>
     </row>
     <row r="309">
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="O309" s="2" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="310">
@@ -17942,7 +17942,7 @@
         </is>
       </c>
       <c r="O310" s="2" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="311">
@@ -17999,7 +17999,7 @@
         </is>
       </c>
       <c r="O311" s="2" t="n">
-        <v>41.67</v>
+        <v>41.98</v>
       </c>
     </row>
     <row r="312">
@@ -18056,7 +18056,7 @@
         </is>
       </c>
       <c r="O312" s="2" t="n">
-        <v>23.35</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="313">
@@ -18102,10 +18102,10 @@
         <v>24</v>
       </c>
       <c r="L313" s="2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M313" s="2" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="N313" s="4" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         </is>
       </c>
       <c r="O313" s="2" t="n">
-        <v>24.68</v>
+        <v>24.86</v>
       </c>
     </row>
     <row r="314">
@@ -18170,7 +18170,7 @@
         </is>
       </c>
       <c r="O314" s="2" t="n">
-        <v>9.25</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="315">
@@ -18227,7 +18227,7 @@
         </is>
       </c>
       <c r="O315" s="2" t="n">
-        <v>18.07</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="316">
@@ -18284,7 +18284,7 @@
         </is>
       </c>
       <c r="O316" s="2" t="n">
-        <v>9.99</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="317">
@@ -18327,13 +18327,13 @@
         <v>47</v>
       </c>
       <c r="K317" s="2" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="L317" s="2" t="n">
         <v>39</v>
       </c>
       <c r="M317" s="2" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="N317" s="4" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         </is>
       </c>
       <c r="O317" s="2" t="n">
-        <v>19.39</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="318">
@@ -18387,10 +18387,10 @@
         <v>2</v>
       </c>
       <c r="L318" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M318" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N318" s="4" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         </is>
       </c>
       <c r="O318" s="2" t="n">
-        <v>31.21</v>
+        <v>31.44</v>
       </c>
     </row>
     <row r="319">
@@ -18455,7 +18455,7 @@
         </is>
       </c>
       <c r="O319" s="2" t="n">
-        <v>8.52</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="320">
@@ -18512,7 +18512,7 @@
         </is>
       </c>
       <c r="O320" s="2" t="n">
-        <v>8.52</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="321">
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="O321" s="2" t="n">
-        <v>8.52</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="322">
@@ -18626,7 +18626,7 @@
         </is>
       </c>
       <c r="O322" s="2" t="n">
-        <v>8.52</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="323">
@@ -18669,13 +18669,13 @@
         <v>14</v>
       </c>
       <c r="K323" s="2" t="n">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="L323" s="2" t="n">
         <v>17</v>
       </c>
       <c r="M323" s="2" t="n">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="N323" s="4" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         </is>
       </c>
       <c r="O323" s="2" t="n">
-        <v>10.72</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="324">
@@ -18740,7 +18740,7 @@
         </is>
       </c>
       <c r="O324" s="2" t="n">
-        <v>10.72</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="325">
@@ -18797,7 +18797,7 @@
         </is>
       </c>
       <c r="O325" s="2" t="n">
-        <v>21.35</v>
+        <v>21.51</v>
       </c>
     </row>
     <row r="326">
@@ -18854,7 +18854,7 @@
         </is>
       </c>
       <c r="O326" s="2" t="n">
-        <v>16.16</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="327">
@@ -18911,7 +18911,7 @@
         </is>
       </c>
       <c r="O327" s="2" t="n">
-        <v>14.43</v>
+        <v>14.54</v>
       </c>
     </row>
     <row r="328">
@@ -18968,7 +18968,7 @@
         </is>
       </c>
       <c r="O328" s="2" t="n">
-        <v>12.93</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="329">
@@ -19025,7 +19025,7 @@
         </is>
       </c>
       <c r="O329" s="2" t="n">
-        <v>12.93</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="330">
@@ -19082,7 +19082,7 @@
         </is>
       </c>
       <c r="O330" s="2" t="n">
-        <v>25.26</v>
+        <v>25.45</v>
       </c>
     </row>
     <row r="331">
@@ -19139,7 +19139,7 @@
         </is>
       </c>
       <c r="O331" s="2" t="n">
-        <v>7.6</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="332">
@@ -19196,7 +19196,7 @@
         </is>
       </c>
       <c r="O332" s="2" t="n">
-        <v>21.32</v>
+        <v>21.47</v>
       </c>
     </row>
     <row r="333">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="O333" s="2" t="n">
-        <v>5.95</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="334">
@@ -19310,7 +19310,7 @@
         </is>
       </c>
       <c r="O334" s="2" t="n">
-        <v>16.96</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="335">
@@ -19353,13 +19353,13 @@
         <v>22</v>
       </c>
       <c r="K335" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L335" s="2" t="n">
         <v>32</v>
       </c>
       <c r="M335" s="2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N335" s="4" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         </is>
       </c>
       <c r="O335" s="2" t="n">
-        <v>25.78</v>
+        <v>25.97</v>
       </c>
     </row>
     <row r="336">
@@ -19424,7 +19424,7 @@
         </is>
       </c>
       <c r="O336" s="2" t="n">
-        <v>12.59</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="337">
@@ -19481,7 +19481,7 @@
         </is>
       </c>
       <c r="O337" s="2" t="n">
-        <v>7.09</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="338">
@@ -19538,7 +19538,7 @@
         </is>
       </c>
       <c r="O338" s="2" t="n">
-        <v>7.09</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="339">
@@ -19595,7 +19595,7 @@
         </is>
       </c>
       <c r="O339" s="2" t="n">
-        <v>7.62</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="340">
@@ -19652,7 +19652,7 @@
         </is>
       </c>
       <c r="O340" s="2" t="n">
-        <v>7.81</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="341">
@@ -19709,7 +19709,7 @@
         </is>
       </c>
       <c r="O341" s="2" t="n">
-        <v>7.81</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="342">
@@ -19752,13 +19752,13 @@
         <v>83</v>
       </c>
       <c r="K342" s="2" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="L342" s="2" t="n">
         <v>34</v>
       </c>
       <c r="M342" s="2" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="N342" s="4" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         </is>
       </c>
       <c r="O342" s="2" t="n">
-        <v>7.08</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="343">
@@ -19823,7 +19823,7 @@
         </is>
       </c>
       <c r="O343" s="2" t="n">
-        <v>7.08</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="344">
@@ -19880,7 +19880,7 @@
         </is>
       </c>
       <c r="O344" s="2" t="n">
-        <v>4.85</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="345">
@@ -19937,7 +19937,7 @@
         </is>
       </c>
       <c r="O345" s="2" t="n">
-        <v>5.22</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="346">
@@ -19994,7 +19994,7 @@
         </is>
       </c>
       <c r="O346" s="2" t="n">
-        <v>48.84</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="347">
@@ -20040,10 +20040,10 @@
         <v>309</v>
       </c>
       <c r="L347" s="2" t="n">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="M347" s="2" t="n">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="N347" s="4" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         </is>
       </c>
       <c r="O347" s="2" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="348">
@@ -20108,7 +20108,7 @@
         </is>
       </c>
       <c r="O348" s="2" t="n">
-        <v>7.05</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="349">
@@ -20165,7 +20165,7 @@
         </is>
       </c>
       <c r="O349" s="2" t="n">
-        <v>12.56</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="350">
@@ -20205,16 +20205,16 @@
         </is>
       </c>
       <c r="J350" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K350" s="2" t="n">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="L350" s="2" t="n">
         <v>32</v>
       </c>
       <c r="M350" s="2" t="n">
-        <v>122</v>
+        <v>177</v>
       </c>
       <c r="N350" s="4" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         </is>
       </c>
       <c r="O350" s="2" t="n">
-        <v>5.58</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="351">
@@ -20279,7 +20279,7 @@
         </is>
       </c>
       <c r="O351" s="2" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="352">
@@ -20336,7 +20336,7 @@
         </is>
       </c>
       <c r="O352" s="2" t="n">
-        <v>12.56</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="353">
@@ -20393,7 +20393,7 @@
         </is>
       </c>
       <c r="O353" s="2" t="n">
-        <v>12.56</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="354">
@@ -20450,7 +20450,7 @@
         </is>
       </c>
       <c r="O354" s="2" t="n">
-        <v>20.52</v>
+        <v>20.67</v>
       </c>
     </row>
     <row r="355">
@@ -20507,7 +20507,7 @@
         </is>
       </c>
       <c r="O355" s="2" t="n">
-        <v>20.93</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="356">
@@ -20564,7 +20564,7 @@
         </is>
       </c>
       <c r="O356" s="2" t="n">
-        <v>41.43</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="357">
@@ -20621,7 +20621,7 @@
         </is>
       </c>
       <c r="O357" s="2" t="n">
-        <v>9.25</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="358">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="O358" s="2" t="n">
-        <v>13.33</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="359">
@@ -20735,7 +20735,7 @@
         </is>
       </c>
       <c r="O359" s="2" t="n">
-        <v>13.33</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="360">
@@ -20792,7 +20792,7 @@
         </is>
       </c>
       <c r="O360" s="2" t="n">
-        <v>34.92</v>
+        <v>35.17</v>
       </c>
     </row>
     <row r="361">
@@ -20849,7 +20849,7 @@
         </is>
       </c>
       <c r="O361" s="2" t="n">
-        <v>34.92</v>
+        <v>35.17</v>
       </c>
     </row>
     <row r="362">
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="O362" s="2" t="n">
-        <v>34.92</v>
+        <v>35.17</v>
       </c>
     </row>
     <row r="363">
@@ -20949,13 +20949,13 @@
         <v>0</v>
       </c>
       <c r="K363" s="2" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L363" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M363" s="2" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N363" s="6" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         </is>
       </c>
       <c r="O363" s="2" t="n">
-        <v>34.92</v>
+        <v>35.17</v>
       </c>
     </row>
     <row r="364">
@@ -21006,13 +21006,13 @@
         <v>0</v>
       </c>
       <c r="K364" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L364" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M364" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N364" s="6" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         </is>
       </c>
       <c r="O364" s="2" t="n">
-        <v>34.92</v>
+        <v>35.17</v>
       </c>
     </row>
     <row r="365">
@@ -21077,7 +21077,7 @@
         </is>
       </c>
       <c r="O365" s="2" t="n">
-        <v>17.92</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="366">
@@ -21134,7 +21134,7 @@
         </is>
       </c>
       <c r="O366" s="2" t="n">
-        <v>34.61</v>
+        <v>34.87</v>
       </c>
     </row>
     <row r="367">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="O367" s="2" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="368">
@@ -21234,13 +21234,13 @@
         <v>100</v>
       </c>
       <c r="K368" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L368" s="2" t="n">
         <v>76</v>
       </c>
       <c r="M368" s="2" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N368" s="4" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="O368" s="2" t="n">
-        <v>9.99</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="369">
@@ -21305,7 +21305,7 @@
         </is>
       </c>
       <c r="O369" s="2" t="n">
-        <v>4.61</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="370">
@@ -21348,13 +21348,13 @@
         <v>38</v>
       </c>
       <c r="K370" s="2" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L370" s="2" t="n">
         <v>47</v>
       </c>
       <c r="M370" s="2" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="N370" s="4" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         </is>
       </c>
       <c r="O370" s="2" t="n">
-        <v>13.51</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="371">
@@ -21419,7 +21419,7 @@
         </is>
       </c>
       <c r="O371" s="2" t="n">
-        <v>5.61</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="372">
@@ -21476,7 +21476,7 @@
         </is>
       </c>
       <c r="O372" s="2" t="n">
-        <v>28.22</v>
+        <v>28.43</v>
       </c>
     </row>
     <row r="373">
@@ -21533,7 +21533,7 @@
         </is>
       </c>
       <c r="O373" s="2" t="n">
-        <v>17.91</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="374">
@@ -21576,21 +21576,21 @@
         <v>3</v>
       </c>
       <c r="K374" s="2" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="L374" s="2" t="n">
         <v>9</v>
       </c>
       <c r="M374" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="N374" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>57</v>
+      </c>
+      <c r="N374" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O374" s="2" t="n">
-        <v>17.91</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="375">
@@ -21647,7 +21647,7 @@
         </is>
       </c>
       <c r="O375" s="2" t="n">
-        <v>23.81</v>
+        <v>23.98</v>
       </c>
     </row>
     <row r="376">
@@ -21704,7 +21704,7 @@
         </is>
       </c>
       <c r="O376" s="2" t="n">
-        <v>13.67</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="377">
@@ -21761,7 +21761,7 @@
         </is>
       </c>
       <c r="O377" s="2" t="n">
-        <v>12.93</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="378">
@@ -21818,7 +21818,7 @@
         </is>
       </c>
       <c r="O378" s="2" t="n">
-        <v>4.79</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="379">
@@ -21875,7 +21875,7 @@
         </is>
       </c>
       <c r="O379" s="2" t="n">
-        <v>6.32</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="380">
@@ -21932,7 +21932,7 @@
         </is>
       </c>
       <c r="O380" s="2" t="n">
-        <v>7.79</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="381">
@@ -21989,7 +21989,7 @@
         </is>
       </c>
       <c r="O381" s="2" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="382">
@@ -22032,13 +22032,13 @@
         <v>14</v>
       </c>
       <c r="K382" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L382" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M382" s="2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N382" s="4" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         </is>
       </c>
       <c r="O382" s="2" t="n">
-        <v>14.98</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="383">
@@ -22103,7 +22103,7 @@
         </is>
       </c>
       <c r="O383" s="2" t="n">
-        <v>7.1</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="384">
@@ -22160,7 +22160,7 @@
         </is>
       </c>
       <c r="O384" s="2" t="n">
-        <v>9.25</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="385">
@@ -22217,7 +22217,7 @@
         </is>
       </c>
       <c r="O385" s="2" t="n">
-        <v>16.99</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="386">
@@ -22274,7 +22274,7 @@
         </is>
       </c>
       <c r="O386" s="2" t="n">
-        <v>13.67</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="387">
@@ -22331,7 +22331,7 @@
         </is>
       </c>
       <c r="O387" s="2" t="n">
-        <v>4.85</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="388">
@@ -22388,7 +22388,7 @@
         </is>
       </c>
       <c r="O388" s="2" t="n">
-        <v>34.28</v>
+        <v>34.53</v>
       </c>
     </row>
     <row r="389">
@@ -22431,13 +22431,13 @@
         <v>0</v>
       </c>
       <c r="K389" s="2" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L389" s="2" t="n">
         <v>86</v>
       </c>
       <c r="M389" s="2" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N389" s="6" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         </is>
       </c>
       <c r="O389" s="2" t="n">
-        <v>4.48</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="390">
@@ -22502,7 +22502,7 @@
         </is>
       </c>
       <c r="O390" s="2" t="n">
-        <v>15.87</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="391">
@@ -22559,7 +22559,7 @@
         </is>
       </c>
       <c r="O391" s="2" t="n">
-        <v>18.82</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="392">
@@ -22616,7 +22616,7 @@
         </is>
       </c>
       <c r="O392" s="2" t="n">
-        <v>28.2</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="393">
@@ -22673,7 +22673,7 @@
         </is>
       </c>
       <c r="O393" s="2" t="n">
-        <v>8.539999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="394">
@@ -22787,7 +22787,7 @@
         </is>
       </c>
       <c r="O395" s="2" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="396">
@@ -22844,7 +22844,7 @@
         </is>
       </c>
       <c r="O396" s="2" t="n">
-        <v>6.19</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="397">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="O397" s="2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="398">
@@ -22940,13 +22940,13 @@
         <v>0</v>
       </c>
       <c r="K398" s="2" t="n">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="L398" s="2" t="n">
         <v>405</v>
       </c>
       <c r="M398" s="2" t="n">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="N398" s="6" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         </is>
       </c>
       <c r="O398" s="2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="399">
@@ -23009,7 +23009,7 @@
         </is>
       </c>
       <c r="O399" s="2" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="400">
@@ -23050,13 +23050,13 @@
         <v>178</v>
       </c>
       <c r="K400" s="2" t="n">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="L400" s="2" t="n">
         <v>93</v>
       </c>
       <c r="M400" s="2" t="n">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="N400" s="4" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="O400" s="2" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="401">
@@ -23235,7 +23235,7 @@
         </is>
       </c>
       <c r="O403" s="2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="404">
@@ -23292,7 +23292,7 @@
         </is>
       </c>
       <c r="O404" s="2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="405">
@@ -23349,7 +23349,7 @@
         </is>
       </c>
       <c r="O405" s="2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="406">
@@ -23406,7 +23406,7 @@
         </is>
       </c>
       <c r="O406" s="2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="407">
@@ -23463,7 +23463,7 @@
         </is>
       </c>
       <c r="O407" s="2" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="408">
@@ -23520,7 +23520,7 @@
         </is>
       </c>
       <c r="O408" s="2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="409">
@@ -23577,7 +23577,7 @@
         </is>
       </c>
       <c r="O409" s="2" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="410">
@@ -23634,7 +23634,7 @@
         </is>
       </c>
       <c r="O410" s="2" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="411">
@@ -23737,10 +23737,10 @@
         <v>1957</v>
       </c>
       <c r="L412" s="2" t="n">
-        <v>715</v>
+        <v>695</v>
       </c>
       <c r="M412" s="2" t="n">
-        <v>3071</v>
+        <v>3051</v>
       </c>
       <c r="N412" s="4" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="O412" s="2" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="413">
@@ -23791,13 +23791,13 @@
         <v>189</v>
       </c>
       <c r="K413" s="2" t="n">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="L413" s="2" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="M413" s="2" t="n">
-        <v>1086</v>
+        <v>1063</v>
       </c>
       <c r="N413" s="4" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         </is>
       </c>
       <c r="O413" s="2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="414">
@@ -23902,16 +23902,16 @@
         </is>
       </c>
       <c r="J415" s="2" t="n">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="K415" s="2" t="n">
-        <v>783</v>
+        <v>771</v>
       </c>
       <c r="L415" s="2" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="M415" s="2" t="n">
-        <v>1179</v>
+        <v>1126</v>
       </c>
       <c r="N415" s="4" t="inlineStr">
         <is>
@@ -24073,16 +24073,16 @@
         </is>
       </c>
       <c r="J418" s="2" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K418" s="2" t="n">
         <v>530</v>
       </c>
       <c r="L418" s="2" t="n">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="M418" s="2" t="n">
-        <v>903</v>
+        <v>883</v>
       </c>
       <c r="N418" s="4" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         </is>
       </c>
       <c r="O418" s="2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="419">
@@ -24147,7 +24147,7 @@
         </is>
       </c>
       <c r="O419" s="2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="420">
@@ -24204,7 +24204,7 @@
         </is>
       </c>
       <c r="O420" s="2" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="421">
@@ -24261,7 +24261,7 @@
         </is>
       </c>
       <c r="O421" s="2" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="422">
@@ -24304,13 +24304,13 @@
         <v>85</v>
       </c>
       <c r="K422" s="2" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L422" s="2" t="n">
         <v>69</v>
       </c>
       <c r="M422" s="2" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="N422" s="4" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         </is>
       </c>
       <c r="O422" s="2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="423">
@@ -24375,7 +24375,7 @@
         </is>
       </c>
       <c r="O423" s="2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="424">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="O424" s="2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="425">
@@ -24475,13 +24475,13 @@
         <v>179</v>
       </c>
       <c r="K425" s="2" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L425" s="2" t="n">
         <v>236</v>
       </c>
       <c r="M425" s="2" t="n">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="N425" s="4" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         </is>
       </c>
       <c r="O425" s="2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="426">
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="O426" s="2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="427">
@@ -24643,16 +24643,16 @@
         </is>
       </c>
       <c r="J428" s="2" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K428" s="2" t="n">
         <v>40</v>
       </c>
       <c r="L428" s="2" t="n">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="M428" s="2" t="n">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="N428" s="4" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         </is>
       </c>
       <c r="O428" s="2" t="n">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="429">
@@ -24717,7 +24717,7 @@
         </is>
       </c>
       <c r="O429" s="2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="430">
@@ -24757,7 +24757,7 @@
         </is>
       </c>
       <c r="J430" s="2" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="K430" s="2" t="n">
         <v>283</v>
@@ -24766,7 +24766,7 @@
         <v>31</v>
       </c>
       <c r="M430" s="2" t="n">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="N430" s="4" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         </is>
       </c>
       <c r="O430" s="2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="431">
@@ -24831,7 +24831,7 @@
         </is>
       </c>
       <c r="O431" s="2" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="432">
@@ -24874,13 +24874,13 @@
         <v>137</v>
       </c>
       <c r="K432" s="2" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="L432" s="2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M432" s="2" t="n">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="N432" s="4" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         </is>
       </c>
       <c r="O432" s="2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="433">
@@ -24945,7 +24945,7 @@
         </is>
       </c>
       <c r="O433" s="2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="434">
@@ -24988,13 +24988,13 @@
         <v>0</v>
       </c>
       <c r="K434" s="2" t="n">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="L434" s="2" t="n">
         <v>157</v>
       </c>
       <c r="M434" s="2" t="n">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="N434" s="6" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         </is>
       </c>
       <c r="O434" s="2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="435">
@@ -25059,7 +25059,7 @@
         </is>
       </c>
       <c r="O435" s="2" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="436">
@@ -25116,7 +25116,7 @@
         </is>
       </c>
       <c r="O436" s="2" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="437">
@@ -25156,7 +25156,7 @@
         </is>
       </c>
       <c r="J437" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K437" s="2" t="n">
         <v>263</v>
@@ -25165,7 +25165,7 @@
         <v>119</v>
       </c>
       <c r="M437" s="2" t="n">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="N437" s="6" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         </is>
       </c>
       <c r="O437" s="2" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="438">
@@ -25216,13 +25216,13 @@
         <v>169</v>
       </c>
       <c r="K438" s="2" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L438" s="2" t="n">
         <v>191</v>
       </c>
       <c r="M438" s="2" t="n">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="N438" s="4" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         </is>
       </c>
       <c r="O438" s="2" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="439">
@@ -25287,7 +25287,7 @@
         </is>
       </c>
       <c r="O439" s="2" t="n">
-        <v>4.79</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="440">
@@ -25330,13 +25330,13 @@
         <v>0</v>
       </c>
       <c r="K440" s="2" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L440" s="2" t="n">
         <v>59</v>
       </c>
       <c r="M440" s="2" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N440" s="6" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         </is>
       </c>
       <c r="O440" s="2" t="n">
-        <v>4.79</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="441">
@@ -25401,7 +25401,7 @@
         </is>
       </c>
       <c r="O441" s="2" t="n">
-        <v>4.64</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="442">
@@ -25458,7 +25458,7 @@
         </is>
       </c>
       <c r="O442" s="2" t="n">
-        <v>4.64</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="443">
@@ -25515,7 +25515,7 @@
         </is>
       </c>
       <c r="O443" s="2" t="n">
-        <v>5.6</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="444">
@@ -25572,7 +25572,7 @@
         </is>
       </c>
       <c r="O444" s="2" t="n">
-        <v>6.56</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="445">
@@ -25629,7 +25629,7 @@
         </is>
       </c>
       <c r="O445" s="2" t="n">
-        <v>8.65</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="446">
@@ -25686,7 +25686,7 @@
         </is>
       </c>
       <c r="O446" s="2" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="447">
@@ -25743,7 +25743,7 @@
         </is>
       </c>
       <c r="O447" s="2" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="448">
@@ -25800,7 +25800,7 @@
         </is>
       </c>
       <c r="O448" s="2" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="449">
@@ -25846,10 +25846,10 @@
         <v>50</v>
       </c>
       <c r="L449" s="2" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M449" s="2" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N449" s="4" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         </is>
       </c>
       <c r="O449" s="2" t="n">
-        <v>17.33</v>
+        <v>17.46</v>
       </c>
     </row>
     <row r="450">
@@ -25914,7 +25914,7 @@
         </is>
       </c>
       <c r="O450" s="2" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="451">
@@ -25957,13 +25957,13 @@
         <v>79</v>
       </c>
       <c r="K451" s="2" t="n">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="L451" s="2" t="n">
-        <v>498</v>
+        <v>463</v>
       </c>
       <c r="M451" s="2" t="n">
-        <v>920</v>
+        <v>875</v>
       </c>
       <c r="N451" s="4" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         </is>
       </c>
       <c r="O451" s="2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="452">
@@ -26028,7 +26028,7 @@
         </is>
       </c>
       <c r="O452" s="2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="453">
@@ -26085,7 +26085,7 @@
         </is>
       </c>
       <c r="O453" s="2" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="454">
@@ -26128,13 +26128,13 @@
         <v>1</v>
       </c>
       <c r="K454" s="2" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L454" s="2" t="n">
         <v>180</v>
       </c>
       <c r="M454" s="2" t="n">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="N454" s="6" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         </is>
       </c>
       <c r="O454" s="2" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="455">
@@ -26199,7 +26199,7 @@
         </is>
       </c>
       <c r="O455" s="2" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="456">
@@ -26256,7 +26256,7 @@
         </is>
       </c>
       <c r="O456" s="2" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="457">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="O457" s="2" t="n">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="458">
@@ -26356,13 +26356,13 @@
         <v>1</v>
       </c>
       <c r="K458" s="2" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L458" s="2" t="n">
         <v>95</v>
       </c>
       <c r="M458" s="2" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="N458" s="6" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         </is>
       </c>
       <c r="O458" s="2" t="n">
-        <v>4.65</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="459">
@@ -26427,7 +26427,7 @@
         </is>
       </c>
       <c r="O459" s="2" t="n">
-        <v>7.55</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="460">
@@ -26470,13 +26470,13 @@
         <v>8</v>
       </c>
       <c r="K460" s="2" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="L460" s="2" t="n">
         <v>60</v>
       </c>
       <c r="M460" s="2" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="N460" s="6" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="O460" s="2" t="n">
-        <v>7.55</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="461">
@@ -26541,7 +26541,7 @@
         </is>
       </c>
       <c r="O461" s="2" t="n">
-        <v>10.39</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="462">
@@ -26584,13 +26584,13 @@
         <v>0</v>
       </c>
       <c r="K462" s="2" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L462" s="2" t="n">
         <v>23</v>
       </c>
       <c r="M462" s="2" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="N462" s="6" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         </is>
       </c>
       <c r="O462" s="2" t="n">
-        <v>10.91</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="463">
@@ -26655,7 +26655,7 @@
         </is>
       </c>
       <c r="O463" s="2" t="n">
-        <v>4.65</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="464">
@@ -26698,13 +26698,13 @@
         <v>0</v>
       </c>
       <c r="K464" s="2" t="n">
-        <v>124</v>
+        <v>1</v>
       </c>
       <c r="L464" s="2" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="M464" s="2" t="n">
-        <v>275</v>
+        <v>141</v>
       </c>
       <c r="N464" s="6" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         </is>
       </c>
       <c r="O464" s="2" t="n">
-        <v>6.45</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="465">
@@ -26769,7 +26769,7 @@
         </is>
       </c>
       <c r="O465" s="2" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="466">
@@ -26826,7 +26826,7 @@
         </is>
       </c>
       <c r="O466" s="2" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="467">
@@ -26883,7 +26883,7 @@
         </is>
       </c>
       <c r="O467" s="2" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="468">
@@ -26926,13 +26926,13 @@
         <v>11</v>
       </c>
       <c r="K468" s="2" t="n">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="L468" s="2" t="n">
         <v>44</v>
       </c>
       <c r="M468" s="2" t="n">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="N468" s="4" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         </is>
       </c>
       <c r="O468" s="2" t="n">
-        <v>6.47</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="469">
@@ -26997,7 +26997,7 @@
         </is>
       </c>
       <c r="O469" s="2" t="n">
-        <v>7.58</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="470">
@@ -27054,7 +27054,7 @@
         </is>
       </c>
       <c r="O470" s="2" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="471">
@@ -27111,7 +27111,7 @@
         </is>
       </c>
       <c r="O471" s="2" t="n">
-        <v>8.65</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="472">
@@ -27168,7 +27168,7 @@
         </is>
       </c>
       <c r="O472" s="2" t="n">
-        <v>8.65</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="473">
@@ -27225,7 +27225,7 @@
         </is>
       </c>
       <c r="O473" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="474">
@@ -27268,13 +27268,13 @@
         <v>0</v>
       </c>
       <c r="K474" s="2" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L474" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M474" s="2" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="N474" s="6" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         </is>
       </c>
       <c r="O474" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="475">
@@ -27339,7 +27339,7 @@
         </is>
       </c>
       <c r="O475" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="476">
@@ -27396,7 +27396,7 @@
         </is>
       </c>
       <c r="O476" s="2" t="n">
-        <v>10.38</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="477">
@@ -27439,13 +27439,13 @@
         <v>0</v>
       </c>
       <c r="K477" s="2" t="n">
-        <v>793</v>
+        <v>456</v>
       </c>
       <c r="L477" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M477" s="2" t="n">
-        <v>793</v>
+        <v>456</v>
       </c>
       <c r="N477" s="6" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         </is>
       </c>
       <c r="O477" s="2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="478">
@@ -27510,7 +27510,7 @@
         </is>
       </c>
       <c r="O478" s="2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="479">
@@ -27567,7 +27567,7 @@
         </is>
       </c>
       <c r="O479" s="2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="480">
@@ -27624,7 +27624,7 @@
         </is>
       </c>
       <c r="O480" s="2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="481">
@@ -27681,7 +27681,7 @@
         </is>
       </c>
       <c r="O481" s="2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="482">
@@ -27738,7 +27738,7 @@
         </is>
       </c>
       <c r="O482" s="2" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="483">
@@ -27795,7 +27795,7 @@
         </is>
       </c>
       <c r="O483" s="2" t="n">
-        <v>4.21</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="484">
@@ -27852,7 +27852,7 @@
         </is>
       </c>
       <c r="O484" s="2" t="n">
-        <v>4.74</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="485">
@@ -27909,7 +27909,7 @@
         </is>
       </c>
       <c r="O485" s="2" t="n">
-        <v>4.74</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="486">
@@ -27966,7 +27966,7 @@
         </is>
       </c>
       <c r="O486" s="2" t="n">
-        <v>7.24</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="487">
@@ -28023,7 +28023,7 @@
         </is>
       </c>
       <c r="O487" s="2" t="n">
-        <v>7.24</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="488">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="O488" s="2" t="n">
-        <v>5.93</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="489">
@@ -28137,7 +28137,7 @@
         </is>
       </c>
       <c r="O489" s="2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="490">
@@ -28194,7 +28194,7 @@
         </is>
       </c>
       <c r="O490" s="2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
     </row>
   </sheetData>

--- a/inventario_expandido.xlsx
+++ b/inventario_expandido.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>€/m (6.85€/kg)</t>
+          <t>€/m (7.0€/kg)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="O2" s="2" t="n">
-        <v>11.58</v>
+        <v>11.84</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>8.859999999999999</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="4">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="5">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="6">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>4.16</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="7">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>7.43</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="8">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>11.56</v>
+        <v>11.81</v>
       </c>
     </row>
     <row r="9">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>16.64</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>29.7</v>
+        <v>30.35</v>
       </c>
     </row>
     <row r="11">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="12">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>46.41</v>
+        <v>47.42</v>
       </c>
     </row>
     <row r="13">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>37.44</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="14">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>22.66</v>
+        <v>23.16</v>
       </c>
     </row>
     <row r="15">
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="16">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="17">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="18">
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="19">
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="20">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>5.81</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="21">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>9.08</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>13.08</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="23">
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>17.8</v>
+        <v>18.19</v>
       </c>
     </row>
     <row r="24">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>23.24</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="25">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>36.33</v>
+        <v>37.12</v>
       </c>
     </row>
     <row r="26">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>52.3</v>
+        <v>53.44</v>
       </c>
     </row>
     <row r="27">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="O27" s="2" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="28">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>7.03</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="29">
@@ -2074,16 +2074,16 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>133</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="30">
@@ -2129,16 +2129,16 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>616</v>
+        <v>318</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>13</v>
+        <v>437</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>526</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1155</v>
+        <v>1281</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="31">
@@ -2187,13 +2187,13 @@
         <v>178</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>158</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="O31" s="2" t="n">
-        <v>3.69</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="32">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="33">
@@ -2297,13 +2297,13 @@
         <v>349</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>244</v>
+        <v>174</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>183</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>776</v>
+        <v>706</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="O33" s="2" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="34">
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="O34" s="2" t="n">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="35">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="O35" s="2" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="36">
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="O36" s="2" t="n">
-        <v>4.44</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="37">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="O37" s="2" t="n">
-        <v>5.57</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="38">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="O38" s="2" t="n">
-        <v>11.1</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="39">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="O39" s="2" t="n">
-        <v>4.44</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="40">
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>342</v>
@@ -2688,7 +2688,7 @@
         <v>17</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="O40" s="2" t="n">
-        <v>5.93</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="41">
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>17</v>
@@ -2743,7 +2743,7 @@
         <v>80</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="O41" s="2" t="n">
-        <v>7.43</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="42">
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="O42" s="2" t="n">
-        <v>11.1</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="43">
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="O43" s="2" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="44">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="O44" s="2" t="n">
-        <v>4.62</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="45">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="O45" s="2" t="n">
-        <v>4.62</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="46">
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="O46" s="2" t="n">
-        <v>4.62</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="47">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="O47" s="2" t="n">
-        <v>7.4</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="48">
@@ -3125,10 +3125,10 @@
         <v>150</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="O48" s="2" t="n">
-        <v>9.279999999999999</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="49">
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="O49" s="2" t="n">
-        <v>13.87</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="50">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>18.5</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="51">
@@ -3287,13 +3287,13 @@
         <v>8</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>283</v>
+        <v>248</v>
       </c>
       <c r="N51" s="6" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="O51" s="2" t="n">
-        <v>11.1</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="52">
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>13.32</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="53">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>16.64</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54">
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="O54" s="2" t="n">
-        <v>22.19</v>
+        <v>22.67</v>
       </c>
     </row>
     <row r="55">
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>12.94</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="56">
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="O56" s="2" t="n">
-        <v>11.87</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="57">
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="O57" s="2" t="n">
-        <v>11.87</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="58">
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="O58" s="2" t="n">
-        <v>14.84</v>
+        <v>15.17</v>
       </c>
     </row>
     <row r="59">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="O59" s="2" t="n">
-        <v>22.28</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="60">
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="O60" s="2" t="n">
-        <v>29.59</v>
+        <v>30.24</v>
       </c>
     </row>
     <row r="61">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="O61" s="2" t="n">
-        <v>14.8</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="62">
@@ -3892,13 +3892,13 @@
         <v>28</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>54</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="O62" s="2" t="n">
-        <v>18.56</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="63">
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="O63" s="2" t="n">
-        <v>21.77</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="64">
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="O64" s="2" t="n">
-        <v>22.15</v>
+        <v>22.64</v>
       </c>
     </row>
     <row r="65">
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="O65" s="2" t="n">
-        <v>26.63</v>
+        <v>27.22</v>
       </c>
     </row>
     <row r="66">
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="O66" s="2" t="n">
-        <v>36.07</v>
+        <v>36.85</v>
       </c>
     </row>
     <row r="67">
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="O67" s="2" t="n">
-        <v>27.73</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="68">
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="O68" s="2" t="n">
-        <v>9.25</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="O69" s="2" t="n">
-        <v>20.8</v>
+        <v>21.26</v>
       </c>
     </row>
     <row r="70">
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="O70" s="2" t="n">
-        <v>36.99</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="71">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="O71" s="2" t="n">
-        <v>14.8</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="72">
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="O72" s="2" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="73">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="O73" s="2" t="n">
-        <v>5.55</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="74">
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="O74" s="2" t="n">
-        <v>8.32</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="75">
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="O75" s="2" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="76">
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="O76" s="2" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="77">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="O77" s="2" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="78">
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="O78" s="2" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="79">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="O79" s="2" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="80">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="O80" s="2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="81">
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="O81" s="2" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="82">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="O82" s="2" t="n">
-        <v>36.99</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="83">
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="O83" s="2" t="n">
-        <v>33.29</v>
+        <v>34.02</v>
       </c>
     </row>
     <row r="84">
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="O84" s="2" t="n">
-        <v>44.39</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="85">
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="O85" s="2" t="n">
-        <v>55.48</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="86">
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="O86" s="2" t="n">
-        <v>27.22</v>
+        <v>27.82</v>
       </c>
     </row>
     <row r="87">
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="O87" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="88">
@@ -5336,7 +5336,7 @@
         </is>
       </c>
       <c r="O88" s="2" t="n">
-        <v>41.61</v>
+        <v>42.52</v>
       </c>
     </row>
     <row r="89">
@@ -5391,7 +5391,7 @@
         </is>
       </c>
       <c r="O89" s="2" t="n">
-        <v>25.89</v>
+        <v>26.46</v>
       </c>
     </row>
     <row r="90">
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="O90" s="2" t="n">
-        <v>7.4</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="91">
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>508</v>
@@ -5493,7 +5493,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="O91" s="2" t="n">
-        <v>3.24</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="92">
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="O92" s="2" t="n">
-        <v>5.55</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="93">
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="O93" s="2" t="n">
-        <v>5.55</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="94">
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="O94" s="2" t="n">
-        <v>22.04</v>
+        <v>22.53</v>
       </c>
     </row>
     <row r="95">
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="O95" s="2" t="n">
-        <v>22.04</v>
+        <v>22.53</v>
       </c>
     </row>
     <row r="96">
@@ -5776,7 +5776,7 @@
         </is>
       </c>
       <c r="O96" s="2" t="n">
-        <v>5.55</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="97">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="O97" s="2" t="n">
-        <v>8.32</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="98">
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="O98" s="2" t="n">
-        <v>6.47</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="99">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="O99" s="2" t="n">
-        <v>4.99</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="100">
@@ -5996,7 +5996,7 @@
         </is>
       </c>
       <c r="O100" s="2" t="n">
-        <v>4.99</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="101">
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="O101" s="2" t="n">
-        <v>4.99</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="102">
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="O102" s="2" t="n">
-        <v>8.32</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="103">
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="O103" s="2" t="n">
-        <v>16.65</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="104">
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="O104" s="2" t="n">
-        <v>17.76</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="105">
@@ -6271,7 +6271,7 @@
         </is>
       </c>
       <c r="O105" s="2" t="n">
-        <v>4.44</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="106">
@@ -6326,7 +6326,7 @@
         </is>
       </c>
       <c r="O106" s="2" t="n">
-        <v>13.32</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="107">
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="O107" s="2" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="108">
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="O108" s="2" t="n">
-        <v>4.62</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="109">
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="O109" s="2" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="110">
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="O110" s="2" t="n">
-        <v>29.59</v>
+        <v>30.24</v>
       </c>
     </row>
     <row r="111">
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="O111" s="2" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="112">
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="O112" s="2" t="n">
-        <v>13.87</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="113">
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="O113" s="2" t="n">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="114">
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="O114" s="2" t="n">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="115">
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="O115" s="2" t="n">
-        <v>11.36</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="116">
@@ -6884,7 +6884,7 @@
         </is>
       </c>
       <c r="O116" s="2" t="n">
-        <v>10.17</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="117">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="O117" s="2" t="n">
-        <v>16.6</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="118">
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="O118" s="2" t="n">
-        <v>26.53</v>
+        <v>27.11</v>
       </c>
     </row>
     <row r="119">
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="O119" s="2" t="n">
-        <v>61.48</v>
+        <v>62.82</v>
       </c>
     </row>
     <row r="120">
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="O120" s="2" t="n">
-        <v>5.23</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="121">
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="O121" s="2" t="n">
-        <v>7.46</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="122">
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="O122" s="2" t="n">
-        <v>3.19</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="123">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="O123" s="2" t="n">
-        <v>23.74</v>
+        <v>24.26</v>
       </c>
     </row>
     <row r="124">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="O124" s="2" t="n">
-        <v>8.4</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="125">
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="O125" s="2" t="n">
-        <v>8.56</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="126">
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="O126" s="2" t="n">
-        <v>8.56</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="127">
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="O127" s="2" t="n">
-        <v>8.289999999999999</v>
+        <v>8.470000000000001</v>
       </c>
     </row>
     <row r="128">
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="O128" s="2" t="n">
-        <v>6.3</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="129">
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="O129" s="2" t="n">
-        <v>16.42</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="130">
@@ -7665,24 +7665,24 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>92</v>
       </c>
       <c r="L130" s="2" t="n">
-        <v>430</v>
+        <v>296</v>
       </c>
       <c r="M130" s="2" t="n">
-        <v>522</v>
-      </c>
-      <c r="N130" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>520</v>
+      </c>
+      <c r="N130" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O130" s="2" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="131">
@@ -7739,7 +7739,7 @@
         </is>
       </c>
       <c r="O131" s="2" t="n">
-        <v>8.359999999999999</v>
+        <v>8.539999999999999</v>
       </c>
     </row>
     <row r="132">
@@ -7796,7 +7796,7 @@
         </is>
       </c>
       <c r="O132" s="2" t="n">
-        <v>10.5</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="133">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="O133" s="2" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="134">
@@ -7896,13 +7896,13 @@
         <v>106</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L134" s="2" t="n">
         <v>124</v>
       </c>
       <c r="M134" s="2" t="n">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="N134" s="4" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="O134" s="2" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="135">
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="O135" s="2" t="n">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="136">
@@ -8010,13 +8010,13 @@
         <v>64</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="L136" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M136" s="2" t="n">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="N136" s="4" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="O136" s="2" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="137">
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="O137" s="2" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="138">
@@ -8121,16 +8121,16 @@
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="L138" s="2" t="n">
         <v>37</v>
       </c>
       <c r="M138" s="2" t="n">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="N138" s="4" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="O138" s="2" t="n">
-        <v>5.64</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="139">
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="O139" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="140">
@@ -8252,7 +8252,7 @@
         </is>
       </c>
       <c r="O140" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="141">
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="O141" s="2" t="n">
-        <v>12.65</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="142">
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="O142" s="2" t="n">
-        <v>14.86</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="143">
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="O143" s="2" t="n">
-        <v>22.49</v>
+        <v>22.98</v>
       </c>
     </row>
     <row r="144">
@@ -8480,7 +8480,7 @@
         </is>
       </c>
       <c r="O144" s="2" t="n">
-        <v>35.14</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="145">
@@ -8523,13 +8523,13 @@
         <v>343</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="L145" s="2" t="n">
         <v>248</v>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="O145" s="2" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="146">
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c r="O146" s="2" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="147">
@@ -8651,7 +8651,7 @@
         </is>
       </c>
       <c r="O147" s="2" t="n">
-        <v>4.83</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="148">
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="O148" s="2" t="n">
-        <v>5.38</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="149">
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="O149" s="2" t="n">
-        <v>8.58</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="150">
@@ -8822,7 +8822,7 @@
         </is>
       </c>
       <c r="O150" s="2" t="n">
-        <v>6.01</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="151">
@@ -8879,7 +8879,7 @@
         </is>
       </c>
       <c r="O151" s="2" t="n">
-        <v>42.68</v>
+        <v>43.61</v>
       </c>
     </row>
     <row r="152">
@@ -8936,7 +8936,7 @@
         </is>
       </c>
       <c r="O152" s="2" t="n">
-        <v>42.68</v>
+        <v>43.61</v>
       </c>
     </row>
     <row r="153">
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="O153" s="2" t="n">
-        <v>11.54</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="154">
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="O154" s="2" t="n">
-        <v>21.53</v>
+        <v>22</v>
       </c>
     </row>
     <row r="155">
@@ -9107,7 +9107,7 @@
         </is>
       </c>
       <c r="O155" s="2" t="n">
-        <v>10.93</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="156">
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="O156" s="2" t="n">
-        <v>6.93</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="157">
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="O157" s="2" t="n">
-        <v>4.36</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="158">
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="O158" s="2" t="n">
-        <v>10.8</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="159">
@@ -9335,7 +9335,7 @@
         </is>
       </c>
       <c r="O159" s="2" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="160">
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="O160" s="2" t="n">
-        <v>4.01</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="161">
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="O161" s="2" t="n">
-        <v>11.06</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="162">
@@ -9492,13 +9492,13 @@
         <v>0</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="L162" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M162" s="2" t="n">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="N162" s="6" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="O162" s="2" t="n">
-        <v>11.06</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="163">
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="O163" s="2" t="n">
-        <v>4.75</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="164">
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="O164" s="2" t="n">
-        <v>40.5</v>
+        <v>41.38</v>
       </c>
     </row>
     <row r="165">
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="O165" s="2" t="n">
-        <v>44.54</v>
+        <v>45.51</v>
       </c>
     </row>
     <row r="166">
@@ -9720,13 +9720,13 @@
         <v>112</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>673</v>
+        <v>609</v>
       </c>
       <c r="L166" s="2" t="n">
         <v>75</v>
       </c>
       <c r="M166" s="2" t="n">
-        <v>860</v>
+        <v>796</v>
       </c>
       <c r="N166" s="4" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         </is>
       </c>
       <c r="O166" s="2" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="167">
@@ -9777,13 +9777,13 @@
         <v>102</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L167" s="2" t="n">
         <v>87</v>
       </c>
       <c r="M167" s="2" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="N167" s="4" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="O167" s="2" t="n">
-        <v>7.12</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="168">
@@ -9848,7 +9848,7 @@
         </is>
       </c>
       <c r="O168" s="2" t="n">
-        <v>8.58</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="169">
@@ -9905,7 +9905,7 @@
         </is>
       </c>
       <c r="O169" s="2" t="n">
-        <v>4.36</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="170">
@@ -9962,7 +9962,7 @@
         </is>
       </c>
       <c r="O170" s="2" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="171">
@@ -10019,7 +10019,7 @@
         </is>
       </c>
       <c r="O171" s="2" t="n">
-        <v>4.27</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="172">
@@ -10076,7 +10076,7 @@
         </is>
       </c>
       <c r="O172" s="2" t="n">
-        <v>15.98</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="173">
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="O173" s="2" t="n">
-        <v>13.41</v>
+        <v>13.71</v>
       </c>
     </row>
     <row r="174">
@@ -10173,7 +10173,7 @@
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K174" s="2" t="n">
         <v>50</v>
@@ -10182,7 +10182,7 @@
         <v>373</v>
       </c>
       <c r="M174" s="2" t="n">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="N174" s="4" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="O174" s="2" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="175">
@@ -10247,7 +10247,7 @@
         </is>
       </c>
       <c r="O175" s="2" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="176">
@@ -10293,10 +10293,10 @@
         <v>52</v>
       </c>
       <c r="L176" s="2" t="n">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="M176" s="2" t="n">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="N176" s="6" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         </is>
       </c>
       <c r="O176" s="2" t="n">
-        <v>5.1</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="177">
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="O177" s="2" t="n">
-        <v>9.27</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="178">
@@ -10418,7 +10418,7 @@
         </is>
       </c>
       <c r="O178" s="2" t="n">
-        <v>3.64</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="179">
@@ -10475,7 +10475,7 @@
         </is>
       </c>
       <c r="O179" s="2" t="n">
-        <v>4.14</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="180">
@@ -10518,21 +10518,21 @@
         <v>9</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="L180" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M180" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="N180" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>26</v>
+      </c>
+      <c r="N180" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O180" s="2" t="n">
-        <v>6.45</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="181">
@@ -10589,7 +10589,7 @@
         </is>
       </c>
       <c r="O181" s="2" t="n">
-        <v>4.29</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="182">
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="O182" s="2" t="n">
-        <v>4.29</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="183">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="O183" s="2" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="184">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="O184" s="2" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="185">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="O185" s="2" t="n">
-        <v>5.72</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="186">
@@ -10874,7 +10874,7 @@
         </is>
       </c>
       <c r="O186" s="2" t="n">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="187">
@@ -10931,7 +10931,7 @@
         </is>
       </c>
       <c r="O187" s="2" t="n">
-        <v>3.99</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="188">
@@ -10988,7 +10988,7 @@
         </is>
       </c>
       <c r="O188" s="2" t="n">
-        <v>4.36</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="189">
@@ -11045,7 +11045,7 @@
         </is>
       </c>
       <c r="O189" s="2" t="n">
-        <v>10.38</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="190">
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="O190" s="2" t="n">
-        <v>3.99</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="191">
@@ -11159,7 +11159,7 @@
         </is>
       </c>
       <c r="O191" s="2" t="n">
-        <v>6.4</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="192">
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="O192" s="2" t="n">
-        <v>5.64</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="193">
@@ -11259,13 +11259,13 @@
         <v>188</v>
       </c>
       <c r="K193" s="2" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L193" s="2" t="n">
         <v>286</v>
       </c>
       <c r="M193" s="2" t="n">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="N193" s="4" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         </is>
       </c>
       <c r="O193" s="2" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="194">
@@ -11330,7 +11330,7 @@
         </is>
       </c>
       <c r="O194" s="2" t="n">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="195">
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="O195" s="2" t="n">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="196">
@@ -11444,7 +11444,7 @@
         </is>
       </c>
       <c r="O196" s="2" t="n">
-        <v>8.779999999999999</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="197">
@@ -11501,7 +11501,7 @@
         </is>
       </c>
       <c r="O197" s="2" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="198">
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="O198" s="2" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="199">
@@ -11615,7 +11615,7 @@
         </is>
       </c>
       <c r="O199" s="2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="200">
@@ -11655,7 +11655,7 @@
         </is>
       </c>
       <c r="J200" s="2" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K200" s="2" t="n">
         <v>378</v>
@@ -11664,7 +11664,7 @@
         <v>300</v>
       </c>
       <c r="M200" s="2" t="n">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="N200" s="4" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="O200" s="2" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="201">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="O201" s="2" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="202">
@@ -11786,7 +11786,7 @@
         </is>
       </c>
       <c r="O202" s="2" t="n">
-        <v>3.85</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="203">
@@ -11843,7 +11843,7 @@
         </is>
       </c>
       <c r="O203" s="2" t="n">
-        <v>5.56</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="204">
@@ -11900,7 +11900,7 @@
         </is>
       </c>
       <c r="O204" s="2" t="n">
-        <v>3.99</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="205">
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="J205" s="2" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K205" s="2" t="n">
         <v>302</v>
@@ -11949,7 +11949,7 @@
         <v>0</v>
       </c>
       <c r="M205" s="2" t="n">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="N205" s="4" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         </is>
       </c>
       <c r="O205" s="2" t="n">
-        <v>7.26</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="206">
@@ -12014,7 +12014,7 @@
         </is>
       </c>
       <c r="O206" s="2" t="n">
-        <v>4.71</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="207">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="O207" s="2" t="n">
-        <v>5.47</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="208">
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="O208" s="2" t="n">
-        <v>10.17</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="209">
@@ -12168,7 +12168,7 @@
         </is>
       </c>
       <c r="J209" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K209" s="2" t="n">
         <v>70</v>
@@ -12177,7 +12177,7 @@
         <v>93</v>
       </c>
       <c r="M209" s="2" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N209" s="6" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="O209" s="2" t="n">
-        <v>10.17</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="210">
@@ -12231,10 +12231,10 @@
         <v>65</v>
       </c>
       <c r="L210" s="2" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="M210" s="2" t="n">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="N210" s="4" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         </is>
       </c>
       <c r="O210" s="2" t="n">
-        <v>8.19</v>
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="211">
@@ -12299,7 +12299,7 @@
         </is>
       </c>
       <c r="O211" s="2" t="n">
-        <v>13.07</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="212">
@@ -12356,7 +12356,7 @@
         </is>
       </c>
       <c r="O212" s="2" t="n">
-        <v>13.07</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="213">
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="O213" s="2" t="n">
-        <v>13.06</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="214">
@@ -12470,7 +12470,7 @@
         </is>
       </c>
       <c r="O214" s="2" t="n">
-        <v>15.97</v>
+        <v>16.32</v>
       </c>
     </row>
     <row r="215">
@@ -12527,7 +12527,7 @@
         </is>
       </c>
       <c r="O215" s="2" t="n">
-        <v>21.87</v>
+        <v>22.35</v>
       </c>
     </row>
     <row r="216">
@@ -12584,7 +12584,7 @@
         </is>
       </c>
       <c r="O216" s="2" t="n">
-        <v>52.29</v>
+        <v>53.44</v>
       </c>
     </row>
     <row r="217">
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="O217" s="2" t="n">
-        <v>52.29</v>
+        <v>53.44</v>
       </c>
     </row>
     <row r="218">
@@ -12698,7 +12698,7 @@
         </is>
       </c>
       <c r="O218" s="2" t="n">
-        <v>26.51</v>
+        <v>27.09</v>
       </c>
     </row>
     <row r="219">
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="O219" s="2" t="n">
-        <v>18.65</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="220">
@@ -12812,7 +12812,7 @@
         </is>
       </c>
       <c r="O220" s="2" t="n">
-        <v>27.59</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="221">
@@ -12869,7 +12869,7 @@
         </is>
       </c>
       <c r="O221" s="2" t="n">
-        <v>27.59</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="222">
@@ -12912,13 +12912,13 @@
         <v>0</v>
       </c>
       <c r="K222" s="2" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L222" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M222" s="2" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="N222" s="6" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         </is>
       </c>
       <c r="O222" s="2" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="223">
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="O223" s="2" t="n">
-        <v>4.42</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="224">
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="O224" s="2" t="n">
-        <v>6.18</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="225">
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="O225" s="2" t="n">
-        <v>13.47</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="226">
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="O226" s="2" t="n">
-        <v>24.69</v>
+        <v>25.24</v>
       </c>
     </row>
     <row r="227">
@@ -13211,7 +13211,7 @@
         </is>
       </c>
       <c r="O227" s="2" t="n">
-        <v>67.64</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="228">
@@ -13268,7 +13268,7 @@
         </is>
       </c>
       <c r="O228" s="2" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="229">
@@ -13311,13 +13311,13 @@
         <v>16</v>
       </c>
       <c r="K229" s="2" t="n">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="L229" s="2" t="n">
         <v>30</v>
       </c>
       <c r="M229" s="2" t="n">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="N229" s="4" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         </is>
       </c>
       <c r="O229" s="2" t="n">
-        <v>6.74</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="230">
@@ -13382,7 +13382,7 @@
         </is>
       </c>
       <c r="O230" s="2" t="n">
-        <v>24.04</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="231">
@@ -13439,7 +13439,7 @@
         </is>
       </c>
       <c r="O231" s="2" t="n">
-        <v>11.43</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="232">
@@ -13496,7 +13496,7 @@
         </is>
       </c>
       <c r="O232" s="2" t="n">
-        <v>8.4</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="233">
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="O233" s="2" t="n">
-        <v>5.57</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="234">
@@ -13593,16 +13593,16 @@
         </is>
       </c>
       <c r="J234" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K234" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L234" s="2" t="n">
         <v>22</v>
       </c>
       <c r="M234" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N234" s="6" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         </is>
       </c>
       <c r="O234" s="2" t="n">
-        <v>11.25</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="235">
@@ -13667,7 +13667,7 @@
         </is>
       </c>
       <c r="O235" s="2" t="n">
-        <v>8.35</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="236">
@@ -13710,13 +13710,13 @@
         <v>282</v>
       </c>
       <c r="K236" s="2" t="n">
-        <v>174</v>
+        <v>732</v>
       </c>
       <c r="L236" s="2" t="n">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="M236" s="2" t="n">
-        <v>456</v>
+        <v>1604</v>
       </c>
       <c r="N236" s="4" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         </is>
       </c>
       <c r="O236" s="2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="237">
@@ -13781,7 +13781,7 @@
         </is>
       </c>
       <c r="O237" s="2" t="n">
-        <v>4.66</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="238">
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="O238" s="2" t="n">
-        <v>20.4</v>
+        <v>20.85</v>
       </c>
     </row>
     <row r="239">
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="O239" s="2" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="240">
@@ -13952,7 +13952,7 @@
         </is>
       </c>
       <c r="O240" s="2" t="n">
-        <v>8.83</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="241">
@@ -13995,13 +13995,13 @@
         <v>7</v>
       </c>
       <c r="K241" s="2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L241" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M241" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N241" s="6" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         </is>
       </c>
       <c r="O241" s="2" t="n">
-        <v>5.07</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="242">
@@ -14066,7 +14066,7 @@
         </is>
       </c>
       <c r="O242" s="2" t="n">
-        <v>5.59</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="243">
@@ -14123,7 +14123,7 @@
         </is>
       </c>
       <c r="O243" s="2" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="244">
@@ -14180,7 +14180,7 @@
         </is>
       </c>
       <c r="O244" s="2" t="n">
-        <v>71.62</v>
+        <v>73.18000000000001</v>
       </c>
     </row>
     <row r="245">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="O245" s="2" t="n">
-        <v>15.33</v>
+        <v>15.67</v>
       </c>
     </row>
     <row r="246">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="O246" s="2" t="n">
-        <v>43.02</v>
+        <v>43.96</v>
       </c>
     </row>
     <row r="247">
@@ -14351,7 +14351,7 @@
         </is>
       </c>
       <c r="O247" s="2" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="248">
@@ -14408,7 +14408,7 @@
         </is>
       </c>
       <c r="O248" s="2" t="n">
-        <v>7.86</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="249">
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="O249" s="2" t="n">
-        <v>6.16</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="250">
@@ -14522,7 +14522,7 @@
         </is>
       </c>
       <c r="O250" s="2" t="n">
-        <v>4.21</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="251">
@@ -14579,7 +14579,7 @@
         </is>
       </c>
       <c r="O251" s="2" t="n">
-        <v>22.39</v>
+        <v>22.88</v>
       </c>
     </row>
     <row r="252">
@@ -14636,7 +14636,7 @@
         </is>
       </c>
       <c r="O252" s="2" t="n">
-        <v>3.26</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="253">
@@ -14676,16 +14676,16 @@
         </is>
       </c>
       <c r="J253" s="2" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K253" s="2" t="n">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="L253" s="2" t="n">
         <v>183</v>
       </c>
       <c r="M253" s="2" t="n">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="N253" s="4" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         </is>
       </c>
       <c r="O253" s="2" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="254">
@@ -14736,13 +14736,13 @@
         <v>0</v>
       </c>
       <c r="K254" s="2" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L254" s="2" t="n">
         <v>45</v>
       </c>
       <c r="M254" s="2" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="N254" s="6" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         </is>
       </c>
       <c r="O254" s="2" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="255">
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="O255" s="2" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="256">
@@ -14864,7 +14864,7 @@
         </is>
       </c>
       <c r="O256" s="2" t="n">
-        <v>5.99</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="257">
@@ -14921,7 +14921,7 @@
         </is>
       </c>
       <c r="O257" s="2" t="n">
-        <v>4.88</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="258">
@@ -14961,16 +14961,16 @@
         </is>
       </c>
       <c r="J258" s="2" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K258" s="2" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L258" s="2" t="n">
         <v>79</v>
       </c>
       <c r="M258" s="2" t="n">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="N258" s="4" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="O258" s="2" t="n">
-        <v>5.64</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="259">
@@ -15035,7 +15035,7 @@
         </is>
       </c>
       <c r="O259" s="2" t="n">
-        <v>6.97</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="260">
@@ -15092,7 +15092,7 @@
         </is>
       </c>
       <c r="O260" s="2" t="n">
-        <v>10.65</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="261">
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="O261" s="2" t="n">
-        <v>7.13</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="262">
@@ -15206,7 +15206,7 @@
         </is>
       </c>
       <c r="O262" s="2" t="n">
-        <v>13.61</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="263">
@@ -15263,7 +15263,7 @@
         </is>
       </c>
       <c r="O263" s="2" t="n">
-        <v>12.71</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="264">
@@ -15306,13 +15306,13 @@
         <v>38</v>
       </c>
       <c r="K264" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L264" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M264" s="2" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N264" s="4" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         </is>
       </c>
       <c r="O264" s="2" t="n">
-        <v>16.57</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="265">
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="O265" s="2" t="n">
-        <v>19.52</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="266">
@@ -15434,7 +15434,7 @@
         </is>
       </c>
       <c r="O266" s="2" t="n">
-        <v>22.48</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="267">
@@ -15491,7 +15491,7 @@
         </is>
       </c>
       <c r="O267" s="2" t="n">
-        <v>42.61</v>
+        <v>43.55</v>
       </c>
     </row>
     <row r="268">
@@ -15548,7 +15548,7 @@
         </is>
       </c>
       <c r="O268" s="2" t="n">
-        <v>28.3</v>
+        <v>28.92</v>
       </c>
     </row>
     <row r="269">
@@ -15605,7 +15605,7 @@
         </is>
       </c>
       <c r="O269" s="2" t="n">
-        <v>17.16</v>
+        <v>17.54</v>
       </c>
     </row>
     <row r="270">
@@ -15662,7 +15662,7 @@
         </is>
       </c>
       <c r="O270" s="2" t="n">
-        <v>4.16</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="271">
@@ -15719,7 +15719,7 @@
         </is>
       </c>
       <c r="O271" s="2" t="n">
-        <v>6.37</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="272">
@@ -15776,7 +15776,7 @@
         </is>
       </c>
       <c r="O272" s="2" t="n">
-        <v>10.1</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="273">
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="O273" s="2" t="n">
-        <v>10.1</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="274">
@@ -15890,7 +15890,7 @@
         </is>
       </c>
       <c r="O274" s="2" t="n">
-        <v>27.36</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="275">
@@ -15947,7 +15947,7 @@
         </is>
       </c>
       <c r="O275" s="2" t="n">
-        <v>27.36</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="276">
@@ -16004,7 +16004,7 @@
         </is>
       </c>
       <c r="O276" s="2" t="n">
-        <v>42.54</v>
+        <v>43.47</v>
       </c>
     </row>
     <row r="277">
@@ -16061,7 +16061,7 @@
         </is>
       </c>
       <c r="O277" s="2" t="n">
-        <v>5.12</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="278">
@@ -16118,7 +16118,7 @@
         </is>
       </c>
       <c r="O278" s="2" t="n">
-        <v>8.58</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="279">
@@ -16175,7 +16175,7 @@
         </is>
       </c>
       <c r="O279" s="2" t="n">
-        <v>8.58</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="280">
@@ -16215,16 +16215,16 @@
         </is>
       </c>
       <c r="J280" s="2" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K280" s="2" t="n">
         <v>511</v>
       </c>
       <c r="L280" s="2" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M280" s="2" t="n">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="N280" s="4" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         </is>
       </c>
       <c r="O280" s="2" t="n">
-        <v>8.210000000000001</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="281">
@@ -16289,7 +16289,7 @@
         </is>
       </c>
       <c r="O281" s="2" t="n">
-        <v>3.77</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="282">
@@ -16346,7 +16346,7 @@
         </is>
       </c>
       <c r="O282" s="2" t="n">
-        <v>10.4</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="283">
@@ -16403,7 +16403,7 @@
         </is>
       </c>
       <c r="O283" s="2" t="n">
-        <v>5.85</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="284">
@@ -16460,7 +16460,7 @@
         </is>
       </c>
       <c r="O284" s="2" t="n">
-        <v>12.64</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="285">
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="O285" s="2" t="n">
-        <v>13.47</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="286">
@@ -16574,7 +16574,7 @@
         </is>
       </c>
       <c r="O286" s="2" t="n">
-        <v>41.35</v>
+        <v>42.25</v>
       </c>
     </row>
     <row r="287">
@@ -16631,7 +16631,7 @@
         </is>
       </c>
       <c r="O287" s="2" t="n">
-        <v>10.43</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="288">
@@ -16688,7 +16688,7 @@
         </is>
       </c>
       <c r="O288" s="2" t="n">
-        <v>28.33</v>
+        <v>28.95</v>
       </c>
     </row>
     <row r="289">
@@ -16745,7 +16745,7 @@
         </is>
       </c>
       <c r="O289" s="2" t="n">
-        <v>28.33</v>
+        <v>28.95</v>
       </c>
     </row>
     <row r="290">
@@ -16785,7 +16785,7 @@
         </is>
       </c>
       <c r="J290" s="2" t="n">
-        <v>254</v>
+        <v>164</v>
       </c>
       <c r="K290" s="2" t="n">
         <v>342</v>
@@ -16794,7 +16794,7 @@
         <v>105</v>
       </c>
       <c r="M290" s="2" t="n">
-        <v>701</v>
+        <v>611</v>
       </c>
       <c r="N290" s="4" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         </is>
       </c>
       <c r="O290" s="2" t="n">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="291">
@@ -16848,18 +16848,18 @@
         <v>0</v>
       </c>
       <c r="L291" s="2" t="n">
-        <v>5</v>
+        <v>309</v>
       </c>
       <c r="M291" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N291" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>309</v>
+      </c>
+      <c r="N291" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O291" s="2" t="n">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="292">
@@ -16916,7 +16916,7 @@
         </is>
       </c>
       <c r="O292" s="2" t="n">
-        <v>21.98</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="293">
@@ -16973,7 +16973,7 @@
         </is>
       </c>
       <c r="O293" s="2" t="n">
-        <v>71.66</v>
+        <v>73.23</v>
       </c>
     </row>
     <row r="294">
@@ -17030,7 +17030,7 @@
         </is>
       </c>
       <c r="O294" s="2" t="n">
-        <v>71.66</v>
+        <v>73.23</v>
       </c>
     </row>
     <row r="295">
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="O295" s="2" t="n">
-        <v>71.66</v>
+        <v>73.23</v>
       </c>
     </row>
     <row r="296">
@@ -17144,7 +17144,7 @@
         </is>
       </c>
       <c r="O296" s="2" t="n">
-        <v>10.64</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="297">
@@ -17184,7 +17184,7 @@
         </is>
       </c>
       <c r="J297" s="2" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="K297" s="2" t="n">
         <v>197</v>
@@ -17193,7 +17193,7 @@
         <v>171</v>
       </c>
       <c r="M297" s="2" t="n">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="N297" s="4" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         </is>
       </c>
       <c r="O297" s="2" t="n">
-        <v>4.14</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="298">
@@ -17258,7 +17258,7 @@
         </is>
       </c>
       <c r="O298" s="2" t="n">
-        <v>4.14</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="299">
@@ -17315,7 +17315,7 @@
         </is>
       </c>
       <c r="O299" s="2" t="n">
-        <v>4.88</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="300">
@@ -17372,7 +17372,7 @@
         </is>
       </c>
       <c r="O300" s="2" t="n">
-        <v>8.210000000000001</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="301">
@@ -17429,7 +17429,7 @@
         </is>
       </c>
       <c r="O301" s="2" t="n">
-        <v>8.210000000000001</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="302">
@@ -17469,16 +17469,16 @@
         </is>
       </c>
       <c r="J302" s="2" t="n">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="K302" s="2" t="n">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="L302" s="2" t="n">
         <v>82</v>
       </c>
       <c r="M302" s="2" t="n">
-        <v>293</v>
+        <v>129</v>
       </c>
       <c r="N302" s="4" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         </is>
       </c>
       <c r="O302" s="2" t="n">
-        <v>5.62</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="303">
@@ -17543,7 +17543,7 @@
         </is>
       </c>
       <c r="O303" s="2" t="n">
-        <v>10.43</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="304">
@@ -17600,7 +17600,7 @@
         </is>
       </c>
       <c r="O304" s="2" t="n">
-        <v>10.43</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="305">
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="O305" s="2" t="n">
-        <v>10.47</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="306">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="O306" s="2" t="n">
-        <v>16.57</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="307">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="O307" s="2" t="n">
-        <v>19.53</v>
+        <v>19.96</v>
       </c>
     </row>
     <row r="308">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="O308" s="2" t="n">
-        <v>21.01</v>
+        <v>21.47</v>
       </c>
     </row>
     <row r="309">
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="O309" s="2" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="310">
@@ -17942,7 +17942,7 @@
         </is>
       </c>
       <c r="O310" s="2" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="311">
@@ -17999,7 +17999,7 @@
         </is>
       </c>
       <c r="O311" s="2" t="n">
-        <v>41.98</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="312">
@@ -18056,7 +18056,7 @@
         </is>
       </c>
       <c r="O312" s="2" t="n">
-        <v>23.52</v>
+        <v>24.04</v>
       </c>
     </row>
     <row r="313">
@@ -18113,7 +18113,7 @@
         </is>
       </c>
       <c r="O313" s="2" t="n">
-        <v>24.86</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="314">
@@ -18170,7 +18170,7 @@
         </is>
       </c>
       <c r="O314" s="2" t="n">
-        <v>9.32</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="315">
@@ -18227,7 +18227,7 @@
         </is>
       </c>
       <c r="O315" s="2" t="n">
-        <v>18.2</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="316">
@@ -18284,7 +18284,7 @@
         </is>
       </c>
       <c r="O316" s="2" t="n">
-        <v>10.06</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="317">
@@ -18341,7 +18341,7 @@
         </is>
       </c>
       <c r="O317" s="2" t="n">
-        <v>19.53</v>
+        <v>19.96</v>
       </c>
     </row>
     <row r="318">
@@ -18398,7 +18398,7 @@
         </is>
       </c>
       <c r="O318" s="2" t="n">
-        <v>31.44</v>
+        <v>32.13</v>
       </c>
     </row>
     <row r="319">
@@ -18441,13 +18441,13 @@
         <v>87</v>
       </c>
       <c r="K319" s="2" t="n">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="L319" s="2" t="n">
         <v>52</v>
       </c>
       <c r="M319" s="2" t="n">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="N319" s="4" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         </is>
       </c>
       <c r="O319" s="2" t="n">
-        <v>8.58</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="320">
@@ -18512,7 +18512,7 @@
         </is>
       </c>
       <c r="O320" s="2" t="n">
-        <v>8.58</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="321">
@@ -18569,7 +18569,7 @@
         </is>
       </c>
       <c r="O321" s="2" t="n">
-        <v>8.58</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="322">
@@ -18626,7 +18626,7 @@
         </is>
       </c>
       <c r="O322" s="2" t="n">
-        <v>8.58</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="323">
@@ -18683,7 +18683,7 @@
         </is>
       </c>
       <c r="O323" s="2" t="n">
-        <v>10.8</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="324">
@@ -18740,7 +18740,7 @@
         </is>
       </c>
       <c r="O324" s="2" t="n">
-        <v>10.8</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="325">
@@ -18797,7 +18797,7 @@
         </is>
       </c>
       <c r="O325" s="2" t="n">
-        <v>21.51</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="326">
@@ -18854,7 +18854,7 @@
         </is>
       </c>
       <c r="O326" s="2" t="n">
-        <v>16.28</v>
+        <v>16.64</v>
       </c>
     </row>
     <row r="327">
@@ -18911,7 +18911,7 @@
         </is>
       </c>
       <c r="O327" s="2" t="n">
-        <v>14.54</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="328">
@@ -18968,7 +18968,7 @@
         </is>
       </c>
       <c r="O328" s="2" t="n">
-        <v>13.02</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="329">
@@ -19025,7 +19025,7 @@
         </is>
       </c>
       <c r="O329" s="2" t="n">
-        <v>13.02</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="330">
@@ -19082,7 +19082,7 @@
         </is>
       </c>
       <c r="O330" s="2" t="n">
-        <v>25.45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="331">
@@ -19139,7 +19139,7 @@
         </is>
       </c>
       <c r="O331" s="2" t="n">
-        <v>7.66</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="332">
@@ -19196,7 +19196,7 @@
         </is>
       </c>
       <c r="O332" s="2" t="n">
-        <v>21.47</v>
+        <v>21.94</v>
       </c>
     </row>
     <row r="333">
@@ -19253,7 +19253,7 @@
         </is>
       </c>
       <c r="O333" s="2" t="n">
-        <v>5.99</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="334">
@@ -19310,7 +19310,7 @@
         </is>
       </c>
       <c r="O334" s="2" t="n">
-        <v>17.09</v>
+        <v>17.46</v>
       </c>
     </row>
     <row r="335">
@@ -19367,7 +19367,7 @@
         </is>
       </c>
       <c r="O335" s="2" t="n">
-        <v>25.97</v>
+        <v>26.54</v>
       </c>
     </row>
     <row r="336">
@@ -19410,13 +19410,13 @@
         <v>92</v>
       </c>
       <c r="K336" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L336" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M336" s="2" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="N336" s="4" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         </is>
       </c>
       <c r="O336" s="2" t="n">
-        <v>12.69</v>
+        <v>12.96</v>
       </c>
     </row>
     <row r="337">
@@ -19481,7 +19481,7 @@
         </is>
       </c>
       <c r="O337" s="2" t="n">
-        <v>7.14</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="338">
@@ -19538,7 +19538,7 @@
         </is>
       </c>
       <c r="O338" s="2" t="n">
-        <v>7.14</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="339">
@@ -19595,7 +19595,7 @@
         </is>
       </c>
       <c r="O339" s="2" t="n">
-        <v>7.67</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="340">
@@ -19652,7 +19652,7 @@
         </is>
       </c>
       <c r="O340" s="2" t="n">
-        <v>7.87</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="341">
@@ -19709,7 +19709,7 @@
         </is>
       </c>
       <c r="O341" s="2" t="n">
-        <v>7.87</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="342">
@@ -19752,13 +19752,13 @@
         <v>83</v>
       </c>
       <c r="K342" s="2" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L342" s="2" t="n">
         <v>34</v>
       </c>
       <c r="M342" s="2" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="N342" s="4" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         </is>
       </c>
       <c r="O342" s="2" t="n">
-        <v>7.13</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="343">
@@ -19823,7 +19823,7 @@
         </is>
       </c>
       <c r="O343" s="2" t="n">
-        <v>7.13</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="344">
@@ -19866,13 +19866,13 @@
         <v>27</v>
       </c>
       <c r="K344" s="2" t="n">
-        <v>127</v>
+        <v>331</v>
       </c>
       <c r="L344" s="2" t="n">
         <v>4</v>
       </c>
       <c r="M344" s="2" t="n">
-        <v>158</v>
+        <v>362</v>
       </c>
       <c r="N344" s="4" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         </is>
       </c>
       <c r="O344" s="2" t="n">
-        <v>4.88</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="345">
@@ -19937,7 +19937,7 @@
         </is>
       </c>
       <c r="O345" s="2" t="n">
-        <v>5.25</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="346">
@@ -19994,7 +19994,7 @@
         </is>
       </c>
       <c r="O346" s="2" t="n">
-        <v>49.2</v>
+        <v>50.27</v>
       </c>
     </row>
     <row r="347">
@@ -20040,10 +20040,10 @@
         <v>309</v>
       </c>
       <c r="L347" s="2" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="M347" s="2" t="n">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="N347" s="4" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         </is>
       </c>
       <c r="O347" s="2" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="348">
@@ -20108,7 +20108,7 @@
         </is>
       </c>
       <c r="O348" s="2" t="n">
-        <v>7.1</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="349">
@@ -20165,7 +20165,7 @@
         </is>
       </c>
       <c r="O349" s="2" t="n">
-        <v>12.65</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="350">
@@ -20222,7 +20222,7 @@
         </is>
       </c>
       <c r="O350" s="2" t="n">
-        <v>5.62</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="351">
@@ -20279,7 +20279,7 @@
         </is>
       </c>
       <c r="O351" s="2" t="n">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="352">
@@ -20336,7 +20336,7 @@
         </is>
       </c>
       <c r="O352" s="2" t="n">
-        <v>12.65</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="353">
@@ -20393,7 +20393,7 @@
         </is>
       </c>
       <c r="O353" s="2" t="n">
-        <v>12.65</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="354">
@@ -20450,7 +20450,7 @@
         </is>
       </c>
       <c r="O354" s="2" t="n">
-        <v>20.67</v>
+        <v>21.13</v>
       </c>
     </row>
     <row r="355">
@@ -20507,7 +20507,7 @@
         </is>
       </c>
       <c r="O355" s="2" t="n">
-        <v>21.08</v>
+        <v>21.55</v>
       </c>
     </row>
     <row r="356">
@@ -20564,7 +20564,7 @@
         </is>
       </c>
       <c r="O356" s="2" t="n">
-        <v>41.73</v>
+        <v>42.64</v>
       </c>
     </row>
     <row r="357">
@@ -20621,7 +20621,7 @@
         </is>
       </c>
       <c r="O357" s="2" t="n">
-        <v>9.32</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="358">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="O358" s="2" t="n">
-        <v>13.43</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="359">
@@ -20735,7 +20735,7 @@
         </is>
       </c>
       <c r="O359" s="2" t="n">
-        <v>13.43</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="360">
@@ -20792,7 +20792,7 @@
         </is>
       </c>
       <c r="O360" s="2" t="n">
-        <v>35.17</v>
+        <v>35.94</v>
       </c>
     </row>
     <row r="361">
@@ -20849,7 +20849,7 @@
         </is>
       </c>
       <c r="O361" s="2" t="n">
-        <v>35.17</v>
+        <v>35.94</v>
       </c>
     </row>
     <row r="362">
@@ -20906,7 +20906,7 @@
         </is>
       </c>
       <c r="O362" s="2" t="n">
-        <v>35.17</v>
+        <v>35.94</v>
       </c>
     </row>
     <row r="363">
@@ -20963,7 +20963,7 @@
         </is>
       </c>
       <c r="O363" s="2" t="n">
-        <v>35.17</v>
+        <v>35.94</v>
       </c>
     </row>
     <row r="364">
@@ -21020,7 +21020,7 @@
         </is>
       </c>
       <c r="O364" s="2" t="n">
-        <v>35.17</v>
+        <v>35.94</v>
       </c>
     </row>
     <row r="365">
@@ -21077,7 +21077,7 @@
         </is>
       </c>
       <c r="O365" s="2" t="n">
-        <v>18.05</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="366">
@@ -21134,7 +21134,7 @@
         </is>
       </c>
       <c r="O366" s="2" t="n">
-        <v>34.87</v>
+        <v>35.63</v>
       </c>
     </row>
     <row r="367">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="O367" s="2" t="n">
-        <v>14.5</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="368">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="O368" s="2" t="n">
-        <v>10.06</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="369">
@@ -21305,7 +21305,7 @@
         </is>
       </c>
       <c r="O369" s="2" t="n">
-        <v>4.64</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="370">
@@ -21362,7 +21362,7 @@
         </is>
       </c>
       <c r="O370" s="2" t="n">
-        <v>13.61</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="371">
@@ -21419,7 +21419,7 @@
         </is>
       </c>
       <c r="O371" s="2" t="n">
-        <v>5.65</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="372">
@@ -21476,7 +21476,7 @@
         </is>
       </c>
       <c r="O372" s="2" t="n">
-        <v>28.43</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="373">
@@ -21533,7 +21533,7 @@
         </is>
       </c>
       <c r="O373" s="2" t="n">
-        <v>18.04</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="374">
@@ -21576,13 +21576,13 @@
         <v>3</v>
       </c>
       <c r="K374" s="2" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="L374" s="2" t="n">
         <v>9</v>
       </c>
       <c r="M374" s="2" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="N374" s="6" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         </is>
       </c>
       <c r="O374" s="2" t="n">
-        <v>18.04</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="375">
@@ -21647,7 +21647,7 @@
         </is>
       </c>
       <c r="O375" s="2" t="n">
-        <v>23.98</v>
+        <v>24.51</v>
       </c>
     </row>
     <row r="376">
@@ -21704,7 +21704,7 @@
         </is>
       </c>
       <c r="O376" s="2" t="n">
-        <v>13.77</v>
+        <v>14.07</v>
       </c>
     </row>
     <row r="377">
@@ -21761,7 +21761,7 @@
         </is>
       </c>
       <c r="O377" s="2" t="n">
-        <v>13.02</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="378">
@@ -21818,7 +21818,7 @@
         </is>
       </c>
       <c r="O378" s="2" t="n">
-        <v>4.83</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="379">
@@ -21864,10 +21864,10 @@
         <v>154</v>
       </c>
       <c r="L379" s="2" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M379" s="2" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N379" s="4" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         </is>
       </c>
       <c r="O379" s="2" t="n">
-        <v>6.36</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="380">
@@ -21932,7 +21932,7 @@
         </is>
       </c>
       <c r="O380" s="2" t="n">
-        <v>7.84</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="381">
@@ -21989,7 +21989,7 @@
         </is>
       </c>
       <c r="O381" s="2" t="n">
-        <v>14.5</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="382">
@@ -22046,7 +22046,7 @@
         </is>
       </c>
       <c r="O382" s="2" t="n">
-        <v>15.09</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="383">
@@ -22103,7 +22103,7 @@
         </is>
       </c>
       <c r="O383" s="2" t="n">
-        <v>7.15</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="384">
@@ -22160,7 +22160,7 @@
         </is>
       </c>
       <c r="O384" s="2" t="n">
-        <v>9.32</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="385">
@@ -22217,7 +22217,7 @@
         </is>
       </c>
       <c r="O385" s="2" t="n">
-        <v>17.11</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="386">
@@ -22274,7 +22274,7 @@
         </is>
       </c>
       <c r="O386" s="2" t="n">
-        <v>13.77</v>
+        <v>14.07</v>
       </c>
     </row>
     <row r="387">
@@ -22331,7 +22331,7 @@
         </is>
       </c>
       <c r="O387" s="2" t="n">
-        <v>4.88</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="388">
@@ -22388,7 +22388,7 @@
         </is>
       </c>
       <c r="O388" s="2" t="n">
-        <v>34.53</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="389">
@@ -22431,13 +22431,13 @@
         <v>0</v>
       </c>
       <c r="K389" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L389" s="2" t="n">
         <v>86</v>
       </c>
       <c r="M389" s="2" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N389" s="6" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         </is>
       </c>
       <c r="O389" s="2" t="n">
-        <v>4.51</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="390">
@@ -22502,7 +22502,7 @@
         </is>
       </c>
       <c r="O390" s="2" t="n">
-        <v>15.99</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="391">
@@ -22559,7 +22559,7 @@
         </is>
       </c>
       <c r="O391" s="2" t="n">
-        <v>18.95</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="392">
@@ -22616,7 +22616,7 @@
         </is>
       </c>
       <c r="O392" s="2" t="n">
-        <v>28.41</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="393">
@@ -22673,7 +22673,7 @@
         </is>
       </c>
       <c r="O393" s="2" t="n">
-        <v>8.6</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="394">
@@ -22730,7 +22730,7 @@
         </is>
       </c>
       <c r="O394" s="2" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="395">
@@ -22787,7 +22787,7 @@
         </is>
       </c>
       <c r="O395" s="2" t="n">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="396">
@@ -22844,7 +22844,7 @@
         </is>
       </c>
       <c r="O396" s="2" t="n">
-        <v>6.24</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="397">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="O397" s="2" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="398">
@@ -22954,7 +22954,7 @@
         </is>
       </c>
       <c r="O398" s="2" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="399">
@@ -23009,7 +23009,7 @@
         </is>
       </c>
       <c r="O399" s="2" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="400">
@@ -23064,7 +23064,7 @@
         </is>
       </c>
       <c r="O400" s="2" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="401">
@@ -23121,7 +23121,7 @@
         </is>
       </c>
       <c r="O401" s="2" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="402">
@@ -23178,7 +23178,7 @@
         </is>
       </c>
       <c r="O402" s="2" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="403">
@@ -23235,7 +23235,7 @@
         </is>
       </c>
       <c r="O403" s="2" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="404">
@@ -23292,7 +23292,7 @@
         </is>
       </c>
       <c r="O404" s="2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="405">
@@ -23349,7 +23349,7 @@
         </is>
       </c>
       <c r="O405" s="2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="406">
@@ -23406,7 +23406,7 @@
         </is>
       </c>
       <c r="O406" s="2" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="407">
@@ -23446,7 +23446,7 @@
         </is>
       </c>
       <c r="J407" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K407" s="2" t="n">
         <v>0</v>
@@ -23455,7 +23455,7 @@
         <v>0</v>
       </c>
       <c r="M407" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N407" s="4" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         </is>
       </c>
       <c r="O407" s="2" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="408">
@@ -23506,13 +23506,13 @@
         <v>73</v>
       </c>
       <c r="K408" s="2" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L408" s="2" t="n">
         <v>1260</v>
       </c>
       <c r="M408" s="2" t="n">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="N408" s="4" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         </is>
       </c>
       <c r="O408" s="2" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="409">
@@ -23577,7 +23577,7 @@
         </is>
       </c>
       <c r="O409" s="2" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="410">
@@ -23634,7 +23634,7 @@
         </is>
       </c>
       <c r="O410" s="2" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="411">
@@ -23677,13 +23677,13 @@
         <v>201</v>
       </c>
       <c r="K411" s="2" t="n">
-        <v>1290</v>
+        <v>1280</v>
       </c>
       <c r="L411" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M411" s="2" t="n">
-        <v>1494</v>
+        <v>1481</v>
       </c>
       <c r="N411" s="4" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         </is>
       </c>
       <c r="O411" s="2" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="412">
@@ -23748,7 +23748,7 @@
         </is>
       </c>
       <c r="O412" s="2" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="413">
@@ -23791,13 +23791,13 @@
         <v>189</v>
       </c>
       <c r="K413" s="2" t="n">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="L413" s="2" t="n">
         <v>111</v>
       </c>
       <c r="M413" s="2" t="n">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="N413" s="4" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         </is>
       </c>
       <c r="O413" s="2" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="414">
@@ -23862,7 +23862,7 @@
         </is>
       </c>
       <c r="O414" s="2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="415">
@@ -23905,13 +23905,13 @@
         <v>279</v>
       </c>
       <c r="K415" s="2" t="n">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="L415" s="2" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="M415" s="2" t="n">
-        <v>1126</v>
+        <v>1114</v>
       </c>
       <c r="N415" s="4" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         </is>
       </c>
       <c r="O415" s="2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="416">
@@ -23976,7 +23976,7 @@
         </is>
       </c>
       <c r="O416" s="2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="417">
@@ -24033,7 +24033,7 @@
         </is>
       </c>
       <c r="O417" s="2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="418">
@@ -24076,13 +24076,13 @@
         <v>79</v>
       </c>
       <c r="K418" s="2" t="n">
-        <v>530</v>
+        <v>494</v>
       </c>
       <c r="L418" s="2" t="n">
         <v>274</v>
       </c>
       <c r="M418" s="2" t="n">
-        <v>883</v>
+        <v>847</v>
       </c>
       <c r="N418" s="4" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         </is>
       </c>
       <c r="O418" s="2" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="419">
@@ -24147,7 +24147,7 @@
         </is>
       </c>
       <c r="O419" s="2" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="420">
@@ -24204,7 +24204,7 @@
         </is>
       </c>
       <c r="O420" s="2" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="421">
@@ -24247,13 +24247,13 @@
         <v>0</v>
       </c>
       <c r="K421" s="2" t="n">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="L421" s="2" t="n">
         <v>109</v>
       </c>
       <c r="M421" s="2" t="n">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="N421" s="6" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         </is>
       </c>
       <c r="O421" s="2" t="n">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="422">
@@ -24304,13 +24304,13 @@
         <v>85</v>
       </c>
       <c r="K422" s="2" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="L422" s="2" t="n">
         <v>69</v>
       </c>
       <c r="M422" s="2" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="N422" s="4" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         </is>
       </c>
       <c r="O422" s="2" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="423">
@@ -24375,7 +24375,7 @@
         </is>
       </c>
       <c r="O423" s="2" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="424">
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="O424" s="2" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="425">
@@ -24475,13 +24475,13 @@
         <v>179</v>
       </c>
       <c r="K425" s="2" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L425" s="2" t="n">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="M425" s="2" t="n">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="N425" s="4" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         </is>
       </c>
       <c r="O425" s="2" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="426">
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="O426" s="2" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="427">
@@ -24589,13 +24589,13 @@
         <v>191</v>
       </c>
       <c r="K427" s="2" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="L427" s="2" t="n">
         <v>60</v>
       </c>
       <c r="M427" s="2" t="n">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="N427" s="4" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="O427" s="2" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="428">
@@ -24649,10 +24649,10 @@
         <v>40</v>
       </c>
       <c r="L428" s="2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="M428" s="2" t="n">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="N428" s="4" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         </is>
       </c>
       <c r="O428" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="429">
@@ -24717,7 +24717,7 @@
         </is>
       </c>
       <c r="O429" s="2" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="430">
@@ -24760,13 +24760,13 @@
         <v>65</v>
       </c>
       <c r="K430" s="2" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="L430" s="2" t="n">
         <v>31</v>
       </c>
       <c r="M430" s="2" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="N430" s="4" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         </is>
       </c>
       <c r="O430" s="2" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="431">
@@ -24831,7 +24831,7 @@
         </is>
       </c>
       <c r="O431" s="2" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="432">
@@ -24888,7 +24888,7 @@
         </is>
       </c>
       <c r="O432" s="2" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="433">
@@ -24945,7 +24945,7 @@
         </is>
       </c>
       <c r="O433" s="2" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="434">
@@ -24988,13 +24988,13 @@
         <v>0</v>
       </c>
       <c r="K434" s="2" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L434" s="2" t="n">
         <v>157</v>
       </c>
       <c r="M434" s="2" t="n">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N434" s="6" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         </is>
       </c>
       <c r="O434" s="2" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="435">
@@ -25059,7 +25059,7 @@
         </is>
       </c>
       <c r="O435" s="2" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="436">
@@ -25116,7 +25116,7 @@
         </is>
       </c>
       <c r="O436" s="2" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="437">
@@ -25159,13 +25159,13 @@
         <v>0</v>
       </c>
       <c r="K437" s="2" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L437" s="2" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="M437" s="2" t="n">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="N437" s="6" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         </is>
       </c>
       <c r="O437" s="2" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="438">
@@ -25216,13 +25216,13 @@
         <v>169</v>
       </c>
       <c r="K438" s="2" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="L438" s="2" t="n">
         <v>191</v>
       </c>
       <c r="M438" s="2" t="n">
-        <v>424</v>
+        <v>382</v>
       </c>
       <c r="N438" s="4" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         </is>
       </c>
       <c r="O438" s="2" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="439">
@@ -25287,7 +25287,7 @@
         </is>
       </c>
       <c r="O439" s="2" t="n">
-        <v>4.83</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="440">
@@ -25344,7 +25344,7 @@
         </is>
       </c>
       <c r="O440" s="2" t="n">
-        <v>4.83</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="441">
@@ -25401,7 +25401,7 @@
         </is>
       </c>
       <c r="O441" s="2" t="n">
-        <v>4.68</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="442">
@@ -25458,7 +25458,7 @@
         </is>
       </c>
       <c r="O442" s="2" t="n">
-        <v>4.68</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="443">
@@ -25515,7 +25515,7 @@
         </is>
       </c>
       <c r="O443" s="2" t="n">
-        <v>5.64</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="444">
@@ -25572,7 +25572,7 @@
         </is>
       </c>
       <c r="O444" s="2" t="n">
-        <v>6.61</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="445">
@@ -25629,7 +25629,7 @@
         </is>
       </c>
       <c r="O445" s="2" t="n">
-        <v>8.710000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="446">
@@ -25686,7 +25686,7 @@
         </is>
       </c>
       <c r="O446" s="2" t="n">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="447">
@@ -25743,7 +25743,7 @@
         </is>
       </c>
       <c r="O447" s="2" t="n">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="448">
@@ -25786,13 +25786,13 @@
         <v>4</v>
       </c>
       <c r="K448" s="2" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L448" s="2" t="n">
         <v>260</v>
       </c>
       <c r="M448" s="2" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N448" s="6" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         </is>
       </c>
       <c r="O448" s="2" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="449">
@@ -25843,13 +25843,13 @@
         <v>26</v>
       </c>
       <c r="K449" s="2" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="L449" s="2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M449" s="2" t="n">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="N449" s="4" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         </is>
       </c>
       <c r="O449" s="2" t="n">
-        <v>17.46</v>
+        <v>17.84</v>
       </c>
     </row>
     <row r="450">
@@ -25914,7 +25914,7 @@
         </is>
       </c>
       <c r="O450" s="2" t="n">
-        <v>4.27</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="451">
@@ -25957,13 +25957,13 @@
         <v>79</v>
       </c>
       <c r="K451" s="2" t="n">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="L451" s="2" t="n">
         <v>463</v>
       </c>
       <c r="M451" s="2" t="n">
-        <v>875</v>
+        <v>885</v>
       </c>
       <c r="N451" s="4" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         </is>
       </c>
       <c r="O451" s="2" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="452">
@@ -26028,7 +26028,7 @@
         </is>
       </c>
       <c r="O452" s="2" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="453">
@@ -26074,10 +26074,10 @@
         <v>118</v>
       </c>
       <c r="L453" s="2" t="n">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="M453" s="2" t="n">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="N453" s="4" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         </is>
       </c>
       <c r="O453" s="2" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="454">
@@ -26128,13 +26128,13 @@
         <v>1</v>
       </c>
       <c r="K454" s="2" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="L454" s="2" t="n">
         <v>180</v>
       </c>
       <c r="M454" s="2" t="n">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="N454" s="6" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         </is>
       </c>
       <c r="O454" s="2" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="455">
@@ -26185,13 +26185,13 @@
         <v>54</v>
       </c>
       <c r="K455" s="2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L455" s="2" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="M455" s="2" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="N455" s="4" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         </is>
       </c>
       <c r="O455" s="2" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="456">
@@ -26256,7 +26256,7 @@
         </is>
       </c>
       <c r="O456" s="2" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="457">
@@ -26299,13 +26299,13 @@
         <v>53</v>
       </c>
       <c r="K457" s="2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L457" s="2" t="n">
         <v>9</v>
       </c>
       <c r="M457" s="2" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N457" s="4" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="O457" s="2" t="n">
-        <v>4.2</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="458">
@@ -26356,13 +26356,13 @@
         <v>1</v>
       </c>
       <c r="K458" s="2" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L458" s="2" t="n">
         <v>95</v>
       </c>
       <c r="M458" s="2" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="N458" s="6" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         </is>
       </c>
       <c r="O458" s="2" t="n">
-        <v>4.68</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="459">
@@ -26427,7 +26427,7 @@
         </is>
       </c>
       <c r="O459" s="2" t="n">
-        <v>7.6</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="460">
@@ -26470,13 +26470,13 @@
         <v>8</v>
       </c>
       <c r="K460" s="2" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="L460" s="2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M460" s="2" t="n">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="N460" s="6" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="O460" s="2" t="n">
-        <v>7.6</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="461">
@@ -26541,7 +26541,7 @@
         </is>
       </c>
       <c r="O461" s="2" t="n">
-        <v>10.47</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="462">
@@ -26598,7 +26598,7 @@
         </is>
       </c>
       <c r="O462" s="2" t="n">
-        <v>10.99</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="463">
@@ -26655,7 +26655,7 @@
         </is>
       </c>
       <c r="O463" s="2" t="n">
-        <v>4.68</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="464">
@@ -26698,13 +26698,13 @@
         <v>0</v>
       </c>
       <c r="K464" s="2" t="n">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="L464" s="2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="M464" s="2" t="n">
-        <v>141</v>
+        <v>257</v>
       </c>
       <c r="N464" s="6" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         </is>
       </c>
       <c r="O464" s="2" t="n">
-        <v>6.49</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="465">
@@ -26769,7 +26769,7 @@
         </is>
       </c>
       <c r="O465" s="2" t="n">
-        <v>3.99</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="466">
@@ -26826,7 +26826,7 @@
         </is>
       </c>
       <c r="O466" s="2" t="n">
-        <v>3.99</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="467">
@@ -26883,7 +26883,7 @@
         </is>
       </c>
       <c r="O467" s="2" t="n">
-        <v>3.24</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="468">
@@ -26940,7 +26940,7 @@
         </is>
       </c>
       <c r="O468" s="2" t="n">
-        <v>6.52</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="469">
@@ -26983,13 +26983,13 @@
         <v>19</v>
       </c>
       <c r="K469" s="2" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L469" s="2" t="n">
         <v>15</v>
       </c>
       <c r="M469" s="2" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N469" s="4" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         </is>
       </c>
       <c r="O469" s="2" t="n">
-        <v>7.63</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="470">
@@ -27054,7 +27054,7 @@
         </is>
       </c>
       <c r="O470" s="2" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="471">
@@ -27111,7 +27111,7 @@
         </is>
       </c>
       <c r="O471" s="2" t="n">
-        <v>8.710000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="472">
@@ -27168,7 +27168,7 @@
         </is>
       </c>
       <c r="O472" s="2" t="n">
-        <v>8.710000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="473">
@@ -27211,21 +27211,21 @@
         <v>1</v>
       </c>
       <c r="K473" s="2" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L473" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M473" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N473" s="5" t="inlineStr">
-        <is>
-          <t>Sin stock</t>
+        <v>73</v>
+      </c>
+      <c r="N473" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O473" s="2" t="n">
-        <v>9.27</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="474">
@@ -27282,7 +27282,7 @@
         </is>
       </c>
       <c r="O474" s="2" t="n">
-        <v>8.19</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="475">
@@ -27339,7 +27339,7 @@
         </is>
       </c>
       <c r="O475" s="2" t="n">
-        <v>8.19</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="476">
@@ -27396,7 +27396,7 @@
         </is>
       </c>
       <c r="O476" s="2" t="n">
-        <v>10.45</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="477">
@@ -27453,7 +27453,7 @@
         </is>
       </c>
       <c r="O477" s="2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="478">
@@ -27510,7 +27510,7 @@
         </is>
       </c>
       <c r="O478" s="2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="479">
@@ -27567,7 +27567,7 @@
         </is>
       </c>
       <c r="O479" s="2" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="480">
@@ -27624,7 +27624,7 @@
         </is>
       </c>
       <c r="O480" s="2" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="481">
@@ -27681,7 +27681,7 @@
         </is>
       </c>
       <c r="O481" s="2" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="482">
@@ -27738,7 +27738,7 @@
         </is>
       </c>
       <c r="O482" s="2" t="n">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="483">
@@ -27795,7 +27795,7 @@
         </is>
       </c>
       <c r="O483" s="2" t="n">
-        <v>4.24</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="484">
@@ -27852,7 +27852,7 @@
         </is>
       </c>
       <c r="O484" s="2" t="n">
-        <v>4.77</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="485">
@@ -27909,7 +27909,7 @@
         </is>
       </c>
       <c r="O485" s="2" t="n">
-        <v>4.77</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="486">
@@ -27966,7 +27966,7 @@
         </is>
       </c>
       <c r="O486" s="2" t="n">
-        <v>7.3</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="487">
@@ -28023,7 +28023,7 @@
         </is>
       </c>
       <c r="O487" s="2" t="n">
-        <v>7.3</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="488">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="O488" s="2" t="n">
-        <v>5.97</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="489">
@@ -28137,7 +28137,7 @@
         </is>
       </c>
       <c r="O489" s="2" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="490">
@@ -28194,7 +28194,7 @@
         </is>
       </c>
       <c r="O490" s="2" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
     </row>
   </sheetData>

--- a/inventario_expandido.xlsx
+++ b/inventario_expandido.xlsx
@@ -618,13 +618,13 @@
         <v>45</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>25</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
@@ -1547,13 +1547,13 @@
         <v>99</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>87</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
@@ -1600,13 +1600,13 @@
         <v>31</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>88</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
@@ -1650,16 +1650,16 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
@@ -1809,16 +1809,16 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" s="2" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
@@ -1971,13 +1971,13 @@
         <v>320</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>324</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>707</v>
+        <v>657</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
@@ -2132,13 +2132,13 @@
         <v>318</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>437</v>
+        <v>399</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>526</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1281</v>
+        <v>1243</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
@@ -2297,13 +2297,13 @@
         <v>349</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>183</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>79</v>
@@ -2413,7 +2413,7 @@
         <v>1</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
@@ -2682,13 +2682,13 @@
         <v>15</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>17</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>201</v>
@@ -3073,7 +3073,7 @@
         <v>118</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
@@ -3510,10 +3510,10 @@
         <v>78</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
@@ -3617,13 +3617,13 @@
         <v>0</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
@@ -3672,13 +3672,13 @@
         <v>28</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>25</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
@@ -3892,13 +3892,13 @@
         <v>28</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>54</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
@@ -4497,13 +4497,13 @@
         <v>42</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -4604,16 +4604,16 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>205</v>
+        <v>151</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>267</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
@@ -4717,13 +4717,13 @@
         <v>117</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>5</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>42</v>
@@ -5273,7 +5273,7 @@
         <v>50</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
@@ -6477,13 +6477,13 @@
         <v>8</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M109" s="2" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="N109" s="6" t="inlineStr">
         <is>
@@ -6587,13 +6587,13 @@
         <v>0</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M111" s="2" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="N111" s="6" t="inlineStr">
         <is>
@@ -7665,16 +7665,16 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>92</v>
       </c>
       <c r="L130" s="2" t="n">
-        <v>296</v>
+        <v>90</v>
       </c>
       <c r="M130" s="2" t="n">
-        <v>520</v>
+        <v>214</v>
       </c>
       <c r="N130" s="4" t="inlineStr">
         <is>
@@ -7953,13 +7953,13 @@
         <v>29</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="L135" s="2" t="n">
         <v>187</v>
       </c>
       <c r="M135" s="2" t="n">
-        <v>310</v>
+        <v>235</v>
       </c>
       <c r="N135" s="4" t="inlineStr">
         <is>
@@ -8124,13 +8124,13 @@
         <v>53</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>458</v>
+        <v>332</v>
       </c>
       <c r="L138" s="2" t="n">
         <v>37</v>
       </c>
       <c r="M138" s="2" t="n">
-        <v>548</v>
+        <v>422</v>
       </c>
       <c r="N138" s="4" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K145" s="2" t="n">
         <v>488</v>
@@ -8529,7 +8529,7 @@
         <v>248</v>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
         <is>
@@ -9321,13 +9321,13 @@
         <v>162</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="L159" s="2" t="n">
         <v>166</v>
       </c>
       <c r="M159" s="2" t="n">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="N159" s="4" t="inlineStr">
         <is>
@@ -9720,13 +9720,13 @@
         <v>112</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="L166" s="2" t="n">
         <v>75</v>
       </c>
       <c r="M166" s="2" t="n">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="N166" s="4" t="inlineStr">
         <is>
@@ -9780,10 +9780,10 @@
         <v>148</v>
       </c>
       <c r="L167" s="2" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M167" s="2" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="N167" s="4" t="inlineStr">
         <is>
@@ -9951,10 +9951,10 @@
         <v>184</v>
       </c>
       <c r="L170" s="2" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="M170" s="2" t="n">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="N170" s="4" t="inlineStr">
         <is>
@@ -10176,13 +10176,13 @@
         <v>71</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L174" s="2" t="n">
         <v>373</v>
       </c>
       <c r="M174" s="2" t="n">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="N174" s="4" t="inlineStr">
         <is>
@@ -11202,13 +11202,13 @@
         <v>192</v>
       </c>
       <c r="K192" s="2" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L192" s="2" t="n">
         <v>20</v>
       </c>
       <c r="M192" s="2" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="N192" s="4" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="J194" s="2" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K194" s="2" t="n">
         <v>69</v>
@@ -11322,7 +11322,7 @@
         <v>0</v>
       </c>
       <c r="M194" s="2" t="n">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N194" s="4" t="inlineStr">
         <is>
@@ -11715,13 +11715,13 @@
         <v>193</v>
       </c>
       <c r="K201" s="2" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L201" s="2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="M201" s="2" t="n">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="N201" s="4" t="inlineStr">
         <is>
@@ -11886,13 +11886,13 @@
         <v>182</v>
       </c>
       <c r="K204" s="2" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="L204" s="2" t="n">
         <v>238</v>
       </c>
       <c r="M204" s="2" t="n">
-        <v>420</v>
+        <v>753</v>
       </c>
       <c r="N204" s="4" t="inlineStr">
         <is>
@@ -11943,13 +11943,13 @@
         <v>80</v>
       </c>
       <c r="K205" s="2" t="n">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="L205" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M205" s="2" t="n">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="N205" s="4" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         </is>
       </c>
       <c r="J210" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K210" s="2" t="n">
         <v>65</v>
@@ -12234,7 +12234,7 @@
         <v>54</v>
       </c>
       <c r="M210" s="2" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N210" s="4" t="inlineStr">
         <is>
@@ -12285,13 +12285,13 @@
         <v>0</v>
       </c>
       <c r="K211" s="2" t="n">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="L211" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M211" s="2" t="n">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="N211" s="6" t="inlineStr">
         <is>
@@ -12513,13 +12513,13 @@
         <v>1</v>
       </c>
       <c r="K215" s="2" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L215" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M215" s="2" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N215" s="6" t="inlineStr">
         <is>
@@ -12855,13 +12855,13 @@
         <v>7</v>
       </c>
       <c r="K221" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L221" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M221" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N221" s="6" t="inlineStr">
         <is>
@@ -13767,13 +13767,13 @@
         <v>62</v>
       </c>
       <c r="K237" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L237" s="2" t="n">
         <v>49</v>
       </c>
       <c r="M237" s="2" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N237" s="4" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         </is>
       </c>
       <c r="J241" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K241" s="2" t="n">
         <v>68</v>
@@ -14001,7 +14001,7 @@
         <v>0</v>
       </c>
       <c r="M241" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N241" s="6" t="inlineStr">
         <is>
@@ -14619,16 +14619,16 @@
         </is>
       </c>
       <c r="J252" s="2" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="K252" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L252" s="2" t="n">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="M252" s="2" t="n">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="N252" s="4" t="inlineStr">
         <is>
@@ -14682,10 +14682,10 @@
         <v>259</v>
       </c>
       <c r="L253" s="2" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M253" s="2" t="n">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="N253" s="4" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="J256" s="2" t="n">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="K256" s="2" t="n">
         <v>228</v>
@@ -14856,7 +14856,7 @@
         <v>295</v>
       </c>
       <c r="M256" s="2" t="n">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="N256" s="4" t="inlineStr">
         <is>
@@ -14910,10 +14910,10 @@
         <v>204</v>
       </c>
       <c r="L257" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M257" s="2" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N257" s="4" t="inlineStr">
         <is>
@@ -14964,13 +14964,13 @@
         <v>65</v>
       </c>
       <c r="K258" s="2" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="L258" s="2" t="n">
         <v>79</v>
       </c>
       <c r="M258" s="2" t="n">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="N258" s="4" t="inlineStr">
         <is>
@@ -15078,13 +15078,13 @@
         <v>71</v>
       </c>
       <c r="K260" s="2" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="L260" s="2" t="n">
         <v>44</v>
       </c>
       <c r="M260" s="2" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="N260" s="4" t="inlineStr">
         <is>
@@ -15192,13 +15192,13 @@
         <v>32</v>
       </c>
       <c r="K262" s="2" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L262" s="2" t="n">
         <v>50</v>
       </c>
       <c r="M262" s="2" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N262" s="4" t="inlineStr">
         <is>
@@ -15249,13 +15249,13 @@
         <v>57</v>
       </c>
       <c r="K263" s="2" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L263" s="2" t="n">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="M263" s="2" t="n">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="N263" s="4" t="inlineStr">
         <is>
@@ -15645,16 +15645,16 @@
         </is>
       </c>
       <c r="J270" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K270" s="2" t="n">
         <v>227</v>
       </c>
       <c r="L270" s="2" t="n">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="M270" s="2" t="n">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="N270" s="4" t="inlineStr">
         <is>
@@ -16221,10 +16221,10 @@
         <v>511</v>
       </c>
       <c r="L280" s="2" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="M280" s="2" t="n">
-        <v>592</v>
+        <v>552</v>
       </c>
       <c r="N280" s="4" t="inlineStr">
         <is>
@@ -16902,13 +16902,13 @@
         <v>15</v>
       </c>
       <c r="K292" s="2" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="L292" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M292" s="2" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="N292" s="4" t="inlineStr">
         <is>
@@ -17076,10 +17076,10 @@
         <v>6</v>
       </c>
       <c r="L295" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M295" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N295" s="5" t="inlineStr">
         <is>
@@ -17187,13 +17187,13 @@
         <v>76</v>
       </c>
       <c r="K297" s="2" t="n">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="L297" s="2" t="n">
         <v>171</v>
       </c>
       <c r="M297" s="2" t="n">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="N297" s="4" t="inlineStr">
         <is>
@@ -17700,13 +17700,13 @@
         <v>43</v>
       </c>
       <c r="K306" s="2" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L306" s="2" t="n">
         <v>92</v>
       </c>
       <c r="M306" s="2" t="n">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="N306" s="4" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         </is>
       </c>
       <c r="J309" s="2" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K309" s="2" t="n">
         <v>1</v>
@@ -17877,7 +17877,7 @@
         <v>127</v>
       </c>
       <c r="M309" s="2" t="n">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="N309" s="4" t="inlineStr">
         <is>
@@ -18042,13 +18042,13 @@
         <v>0</v>
       </c>
       <c r="K312" s="2" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L312" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M312" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N312" s="6" t="inlineStr">
         <is>
@@ -18381,20 +18381,20 @@
         </is>
       </c>
       <c r="J318" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K318" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L318" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L318" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M318" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="N318" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>2</v>
+      </c>
+      <c r="N318" s="5" t="inlineStr">
+        <is>
+          <t>Sin stock</t>
         </is>
       </c>
       <c r="O318" s="2" t="n">
@@ -18441,13 +18441,13 @@
         <v>87</v>
       </c>
       <c r="K319" s="2" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L319" s="2" t="n">
         <v>52</v>
       </c>
       <c r="M319" s="2" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="N319" s="4" t="inlineStr">
         <is>
@@ -19239,13 +19239,13 @@
         <v>56</v>
       </c>
       <c r="K333" s="2" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L333" s="2" t="n">
         <v>155</v>
       </c>
       <c r="M333" s="2" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="N333" s="4" t="inlineStr">
         <is>
@@ -19863,16 +19863,16 @@
         </is>
       </c>
       <c r="J344" s="2" t="n">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="K344" s="2" t="n">
-        <v>331</v>
+        <v>289</v>
       </c>
       <c r="L344" s="2" t="n">
         <v>4</v>
       </c>
       <c r="M344" s="2" t="n">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="N344" s="4" t="inlineStr">
         <is>
@@ -19920,20 +19920,20 @@
         </is>
       </c>
       <c r="J345" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K345" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L345" s="2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M345" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="N345" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>48</v>
+      </c>
+      <c r="N345" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O345" s="2" t="n">
@@ -20205,7 +20205,7 @@
         </is>
       </c>
       <c r="J350" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K350" s="2" t="n">
         <v>135</v>
@@ -20214,11 +20214,11 @@
         <v>32</v>
       </c>
       <c r="M350" s="2" t="n">
-        <v>177</v>
-      </c>
-      <c r="N350" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>174</v>
+      </c>
+      <c r="N350" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O350" s="2" t="n">
@@ -20490,20 +20490,20 @@
         </is>
       </c>
       <c r="J355" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K355" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L355" s="2" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="M355" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="N355" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+        <v>35</v>
+      </c>
+      <c r="N355" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O355" s="2" t="n">
@@ -21123,10 +21123,10 @@
         <v>2</v>
       </c>
       <c r="L366" s="2" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M366" s="2" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="N366" s="6" t="inlineStr">
         <is>
@@ -21237,10 +21237,10 @@
         <v>51</v>
       </c>
       <c r="L368" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M368" s="2" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N368" s="4" t="inlineStr">
         <is>
@@ -21351,10 +21351,10 @@
         <v>75</v>
       </c>
       <c r="L370" s="2" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M370" s="2" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N370" s="4" t="inlineStr">
         <is>
@@ -21573,13 +21573,13 @@
         </is>
       </c>
       <c r="J374" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K374" s="2" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="L374" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M374" s="2" t="n">
         <v>69</v>
@@ -21747,13 +21747,13 @@
         <v>0</v>
       </c>
       <c r="K377" s="2" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L377" s="2" t="n">
         <v>22</v>
       </c>
       <c r="M377" s="2" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N377" s="6" t="inlineStr">
         <is>
@@ -22716,13 +22716,13 @@
         <v>118</v>
       </c>
       <c r="K394" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L394" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M394" s="2" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="N394" s="4" t="inlineStr">
         <is>
@@ -23050,13 +23050,13 @@
         <v>178</v>
       </c>
       <c r="K400" s="2" t="n">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="L400" s="2" t="n">
         <v>93</v>
       </c>
       <c r="M400" s="2" t="n">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="N400" s="4" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         </is>
       </c>
       <c r="J407" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K407" s="2" t="n">
         <v>0</v>
@@ -23455,7 +23455,7 @@
         <v>0</v>
       </c>
       <c r="M407" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N407" s="4" t="inlineStr">
         <is>
@@ -23509,10 +23509,10 @@
         <v>91</v>
       </c>
       <c r="L408" s="2" t="n">
-        <v>1260</v>
+        <v>908</v>
       </c>
       <c r="M408" s="2" t="n">
-        <v>1424</v>
+        <v>1072</v>
       </c>
       <c r="N408" s="4" t="inlineStr">
         <is>
@@ -23677,13 +23677,13 @@
         <v>201</v>
       </c>
       <c r="K411" s="2" t="n">
-        <v>1280</v>
+        <v>1258</v>
       </c>
       <c r="L411" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M411" s="2" t="n">
-        <v>1481</v>
+        <v>1459</v>
       </c>
       <c r="N411" s="4" t="inlineStr">
         <is>
@@ -23731,16 +23731,16 @@
         </is>
       </c>
       <c r="J412" s="2" t="n">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="K412" s="2" t="n">
-        <v>1957</v>
+        <v>1948</v>
       </c>
       <c r="L412" s="2" t="n">
         <v>695</v>
       </c>
       <c r="M412" s="2" t="n">
-        <v>3051</v>
+        <v>3040</v>
       </c>
       <c r="N412" s="4" t="inlineStr">
         <is>
@@ -24076,13 +24076,13 @@
         <v>79</v>
       </c>
       <c r="K418" s="2" t="n">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="L418" s="2" t="n">
         <v>274</v>
       </c>
       <c r="M418" s="2" t="n">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="N418" s="4" t="inlineStr">
         <is>
@@ -24190,13 +24190,13 @@
         <v>128</v>
       </c>
       <c r="K420" s="2" t="n">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="L420" s="2" t="n">
         <v>83</v>
       </c>
       <c r="M420" s="2" t="n">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="N420" s="4" t="inlineStr">
         <is>
@@ -24304,13 +24304,13 @@
         <v>85</v>
       </c>
       <c r="K422" s="2" t="n">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="L422" s="2" t="n">
         <v>69</v>
       </c>
       <c r="M422" s="2" t="n">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="N422" s="4" t="inlineStr">
         <is>
@@ -24475,13 +24475,13 @@
         <v>179</v>
       </c>
       <c r="K425" s="2" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L425" s="2" t="n">
         <v>226</v>
       </c>
       <c r="M425" s="2" t="n">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="N425" s="4" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         </is>
       </c>
       <c r="J427" s="2" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="K427" s="2" t="n">
         <v>205</v>
@@ -24595,11 +24595,11 @@
         <v>60</v>
       </c>
       <c r="M427" s="2" t="n">
-        <v>456</v>
-      </c>
-      <c r="N427" s="4" t="inlineStr">
-        <is>
-          <t>Stock</t>
+        <v>265</v>
+      </c>
+      <c r="N427" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
         </is>
       </c>
       <c r="O427" s="2" t="n">
@@ -24643,7 +24643,7 @@
         </is>
       </c>
       <c r="J428" s="2" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K428" s="2" t="n">
         <v>40</v>
@@ -24652,7 +24652,7 @@
         <v>120</v>
       </c>
       <c r="M428" s="2" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N428" s="4" t="inlineStr">
         <is>
@@ -24874,13 +24874,13 @@
         <v>137</v>
       </c>
       <c r="K432" s="2" t="n">
-        <v>500</v>
+        <v>479</v>
       </c>
       <c r="L432" s="2" t="n">
         <v>81</v>
       </c>
       <c r="M432" s="2" t="n">
-        <v>718</v>
+        <v>697</v>
       </c>
       <c r="N432" s="4" t="inlineStr">
         <is>
@@ -24988,13 +24988,13 @@
         <v>0</v>
       </c>
       <c r="K434" s="2" t="n">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L434" s="2" t="n">
         <v>157</v>
       </c>
       <c r="M434" s="2" t="n">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="N434" s="6" t="inlineStr">
         <is>
@@ -25159,13 +25159,13 @@
         <v>0</v>
       </c>
       <c r="K437" s="2" t="n">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L437" s="2" t="n">
         <v>104</v>
       </c>
       <c r="M437" s="2" t="n">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N437" s="6" t="inlineStr">
         <is>
@@ -25216,13 +25216,13 @@
         <v>169</v>
       </c>
       <c r="K438" s="2" t="n">
-        <v>22</v>
+        <v>198</v>
       </c>
       <c r="L438" s="2" t="n">
         <v>191</v>
       </c>
       <c r="M438" s="2" t="n">
-        <v>382</v>
+        <v>558</v>
       </c>
       <c r="N438" s="4" t="inlineStr">
         <is>
@@ -25615,13 +25615,13 @@
         <v>11</v>
       </c>
       <c r="K445" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L445" s="2" t="n">
         <v>6</v>
       </c>
       <c r="M445" s="2" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N445" s="4" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         </is>
       </c>
       <c r="J451" s="2" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K451" s="2" t="n">
         <v>343</v>
@@ -25963,7 +25963,7 @@
         <v>463</v>
       </c>
       <c r="M451" s="2" t="n">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="N451" s="4" t="inlineStr">
         <is>
@@ -26071,13 +26071,13 @@
         <v>42</v>
       </c>
       <c r="K453" s="2" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="L453" s="2" t="n">
         <v>257</v>
       </c>
       <c r="M453" s="2" t="n">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="N453" s="4" t="inlineStr">
         <is>
@@ -26128,13 +26128,13 @@
         <v>1</v>
       </c>
       <c r="K454" s="2" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="L454" s="2" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="M454" s="2" t="n">
-        <v>259</v>
+        <v>197</v>
       </c>
       <c r="N454" s="6" t="inlineStr">
         <is>
@@ -26245,10 +26245,10 @@
         <v>117</v>
       </c>
       <c r="L456" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M456" s="2" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="N456" s="4" t="inlineStr">
         <is>
@@ -26356,13 +26356,13 @@
         <v>1</v>
       </c>
       <c r="K458" s="2" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="L458" s="2" t="n">
         <v>95</v>
       </c>
       <c r="M458" s="2" t="n">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="N458" s="6" t="inlineStr">
         <is>
@@ -26698,13 +26698,13 @@
         <v>0</v>
       </c>
       <c r="K464" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="L464" s="2" t="n">
         <v>127</v>
       </c>
-      <c r="L464" s="2" t="n">
-        <v>130</v>
-      </c>
       <c r="M464" s="2" t="n">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="N464" s="6" t="inlineStr">
         <is>
@@ -27211,13 +27211,13 @@
         <v>1</v>
       </c>
       <c r="K473" s="2" t="n">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="L473" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M473" s="2" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="N473" s="6" t="inlineStr">
         <is>
@@ -27439,13 +27439,13 @@
         <v>0</v>
       </c>
       <c r="K477" s="2" t="n">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="L477" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M477" s="2" t="n">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="N477" s="6" t="inlineStr">
         <is>
@@ -27781,13 +27781,13 @@
         <v>8</v>
       </c>
       <c r="K483" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L483" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M483" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N483" s="6" t="inlineStr">
         <is>
@@ -27895,13 +27895,13 @@
         <v>2</v>
       </c>
       <c r="K485" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L485" s="2" t="n">
         <v>46</v>
       </c>
       <c r="M485" s="2" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N485" s="6" t="inlineStr">
         <is>

--- a/inventario_expandido.xlsx
+++ b/inventario_expandido.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inventario'!$A$1:$O$490</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inventario'!$A$1:$O$496</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O490"/>
+  <dimension ref="A1:O496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12</v>
+        <v>347</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>11</v>
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>23</v>
+        <v>358</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
@@ -787,13 +787,13 @@
         <v>300</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>567</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1304</v>
+        <v>1294</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>345</v>
@@ -1394,7 +1394,7 @@
         <v>56</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
@@ -1547,13 +1547,13 @@
         <v>99</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>87</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
@@ -2349,16 +2349,16 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>273</v>
+        <v>198</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>562</v>
+        <v>477</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>99</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
@@ -2462,13 +2462,13 @@
         <v>90</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>184</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>502</v>
@@ -2633,7 +2633,7 @@
         <v>176</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>17</v>
@@ -2743,7 +2743,7 @@
         <v>80</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
@@ -2847,13 +2847,13 @@
         <v>10</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>23</v>
@@ -3018,7 +3018,7 @@
         <v>24</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         <v>73</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
@@ -3617,13 +3617,13 @@
         <v>0</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
@@ -3672,13 +3672,13 @@
         <v>28</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>25</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
@@ -4332,13 +4332,13 @@
         <v>13</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
@@ -4497,13 +4497,13 @@
         <v>42</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
@@ -4552,13 +4552,13 @@
         <v>85</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>92</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
@@ -5270,10 +5270,10 @@
         <v>42</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5438,7 +5438,7 @@
         <v>97</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>97</v>
@@ -5878,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="N98" s="4" t="inlineStr">
         <is>
@@ -6870,13 +6870,13 @@
         <v>23</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>115</v>
+        <v>192</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M116" s="2" t="n">
-        <v>138</v>
+        <v>215</v>
       </c>
       <c r="N116" s="4" t="inlineStr">
         <is>
@@ -7671,10 +7671,10 @@
         <v>92</v>
       </c>
       <c r="L130" s="2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M130" s="2" t="n">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="N130" s="4" t="inlineStr">
         <is>
@@ -7953,13 +7953,13 @@
         <v>29</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>19</v>
+        <v>334</v>
       </c>
       <c r="L135" s="2" t="n">
         <v>187</v>
       </c>
       <c r="M135" s="2" t="n">
-        <v>235</v>
+        <v>550</v>
       </c>
       <c r="N135" s="4" t="inlineStr">
         <is>
@@ -8520,16 +8520,16 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>488</v>
+        <v>468</v>
       </c>
       <c r="L145" s="2" t="n">
         <v>248</v>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1078</v>
+        <v>1051</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
         <is>
@@ -8694,13 +8694,13 @@
         <v>0</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="L148" s="2" t="n">
         <v>22</v>
       </c>
       <c r="M148" s="2" t="n">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="N148" s="6" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K155" s="2" t="n">
         <v>0</v>
@@ -9099,7 +9099,7 @@
         <v>82</v>
       </c>
       <c r="M155" s="2" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N155" s="4" t="inlineStr">
         <is>
@@ -9720,13 +9720,13 @@
         <v>112</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="L166" s="2" t="n">
         <v>75</v>
       </c>
       <c r="M166" s="2" t="n">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="N166" s="4" t="inlineStr">
         <is>
@@ -10347,13 +10347,13 @@
         <v>0</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="L177" s="2" t="n">
         <v>48</v>
       </c>
       <c r="M177" s="2" t="n">
-        <v>166</v>
+        <v>48</v>
       </c>
       <c r="N177" s="6" t="inlineStr">
         <is>
@@ -10404,13 +10404,13 @@
         <v>169</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="L178" s="2" t="n">
         <v>70</v>
       </c>
       <c r="M178" s="2" t="n">
-        <v>239</v>
+        <v>388</v>
       </c>
       <c r="N178" s="4" t="inlineStr">
         <is>
@@ -10518,13 +10518,13 @@
         <v>9</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L180" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M180" s="2" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="N180" s="6" t="inlineStr">
         <is>
@@ -10689,13 +10689,13 @@
         <v>0</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>87</v>
+        <v>302</v>
       </c>
       <c r="L183" s="2" t="n">
         <v>100</v>
       </c>
       <c r="M183" s="2" t="n">
-        <v>187</v>
+        <v>402</v>
       </c>
       <c r="N183" s="6" t="inlineStr">
         <is>
@@ -11544,13 +11544,13 @@
         <v>106</v>
       </c>
       <c r="K198" s="2" t="n">
-        <v>361</v>
+        <v>321</v>
       </c>
       <c r="L198" s="2" t="n">
         <v>180</v>
       </c>
       <c r="M198" s="2" t="n">
-        <v>647</v>
+        <v>607</v>
       </c>
       <c r="N198" s="4" t="inlineStr">
         <is>
@@ -11769,16 +11769,16 @@
         </is>
       </c>
       <c r="J202" s="2" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="K202" s="2" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L202" s="2" t="n">
         <v>120</v>
       </c>
       <c r="M202" s="2" t="n">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="N202" s="4" t="inlineStr">
         <is>
@@ -12000,13 +12000,13 @@
         <v>147</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="L206" s="2" t="n">
         <v>96</v>
       </c>
       <c r="M206" s="2" t="n">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="N206" s="4" t="inlineStr">
         <is>
@@ -12057,13 +12057,13 @@
         <v>116</v>
       </c>
       <c r="K207" s="2" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L207" s="2" t="n">
         <v>46</v>
       </c>
       <c r="M207" s="2" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="N207" s="4" t="inlineStr">
         <is>
@@ -12342,13 +12342,13 @@
         <v>129</v>
       </c>
       <c r="K212" s="2" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L212" s="2" t="n">
         <v>41</v>
       </c>
       <c r="M212" s="2" t="n">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N212" s="4" t="inlineStr">
         <is>
@@ -12399,13 +12399,13 @@
         <v>0</v>
       </c>
       <c r="K213" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L213" s="2" t="n">
         <v>35</v>
       </c>
       <c r="M213" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N213" s="6" t="inlineStr">
         <is>
@@ -13485,10 +13485,10 @@
         <v>179</v>
       </c>
       <c r="L232" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M232" s="2" t="n">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="N232" s="4" t="inlineStr">
         <is>
@@ -13596,13 +13596,13 @@
         <v>6</v>
       </c>
       <c r="K234" s="2" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="L234" s="2" t="n">
         <v>22</v>
       </c>
       <c r="M234" s="2" t="n">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="N234" s="6" t="inlineStr">
         <is>
@@ -14625,10 +14625,10 @@
         <v>0</v>
       </c>
       <c r="L252" s="2" t="n">
-        <v>211</v>
+        <v>151</v>
       </c>
       <c r="M252" s="2" t="n">
-        <v>264</v>
+        <v>204</v>
       </c>
       <c r="N252" s="4" t="inlineStr">
         <is>
@@ -14676,16 +14676,16 @@
         </is>
       </c>
       <c r="J253" s="2" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="K253" s="2" t="n">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="L253" s="2" t="n">
         <v>181</v>
       </c>
       <c r="M253" s="2" t="n">
-        <v>636</v>
+        <v>616</v>
       </c>
       <c r="N253" s="4" t="inlineStr">
         <is>
@@ -14736,13 +14736,13 @@
         <v>0</v>
       </c>
       <c r="K254" s="2" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="L254" s="2" t="n">
         <v>45</v>
       </c>
       <c r="M254" s="2" t="n">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="N254" s="6" t="inlineStr">
         <is>
@@ -14961,16 +14961,16 @@
         </is>
       </c>
       <c r="J258" s="2" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K258" s="2" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="L258" s="2" t="n">
         <v>79</v>
       </c>
       <c r="M258" s="2" t="n">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="N258" s="4" t="inlineStr">
         <is>
@@ -15078,13 +15078,13 @@
         <v>71</v>
       </c>
       <c r="K260" s="2" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L260" s="2" t="n">
         <v>44</v>
       </c>
       <c r="M260" s="2" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N260" s="4" t="inlineStr">
         <is>
@@ -15138,10 +15138,10 @@
         <v>103</v>
       </c>
       <c r="L261" s="2" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="M261" s="2" t="n">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="N261" s="4" t="inlineStr">
         <is>
@@ -15477,13 +15477,13 @@
         <v>4</v>
       </c>
       <c r="K267" s="2" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="L267" s="2" t="n">
         <v>12</v>
       </c>
       <c r="M267" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="N267" s="6" t="inlineStr">
         <is>
@@ -15591,13 +15591,13 @@
         <v>39</v>
       </c>
       <c r="K269" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L269" s="2" t="n">
         <v>10</v>
       </c>
       <c r="M269" s="2" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N269" s="4" t="inlineStr">
         <is>
@@ -15645,16 +15645,16 @@
         </is>
       </c>
       <c r="J270" s="2" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K270" s="2" t="n">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="L270" s="2" t="n">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="M270" s="2" t="n">
-        <v>444</v>
+        <v>377</v>
       </c>
       <c r="N270" s="4" t="inlineStr">
         <is>
@@ -16161,13 +16161,13 @@
         <v>81</v>
       </c>
       <c r="K279" s="2" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="L279" s="2" t="n">
         <v>69</v>
       </c>
       <c r="M279" s="2" t="n">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="N279" s="4" t="inlineStr">
         <is>
@@ -16392,10 +16392,10 @@
         <v>246</v>
       </c>
       <c r="L283" s="2" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M283" s="2" t="n">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N283" s="6" t="inlineStr">
         <is>
@@ -16734,10 +16734,10 @@
         <v>6</v>
       </c>
       <c r="L289" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M289" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N289" s="4" t="inlineStr">
         <is>
@@ -17184,16 +17184,16 @@
         </is>
       </c>
       <c r="J297" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K297" s="2" t="n">
-        <v>191</v>
+        <v>145</v>
       </c>
       <c r="L297" s="2" t="n">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="M297" s="2" t="n">
-        <v>438</v>
+        <v>383</v>
       </c>
       <c r="N297" s="4" t="inlineStr">
         <is>
@@ -17301,13 +17301,13 @@
         <v>0</v>
       </c>
       <c r="K299" s="2" t="n">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="L299" s="2" t="n">
         <v>69</v>
       </c>
       <c r="M299" s="2" t="n">
-        <v>82</v>
+        <v>162</v>
       </c>
       <c r="N299" s="6" t="inlineStr">
         <is>
@@ -17532,10 +17532,10 @@
         <v>135</v>
       </c>
       <c r="L303" s="2" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="M303" s="2" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="N303" s="4" t="inlineStr">
         <is>
@@ -17700,13 +17700,13 @@
         <v>43</v>
       </c>
       <c r="K306" s="2" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L306" s="2" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M306" s="2" t="n">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="N306" s="4" t="inlineStr">
         <is>
@@ -17760,10 +17760,10 @@
         <v>67</v>
       </c>
       <c r="L307" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M307" s="2" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="N307" s="4" t="inlineStr">
         <is>
@@ -17985,13 +17985,13 @@
         <v>13</v>
       </c>
       <c r="K311" s="2" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="L311" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M311" s="2" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="N311" s="4" t="inlineStr">
         <is>
@@ -18441,13 +18441,13 @@
         <v>87</v>
       </c>
       <c r="K319" s="2" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L319" s="2" t="n">
         <v>52</v>
       </c>
       <c r="M319" s="2" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N319" s="4" t="inlineStr">
         <is>
@@ -19752,13 +19752,13 @@
         <v>83</v>
       </c>
       <c r="K342" s="2" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L342" s="2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M342" s="2" t="n">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="N342" s="4" t="inlineStr">
         <is>
@@ -20037,13 +20037,13 @@
         <v>115</v>
       </c>
       <c r="K347" s="2" t="n">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="L347" s="2" t="n">
         <v>187</v>
       </c>
       <c r="M347" s="2" t="n">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="N347" s="4" t="inlineStr">
         <is>
@@ -20208,13 +20208,13 @@
         <v>7</v>
       </c>
       <c r="K350" s="2" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="L350" s="2" t="n">
         <v>32</v>
       </c>
       <c r="M350" s="2" t="n">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="N350" s="6" t="inlineStr">
         <is>
@@ -20949,13 +20949,13 @@
         <v>0</v>
       </c>
       <c r="K363" s="2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L363" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M363" s="2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="N363" s="6" t="inlineStr">
         <is>
@@ -21348,13 +21348,13 @@
         <v>38</v>
       </c>
       <c r="K370" s="2" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L370" s="2" t="n">
         <v>44</v>
       </c>
       <c r="M370" s="2" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N370" s="4" t="inlineStr">
         <is>
@@ -21636,10 +21636,10 @@
         <v>30</v>
       </c>
       <c r="L375" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M375" s="2" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="N375" s="6" t="inlineStr">
         <is>
@@ -21747,13 +21747,13 @@
         <v>0</v>
       </c>
       <c r="K377" s="2" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="L377" s="2" t="n">
         <v>22</v>
       </c>
       <c r="M377" s="2" t="n">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="N377" s="6" t="inlineStr">
         <is>
@@ -21807,10 +21807,10 @@
         <v>7</v>
       </c>
       <c r="L378" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M378" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N378" s="5" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         </is>
       </c>
       <c r="J380" s="2" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K380" s="2" t="n">
         <v>138</v>
@@ -21924,7 +21924,7 @@
         <v>25</v>
       </c>
       <c r="M380" s="2" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N380" s="4" t="inlineStr">
         <is>
@@ -21975,13 +21975,13 @@
         <v>58</v>
       </c>
       <c r="K381" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L381" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M381" s="2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N381" s="4" t="inlineStr">
         <is>
@@ -23050,13 +23050,13 @@
         <v>178</v>
       </c>
       <c r="K400" s="2" t="n">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="L400" s="2" t="n">
         <v>93</v>
       </c>
       <c r="M400" s="2" t="n">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="N400" s="4" t="inlineStr">
         <is>
@@ -23677,13 +23677,13 @@
         <v>201</v>
       </c>
       <c r="K411" s="2" t="n">
-        <v>1258</v>
+        <v>1185</v>
       </c>
       <c r="L411" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M411" s="2" t="n">
-        <v>1459</v>
+        <v>1386</v>
       </c>
       <c r="N411" s="4" t="inlineStr">
         <is>
@@ -23731,16 +23731,16 @@
         </is>
       </c>
       <c r="J412" s="2" t="n">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="K412" s="2" t="n">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="L412" s="2" t="n">
         <v>695</v>
       </c>
       <c r="M412" s="2" t="n">
-        <v>3040</v>
+        <v>3037</v>
       </c>
       <c r="N412" s="4" t="inlineStr">
         <is>
@@ -23905,13 +23905,13 @@
         <v>279</v>
       </c>
       <c r="K415" s="2" t="n">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="L415" s="2" t="n">
         <v>66</v>
       </c>
       <c r="M415" s="2" t="n">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="N415" s="4" t="inlineStr">
         <is>
@@ -24073,16 +24073,16 @@
         </is>
       </c>
       <c r="J418" s="2" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="K418" s="2" t="n">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="L418" s="2" t="n">
         <v>274</v>
       </c>
       <c r="M418" s="2" t="n">
-        <v>841</v>
+        <v>818</v>
       </c>
       <c r="N418" s="4" t="inlineStr">
         <is>
@@ -24247,13 +24247,13 @@
         <v>0</v>
       </c>
       <c r="K421" s="2" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="L421" s="2" t="n">
         <v>109</v>
       </c>
       <c r="M421" s="2" t="n">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="N421" s="6" t="inlineStr">
         <is>
@@ -24475,13 +24475,13 @@
         <v>179</v>
       </c>
       <c r="K425" s="2" t="n">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="L425" s="2" t="n">
         <v>226</v>
       </c>
       <c r="M425" s="2" t="n">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="N425" s="4" t="inlineStr">
         <is>
@@ -24760,13 +24760,13 @@
         <v>65</v>
       </c>
       <c r="K430" s="2" t="n">
-        <v>281</v>
+        <v>69</v>
       </c>
       <c r="L430" s="2" t="n">
         <v>31</v>
       </c>
       <c r="M430" s="2" t="n">
-        <v>377</v>
+        <v>165</v>
       </c>
       <c r="N430" s="4" t="inlineStr">
         <is>
@@ -24871,16 +24871,16 @@
         </is>
       </c>
       <c r="J432" s="2" t="n">
-        <v>137</v>
+        <v>49</v>
       </c>
       <c r="K432" s="2" t="n">
-        <v>479</v>
+        <v>403</v>
       </c>
       <c r="L432" s="2" t="n">
         <v>81</v>
       </c>
       <c r="M432" s="2" t="n">
-        <v>697</v>
+        <v>533</v>
       </c>
       <c r="N432" s="4" t="inlineStr">
         <is>
@@ -24991,10 +24991,10 @@
         <v>325</v>
       </c>
       <c r="L434" s="2" t="n">
-        <v>157</v>
+        <v>117</v>
       </c>
       <c r="M434" s="2" t="n">
-        <v>482</v>
+        <v>442</v>
       </c>
       <c r="N434" s="6" t="inlineStr">
         <is>
@@ -25102,13 +25102,13 @@
         <v>218</v>
       </c>
       <c r="K436" s="2" t="n">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="L436" s="2" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="M436" s="2" t="n">
-        <v>481</v>
+        <v>441</v>
       </c>
       <c r="N436" s="4" t="inlineStr">
         <is>
@@ -25159,13 +25159,13 @@
         <v>0</v>
       </c>
       <c r="K437" s="2" t="n">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="L437" s="2" t="n">
         <v>104</v>
       </c>
       <c r="M437" s="2" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="N437" s="6" t="inlineStr">
         <is>
@@ -25216,13 +25216,13 @@
         <v>169</v>
       </c>
       <c r="K438" s="2" t="n">
-        <v>198</v>
+        <v>272</v>
       </c>
       <c r="L438" s="2" t="n">
         <v>191</v>
       </c>
       <c r="M438" s="2" t="n">
-        <v>558</v>
+        <v>632</v>
       </c>
       <c r="N438" s="4" t="inlineStr">
         <is>
@@ -25330,13 +25330,13 @@
         <v>0</v>
       </c>
       <c r="K440" s="2" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L440" s="2" t="n">
         <v>59</v>
       </c>
       <c r="M440" s="2" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N440" s="6" t="inlineStr">
         <is>
@@ -25444,13 +25444,13 @@
         <v>19</v>
       </c>
       <c r="K442" s="2" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="L442" s="2" t="n">
         <v>61</v>
       </c>
       <c r="M442" s="2" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="N442" s="4" t="inlineStr">
         <is>
@@ -25729,13 +25729,13 @@
         <v>0</v>
       </c>
       <c r="K447" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L447" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M447" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N447" s="6" t="inlineStr">
         <is>
@@ -25786,13 +25786,13 @@
         <v>4</v>
       </c>
       <c r="K448" s="2" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="L448" s="2" t="n">
         <v>260</v>
       </c>
       <c r="M448" s="2" t="n">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="N448" s="6" t="inlineStr">
         <is>
@@ -25957,13 +25957,13 @@
         <v>77</v>
       </c>
       <c r="K451" s="2" t="n">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="L451" s="2" t="n">
         <v>463</v>
       </c>
       <c r="M451" s="2" t="n">
-        <v>883</v>
+        <v>853</v>
       </c>
       <c r="N451" s="4" t="inlineStr">
         <is>
@@ -26074,10 +26074,10 @@
         <v>108</v>
       </c>
       <c r="L453" s="2" t="n">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="M453" s="2" t="n">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="N453" s="4" t="inlineStr">
         <is>
@@ -26128,13 +26128,13 @@
         <v>1</v>
       </c>
       <c r="K454" s="2" t="n">
-        <v>56</v>
+        <v>413</v>
       </c>
       <c r="L454" s="2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="M454" s="2" t="n">
-        <v>197</v>
+        <v>544</v>
       </c>
       <c r="N454" s="6" t="inlineStr">
         <is>
@@ -26185,13 +26185,13 @@
         <v>54</v>
       </c>
       <c r="K455" s="2" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="L455" s="2" t="n">
         <v>24</v>
       </c>
       <c r="M455" s="2" t="n">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="N455" s="4" t="inlineStr">
         <is>
@@ -26242,13 +26242,13 @@
         <v>98</v>
       </c>
       <c r="K456" s="2" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="L456" s="2" t="n">
         <v>82</v>
       </c>
       <c r="M456" s="2" t="n">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="N456" s="4" t="inlineStr">
         <is>
@@ -26356,13 +26356,13 @@
         <v>1</v>
       </c>
       <c r="K458" s="2" t="n">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="L458" s="2" t="n">
         <v>95</v>
       </c>
       <c r="M458" s="2" t="n">
-        <v>130</v>
+        <v>211</v>
       </c>
       <c r="N458" s="6" t="inlineStr">
         <is>
@@ -26470,13 +26470,13 @@
         <v>8</v>
       </c>
       <c r="K460" s="2" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L460" s="2" t="n">
         <v>55</v>
       </c>
       <c r="M460" s="2" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N460" s="6" t="inlineStr">
         <is>
@@ -26641,13 +26641,13 @@
         <v>11</v>
       </c>
       <c r="K463" s="2" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L463" s="2" t="n">
         <v>45</v>
       </c>
       <c r="M463" s="2" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N463" s="4" t="inlineStr">
         <is>
@@ -26701,10 +26701,10 @@
         <v>125</v>
       </c>
       <c r="L464" s="2" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M464" s="2" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N464" s="6" t="inlineStr">
         <is>
@@ -26812,13 +26812,13 @@
         <v>25</v>
       </c>
       <c r="K466" s="2" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="L466" s="2" t="n">
         <v>78</v>
       </c>
       <c r="M466" s="2" t="n">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="N466" s="4" t="inlineStr">
         <is>
@@ -26869,13 +26869,13 @@
         <v>16</v>
       </c>
       <c r="K467" s="2" t="n">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="L467" s="2" t="n">
         <v>148</v>
       </c>
       <c r="M467" s="2" t="n">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="N467" s="4" t="inlineStr">
         <is>
@@ -26926,13 +26926,13 @@
         <v>11</v>
       </c>
       <c r="K468" s="2" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L468" s="2" t="n">
         <v>44</v>
       </c>
       <c r="M468" s="2" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N468" s="4" t="inlineStr">
         <is>
@@ -27727,10 +27727,10 @@
         <v>195</v>
       </c>
       <c r="L482" s="2" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="M482" s="2" t="n">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="N482" s="6" t="inlineStr">
         <is>
@@ -28197,8 +28197,348 @@
         <v>1.66</v>
       </c>
     </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>NOI0088753</t>
+        </is>
+      </c>
+      <c r="B491" s="3" t="inlineStr">
+        <is>
+          <t>TUBO REDONDO 30 X 1.5 (30/27)</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="inlineStr">
+        <is>
+          <t>TUBO REDONDO</t>
+        </is>
+      </c>
+      <c r="D491" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E491" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F491" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G491" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H491" s="2" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="I491" s="2" t="inlineStr">
+        <is>
+          <t>BRUTO</t>
+        </is>
+      </c>
+      <c r="J491" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K491" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="L491" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M491" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="N491" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
+        </is>
+      </c>
+      <c r="O491" s="2" t="n">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>NOR0032108</t>
+        </is>
+      </c>
+      <c r="B492" s="3" t="inlineStr">
+        <is>
+          <t>ANGULO 20 X 10 X 1.5</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>ANGULO</t>
+        </is>
+      </c>
+      <c r="D492" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E492" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F492" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G492" s="2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H492" s="2" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="I492" s="2" t="inlineStr">
+        <is>
+          <t>BRUTO</t>
+        </is>
+      </c>
+      <c r="J492" s="2" t="n">
+        <v>534</v>
+      </c>
+      <c r="K492" s="2" t="n">
+        <v>357</v>
+      </c>
+      <c r="L492" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="M492" s="2" t="n">
+        <v>1082</v>
+      </c>
+      <c r="N492" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="O492" s="2" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>NOR0032002</t>
+        </is>
+      </c>
+      <c r="B493" s="3" t="inlineStr">
+        <is>
+          <t>PLETINA 30 X 4</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
+          <t>PLETINA</t>
+        </is>
+      </c>
+      <c r="D493" s="2" t="inlineStr"/>
+      <c r="E493" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F493" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G493" s="2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H493" s="2" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="I493" s="2" t="inlineStr">
+        <is>
+          <t>BRUTO</t>
+        </is>
+      </c>
+      <c r="J493" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="K493" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="L493" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="M493" s="2" t="n">
+        <v>702</v>
+      </c>
+      <c r="N493" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="O493" s="2" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>NOR0032402</t>
+        </is>
+      </c>
+      <c r="B494" s="3" t="inlineStr">
+        <is>
+          <t>TUBO REDONDO 18 X 1.5</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>TUBO REDONDO</t>
+        </is>
+      </c>
+      <c r="D494" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E494" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F494" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G494" s="2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H494" s="2" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="I494" s="2" t="inlineStr">
+        <is>
+          <t>BRUTO</t>
+        </is>
+      </c>
+      <c r="J494" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K494" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="L494" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="M494" s="2" t="n">
+        <v>431</v>
+      </c>
+      <c r="N494" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
+        </is>
+      </c>
+      <c r="O494" s="2" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>NOI0088717</t>
+        </is>
+      </c>
+      <c r="B495" s="3" t="inlineStr">
+        <is>
+          <t>TUBO REDONDO 110 X 5 (110/100)</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>TUBO REDONDO</t>
+        </is>
+      </c>
+      <c r="D495" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="E495" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="F495" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G495" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H495" s="2" t="n">
+        <v>4.452</v>
+      </c>
+      <c r="I495" s="2" t="inlineStr">
+        <is>
+          <t>BRUTO</t>
+        </is>
+      </c>
+      <c r="J495" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="K495" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L495" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M495" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="N495" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="O495" s="2" t="n">
+        <v>31.16</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>NOR0032404</t>
+        </is>
+      </c>
+      <c r="B496" s="3" t="inlineStr">
+        <is>
+          <t>TUBO REDONDO 25 X 1,3</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>TUBO REDONDO</t>
+        </is>
+      </c>
+      <c r="D496" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E496" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F496" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G496" s="2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H496" s="2" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="I496" s="2" t="inlineStr">
+        <is>
+          <t>BRUTO</t>
+        </is>
+      </c>
+      <c r="J496" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K496" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="L496" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M496" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="N496" s="6" t="inlineStr">
+        <is>
+          <t>7/10 Días</t>
+        </is>
+      </c>
+      <c r="O496" s="2" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O490"/>
+  <autoFilter ref="A1:O496"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/inventario_expandido.xlsx
+++ b/inventario_expandido.xlsx
@@ -618,13 +618,13 @@
         <v>45</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>25</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
@@ -897,13 +897,13 @@
         <v>48</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>8</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
@@ -1391,10 +1391,10 @@
         <v>345</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
@@ -1547,13 +1547,13 @@
         <v>99</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>87</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>6</v>
@@ -1606,7 +1606,7 @@
         <v>88</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1818,7 +1818,7 @@
         <v>16</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
@@ -2132,13 +2132,13 @@
         <v>318</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>396</v>
+        <v>1045</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>525</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1239</v>
+        <v>1888</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
@@ -2297,13 +2297,13 @@
         <v>348</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>183</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
@@ -2630,10 +2630,10 @@
         <v>496</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
@@ -2682,13 +2682,13 @@
         <v>15</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>17</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
@@ -2792,13 +2792,13 @@
         <v>64</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>57</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
@@ -3015,10 +3015,10 @@
         <v>23</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
@@ -3125,10 +3125,10 @@
         <v>150</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
@@ -3287,13 +3287,13 @@
         <v>8</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="N51" s="6" t="inlineStr">
         <is>
@@ -3342,13 +3342,13 @@
         <v>50</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>42</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
@@ -3617,13 +3617,13 @@
         <v>0</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
@@ -3672,13 +3672,13 @@
         <v>28</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>25</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
@@ -4662,13 +4662,13 @@
         <v>401</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>8</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
@@ -4772,13 +4772,13 @@
         <v>87</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>272</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
@@ -4827,13 +4827,13 @@
         <v>80</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>83</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
@@ -5487,13 +5487,13 @@
         <v>14</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
@@ -7953,13 +7953,13 @@
         <v>28</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L135" s="2" t="n">
         <v>187</v>
       </c>
       <c r="M135" s="2" t="n">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="N135" s="4" t="inlineStr">
         <is>
@@ -8010,13 +8010,13 @@
         <v>62</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="L136" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M136" s="2" t="n">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="N136" s="4" t="inlineStr">
         <is>
@@ -8238,13 +8238,13 @@
         <v>0</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L140" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M140" s="2" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N140" s="6" t="inlineStr">
         <is>
@@ -8520,16 +8520,16 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>468</v>
+        <v>434</v>
       </c>
       <c r="L145" s="2" t="n">
         <v>248</v>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1050</v>
+        <v>1015</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K160" s="2" t="n">
         <v>111</v>
@@ -9384,7 +9384,7 @@
         <v>156</v>
       </c>
       <c r="M160" s="2" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="N160" s="4" t="inlineStr">
         <is>
@@ -9777,13 +9777,13 @@
         <v>102</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L167" s="2" t="n">
         <v>84</v>
       </c>
       <c r="M167" s="2" t="n">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="N167" s="4" t="inlineStr">
         <is>
@@ -10005,13 +10005,13 @@
         <v>116</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L171" s="2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M171" s="2" t="n">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="N171" s="4" t="inlineStr">
         <is>
@@ -10347,13 +10347,13 @@
         <v>0</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L177" s="2" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="M177" s="2" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="N177" s="6" t="inlineStr">
         <is>
@@ -11886,13 +11886,13 @@
         <v>182</v>
       </c>
       <c r="K204" s="2" t="n">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L204" s="2" t="n">
         <v>238</v>
       </c>
       <c r="M204" s="2" t="n">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="N204" s="4" t="inlineStr">
         <is>
@@ -12000,13 +12000,13 @@
         <v>147</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="L206" s="2" t="n">
         <v>96</v>
       </c>
       <c r="M206" s="2" t="n">
-        <v>299</v>
+        <v>274</v>
       </c>
       <c r="N206" s="4" t="inlineStr">
         <is>
@@ -12054,16 +12054,16 @@
         </is>
       </c>
       <c r="J207" s="2" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="K207" s="2" t="n">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="L207" s="2" t="n">
         <v>41</v>
       </c>
       <c r="M207" s="2" t="n">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="N207" s="4" t="inlineStr">
         <is>
@@ -12171,13 +12171,13 @@
         <v>4</v>
       </c>
       <c r="K209" s="2" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="L209" s="2" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M209" s="2" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="N209" s="6" t="inlineStr">
         <is>
@@ -13539,13 +13539,13 @@
         <v>76</v>
       </c>
       <c r="K233" s="2" t="n">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="L233" s="2" t="n">
         <v>7</v>
       </c>
       <c r="M233" s="2" t="n">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="N233" s="4" t="inlineStr">
         <is>
@@ -13824,13 +13824,13 @@
         <v>42</v>
       </c>
       <c r="K238" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L238" s="2" t="n">
         <v>49</v>
       </c>
       <c r="M238" s="2" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N238" s="4" t="inlineStr">
         <is>
@@ -14508,13 +14508,13 @@
         <v>18</v>
       </c>
       <c r="K250" s="2" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L250" s="2" t="n">
         <v>26</v>
       </c>
       <c r="M250" s="2" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="N250" s="4" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         </is>
       </c>
       <c r="J253" s="2" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="K253" s="2" t="n">
         <v>0</v>
@@ -14685,7 +14685,7 @@
         <v>151</v>
       </c>
       <c r="M253" s="2" t="n">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="N253" s="4" t="inlineStr">
         <is>
@@ -14736,13 +14736,13 @@
         <v>193</v>
       </c>
       <c r="K254" s="2" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L254" s="2" t="n">
         <v>181</v>
       </c>
       <c r="M254" s="2" t="n">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="N254" s="4" t="inlineStr">
         <is>
@@ -14793,13 +14793,13 @@
         <v>0</v>
       </c>
       <c r="K255" s="2" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L255" s="2" t="n">
         <v>45</v>
       </c>
       <c r="M255" s="2" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N255" s="6" t="inlineStr">
         <is>
@@ -14964,13 +14964,13 @@
         <v>139</v>
       </c>
       <c r="K258" s="2" t="n">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="L258" s="2" t="n">
         <v>35</v>
       </c>
       <c r="M258" s="2" t="n">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="N258" s="4" t="inlineStr">
         <is>
@@ -15021,13 +15021,13 @@
         <v>63</v>
       </c>
       <c r="K259" s="2" t="n">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="L259" s="2" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="M259" s="2" t="n">
-        <v>283</v>
+        <v>250</v>
       </c>
       <c r="N259" s="4" t="inlineStr">
         <is>
@@ -15192,13 +15192,13 @@
         <v>94</v>
       </c>
       <c r="K262" s="2" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="L262" s="2" t="n">
         <v>100</v>
       </c>
       <c r="M262" s="2" t="n">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="N262" s="4" t="inlineStr">
         <is>
@@ -15249,13 +15249,13 @@
         <v>32</v>
       </c>
       <c r="K263" s="2" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L263" s="2" t="n">
         <v>50</v>
       </c>
       <c r="M263" s="2" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N263" s="4" t="inlineStr">
         <is>
@@ -15363,13 +15363,13 @@
         <v>38</v>
       </c>
       <c r="K265" s="2" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="L265" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M265" s="2" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="N265" s="4" t="inlineStr">
         <is>
@@ -15762,13 +15762,13 @@
         <v>96</v>
       </c>
       <c r="K272" s="2" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L272" s="2" t="n">
         <v>114</v>
       </c>
       <c r="M272" s="2" t="n">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="N272" s="4" t="inlineStr">
         <is>
@@ -16278,10 +16278,10 @@
         <v>511</v>
       </c>
       <c r="L281" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M281" s="2" t="n">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="N281" s="4" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         </is>
       </c>
       <c r="J288" s="2" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K288" s="2" t="n">
         <v>72</v>
@@ -16680,7 +16680,7 @@
         <v>54</v>
       </c>
       <c r="M288" s="2" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N288" s="4" t="inlineStr">
         <is>
@@ -17241,16 +17241,16 @@
         </is>
       </c>
       <c r="J298" s="2" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K298" s="2" t="n">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="L298" s="2" t="n">
-        <v>163</v>
+        <v>121</v>
       </c>
       <c r="M298" s="2" t="n">
-        <v>383</v>
+        <v>328</v>
       </c>
       <c r="N298" s="4" t="inlineStr">
         <is>
@@ -17526,16 +17526,16 @@
         </is>
       </c>
       <c r="J303" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K303" s="2" t="n">
         <v>7</v>
       </c>
       <c r="L303" s="2" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="M303" s="2" t="n">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="N303" s="4" t="inlineStr">
         <is>
@@ -17589,10 +17589,10 @@
         <v>135</v>
       </c>
       <c r="L304" s="2" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="M304" s="2" t="n">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="N304" s="4" t="inlineStr">
         <is>
@@ -17754,16 +17754,16 @@
         </is>
       </c>
       <c r="J307" s="2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K307" s="2" t="n">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="L307" s="2" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="M307" s="2" t="n">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="N307" s="4" t="inlineStr">
         <is>
@@ -17817,10 +17817,10 @@
         <v>62</v>
       </c>
       <c r="L308" s="2" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="M308" s="2" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="N308" s="4" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         </is>
       </c>
       <c r="J310" s="2" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="K310" s="2" t="n">
         <v>1</v>
@@ -17934,7 +17934,7 @@
         <v>127</v>
       </c>
       <c r="M310" s="2" t="n">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="N310" s="4" t="inlineStr">
         <is>
@@ -18327,13 +18327,13 @@
         <v>93</v>
       </c>
       <c r="K317" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L317" s="2" t="n">
         <v>74</v>
       </c>
       <c r="M317" s="2" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="N317" s="4" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="J318" s="2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K318" s="2" t="n">
         <v>77</v>
@@ -18390,7 +18390,7 @@
         <v>38</v>
       </c>
       <c r="M318" s="2" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N318" s="4" t="inlineStr">
         <is>
@@ -18669,13 +18669,13 @@
         <v>14</v>
       </c>
       <c r="K323" s="2" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L323" s="2" t="n">
         <v>17</v>
       </c>
       <c r="M323" s="2" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N323" s="4" t="inlineStr">
         <is>
@@ -19182,13 +19182,13 @@
         <v>7</v>
       </c>
       <c r="K332" s="2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L332" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M332" s="2" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N332" s="6" t="inlineStr">
         <is>
@@ -19353,13 +19353,13 @@
         <v>22</v>
       </c>
       <c r="K335" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L335" s="2" t="n">
         <v>32</v>
       </c>
       <c r="M335" s="2" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N335" s="4" t="inlineStr">
         <is>
@@ -19752,13 +19752,13 @@
         <v>83</v>
       </c>
       <c r="K342" s="2" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L342" s="2" t="n">
         <v>28</v>
       </c>
       <c r="M342" s="2" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="N342" s="4" t="inlineStr">
         <is>
@@ -19923,13 +19923,13 @@
         <v>4</v>
       </c>
       <c r="K345" s="2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="L345" s="2" t="n">
         <v>18</v>
       </c>
       <c r="M345" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N345" s="6" t="inlineStr">
         <is>
@@ -20262,10 +20262,10 @@
         </is>
       </c>
       <c r="J351" s="2" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="K351" s="2" t="n">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="L351" s="2" t="n">
         <v>26</v>
@@ -20273,9 +20273,9 @@
       <c r="M351" s="2" t="n">
         <v>266</v>
       </c>
-      <c r="N351" s="6" t="inlineStr">
-        <is>
-          <t>7/10 Días</t>
+      <c r="N351" s="4" t="inlineStr">
+        <is>
+          <t>Stock</t>
         </is>
       </c>
       <c r="O351" s="2" t="n">
@@ -21177,13 +21177,13 @@
         <v>3</v>
       </c>
       <c r="K367" s="2" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L367" s="2" t="n">
         <v>7</v>
       </c>
       <c r="M367" s="2" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N367" s="6" t="inlineStr">
         <is>
@@ -21237,10 +21237,10 @@
         <v>51</v>
       </c>
       <c r="L368" s="2" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="M368" s="2" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="N368" s="4" t="inlineStr">
         <is>
@@ -21462,13 +21462,13 @@
         <v>0</v>
       </c>
       <c r="K372" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L372" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M372" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N372" s="6" t="inlineStr">
         <is>
@@ -22488,13 +22488,13 @@
         <v>27</v>
       </c>
       <c r="K390" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L390" s="2" t="n">
         <v>57</v>
       </c>
       <c r="M390" s="2" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="N390" s="4" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         </is>
       </c>
       <c r="J394" s="2" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K394" s="2" t="n">
         <v>46</v>
@@ -22722,7 +22722,7 @@
         <v>0</v>
       </c>
       <c r="M394" s="2" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="N394" s="4" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         </is>
       </c>
       <c r="J397" s="2" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K397" s="2" t="n">
         <v>0</v>
@@ -22891,7 +22891,7 @@
         <v>854</v>
       </c>
       <c r="M397" s="2" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="N397" s="4" t="inlineStr">
         <is>
@@ -23105,13 +23105,13 @@
         <v>178</v>
       </c>
       <c r="K401" s="2" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L401" s="2" t="n">
         <v>91</v>
       </c>
       <c r="M401" s="2" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N401" s="4" t="inlineStr">
         <is>
@@ -23615,16 +23615,16 @@
         </is>
       </c>
       <c r="J410" s="2" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K410" s="2" t="n">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="L410" s="2" t="n">
         <v>49</v>
       </c>
       <c r="M410" s="2" t="n">
-        <v>654</v>
+        <v>632</v>
       </c>
       <c r="N410" s="4" t="inlineStr">
         <is>
@@ -23732,13 +23732,13 @@
         <v>201</v>
       </c>
       <c r="K412" s="2" t="n">
-        <v>1185</v>
+        <v>1172</v>
       </c>
       <c r="L412" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M412" s="2" t="n">
-        <v>1386</v>
+        <v>1373</v>
       </c>
       <c r="N412" s="4" t="inlineStr">
         <is>
@@ -23789,13 +23789,13 @@
         <v>395</v>
       </c>
       <c r="K413" s="2" t="n">
-        <v>1939</v>
+        <v>1933</v>
       </c>
       <c r="L413" s="2" t="n">
         <v>695</v>
       </c>
       <c r="M413" s="2" t="n">
-        <v>3029</v>
+        <v>3023</v>
       </c>
       <c r="N413" s="4" t="inlineStr">
         <is>
@@ -23846,13 +23846,13 @@
         <v>189</v>
       </c>
       <c r="K414" s="2" t="n">
-        <v>753</v>
+        <v>727</v>
       </c>
       <c r="L414" s="2" t="n">
         <v>91</v>
       </c>
       <c r="M414" s="2" t="n">
-        <v>1033</v>
+        <v>1007</v>
       </c>
       <c r="N414" s="4" t="inlineStr">
         <is>
@@ -23960,13 +23960,13 @@
         <v>279</v>
       </c>
       <c r="K416" s="2" t="n">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="L416" s="2" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="M416" s="2" t="n">
-        <v>1103</v>
+        <v>1076</v>
       </c>
       <c r="N416" s="4" t="inlineStr">
         <is>
@@ -24131,13 +24131,13 @@
         <v>67</v>
       </c>
       <c r="K419" s="2" t="n">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="L419" s="2" t="n">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="M419" s="2" t="n">
-        <v>815</v>
+        <v>780</v>
       </c>
       <c r="N419" s="4" t="inlineStr">
         <is>
@@ -24245,13 +24245,13 @@
         <v>128</v>
       </c>
       <c r="K421" s="2" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="L421" s="2" t="n">
         <v>83</v>
       </c>
       <c r="M421" s="2" t="n">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="N421" s="4" t="inlineStr">
         <is>
@@ -24416,13 +24416,13 @@
         <v>85</v>
       </c>
       <c r="K424" s="2" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="L424" s="2" t="n">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="M424" s="2" t="n">
-        <v>336</v>
+        <v>297</v>
       </c>
       <c r="N424" s="4" t="inlineStr">
         <is>
@@ -24590,10 +24590,10 @@
         <v>214</v>
       </c>
       <c r="L427" s="2" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M427" s="2" t="n">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="N427" s="4" t="inlineStr">
         <is>
@@ -24704,10 +24704,10 @@
         <v>205</v>
       </c>
       <c r="L429" s="2" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="M429" s="2" t="n">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="N429" s="6" t="inlineStr">
         <is>
@@ -24758,13 +24758,13 @@
         <v>141</v>
       </c>
       <c r="K430" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L430" s="2" t="n">
         <v>120</v>
       </c>
       <c r="M430" s="2" t="n">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="N430" s="4" t="inlineStr">
         <is>
@@ -24872,13 +24872,13 @@
         <v>60</v>
       </c>
       <c r="K432" s="2" t="n">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="L432" s="2" t="n">
         <v>31</v>
       </c>
       <c r="M432" s="2" t="n">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="N432" s="4" t="inlineStr">
         <is>
@@ -24986,13 +24986,13 @@
         <v>49</v>
       </c>
       <c r="K434" s="2" t="n">
-        <v>401</v>
+        <v>366</v>
       </c>
       <c r="L434" s="2" t="n">
         <v>81</v>
       </c>
       <c r="M434" s="2" t="n">
-        <v>531</v>
+        <v>496</v>
       </c>
       <c r="N434" s="4" t="inlineStr">
         <is>
@@ -25100,13 +25100,13 @@
         <v>0</v>
       </c>
       <c r="K436" s="2" t="n">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L436" s="2" t="n">
         <v>117</v>
       </c>
       <c r="M436" s="2" t="n">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="N436" s="6" t="inlineStr">
         <is>
@@ -25271,13 +25271,13 @@
         <v>0</v>
       </c>
       <c r="K439" s="2" t="n">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="L439" s="2" t="n">
         <v>94</v>
       </c>
       <c r="M439" s="2" t="n">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="N439" s="6" t="inlineStr">
         <is>
@@ -25328,13 +25328,13 @@
         <v>169</v>
       </c>
       <c r="K440" s="2" t="n">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="L440" s="2" t="n">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="M440" s="2" t="n">
-        <v>617</v>
+        <v>566</v>
       </c>
       <c r="N440" s="4" t="inlineStr">
         <is>
@@ -25442,13 +25442,13 @@
         <v>0</v>
       </c>
       <c r="K442" s="2" t="n">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="L442" s="2" t="n">
         <v>59</v>
       </c>
       <c r="M442" s="2" t="n">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="N442" s="6" t="inlineStr">
         <is>
@@ -25841,13 +25841,13 @@
         <v>0</v>
       </c>
       <c r="K449" s="2" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L449" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M449" s="2" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="N449" s="6" t="inlineStr">
         <is>
@@ -26126,13 +26126,13 @@
         <v>7</v>
       </c>
       <c r="K454" s="2" t="n">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="L454" s="2" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="M454" s="2" t="n">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="N454" s="6" t="inlineStr">
         <is>
@@ -26183,13 +26183,13 @@
         <v>42</v>
       </c>
       <c r="K455" s="2" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="L455" s="2" t="n">
         <v>241</v>
       </c>
       <c r="M455" s="2" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="N455" s="4" t="inlineStr">
         <is>
@@ -26240,13 +26240,13 @@
         <v>1</v>
       </c>
       <c r="K456" s="2" t="n">
-        <v>391</v>
+        <v>507</v>
       </c>
       <c r="L456" s="2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="M456" s="2" t="n">
-        <v>522</v>
+        <v>628</v>
       </c>
       <c r="N456" s="6" t="inlineStr">
         <is>
@@ -26297,13 +26297,13 @@
         <v>51</v>
       </c>
       <c r="K457" s="2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L457" s="2" t="n">
         <v>24</v>
       </c>
       <c r="M457" s="2" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="N457" s="4" t="inlineStr">
         <is>
@@ -26354,13 +26354,13 @@
         <v>98</v>
       </c>
       <c r="K458" s="2" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="L458" s="2" t="n">
         <v>82</v>
       </c>
       <c r="M458" s="2" t="n">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="N458" s="4" t="inlineStr">
         <is>
@@ -26468,13 +26468,13 @@
         <v>1</v>
       </c>
       <c r="K460" s="2" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="L460" s="2" t="n">
         <v>95</v>
       </c>
       <c r="M460" s="2" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="N460" s="6" t="inlineStr">
         <is>
@@ -26753,13 +26753,13 @@
         <v>11</v>
       </c>
       <c r="K465" s="2" t="n">
-        <v>147</v>
+        <v>95</v>
       </c>
       <c r="L465" s="2" t="n">
         <v>45</v>
       </c>
       <c r="M465" s="2" t="n">
-        <v>203</v>
+        <v>151</v>
       </c>
       <c r="N465" s="4" t="inlineStr">
         <is>
@@ -27038,13 +27038,13 @@
         <v>11</v>
       </c>
       <c r="K470" s="2" t="n">
-        <v>351</v>
+        <v>405</v>
       </c>
       <c r="L470" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M470" s="2" t="n">
-        <v>379</v>
+        <v>432</v>
       </c>
       <c r="N470" s="4" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         </is>
       </c>
       <c r="J480" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K480" s="2" t="n">
         <v>0</v>
@@ -27614,7 +27614,7 @@
         <v>0</v>
       </c>
       <c r="M480" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N480" s="4" t="inlineStr">
         <is>
@@ -27665,13 +27665,13 @@
         <v>0</v>
       </c>
       <c r="K481" s="2" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L481" s="2" t="n">
         <v>41</v>
       </c>
       <c r="M481" s="2" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N481" s="6" t="inlineStr">
         <is>
@@ -27779,13 +27779,13 @@
         <v>117</v>
       </c>
       <c r="K483" s="2" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="L483" s="2" t="n">
         <v>330</v>
       </c>
       <c r="M483" s="2" t="n">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="N483" s="4" t="inlineStr">
         <is>
@@ -28007,13 +28007,13 @@
         <v>8</v>
       </c>
       <c r="K487" s="2" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="L487" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M487" s="2" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="N487" s="6" t="inlineStr">
         <is>
@@ -28292,13 +28292,13 @@
         <v>7</v>
       </c>
       <c r="K492" s="2" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L492" s="2" t="n">
         <v>30</v>
       </c>
       <c r="M492" s="2" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="N492" s="6" t="inlineStr">
         <is>
